--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -17269,36 +17269,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Lead ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>Add Time</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Person Name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Organization</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Creator</t>
         </is>
@@ -17307,182 +17322,353 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>bcb7a5f0-2c3f-11f1-85b3-ed52a72cdd60</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Manually created</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>2026-03-30T13:52:48.591Z</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Christine Maitland</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Eric Wyson</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>wysontrucking</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>6d947150-2c40-11f1-890c-e37687d9d35b</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Godoubler</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Manually created</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-03-30T13:57:45.317Z</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Christine Maitland</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ROBERTO WINSTON ROSARIO</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Godoubler</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>87911f40-2c40-11f1-9563-c576cd479f94</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Manually created</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>2026-03-30T13:58:28.916Z</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Christine Maitland</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STEPHEN FONTAINE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Libertymovers</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>e92c9c20-2c40-11f1-9563-c576cd479f94</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Manually created</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>2026-03-30T14:01:12.674Z</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Christine Maitland</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ENKELEJD HOXHA</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hoxha Construction LLC</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>1c4fe350-2c41-11f1-a148-5bcfb89573f4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Altium Packaging</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Manually created</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>2026-03-30T14:02:38.469Z</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Christine Maitland</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Robbin Dougherty</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Altium Packaging</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>86e75540-2c41-11f1-ab62-f5159abe34dc</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>goici</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Manually created</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>2026-03-30T14:05:37.300Z</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Christine Maitland</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ed Losiewicz</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>goici</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>0a3c7ca0-2ddb-11f1-a212-3dc165ea2a18</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Manually created</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>2026-04-01T14:57:01.802Z</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Christine Maitland</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CHRISTOPHER MICHAEL NUSSEY</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cmn Hardscaping And Lawn Care</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>be789ce0-3992-11f1-9cc1-85614b566347</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Superior Waste &amp; Recycling</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Manually created</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>2026-04-16T12:49:44.878Z</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Christine Maitland</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>DENNIS OCONNOR</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Superior Waste &amp; Recycling</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>14779c30-3da4-11f1-8f82-5dede5a2c9d5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>Apache Trucking</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Manually created</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>2026-04-21T17:03:55.251Z</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Christine Maitland</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Jay Singh</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Apache Trucking</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -1042,7 +1042,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>Meeting Booked</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>Follow up</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>Not Answered</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>Not Answered</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>Meeting Booked</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>Meeting Booked</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>Wrong Number</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>Wrong Number</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>Not Answered</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>Meeting Booked</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>Meeting Booked</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>Wrong Number</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>Follow up</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>Call Back</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>Meeting Booked</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>Call Back</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>Call Back</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>Meeting Booked</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>Meeting Booked</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>Call Back</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -7549,7 +7549,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7697,7 +7697,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>Meeting Booked</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -17269,7 +17269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17315,7 +17315,12 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Creator</t>
+          <t>Labels</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Deal Value</t>
         </is>
       </c>
     </row>
@@ -17357,6 +17362,7 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17396,6 +17402,7 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17435,6 +17442,7 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17474,6 +17482,7 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17513,6 +17522,7 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17552,6 +17562,7 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17591,6 +17602,7 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17630,6 +17642,7 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17669,6 +17682,7 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -17361,7 +17361,11 @@
           <t>Christine Maitland</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -17401,7 +17405,11 @@
           <t>Christine Maitland</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -17441,7 +17449,11 @@
           <t>Christine Maitland</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -17481,7 +17493,11 @@
           <t>Christine Maitland</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -17521,7 +17537,11 @@
           <t>Christine Maitland</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -17561,7 +17581,11 @@
           <t>Christine Maitland</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -17601,7 +17625,11 @@
           <t>Christine Maitland</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -17641,7 +17669,11 @@
           <t>Christine Maitland</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -17681,7 +17713,11 @@
           <t>Christine Maitland</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
     </row>
   </sheetData>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G255"/>
+  <dimension ref="A1:H255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,11 @@
           <t>Organization</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Update Time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -491,6 +496,11 @@
           <t>lavalleesystems</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-02-20 18:21:58</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -524,6 +534,11 @@
           <t>premierhvaccompany</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-02-18 19:32:20</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,6 +574,11 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>callcontrolpoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-02-20 16:23:21</t>
         </is>
       </c>
     </row>
@@ -590,6 +610,11 @@
           <t>phcprecision</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-02-06 17:05:51</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -627,6 +652,11 @@
           <t>gandcplumbing</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-02-06 17:05:51</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -664,6 +694,11 @@
           <t>wflynchinc</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-02-20 18:22:13</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -701,6 +736,11 @@
           <t>airtekma</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-02-11 19:00:37</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -738,6 +778,11 @@
           <t>flooringamerica1</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-02-06 17:05:53</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -771,6 +816,11 @@
           <t>cleanharbors</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-02-06 17:05:53</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -808,6 +858,11 @@
           <t>servicepumpingdrain</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-02-06 17:05:53</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -845,6 +900,11 @@
           <t>skillingsandsons</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-02-06 17:05:53</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -878,6 +938,11 @@
           <t>Triumvirate Environmental, Inc.</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-02-06 17:05:53</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -915,6 +980,11 @@
           <t>jfwhite</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-02-06 17:05:55</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -950,6 +1020,11 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>aspentransnewengland</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-02-18 15:28:21</t>
         </is>
       </c>
     </row>
@@ -981,6 +1056,11 @@
           <t>aquabounty</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-02-18 19:13:40</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1018,6 +1098,11 @@
           <t>medwayoilpropane</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-02-06 17:05:55</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1055,6 +1140,11 @@
           <t>westonnurseries</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-02-20 18:23:10</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1092,6 +1182,11 @@
           <t>imagediagnostics</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-02-18 15:28:17</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1127,6 +1222,11 @@
       <c r="G20" t="inlineStr">
         <is>
           <t>businessinstallations</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-02-18 19:13:41</t>
         </is>
       </c>
     </row>
@@ -1154,6 +1254,11 @@
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-02-06 17:05:55</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1191,6 +1296,11 @@
           <t>josephslimousine</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-02-06 17:05:55</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1228,6 +1338,11 @@
           <t>regencytrans</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-03-12 19:17:30</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1265,6 +1380,11 @@
           <t>performancetransinc</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-03-27 17:53:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1302,6 +1422,11 @@
           <t>r-dtransport</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-02-24 19:02:25</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1339,6 +1464,11 @@
           <t>trucbrush</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-04-08 14:32:16</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1376,6 +1506,11 @@
           <t>airflowdeflector</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-04-15 16:05:12</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1413,6 +1548,11 @@
           <t>camposexp</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-03-27 18:02:28</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1450,6 +1590,11 @@
           <t>28freight</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-03-27 18:05:08</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1483,6 +1628,11 @@
           <t>truckcourier</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-03-27 18:06:04</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1516,6 +1666,11 @@
           <t>RINN CORP</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-04-30 16:43:14</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1553,6 +1708,11 @@
           <t>Transgas Inc</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-02-10 19:01:09</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1590,6 +1750,11 @@
           <t>wysontrucking</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-04-13 15:45:27</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1627,6 +1792,11 @@
           <t>castinemovers</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-04-30 16:57:20</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1664,6 +1834,11 @@
           <t>Tighe Logistics</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-04-17 18:32:56</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1701,6 +1876,11 @@
           <t>Lily Transportation</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-04-30 16:49:38</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1738,6 +1918,11 @@
           <t>jrhudsonhorsetrans</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-04-30 16:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1773,6 +1958,11 @@
       <c r="G38" t="e">
         <v>#VALUE!</v>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-04-23 18:25:02</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1810,6 +2000,11 @@
           <t>jandstrans</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-04-30 17:03:09</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1847,6 +2042,11 @@
           <t>burkeoil</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-04-23 18:27:36</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1884,6 +2084,11 @@
           <t>safewaycollision</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026-02-06 17:06:01</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1921,6 +2126,11 @@
           <t>David's Service Transportation</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-02-17 13:18:43</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1958,6 +2168,11 @@
           <t>miniwarehousing</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-03-12 14:01:00</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1995,6 +2210,11 @@
           <t>randwhitney</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-02-09 16:55:03</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2032,6 +2252,11 @@
           <t>DJK'S HEAVY HAUL &amp; TRANSPORT LLC.</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026-04-02 19:52:54</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2069,6 +2294,11 @@
           <t>corrpackinc</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026-04-07 14:49:53</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2106,6 +2336,11 @@
           <t>yourfuelsolution</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-04-07 14:55:18</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2143,6 +2378,11 @@
           <t>roycodistributors</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026-04-07 14:53:07</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2180,6 +2420,11 @@
           <t>denlube</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2026-04-07 15:13:40</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2217,6 +2462,11 @@
           <t>toreku</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2026-02-06 17:06:05</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2250,6 +2500,11 @@
           <t>devonlane</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2026-02-06 17:06:05</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2287,6 +2542,11 @@
           <t>ahearnequipment</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2026-02-06 17:06:05</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2324,6 +2584,11 @@
           <t>cmsblock</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:21:26</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2361,6 +2626,11 @@
           <t>munsonmachinery</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2026-02-06 17:06:05</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2398,6 +2668,11 @@
           <t>wlfrench</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:39:57</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2435,6 +2710,11 @@
           <t>aldrichcleantech</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2026-02-06 17:06:05</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2468,6 +2748,11 @@
           <t>mikesmoonwalkrentals</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2026-02-06 17:06:07</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2505,6 +2790,11 @@
           <t>rosadoandsons</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:22:42</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2542,6 +2832,11 @@
           <t>thelagassegroup</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2026-02-06 17:06:07</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2579,6 +2874,11 @@
           <t>cavicchio</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:25:07</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2616,6 +2916,11 @@
           <t>bigelownurseries</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2026-02-06 17:06:07</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2653,6 +2958,11 @@
           <t>koopmanlumber</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2026-03-20 18:51:23</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2690,6 +3000,11 @@
           <t>howelumber</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2026-03-20 18:49:21</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2723,6 +3038,11 @@
           <t>arlcoal</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2026-02-06 17:06:07</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2756,6 +3076,11 @@
           <t>spauldingfencesupply</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2026-02-06 17:06:09</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2793,6 +3118,11 @@
           <t>alprimeenergy</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2026-02-06 17:06:09</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2826,6 +3156,11 @@
           <t>moorelumber</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2026-02-06 17:06:09</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2863,6 +3198,11 @@
           <t>lumberliquidators</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:09:15</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2900,6 +3240,11 @@
           <t>goici</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2026-04-23 14:51:55</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2937,6 +3282,11 @@
           <t>Whitinsvillewater</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2026-03-27 18:28:41</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2974,6 +3324,11 @@
           <t>wcairfreight</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:02:09</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3011,6 +3366,11 @@
           <t>Gallagher Property Services Inc</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:32:55</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3048,6 +3408,11 @@
           <t>simonciniconstruction</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2026-04-27 18:05:51</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3085,6 +3450,11 @@
           <t>Ucxinc</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2026-04-28 19:35:07</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3122,6 +3492,11 @@
           <t>Altium Packaging</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2026-04-23 14:50:58</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3159,6 +3534,11 @@
           <t>K5corporation</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2026-03-23 19:48:50</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3196,6 +3576,11 @@
           <t>Drilexenv</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2026-03-16 13:12:26</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3233,6 +3618,11 @@
           <t>Industrialhearing</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:07:20</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3270,6 +3660,11 @@
           <t>Pratt transport</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2026-03-24 17:23:39</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3307,6 +3702,11 @@
           <t>Old philly trucking inc</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2026-03-23 19:47:11</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3344,6 +3744,11 @@
           <t>Smt Trans Llc</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2026-03-23 19:46:24</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3381,6 +3786,11 @@
           <t>Estes-express</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2026-03-23 19:45:19</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3418,6 +3828,11 @@
           <t>haye transportation</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:09:18</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3455,6 +3870,11 @@
           <t>PEGASUS COURIER LIMO</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:11:12</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3492,6 +3912,11 @@
           <t>aatransportation</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:14:37</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3529,6 +3954,11 @@
           <t>3 LIONS LOGISTICS INC</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:17:56</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3566,6 +3996,11 @@
           <t>RANGER INC</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2026-04-10 16:24:20</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3603,6 +4038,11 @@
           <t>Townmove</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2026-03-17 17:51:06</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3640,6 +4080,11 @@
           <t>phoenix-fiber</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2026-04-28 16:45:43</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3677,6 +4122,11 @@
           <t>Nouria</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2026-03-31 19:41:40</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3714,6 +4164,11 @@
           <t>Lamountainbros</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2026-03-23 18:30:00</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3751,6 +4206,11 @@
           <t>Randwhitney</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:21:45</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3788,6 +4248,11 @@
           <t>NEW ENGLAND STYLE INC</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2026-04-06 19:59:10</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3825,6 +4290,11 @@
           <t>RUSSO BROS INC</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2026-04-28 19:09:07</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3862,6 +4332,11 @@
           <t>Jolinconstruction</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2026-04-28 19:05:38</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3899,6 +4374,11 @@
           <t>Millerfence</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:59:52</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3936,6 +4416,11 @@
           <t>PIOPPI CONSTRUCTION INC</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2026-03-23 18:27:32</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3973,6 +4458,11 @@
           <t>JAM CORPORATION</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2026-03-23 18:39:11</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4010,6 +4500,11 @@
           <t>Fordshometown</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2026-03-31 17:23:20</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4047,6 +4542,11 @@
           <t>Godoubler</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2026-04-23 14:50:36</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4084,6 +4584,11 @@
           <t>Libertymovers</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2026-04-23 14:50:20</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4121,6 +4626,11 @@
           <t>starkmovers</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2026-03-24 15:48:39</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4158,6 +4668,11 @@
           <t>Boyletransport</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2026-04-23 19:09:01</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4195,6 +4710,11 @@
           <t>Niko Transportation Inc</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2026-03-24 16:11:19</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4232,6 +4752,11 @@
           <t>Garcia G Transportation LLC</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2026-03-27 18:24:47</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4269,6 +4794,11 @@
           <t>polarbeverages</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2026-04-30 11:56:21</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4306,6 +4836,11 @@
           <t>Atlasdistributing</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2026-03-24 18:17:19</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4343,6 +4878,11 @@
           <t>Thencd</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:27:47</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4380,6 +4920,11 @@
           <t>Brightops</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2026-04-27 16:43:45</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4417,6 +4962,11 @@
           <t>Casella</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2026-03-24 18:57:44</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4454,6 +5004,11 @@
           <t>dillontree</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2026-04-27 16:47:40</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4491,6 +5046,11 @@
           <t>Aldrichautobody</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2026-04-27 16:50:27</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4528,6 +5088,11 @@
           <t>Wwcontractingcorp</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2026-03-25 15:00:34</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4565,6 +5130,11 @@
           <t>Geosearchinc</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2026-04-27 16:32:05</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4602,6 +5172,11 @@
           <t>Hydratechwater</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2026-04-27 16:34:07</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4639,6 +5214,11 @@
           <t>Twinslawnservice</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:47:57</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4676,6 +5256,11 @@
           <t>Princetonscapes</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2026-03-25 16:55:15</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4713,6 +5298,11 @@
           <t>Mobilemedtransport</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2026-03-25 18:20:52</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4750,6 +5340,11 @@
           <t>Reillysexpressne</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2026-03-25 18:32:05</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4787,6 +5382,11 @@
           <t>a1drillingandblasting</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2026-04-20 15:20:49</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4824,6 +5424,11 @@
           <t>Hoxha Construction LLC</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2026-04-23 14:51:10</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4861,6 +5466,11 @@
           <t>Garveytransport</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2026-03-26 15:04:09</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4898,6 +5508,11 @@
           <t>Peterpanbus</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>2026-03-26 15:35:49</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4935,6 +5550,11 @@
           <t>Abextrans</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2026-04-13 18:46:14</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4972,6 +5592,11 @@
           <t>Wbmason</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>2026-03-26 19:21:36</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5009,6 +5634,11 @@
           <t>Applied Roofing</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>2026-04-28 16:50:41</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5046,6 +5676,11 @@
           <t>COLLAZO TRANSPORT LLC</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>2026-03-27 15:05:33</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5083,6 +5718,11 @@
           <t>J I Express Inc</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>2026-04-23 18:46:12</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5120,6 +5760,11 @@
           <t>leisite</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>2026-03-27 18:37:01</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5157,6 +5802,11 @@
           <t>Worcester Building Systems Inc</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:23:11</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5194,6 +5844,11 @@
           <t>general inc</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>2026-04-28 19:29:59</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5231,6 +5886,11 @@
           <t>tang logistics llc</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:35:26</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5268,6 +5928,11 @@
           <t>Shrewsburylumber</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>2026-03-30 15:11:28</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5305,6 +5970,11 @@
           <t>stairhoppers</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2026-03-30 16:46:09</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5342,6 +6012,11 @@
           <t>mccarthybus</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>2026-03-30 16:52:26</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5379,6 +6054,11 @@
           <t>Dnvanlines</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>2026-03-30 16:56:47</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5416,6 +6096,11 @@
           <t>RSTZ TRANSPORT INC</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>2026-03-30 17:02:38</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5453,6 +6138,11 @@
           <t>Custominsulation</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>2026-04-27 16:19:30</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5490,6 +6180,11 @@
           <t>Pioneersealcoat</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>2026-04-27 16:21:26</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5527,6 +6222,11 @@
           <t>Waynesdrains</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>2026-04-27 16:22:53</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5564,6 +6264,11 @@
           <t>Splendid Junk Removal Inc</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>2026-04-27 16:24:24</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5601,6 +6306,11 @@
           <t>JC COMMUNICATIONS</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>2026-03-31 13:57:09</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5638,6 +6348,11 @@
           <t>Dowling corporation</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>2026-04-28 19:17:29</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5675,6 +6390,11 @@
           <t>RJ PAQUETTE LLC</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>2026-04-28 19:11:43</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5712,6 +6432,11 @@
           <t>Eastland partners</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>2026-04-30 20:13:07</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5749,6 +6474,11 @@
           <t>Driscoll Electric</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>2026-04-23 11:55:48</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5786,6 +6516,11 @@
           <t>Arlington Coal &amp; Lumber Company, Inc</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:13:12</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5823,6 +6558,11 @@
           <t>Centralmasslandscapes</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:30:00</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5860,6 +6600,11 @@
           <t>Cmn Hardscaping And Lawn Care</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>2026-04-13 15:46:25</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5897,6 +6642,11 @@
           <t>Evergreen Lawn Maintenance And Landscape Corporation</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:37:17</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5934,6 +6684,11 @@
           <t>sunset landscaping</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:42:40</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5971,6 +6726,11 @@
           <t>Phoenix Landscaping</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:46:19</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6008,6 +6768,11 @@
           <t>mamblo21</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>2026-04-01 15:01:44</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6045,6 +6810,11 @@
           <t>National glass works</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:42:52</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6082,6 +6852,11 @@
           <t>leisite</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>2026-04-08 19:14:17</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6119,6 +6894,11 @@
           <t>Industrialpackaging</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>2026-04-24 11:55:39</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6156,6 +6936,11 @@
           <t>Trojan Oil</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>2026-04-07 15:24:02</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6193,6 +6978,11 @@
           <t>Centuri</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>2026-04-07 15:27:39</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6230,6 +7020,11 @@
           <t>Goldmedalbakery</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>2026-04-07 15:34:09</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6267,6 +7062,11 @@
           <t>Colony Foods</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>2026-04-07 15:42:11</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6304,6 +7104,11 @@
           <t>Royal steam heater</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>2026-04-07 15:45:00</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6341,6 +7146,11 @@
           <t>Perrone Landscaping</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>2026-04-07 15:53:15</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6378,6 +7188,11 @@
           <t>Wachusett Landscape</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>2026-04-07 16:00:48</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6415,6 +7230,11 @@
           <t>Superior Waste &amp; Recycling</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>2026-04-27 16:45:32</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6452,6 +7272,11 @@
           <t>Star Waste Systems</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>2026-04-27 16:48:30</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6489,6 +7314,11 @@
           <t>airfreightexp</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>2026-04-27 16:52:02</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6526,6 +7356,11 @@
           <t>Ross Express Logistics</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>2026-04-08 18:03:51</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6563,6 +7398,11 @@
           <t>CENTRALIA HOLDINGS LLC</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>2026-04-08 18:06:17</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6600,6 +7440,11 @@
           <t>COMMONWEALTH MEDICAL CARRIER INC</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>2026-04-08 18:09:17</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6637,6 +7482,11 @@
           <t>AURORA EXPRESS INC</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>2026-04-30 17:20:16</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6674,6 +7524,11 @@
           <t>robertsnrg</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>2026-04-08 18:28:18</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6711,6 +7566,11 @@
           <t>UNIQUE GLOBAL TRAVEL LLC</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>2026-04-08 18:32:02</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6748,6 +7608,11 @@
           <t>drusouth</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>2026-04-23 11:55:47</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6785,6 +7650,11 @@
           <t>Rolane transportation</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>2026-04-09 14:50:24</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6822,6 +7692,11 @@
           <t>Rkntransportation</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>2026-04-09 14:53:47</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6859,6 +7734,11 @@
           <t>mcginnbus</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>2026-04-09 15:25:34</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6896,6 +7776,11 @@
           <t>Jderenzo</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>2026-04-28 19:20:41</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6933,6 +7818,11 @@
           <t>Algar construction</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>2026-04-28 19:22:48</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6970,6 +7860,11 @@
           <t>Bullet Express</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>2026-04-30 17:07:20</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7007,6 +7902,11 @@
           <t>Jgmaclellan</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>2026-04-10 13:20:44</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -7044,6 +7944,11 @@
           <t>Cargo Management Group Inc</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>2026-04-10 16:33:51</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7081,6 +7986,11 @@
           <t>Deccorp</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>2026-04-13 15:53:15</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7118,6 +8028,11 @@
           <t>Sandrcorp</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>2026-04-13 15:56:19</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7155,6 +8070,11 @@
           <t>Scrapitus</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>2026-04-13 15:58:50</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7192,6 +8112,11 @@
           <t>Antonelliconstruction</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>2026-04-13 16:10:59</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7229,6 +8154,11 @@
           <t>Adcco</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>2026-04-14 18:12:14</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7266,6 +8196,11 @@
           <t>Purestar</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:46:55</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7303,6 +8238,11 @@
           <t>Lindenmeyr</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>2026-04-15 12:38:26</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7340,6 +8280,11 @@
           <t>J Anthony Express Inc</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>2026-04-15 18:17:17</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -7377,6 +8322,11 @@
           <t>KD TRANSPORT LLC</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>2026-04-15 18:20:12</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -7414,6 +8364,11 @@
           <t>sports turf specialties</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>2026-04-27 16:37:49</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -7451,6 +8406,11 @@
           <t>SPB CONTRACTING INC</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>2026-04-23 18:35:35</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7488,6 +8448,11 @@
           <t>Donovan logistics</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>2026-04-20 18:09:10</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7525,6 +8490,11 @@
           <t>North east group</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>2026-04-21 11:58:39</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7562,6 +8532,11 @@
           <t>Brockway transport inc</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>2026-04-21 14:23:48</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7599,6 +8574,11 @@
           <t>Toupin rigging</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>2026-04-21 15:49:29</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7636,6 +8616,11 @@
           <t>Pride Express</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>2026-04-21 15:52:28</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7673,6 +8658,11 @@
           <t>Sulco-lancer</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>2026-04-21 15:56:46</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7710,6 +8700,11 @@
           <t>Apache Trucking</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>2026-04-21 17:04:32</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7747,6 +8742,11 @@
           <t>Leones landscaping</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:41:07</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7784,6 +8784,11 @@
           <t>Joy ride logistics</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>2026-04-22 18:52:19</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7821,6 +8826,11 @@
           <t>Ugpg2</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2026-04-27 18:12:49</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7858,6 +8868,11 @@
           <t>J. A. MIARA TRANSPORTATION INC</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>2026-04-23 15:49:56</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7895,6 +8910,11 @@
           <t>Imperialworldwide</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>2026-04-23 18:41:25</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7932,6 +8952,11 @@
           <t>Aduiepyle</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>2026-04-23 18:58:16</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7969,6 +8994,11 @@
           <t>Bloombus</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>2026-04-23 19:28:15</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -8006,6 +9036,11 @@
           <t>North Atlantic Trucking Inc</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>2026-04-23 19:33:02</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -8043,6 +9078,11 @@
           <t>Gprinting</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>2026-04-27 18:25:23</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -8080,6 +9120,11 @@
           <t>Performance trans inc</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>2026-04-24 11:52:45</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -8117,6 +9162,11 @@
           <t>Astrochemicals</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>2026-04-24 12:13:00</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -8154,6 +9204,11 @@
           <t>Riley brothers</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>2026-04-24 12:17:05</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -8191,6 +9246,11 @@
           <t>Redline freight systems</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:44:06</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -8228,6 +9288,11 @@
           <t>Ocean express ma</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>2026-04-24 12:31:15</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -8265,6 +9330,11 @@
           <t>MID TRANSPORT INC</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>2026-04-27 18:26:29</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -8302,6 +9372,11 @@
           <t>Traffic safety service</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>2026-04-24 14:36:39</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -8339,6 +9414,11 @@
           <t>Aveneltruck</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>2026-04-24 14:43:03</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -8376,6 +9456,11 @@
           <t>Law logistics</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>2026-04-24 14:58:00</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -8413,6 +9498,11 @@
           <t>Nwdtrucking</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>2026-04-27 14:06:10</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -8450,6 +9540,11 @@
           <t>On track freight systems</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>2026-04-27 14:10:21</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -8487,6 +9582,11 @@
           <t>Sbsewer</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>2026-04-28 16:58:21</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -8524,6 +9624,11 @@
           <t>Overhead door</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>2026-04-27 16:26:16</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -8561,6 +9666,11 @@
           <t>WATTSON HOME SOLUTIONS CO INC</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>2026-04-27 16:28:22</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -8598,6 +9708,11 @@
           <t>Baystatehealth</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>2026-04-30 15:03:19</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8635,6 +9750,11 @@
           <t>aquabounty</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>2026-04-27 16:49:41</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -8672,6 +9792,11 @@
           <t>MA LOGISTICS LLC</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>2026-04-27 18:08:12</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -8709,6 +9834,11 @@
           <t>ARETE DIRECT LLC</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>2026-04-27 18:10:09</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8746,6 +9876,11 @@
           <t>Mozart moving</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>2026-04-27 18:28:56</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -8783,6 +9918,11 @@
           <t>Crlevesque trucking</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>2026-04-27 18:32:13</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -8820,6 +9960,11 @@
           <t>Climate companies</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>2026-04-27 19:10:15</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -8857,6 +10002,11 @@
           <t>Sugarfoods</t>
         </is>
       </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>2026-04-28 13:06:06</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -8894,6 +10044,11 @@
           <t>46logistics</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>2026-04-28 13:09:10</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -8931,6 +10086,11 @@
           <t>Jrc transportation</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>2026-04-28 13:31:57</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -8968,6 +10128,11 @@
           <t>Transport Grayson</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>2026-04-28 16:36:52</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -9005,6 +10170,11 @@
           <t>Ward Transport &amp; Logistics</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>2026-04-28 16:41:55</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -9042,6 +10212,11 @@
           <t>Jycarriers</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>2026-04-28 19:27:32</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -9079,6 +10254,11 @@
           <t>Rhwhite</t>
         </is>
       </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>2026-04-28 19:38:54</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -9116,6 +10296,11 @@
           <t>Afamorello</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>2026-04-28 19:46:42</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -9153,6 +10338,11 @@
           <t>Giexpress</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>2026-04-29 15:54:41</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -9190,6 +10380,11 @@
           <t>Featherlite logistics</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>2026-04-29 15:56:41</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -9227,6 +10422,11 @@
           <t>Diversitygo</t>
         </is>
       </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>2026-04-29 16:10:35</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -9264,6 +10464,11 @@
           <t>Gmhtrans</t>
         </is>
       </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>2026-04-29 16:13:57</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -9301,6 +10506,11 @@
           <t>Uqtrucking</t>
         </is>
       </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>2026-04-29 16:17:13</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -9338,6 +10548,11 @@
           <t>Bound logistics</t>
         </is>
       </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>2026-04-29 16:21:56</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -9375,6 +10590,11 @@
           <t>Por-shun</t>
         </is>
       </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>2026-04-29 16:26:19</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -9412,6 +10632,11 @@
           <t>Amerstal</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:18:39</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -9449,6 +10674,11 @@
           <t>joyride logistics</t>
         </is>
       </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:33:48</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -9486,6 +10716,11 @@
           <t>Go2</t>
         </is>
       </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:39:11</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -9523,6 +10758,11 @@
           <t>BILLY TRUCKING INC</t>
         </is>
       </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:50:48</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -9560,6 +10800,11 @@
           <t>TEARY EYEZ LLC</t>
         </is>
       </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>2026-05-04 12:40:26</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -9597,6 +10842,11 @@
           <t>Aramark</t>
         </is>
       </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>2026-05-04 13:27:46</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -9634,6 +10884,11 @@
           <t>United Refrigeration Inc</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>2026-05-04 13:35:31</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -9671,6 +10926,11 @@
           <t>Globaldesigngroupinc</t>
         </is>
       </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>2026-05-04 13:52:33</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -9708,6 +10968,11 @@
           <t>Guidos services</t>
         </is>
       </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>2026-05-04 14:15:29</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -9745,6 +11010,11 @@
           <t>Ngranese</t>
         </is>
       </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>2026-05-04 14:21:26</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -9780,6 +11050,11 @@
       <c r="G255" t="inlineStr">
         <is>
           <t>Salem glass</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>2026-05-04 14:28:28</t>
         </is>
       </c>
     </row>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H255"/>
+  <dimension ref="A1:H259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11055,6 +11055,174 @@
       <c r="H255" t="inlineStr">
         <is>
           <t>2026-05-04 14:28:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Albert Santamaria</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>melanie@santamariatrans.com</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>(781) 953-2697</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Santamariatrans</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>2026-05-05 12:33:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>MATTHEW COWLES</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>matt@brodeurcampbellfence.com</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (413) 783-6141</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Brodeurcampbellfence</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>2026-05-05 12:36:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>GEORGE JOSEPH CANAVAN JR.</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>canconstr@yahoo.com</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(508) 208-7679 </t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Canavan Construction Corp</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:16:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>ROBERT BRYANT</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>rwbryantinc@rwbryant.com</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>(508) 730-9600</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Rwbryant</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:22:28</t>
         </is>
       </c>
     </row>
@@ -11069,7 +11237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G257"/>
+  <dimension ref="A1:G261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18532,6 +18700,122 @@
       </c>
       <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>2026-05-05 12:33:28</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>2026-05-05 12:36:49</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:16:10</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>476</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:22:28</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -7316,7 +7316,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-04-27 16:52:02</t>
+          <t>2026-05-05 15:49:32</t>
         </is>
       </c>
     </row>
@@ -11237,7 +11237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G261"/>
+  <dimension ref="A1:G262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18816,6 +18816,35 @@
       </c>
       <c r="F261" t="inlineStr"/>
       <c r="G261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>2026-05-05 15:49:32</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H259"/>
+  <dimension ref="A1:H262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11223,6 +11223,132 @@
       <c r="H259" t="inlineStr">
         <is>
           <t>2026-05-05 13:22:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Dennis Reutter</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>dreutter@foodauthority.com</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>(347) 551-9103</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Food Authority</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>2026-05-05 18:17:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Joseph Mazzotta</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>joe@mazzottarentals.com</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>(860) 344-0178</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Mazzotta rentals</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>2026-05-05 18:23:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Shawn DeLude</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>shawn@nausetdisposal.com</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(508) 747-1055 </t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Nauset disposal</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>2026-05-05 18:30:18</t>
         </is>
       </c>
     </row>
@@ -11237,7 +11363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G262"/>
+  <dimension ref="A1:G265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18845,6 +18971,93 @@
       </c>
       <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>2026-05-05 18:17:18</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>2026-05-05 18:23:24</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>NO ANSWER</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>no_answer</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>2026-05-05 18:30:18</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H262"/>
+  <dimension ref="A1:H263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11349,6 +11349,48 @@
       <c r="H262" t="inlineStr">
         <is>
           <t>2026-05-05 18:30:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>JOCELINE SALGUERO ORTEGA</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>joceline@goldengatefreight.com</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>(609) 218-8268</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Goldengate freight</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>2026-05-05 19:24:36</t>
         </is>
       </c>
     </row>
@@ -11363,7 +11405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G265"/>
+  <dimension ref="A1:G266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19058,6 +19100,35 @@
       </c>
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>2026-05-05 19:24:36</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H263"/>
+  <dimension ref="A1:H270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11390,7 +11390,301 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>2026-05-05 19:24:36</t>
+          <t>2026-05-06 15:08:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Chris Cooney</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>chris@ccconstruction.net</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>(508) 398-1811</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Cc construction</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:07:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>STEPHEN  SALWAK</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>stsalwak@sscac.org</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(508) 747-7575 </t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Sscac</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:12:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Gino Mersino</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>gino@mersino.com</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>(810) 658-3472</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Mersino</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:15:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Stefan Freeman</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>sfreeman@flexlogistics.com</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>779-707-9801</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Flex logistics</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:59:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Joel becker</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>jbecker@torrco.com</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>203-465-4262</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Torrco</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:04:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>DONALD DUNHAM</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>dond@yankeeline.us</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>(617) 268-8890</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Yankee line</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:28:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Robin BUITRAGO</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>robin@bayviewlogistics.com</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>(201) 683-8740</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Bayview logistics</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:31:36</t>
         </is>
       </c>
     </row>
@@ -11405,7 +11699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G266"/>
+  <dimension ref="A1:G274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19129,6 +19423,238 @@
       </c>
       <c r="F266" t="inlineStr"/>
       <c r="G266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:07:52</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:12:50</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:15:34</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:59:26</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:04:52</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:08:51</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Busy</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>busy_call_back</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:28:38</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:31:36</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -2002,7 +2002,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-04-30 17:03:09</t>
+          <t>2026-05-06 17:59:31</t>
         </is>
       </c>
     </row>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-04-30 11:56:21</t>
+          <t>2026-05-06 19:18:14</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-04-27 16:43:45</t>
+          <t>2026-05-06 19:25:27</t>
         </is>
       </c>
     </row>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-04-27 16:47:40</t>
+          <t>2026-05-06 19:27:23</t>
         </is>
       </c>
     </row>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-04-27 16:48:30</t>
+          <t>2026-05-06 19:39:21</t>
         </is>
       </c>
     </row>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-04-22 18:52:19</t>
+          <t>2026-05-06 17:53:50</t>
         </is>
       </c>
     </row>
@@ -9710,7 +9710,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-04-30 15:03:19</t>
+          <t>2026-05-06 19:21:01</t>
         </is>
       </c>
     </row>
@@ -11699,7 +11699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G274"/>
+  <dimension ref="A1:G282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16614,17 +16614,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>500</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -16634,7 +16634,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-04-23 15:49:56</t>
+          <t>2026-05-06 17:53:39</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
@@ -16643,17 +16643,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>306</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -16663,7 +16663,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-04-23 18:16:45</t>
+          <t>2026-04-23 15:49:56</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
@@ -16672,7 +16672,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>307</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-04-23 18:22:46</t>
+          <t>2026-04-23 18:16:45</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -16701,7 +16701,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>309</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-04-23 18:25:02</t>
+          <t>2026-04-23 18:22:46</t>
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
@@ -16730,7 +16730,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>311</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -16750,7 +16750,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-04-23 18:27:36</t>
+          <t>2026-04-23 18:25:02</t>
         </is>
       </c>
       <c r="F174" t="inlineStr"/>
@@ -16759,7 +16759,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>313</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -16779,7 +16779,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-04-27 18:07:45</t>
+          <t>2026-04-23 18:27:36</t>
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
@@ -16788,7 +16788,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>394</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-04-27 18:12:10</t>
+          <t>2026-04-27 18:07:45</t>
         </is>
       </c>
       <c r="F176" t="inlineStr"/>
@@ -16817,7 +16817,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>397</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -16837,7 +16837,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-04-23 18:30:34</t>
+          <t>2026-04-27 18:12:10</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -16846,17 +16846,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>315</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -16866,7 +16866,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-04-23 18:35:35</t>
+          <t>2026-04-23 18:30:34</t>
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
@@ -16875,17 +16875,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>316</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -16895,7 +16895,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-04-23 18:41:25</t>
+          <t>2026-04-23 18:35:35</t>
         </is>
       </c>
       <c r="F179" t="inlineStr"/>
@@ -16904,17 +16904,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>318</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -16924,7 +16924,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-04-23 18:46:12</t>
+          <t>2026-04-23 18:41:25</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
@@ -16933,17 +16933,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -16953,7 +16953,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-04-23 18:58:17</t>
+          <t>2026-04-23 18:46:12</t>
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
@@ -16962,17 +16962,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>321</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -16982,7 +16982,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2026-04-23 19:09:01</t>
+          <t>2026-04-23 18:58:17</t>
         </is>
       </c>
       <c r="F182" t="inlineStr"/>
@@ -16991,17 +16991,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>322</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -17011,7 +17011,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-04-23 19:28:02</t>
+          <t>2026-04-23 19:09:01</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
@@ -17020,7 +17020,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>323</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -17040,7 +17040,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-04-23 19:33:02</t>
+          <t>2026-04-23 19:28:02</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -17049,17 +17049,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>324</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -17069,7 +17069,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-04-23 19:35:57</t>
+          <t>2026-04-23 19:33:02</t>
         </is>
       </c>
       <c r="F185" t="inlineStr"/>
@@ -17078,17 +17078,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>325</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -17098,7 +17098,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-04-24 11:52:45</t>
+          <t>2026-04-23 19:35:57</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
@@ -17107,17 +17107,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>326</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -17127,7 +17127,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-04-24 11:55:39</t>
+          <t>2026-04-24 11:52:45</t>
         </is>
       </c>
       <c r="F187" t="inlineStr"/>
@@ -17136,17 +17136,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>328</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-04-24 12:13:00</t>
+          <t>2026-04-24 11:55:39</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
@@ -17165,7 +17165,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>329</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -17185,7 +17185,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-04-24 12:17:05</t>
+          <t>2026-04-24 12:13:00</t>
         </is>
       </c>
       <c r="F189" t="inlineStr"/>
@@ -17194,17 +17194,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>330</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -17214,7 +17214,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2026-04-24 12:19:39</t>
+          <t>2026-04-24 12:17:05</t>
         </is>
       </c>
       <c r="F190" t="inlineStr"/>
@@ -17223,17 +17223,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>331</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -17243,7 +17243,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-04-24 12:31:15</t>
+          <t>2026-04-24 12:19:39</t>
         </is>
       </c>
       <c r="F191" t="inlineStr"/>
@@ -17252,17 +17252,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>332</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -17272,7 +17272,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-04-24 12:33:01</t>
+          <t>2026-04-24 12:31:15</t>
         </is>
       </c>
       <c r="F192" t="inlineStr"/>
@@ -17281,17 +17281,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>333</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-04-24 14:36:24</t>
+          <t>2026-04-24 12:33:01</t>
         </is>
       </c>
       <c r="F193" t="inlineStr"/>
@@ -17310,7 +17310,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>334</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -17330,7 +17330,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-04-24 14:43:03</t>
+          <t>2026-04-24 14:36:24</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -17339,17 +17339,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>335</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -17359,7 +17359,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-04-24 14:58:00</t>
+          <t>2026-04-24 14:43:03</t>
         </is>
       </c>
       <c r="F195" t="inlineStr"/>
@@ -17368,17 +17368,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>336</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -17388,7 +17388,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2026-04-27 14:06:10</t>
+          <t>2026-04-24 14:58:00</t>
         </is>
       </c>
       <c r="F196" t="inlineStr"/>
@@ -17397,17 +17397,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>337</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-04-27 14:10:21</t>
+          <t>2026-04-27 14:06:10</t>
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
@@ -17426,17 +17426,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>338</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-04-27 14:13:06</t>
+          <t>2026-04-27 14:10:21</t>
         </is>
       </c>
       <c r="F198" t="inlineStr"/>
@@ -17455,17 +17455,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>339</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -17475,7 +17475,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-04-27 14:15:47</t>
+          <t>2026-04-27 14:13:06</t>
         </is>
       </c>
       <c r="F199" t="inlineStr"/>
@@ -17484,17 +17484,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>340</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -17504,7 +17504,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:51</t>
+          <t>2026-04-27 14:15:47</t>
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
@@ -17513,17 +17513,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>393</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -17533,7 +17533,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-04-27 18:08:12</t>
+          <t>2026-04-27 18:05:51</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -17542,17 +17542,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>395</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -17562,7 +17562,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-04-27 18:10:09</t>
+          <t>2026-04-27 18:08:12</t>
         </is>
       </c>
       <c r="F202" t="inlineStr"/>
@@ -17571,17 +17571,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>396</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -17591,7 +17591,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-04-27 18:12:49</t>
+          <t>2026-04-27 18:10:09</t>
         </is>
       </c>
       <c r="F203" t="inlineStr"/>
@@ -17600,17 +17600,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>398</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -17620,7 +17620,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-04-27 18:25:23</t>
+          <t>2026-04-27 18:12:49</t>
         </is>
       </c>
       <c r="F204" t="inlineStr"/>
@@ -17629,17 +17629,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>399</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -17649,7 +17649,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-04-27 18:26:29</t>
+          <t>2026-04-27 18:25:23</t>
         </is>
       </c>
       <c r="F205" t="inlineStr"/>
@@ -17658,7 +17658,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>400</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17678,7 +17678,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-04-27 18:28:56</t>
+          <t>2026-04-27 18:26:29</t>
         </is>
       </c>
       <c r="F206" t="inlineStr"/>
@@ -17687,7 +17687,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>401</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17707,7 +17707,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-04-27 18:32:14</t>
+          <t>2026-04-27 18:28:56</t>
         </is>
       </c>
       <c r="F207" t="inlineStr"/>
@@ -17716,7 +17716,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>402</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17736,7 +17736,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-04-27 19:10:16</t>
+          <t>2026-04-27 18:32:14</t>
         </is>
       </c>
       <c r="F208" t="inlineStr"/>
@@ -17745,7 +17745,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>403</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17765,7 +17765,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-04-28 13:06:06</t>
+          <t>2026-04-27 19:10:16</t>
         </is>
       </c>
       <c r="F209" t="inlineStr"/>
@@ -17774,17 +17774,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>404</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2026-04-28 13:09:10</t>
+          <t>2026-04-28 13:06:06</t>
         </is>
       </c>
       <c r="F210" t="inlineStr"/>
@@ -17803,17 +17803,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>405</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -17823,7 +17823,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-04-28 13:31:57</t>
+          <t>2026-04-28 13:09:10</t>
         </is>
       </c>
       <c r="F211" t="inlineStr"/>
@@ -17832,7 +17832,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>406</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17852,7 +17852,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-04-28 16:36:52</t>
+          <t>2026-04-28 13:31:57</t>
         </is>
       </c>
       <c r="F212" t="inlineStr"/>
@@ -17861,17 +17861,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>408</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -17881,7 +17881,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-04-28 16:41:55</t>
+          <t>2026-04-28 16:36:52</t>
         </is>
       </c>
       <c r="F213" t="inlineStr"/>
@@ -17890,7 +17890,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>409</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17910,7 +17910,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-04-28 16:45:43</t>
+          <t>2026-04-28 16:41:55</t>
         </is>
       </c>
       <c r="F214" t="inlineStr"/>
@@ -17919,17 +17919,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>410</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -17939,7 +17939,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-04-28 16:50:41</t>
+          <t>2026-04-28 16:45:43</t>
         </is>
       </c>
       <c r="F215" t="inlineStr"/>
@@ -17948,17 +17948,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>411</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -17968,7 +17968,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-04-28 16:58:22</t>
+          <t>2026-04-28 16:50:41</t>
         </is>
       </c>
       <c r="F216" t="inlineStr"/>
@@ -17977,17 +17977,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>412</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-04-28 19:11:43</t>
+          <t>2026-04-28 16:58:22</t>
         </is>
       </c>
       <c r="F217" t="inlineStr"/>
@@ -18006,17 +18006,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>422</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-04-28 19:17:29</t>
+          <t>2026-04-28 19:11:43</t>
         </is>
       </c>
       <c r="F218" t="inlineStr"/>
@@ -18035,17 +18035,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>425</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -18055,7 +18055,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-04-28 19:20:41</t>
+          <t>2026-04-28 19:17:29</t>
         </is>
       </c>
       <c r="F219" t="inlineStr"/>
@@ -18064,7 +18064,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>427</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18084,7 +18084,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-04-28 19:27:32</t>
+          <t>2026-04-28 19:20:41</t>
         </is>
       </c>
       <c r="F220" t="inlineStr"/>
@@ -18093,17 +18093,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>431</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -18113,7 +18113,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-04-28 19:29:59</t>
+          <t>2026-04-28 19:27:32</t>
         </is>
       </c>
       <c r="F221" t="inlineStr"/>
@@ -18122,17 +18122,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>432</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -18142,7 +18142,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-04-28 19:38:54</t>
+          <t>2026-04-28 19:29:59</t>
         </is>
       </c>
       <c r="F222" t="inlineStr"/>
@@ -18151,17 +18151,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>438</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -18171,7 +18171,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-04-28 18:59:52</t>
+          <t>2026-04-28 19:38:54</t>
         </is>
       </c>
       <c r="F223" t="inlineStr"/>
@@ -18180,17 +18180,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>413</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -18200,7 +18200,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-04-28 19:05:38</t>
+          <t>2026-04-28 18:59:52</t>
         </is>
       </c>
       <c r="F224" t="inlineStr"/>
@@ -18209,7 +18209,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>416</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-04-28 19:09:07</t>
+          <t>2026-04-28 19:05:38</t>
         </is>
       </c>
       <c r="F225" t="inlineStr"/>
@@ -18238,7 +18238,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>420</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18258,7 +18258,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-04-28 19:22:49</t>
+          <t>2026-04-28 19:09:07</t>
         </is>
       </c>
       <c r="F226" t="inlineStr"/>
@@ -18267,17 +18267,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>429</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -18287,7 +18287,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-04-28 19:46:42</t>
+          <t>2026-04-28 19:22:49</t>
         </is>
       </c>
       <c r="F227" t="inlineStr"/>
@@ -18296,17 +18296,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>439</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -18316,7 +18316,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-04-29 15:54:41</t>
+          <t>2026-04-28 19:46:42</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
@@ -18325,7 +18325,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>440</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18345,7 +18345,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-04-29 15:56:41</t>
+          <t>2026-04-29 15:54:41</t>
         </is>
       </c>
       <c r="F229" t="inlineStr"/>
@@ -18354,17 +18354,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>441</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-04-29 16:10:35</t>
+          <t>2026-04-29 15:56:41</t>
         </is>
       </c>
       <c r="F230" t="inlineStr"/>
@@ -18383,17 +18383,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>442</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -18403,7 +18403,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-04-29 16:13:57</t>
+          <t>2026-04-29 16:10:35</t>
         </is>
       </c>
       <c r="F231" t="inlineStr"/>
@@ -18412,17 +18412,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>443</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -18432,7 +18432,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-04-29 16:17:13</t>
+          <t>2026-04-29 16:13:57</t>
         </is>
       </c>
       <c r="F232" t="inlineStr"/>
@@ -18441,7 +18441,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>444</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18461,7 +18461,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-04-29 16:21:56</t>
+          <t>2026-04-29 16:17:13</t>
         </is>
       </c>
       <c r="F233" t="inlineStr"/>
@@ -18470,7 +18470,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>445</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18490,7 +18490,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-04-29 16:26:19</t>
+          <t>2026-04-29 16:21:56</t>
         </is>
       </c>
       <c r="F234" t="inlineStr"/>
@@ -18499,7 +18499,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>446</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18519,7 +18519,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-04-30 11:56:22</t>
+          <t>2026-04-29 16:26:19</t>
         </is>
       </c>
       <c r="F235" t="inlineStr"/>
@@ -18528,7 +18528,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>447</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18548,7 +18548,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2026-04-30 12:18:39</t>
+          <t>2026-04-30 11:56:22</t>
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
@@ -18557,7 +18557,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>448</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18577,7 +18577,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-04-30 12:27:47</t>
+          <t>2026-04-30 12:18:39</t>
         </is>
       </c>
       <c r="F237" t="inlineStr"/>
@@ -18586,17 +18586,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>449</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -18606,7 +18606,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-04-30 14:33:48</t>
+          <t>2026-04-30 12:27:47</t>
         </is>
       </c>
       <c r="F238" t="inlineStr"/>
@@ -18615,17 +18615,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>450</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -18635,7 +18635,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-04-30 14:39:11</t>
+          <t>2026-04-30 14:33:48</t>
         </is>
       </c>
       <c r="F239" t="inlineStr"/>
@@ -18644,17 +18644,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>452</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -18664,7 +18664,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-04-30 14:44:06</t>
+          <t>2026-04-30 14:39:11</t>
         </is>
       </c>
       <c r="F240" t="inlineStr"/>
@@ -18673,17 +18673,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>453</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-04-30 14:50:48</t>
+          <t>2026-04-30 14:44:06</t>
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
@@ -18702,17 +18702,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>454</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-04-30 15:03:19</t>
+          <t>2026-04-30 14:50:48</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
@@ -18731,7 +18731,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>455</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18751,7 +18751,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-04-30 16:43:14</t>
+          <t>2026-04-30 15:03:19</t>
         </is>
       </c>
       <c r="F243" t="inlineStr"/>
@@ -18760,7 +18760,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>456</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -18780,7 +18780,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-04-30 16:49:38</t>
+          <t>2026-04-30 16:43:14</t>
         </is>
       </c>
       <c r="F244" t="inlineStr"/>
@@ -18789,17 +18789,17 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>457</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -18809,7 +18809,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-04-30 16:57:13</t>
+          <t>2026-04-30 16:49:38</t>
         </is>
       </c>
       <c r="F245" t="inlineStr"/>
@@ -18818,17 +18818,17 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>458</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -18838,7 +18838,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-04-30 16:59:14</t>
+          <t>2026-04-30 16:57:13</t>
         </is>
       </c>
       <c r="F246" t="inlineStr"/>
@@ -18847,17 +18847,17 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>459</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -18867,7 +18867,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-04-30 17:03:09</t>
+          <t>2026-04-30 16:59:14</t>
         </is>
       </c>
       <c r="F247" t="inlineStr"/>
@@ -18876,7 +18876,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -18896,7 +18896,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-04-30 17:07:20</t>
+          <t>2026-04-30 17:03:09</t>
         </is>
       </c>
       <c r="F248" t="inlineStr"/>
@@ -18905,7 +18905,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>461</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -18925,7 +18925,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-04-30 17:20:16</t>
+          <t>2026-04-30 17:07:20</t>
         </is>
       </c>
       <c r="F249" t="inlineStr"/>
@@ -18934,7 +18934,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>462</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -18954,7 +18954,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-05-04 12:40:26</t>
+          <t>2026-04-30 17:20:16</t>
         </is>
       </c>
       <c r="F250" t="inlineStr"/>
@@ -18963,17 +18963,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>465</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-05-04 13:27:46</t>
+          <t>2026-05-04 12:40:26</t>
         </is>
       </c>
       <c r="F251" t="inlineStr"/>
@@ -18992,17 +18992,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>466</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-05-04 13:32:27</t>
+          <t>2026-05-04 13:27:46</t>
         </is>
       </c>
       <c r="F252" t="inlineStr"/>
@@ -19021,17 +19021,17 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>467</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -19041,7 +19041,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-05-04 13:35:31</t>
+          <t>2026-05-04 13:32:27</t>
         </is>
       </c>
       <c r="F253" t="inlineStr"/>
@@ -19050,7 +19050,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>468</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19070,7 +19070,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-05-04 13:52:33</t>
+          <t>2026-05-04 13:35:31</t>
         </is>
       </c>
       <c r="F254" t="inlineStr"/>
@@ -19079,17 +19079,17 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>469</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -19099,7 +19099,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-05-04 14:15:29</t>
+          <t>2026-05-04 13:52:33</t>
         </is>
       </c>
       <c r="F255" t="inlineStr"/>
@@ -19108,7 +19108,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>470</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -19128,7 +19128,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2026-05-04 14:21:26</t>
+          <t>2026-05-04 14:15:29</t>
         </is>
       </c>
       <c r="F256" t="inlineStr"/>
@@ -19137,7 +19137,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>471</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -19157,7 +19157,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-05-04 14:28:28</t>
+          <t>2026-05-04 14:21:26</t>
         </is>
       </c>
       <c r="F257" t="inlineStr"/>
@@ -19166,17 +19166,17 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>472</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -19186,7 +19186,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-05-05 12:33:28</t>
+          <t>2026-05-04 14:28:28</t>
         </is>
       </c>
       <c r="F258" t="inlineStr"/>
@@ -19195,17 +19195,17 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>473</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -19215,7 +19215,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-05-05 12:36:49</t>
+          <t>2026-05-05 12:33:28</t>
         </is>
       </c>
       <c r="F259" t="inlineStr"/>
@@ -19224,17 +19224,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>474</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -19244,7 +19244,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-05-05 13:16:10</t>
+          <t>2026-05-05 12:36:49</t>
         </is>
       </c>
       <c r="F260" t="inlineStr"/>
@@ -19253,7 +19253,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>475</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -19273,7 +19273,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-05-05 13:22:28</t>
+          <t>2026-05-05 13:16:10</t>
         </is>
       </c>
       <c r="F261" t="inlineStr"/>
@@ -19282,7 +19282,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>476</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -19302,7 +19302,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-05-05 15:49:32</t>
+          <t>2026-05-05 13:22:28</t>
         </is>
       </c>
       <c r="F262" t="inlineStr"/>
@@ -19311,7 +19311,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>478</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -19331,7 +19331,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-05-05 18:17:18</t>
+          <t>2026-05-05 15:49:32</t>
         </is>
       </c>
       <c r="F263" t="inlineStr"/>
@@ -19340,17 +19340,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>484</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -19360,7 +19360,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-05-05 18:23:24</t>
+          <t>2026-05-05 18:17:18</t>
         </is>
       </c>
       <c r="F264" t="inlineStr"/>
@@ -19369,17 +19369,17 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>485</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-05-05 18:30:18</t>
+          <t>2026-05-05 18:23:24</t>
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
@@ -19398,17 +19398,17 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>486</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -19418,7 +19418,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-05-05 19:24:36</t>
+          <t>2026-05-05 18:30:18</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
@@ -19427,17 +19427,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>487</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -19447,7 +19447,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-05-06 14:07:52</t>
+          <t>2026-05-05 19:24:36</t>
         </is>
       </c>
       <c r="F267" t="inlineStr"/>
@@ -19456,17 +19456,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>488</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -19476,7 +19476,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-05-06 14:12:50</t>
+          <t>2026-05-06 14:07:52</t>
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
@@ -19485,17 +19485,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>489</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -19505,7 +19505,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-05-06 14:15:34</t>
+          <t>2026-05-06 14:12:50</t>
         </is>
       </c>
       <c r="F269" t="inlineStr"/>
@@ -19514,17 +19514,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>490</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -19534,7 +19534,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-05-06 14:59:26</t>
+          <t>2026-05-06 14:15:34</t>
         </is>
       </c>
       <c r="F270" t="inlineStr"/>
@@ -19543,17 +19543,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -19563,7 +19563,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-05-06 15:04:52</t>
+          <t>2026-05-06 14:59:26</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
@@ -19572,7 +19572,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>492</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -19592,7 +19592,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-05-06 15:08:51</t>
+          <t>2026-05-06 15:04:52</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
@@ -19601,17 +19601,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>493</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Busy</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -19621,7 +19621,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-05-06 15:28:38</t>
+          <t>2026-05-06 15:08:51</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
@@ -19630,17 +19630,17 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>494</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Busy</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -19650,11 +19650,243 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-05-06 15:31:36</t>
+          <t>2026-05-06 15:28:38</t>
         </is>
       </c>
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:31:36</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:53:50</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:59:31</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>2026-05-06 19:18:14</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>2026-05-06 19:21:01</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>2026-05-06 19:25:27</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>2026-05-06 19:27:23</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>2026-05-06 19:39:21</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -5300,7 +5300,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-03-25 18:20:52</t>
+          <t>2026-05-06 20:12:28</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-03-30 16:56:47</t>
+          <t>2026-05-06 20:09:52</t>
         </is>
       </c>
     </row>
@@ -11699,7 +11699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G282"/>
+  <dimension ref="A1:G286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13656,17 +13656,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>510</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-03-26 14:46:03</t>
+          <t>2026-05-06 20:12:18</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -13685,17 +13685,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>217</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13705,7 +13705,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-03-26 14:57:57</t>
+          <t>2026-03-26 14:46:03</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -13714,17 +13714,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>218</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-03-26 15:12:09</t>
+          <t>2026-03-26 14:57:57</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -13743,17 +13743,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>220</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -13763,7 +13763,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-03-26 15:45:11</t>
+          <t>2026-03-26 15:12:09</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -13772,7 +13772,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>221</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -13792,7 +13792,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-04-27 16:39:08</t>
+          <t>2026-03-26 15:45:11</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -13801,17 +13801,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>370</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-03-27 18:06:04</t>
+          <t>2026-04-27 16:39:08</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -13830,17 +13830,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>228</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -13850,7 +13850,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-03-27 18:09:32</t>
+          <t>2026-03-27 18:06:04</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -13859,12 +13859,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>229</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Call on Monday</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -13879,7 +13879,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-03-27 18:13:29</t>
+          <t>2026-03-27 18:09:32</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -13888,17 +13888,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>230</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call on Monday</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-03-27 18:16:14</t>
+          <t>2026-03-27 18:13:29</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -13917,17 +13917,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>231</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -13937,7 +13937,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-03-27 18:28:41</t>
+          <t>2026-03-27 18:16:14</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -13946,17 +13946,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>232</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -13966,7 +13966,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-04-23 18:46:03</t>
+          <t>2026-03-27 18:28:41</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -13975,7 +13975,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>319</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -13995,7 +13995,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-04-27 16:34:45</t>
+          <t>2026-04-23 18:46:03</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -14004,17 +14004,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>363</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-03-27 19:30:50</t>
+          <t>2026-04-27 16:34:45</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -14033,17 +14033,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>233</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -14053,7 +14053,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-03-30 16:46:09</t>
+          <t>2026-03-27 19:30:50</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
@@ -14062,17 +14062,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>239</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-03-31 13:50:49</t>
+          <t>2026-03-30 16:46:09</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -14091,17 +14091,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>508</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Busy</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-03-31 13:57:09</t>
+          <t>2026-05-06 20:09:36</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
@@ -14120,17 +14120,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>245</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -14140,7 +14140,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-03-31 14:01:39</t>
+          <t>2026-03-31 13:50:49</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -14149,17 +14149,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>246</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14169,7 +14169,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-03-31 14:09:41</t>
+          <t>2026-03-31 13:57:09</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -14178,17 +14178,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>247</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-03-31 19:13:49</t>
+          <t>2026-03-31 14:01:39</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -14207,17 +14207,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>248</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14227,7 +14227,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-04-27 16:17:22</t>
+          <t>2026-03-31 14:09:41</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
@@ -14236,17 +14236,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>249</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14256,7 +14256,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-04-27 16:22:28</t>
+          <t>2026-03-31 19:13:49</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
@@ -14265,7 +14265,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>341</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-04-27 16:23:48</t>
+          <t>2026-04-27 16:17:22</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
@@ -14294,17 +14294,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>347</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14314,7 +14314,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-04-27 16:26:16</t>
+          <t>2026-04-27 16:22:28</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -14323,7 +14323,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>349</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-04-27 16:32:05</t>
+          <t>2026-04-27 16:23:48</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -14352,7 +14352,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>352</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -14372,7 +14372,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-04-27 16:33:04</t>
+          <t>2026-04-27 16:26:16</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -14381,7 +14381,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -14401,7 +14401,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-04-27 16:34:57</t>
+          <t>2026-04-27 16:32:05</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -14410,7 +14410,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>361</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:15</t>
+          <t>2026-04-27 16:33:04</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
@@ -14439,7 +14439,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>364</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -14459,7 +14459,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-04-28 19:05:25</t>
+          <t>2026-04-27 16:34:57</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -14468,7 +14468,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>390</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-04-28 19:06:58</t>
+          <t>2026-04-27 18:05:15</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -14497,17 +14497,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>415</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -14517,7 +14517,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-04-28 19:16:34</t>
+          <t>2026-04-28 19:05:25</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -14526,7 +14526,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>418</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-04-28 19:34:42</t>
+          <t>2026-04-28 19:06:58</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
@@ -14555,7 +14555,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>423</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-03-31 19:22:45</t>
+          <t>2026-04-28 19:16:34</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
@@ -14584,17 +14584,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>435</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -14604,7 +14604,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-03-31 19:37:10</t>
+          <t>2026-04-28 19:34:42</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -14613,17 +14613,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>250</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>follow_up</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-04-01 14:30:00</t>
+          <t>2026-03-31 19:22:45</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
@@ -14642,17 +14642,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>251</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -14662,7 +14662,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-04-01 16:53:36</t>
+          <t>2026-03-31 19:37:10</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -14671,17 +14671,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>252</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -14691,7 +14691,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-04-07 15:24:02</t>
+          <t>2026-04-01 14:30:00</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -14700,17 +14700,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>253</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-04-07 16:00:48</t>
+          <t>2026-04-01 16:53:36</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -14729,17 +14729,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>271</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-04-24 11:55:32</t>
+          <t>2026-04-07 15:24:02</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -14758,17 +14758,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>272</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14778,7 +14778,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-04-27 16:17:36</t>
+          <t>2026-04-07 16:00:48</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -14787,7 +14787,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>327</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -14807,7 +14807,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-04-27 16:20:52</t>
+          <t>2026-04-24 11:55:32</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
@@ -14816,7 +14816,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>342</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -14836,7 +14836,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-04-27 16:22:53</t>
+          <t>2026-04-27 16:17:36</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
@@ -14845,7 +14845,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>345</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -14865,7 +14865,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-04-27 16:24:00</t>
+          <t>2026-04-27 16:20:52</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
@@ -14874,7 +14874,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>348</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-04-27 16:27:53</t>
+          <t>2026-04-27 16:22:53</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
@@ -14903,17 +14903,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>350</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-04-08 16:38:00</t>
+          <t>2026-04-27 16:24:00</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
@@ -14932,7 +14932,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>353</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-04-08 18:21:03</t>
+          <t>2026-04-27 16:27:53</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
@@ -14961,17 +14961,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>274</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-04-23 18:22:34</t>
+          <t>2026-04-08 16:38:00</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
@@ -14990,7 +14990,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>275</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -15010,7 +15010,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-04-23 18:24:52</t>
+          <t>2026-04-08 18:21:03</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -15019,7 +15019,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>308</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -15039,7 +15039,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-04-27 16:43:32</t>
+          <t>2026-04-23 18:22:34</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
@@ -15048,17 +15048,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>310</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15068,7 +15068,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-04-27 16:44:32</t>
+          <t>2026-04-23 18:24:52</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
@@ -15077,7 +15077,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>376</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -15097,7 +15097,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-04-27 16:47:27</t>
+          <t>2026-04-27 16:43:32</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
@@ -15106,17 +15106,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>378</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-04-27 16:48:30</t>
+          <t>2026-04-27 16:44:32</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
@@ -15135,17 +15135,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>381</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15155,7 +15155,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-04-27 16:49:41</t>
+          <t>2026-04-27 16:47:27</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
@@ -15164,7 +15164,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>383</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -15184,7 +15184,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-04-27 16:51:50</t>
+          <t>2026-04-27 16:48:30</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
@@ -15193,17 +15193,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>384</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-04-28 19:34:54</t>
+          <t>2026-04-27 16:49:41</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
@@ -15222,17 +15222,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>386</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -15242,7 +15242,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-04-09 14:38:33</t>
+          <t>2026-04-27 16:51:50</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
@@ -15251,17 +15251,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>436</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15271,7 +15271,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-04-09 14:50:24</t>
+          <t>2026-04-28 19:34:54</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
@@ -15280,17 +15280,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>276</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-04-27 16:17:54</t>
+          <t>2026-04-09 14:38:33</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
@@ -15309,17 +15309,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>277</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15329,7 +15329,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-04-27 16:19:16</t>
+          <t>2026-04-09 14:50:24</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -15338,17 +15338,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>343</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15358,7 +15358,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-04-27 16:21:26</t>
+          <t>2026-04-27 16:17:54</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -15367,17 +15367,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>344</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>email</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15387,7 +15387,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-04-27 16:30:33</t>
+          <t>2026-04-27 16:19:16</t>
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
@@ -15396,17 +15396,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>346</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-04-27 16:34:07</t>
+          <t>2026-04-27 16:21:26</t>
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
@@ -15425,17 +15425,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>357</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15445,7 +15445,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-04-27 16:35:11</t>
+          <t>2026-04-27 16:30:33</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -15454,17 +15454,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>362</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15474,7 +15474,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:29</t>
+          <t>2026-04-27 16:34:07</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
@@ -15483,7 +15483,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>365</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -15503,7 +15503,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-04-28 19:20:18</t>
+          <t>2026-04-27 16:35:11</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -15512,7 +15512,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>391</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -15532,7 +15532,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-04-28 19:22:33</t>
+          <t>2026-04-27 18:05:29</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
@@ -15541,7 +15541,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>426</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -15561,7 +15561,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-04-28 19:27:09</t>
+          <t>2026-04-28 19:20:18</t>
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
@@ -15570,17 +15570,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>428</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -15590,7 +15590,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-04-13 15:45:27</t>
+          <t>2026-04-28 19:22:33</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
@@ -15599,17 +15599,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>430</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -15619,7 +15619,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-04-13 15:46:25</t>
+          <t>2026-04-28 19:27:09</t>
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
@@ -15628,17 +15628,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>286</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -15648,7 +15648,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-04-13 15:53:15</t>
+          <t>2026-04-13 15:45:27</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
@@ -15657,17 +15657,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>287</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-04-13 15:58:50</t>
+          <t>2026-04-13 15:46:25</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
@@ -15686,7 +15686,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>288</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -15706,7 +15706,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-04-27 16:24:24</t>
+          <t>2026-04-13 15:53:15</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
@@ -15715,17 +15715,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>289</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-04-27 16:28:22</t>
+          <t>2026-04-13 15:58:50</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -15744,17 +15744,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>351</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-04-27 16:35:40</t>
+          <t>2026-04-27 16:24:24</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -15773,17 +15773,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>354</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-04-28 19:07:14</t>
+          <t>2026-04-27 16:28:22</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
@@ -15802,7 +15802,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>366</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -15822,7 +15822,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-04-28 19:16:45</t>
+          <t>2026-04-27 16:35:40</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
@@ -15831,17 +15831,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>419</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -15851,7 +15851,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-04-27 16:29:25</t>
+          <t>2026-04-28 19:07:14</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
@@ -15860,17 +15860,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>424</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-04-27 16:31:00</t>
+          <t>2026-04-28 19:16:45</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
@@ -15889,17 +15889,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>356</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -15909,7 +15909,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-04-27 16:39:21</t>
+          <t>2026-04-27 16:29:25</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
@@ -15918,17 +15918,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>358</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -15938,7 +15938,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-04-27 16:40:26</t>
+          <t>2026-04-27 16:31:00</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
@@ -15947,7 +15947,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>371</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -15967,7 +15967,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-04-27 16:42:47</t>
+          <t>2026-04-27 16:39:21</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
@@ -15976,17 +15976,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>373</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -15996,7 +15996,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-04-15 16:05:12</t>
+          <t>2026-04-27 16:40:26</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
@@ -16005,17 +16005,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>374</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -16025,7 +16025,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-04-15 18:17:17</t>
+          <t>2026-04-27 16:42:47</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
@@ -16034,17 +16034,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>294</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -16054,7 +16054,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-04-27 16:35:57</t>
+          <t>2026-04-15 16:05:12</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
@@ -16063,17 +16063,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>295</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -16083,7 +16083,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-04-27 16:52:02</t>
+          <t>2026-04-15 18:17:17</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
@@ -16092,17 +16092,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>367</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -16112,7 +16112,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-04-28 19:11:23</t>
+          <t>2026-04-27 16:35:57</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
@@ -16121,17 +16121,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>387</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -16141,7 +16141,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-04-30 14:38:42</t>
+          <t>2026-04-27 16:52:02</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -16150,17 +16150,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>421</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -16170,7 +16170,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-04-16 12:32:37</t>
+          <t>2026-04-28 19:11:23</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -16179,17 +16179,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>451</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -16199,7 +16199,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-04-16 12:52:16</t>
+          <t>2026-04-30 14:38:42</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -16208,17 +16208,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>296</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -16228,7 +16228,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-04-27 16:37:49</t>
+          <t>2026-04-16 12:32:37</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
@@ -16237,17 +16237,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>297</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -16257,7 +16257,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-04-27 16:45:32</t>
+          <t>2026-04-16 12:52:16</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -16266,7 +16266,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>368</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-04-27 16:47:40</t>
+          <t>2026-04-27 16:37:49</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
@@ -16295,17 +16295,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>379</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -16315,7 +16315,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-04-16 18:41:52</t>
+          <t>2026-04-27 16:45:32</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -16324,7 +16324,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>382</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -16344,7 +16344,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-04-23 18:27:22</t>
+          <t>2026-04-27 16:47:40</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
@@ -16353,17 +16353,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>299</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-04-23 18:30:25</t>
+          <t>2026-04-16 18:41:52</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
@@ -16382,7 +16382,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>312</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -16402,7 +16402,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-04-27 16:43:45</t>
+          <t>2026-04-23 18:27:22</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
@@ -16411,17 +16411,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>314</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -16431,7 +16431,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-04-23 18:40:56</t>
+          <t>2026-04-23 18:30:25</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -16440,17 +16440,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>377</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -16460,7 +16460,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-04-21 15:49:30</t>
+          <t>2026-04-27 16:43:45</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
@@ -16469,17 +16469,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>317</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -16489,7 +16489,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-04-21 15:52:28</t>
+          <t>2026-04-23 18:40:56</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
@@ -16498,17 +16498,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -16518,7 +16518,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-04-21 17:03:38</t>
+          <t>2026-04-21 15:49:30</t>
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
@@ -16527,7 +16527,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>301</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -16547,7 +16547,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-04-22 16:41:07</t>
+          <t>2026-04-21 15:52:28</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
@@ -16556,17 +16556,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>302</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -16576,7 +16576,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:41</t>
+          <t>2026-04-21 17:03:38</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
@@ -16585,17 +16585,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>303</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -16605,7 +16605,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-04-28 19:35:07</t>
+          <t>2026-04-22 16:41:07</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
@@ -16614,7 +16614,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>392</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -16634,7 +16634,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-05-06 17:53:39</t>
+          <t>2026-04-27 18:05:41</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
@@ -16643,17 +16643,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>437</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -16663,7 +16663,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-04-23 15:49:56</t>
+          <t>2026-04-28 19:35:07</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
@@ -16672,7 +16672,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>500</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-04-23 18:16:45</t>
+          <t>2026-05-06 17:53:39</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -16701,17 +16701,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>306</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-04-23 18:22:46</t>
+          <t>2026-04-23 15:49:56</t>
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
@@ -16730,7 +16730,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>307</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -16750,7 +16750,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-04-23 18:25:02</t>
+          <t>2026-04-23 18:16:45</t>
         </is>
       </c>
       <c r="F174" t="inlineStr"/>
@@ -16759,7 +16759,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>309</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -16779,7 +16779,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-04-23 18:27:36</t>
+          <t>2026-04-23 18:22:46</t>
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
@@ -16788,7 +16788,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>311</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-04-27 18:07:45</t>
+          <t>2026-04-23 18:25:02</t>
         </is>
       </c>
       <c r="F176" t="inlineStr"/>
@@ -16817,7 +16817,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>313</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -16837,7 +16837,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-04-27 18:12:10</t>
+          <t>2026-04-23 18:27:36</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -16846,7 +16846,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>394</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -16866,7 +16866,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-04-23 18:30:34</t>
+          <t>2026-04-27 18:07:45</t>
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
@@ -16875,17 +16875,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>397</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -16895,7 +16895,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-04-23 18:35:35</t>
+          <t>2026-04-27 18:12:10</t>
         </is>
       </c>
       <c r="F179" t="inlineStr"/>
@@ -16904,17 +16904,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>315</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -16924,7 +16924,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-04-23 18:41:25</t>
+          <t>2026-04-23 18:30:34</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
@@ -16933,17 +16933,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>316</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -16953,7 +16953,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-04-23 18:46:12</t>
+          <t>2026-04-23 18:35:35</t>
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
@@ -16962,17 +16962,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>318</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -16982,7 +16982,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2026-04-23 18:58:17</t>
+          <t>2026-04-23 18:41:25</t>
         </is>
       </c>
       <c r="F182" t="inlineStr"/>
@@ -16991,17 +16991,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -17011,7 +17011,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-04-23 19:09:01</t>
+          <t>2026-04-23 18:46:12</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
@@ -17020,17 +17020,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>321</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -17040,7 +17040,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-04-23 19:28:02</t>
+          <t>2026-04-23 18:58:17</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -17049,17 +17049,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>322</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -17069,7 +17069,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-04-23 19:33:02</t>
+          <t>2026-04-23 19:09:01</t>
         </is>
       </c>
       <c r="F185" t="inlineStr"/>
@@ -17078,17 +17078,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>323</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -17098,7 +17098,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-04-23 19:35:57</t>
+          <t>2026-04-23 19:28:02</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
@@ -17107,17 +17107,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>324</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -17127,7 +17127,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-04-24 11:52:45</t>
+          <t>2026-04-23 19:33:02</t>
         </is>
       </c>
       <c r="F187" t="inlineStr"/>
@@ -17136,17 +17136,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>325</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-04-24 11:55:39</t>
+          <t>2026-04-23 19:35:57</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
@@ -17165,7 +17165,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>326</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -17185,7 +17185,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-04-24 12:13:00</t>
+          <t>2026-04-24 11:52:45</t>
         </is>
       </c>
       <c r="F189" t="inlineStr"/>
@@ -17194,17 +17194,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>328</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -17214,7 +17214,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2026-04-24 12:17:05</t>
+          <t>2026-04-24 11:55:39</t>
         </is>
       </c>
       <c r="F190" t="inlineStr"/>
@@ -17223,17 +17223,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>329</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -17243,7 +17243,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-04-24 12:19:39</t>
+          <t>2026-04-24 12:13:00</t>
         </is>
       </c>
       <c r="F191" t="inlineStr"/>
@@ -17252,17 +17252,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>330</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -17272,7 +17272,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-04-24 12:31:15</t>
+          <t>2026-04-24 12:17:05</t>
         </is>
       </c>
       <c r="F192" t="inlineStr"/>
@@ -17281,7 +17281,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>331</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-04-24 12:33:01</t>
+          <t>2026-04-24 12:19:39</t>
         </is>
       </c>
       <c r="F193" t="inlineStr"/>
@@ -17310,17 +17310,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>332</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -17330,7 +17330,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-04-24 14:36:24</t>
+          <t>2026-04-24 12:31:15</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -17339,17 +17339,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>333</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -17359,7 +17359,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-04-24 14:43:03</t>
+          <t>2026-04-24 12:33:01</t>
         </is>
       </c>
       <c r="F195" t="inlineStr"/>
@@ -17368,17 +17368,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>334</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -17388,7 +17388,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2026-04-24 14:58:00</t>
+          <t>2026-04-24 14:36:24</t>
         </is>
       </c>
       <c r="F196" t="inlineStr"/>
@@ -17397,17 +17397,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>335</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-04-27 14:06:10</t>
+          <t>2026-04-24 14:43:03</t>
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
@@ -17426,7 +17426,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>336</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-04-27 14:10:21</t>
+          <t>2026-04-24 14:58:00</t>
         </is>
       </c>
       <c r="F198" t="inlineStr"/>
@@ -17455,17 +17455,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>337</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -17475,7 +17475,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-04-27 14:13:06</t>
+          <t>2026-04-27 14:06:10</t>
         </is>
       </c>
       <c r="F199" t="inlineStr"/>
@@ -17484,17 +17484,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>338</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -17504,7 +17504,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2026-04-27 14:15:47</t>
+          <t>2026-04-27 14:10:21</t>
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
@@ -17513,17 +17513,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>339</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -17533,7 +17533,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:51</t>
+          <t>2026-04-27 14:13:06</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -17542,7 +17542,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>340</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -17562,7 +17562,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-04-27 18:08:12</t>
+          <t>2026-04-27 14:15:47</t>
         </is>
       </c>
       <c r="F202" t="inlineStr"/>
@@ -17571,7 +17571,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>393</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -17591,7 +17591,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-04-27 18:10:09</t>
+          <t>2026-04-27 18:05:51</t>
         </is>
       </c>
       <c r="F203" t="inlineStr"/>
@@ -17600,17 +17600,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>395</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -17620,7 +17620,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-04-27 18:12:49</t>
+          <t>2026-04-27 18:08:12</t>
         </is>
       </c>
       <c r="F204" t="inlineStr"/>
@@ -17629,17 +17629,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>396</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -17649,7 +17649,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-04-27 18:25:23</t>
+          <t>2026-04-27 18:10:09</t>
         </is>
       </c>
       <c r="F205" t="inlineStr"/>
@@ -17658,17 +17658,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>398</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -17678,7 +17678,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-04-27 18:26:29</t>
+          <t>2026-04-27 18:12:49</t>
         </is>
       </c>
       <c r="F206" t="inlineStr"/>
@@ -17687,17 +17687,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>399</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -17707,7 +17707,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-04-27 18:28:56</t>
+          <t>2026-04-27 18:25:23</t>
         </is>
       </c>
       <c r="F207" t="inlineStr"/>
@@ -17716,7 +17716,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>400</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17736,7 +17736,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-04-27 18:32:14</t>
+          <t>2026-04-27 18:26:29</t>
         </is>
       </c>
       <c r="F208" t="inlineStr"/>
@@ -17745,7 +17745,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>401</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17765,7 +17765,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-04-27 19:10:16</t>
+          <t>2026-04-27 18:28:56</t>
         </is>
       </c>
       <c r="F209" t="inlineStr"/>
@@ -17774,7 +17774,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>402</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2026-04-28 13:06:06</t>
+          <t>2026-04-27 18:32:14</t>
         </is>
       </c>
       <c r="F210" t="inlineStr"/>
@@ -17803,17 +17803,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>403</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -17823,7 +17823,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-04-28 13:09:10</t>
+          <t>2026-04-27 19:10:16</t>
         </is>
       </c>
       <c r="F211" t="inlineStr"/>
@@ -17832,17 +17832,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>404</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -17852,7 +17852,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-04-28 13:31:57</t>
+          <t>2026-04-28 13:06:06</t>
         </is>
       </c>
       <c r="F212" t="inlineStr"/>
@@ -17861,17 +17861,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>405</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -17881,7 +17881,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-04-28 16:36:52</t>
+          <t>2026-04-28 13:09:10</t>
         </is>
       </c>
       <c r="F213" t="inlineStr"/>
@@ -17890,17 +17890,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>406</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -17910,7 +17910,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-04-28 16:41:55</t>
+          <t>2026-04-28 13:31:57</t>
         </is>
       </c>
       <c r="F214" t="inlineStr"/>
@@ -17919,17 +17919,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>408</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -17939,7 +17939,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-04-28 16:45:43</t>
+          <t>2026-04-28 16:36:52</t>
         </is>
       </c>
       <c r="F215" t="inlineStr"/>
@@ -17948,17 +17948,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>409</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -17968,7 +17968,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-04-28 16:50:41</t>
+          <t>2026-04-28 16:41:55</t>
         </is>
       </c>
       <c r="F216" t="inlineStr"/>
@@ -17977,17 +17977,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>410</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-04-28 16:58:22</t>
+          <t>2026-04-28 16:45:43</t>
         </is>
       </c>
       <c r="F217" t="inlineStr"/>
@@ -18006,17 +18006,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>411</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-04-28 19:11:43</t>
+          <t>2026-04-28 16:50:41</t>
         </is>
       </c>
       <c r="F218" t="inlineStr"/>
@@ -18035,17 +18035,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>412</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -18055,7 +18055,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-04-28 19:17:29</t>
+          <t>2026-04-28 16:58:22</t>
         </is>
       </c>
       <c r="F219" t="inlineStr"/>
@@ -18064,17 +18064,17 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>422</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -18084,7 +18084,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-04-28 19:20:41</t>
+          <t>2026-04-28 19:11:43</t>
         </is>
       </c>
       <c r="F220" t="inlineStr"/>
@@ -18093,17 +18093,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>425</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -18113,7 +18113,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-04-28 19:27:32</t>
+          <t>2026-04-28 19:17:29</t>
         </is>
       </c>
       <c r="F221" t="inlineStr"/>
@@ -18122,17 +18122,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>427</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -18142,7 +18142,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-04-28 19:29:59</t>
+          <t>2026-04-28 19:20:41</t>
         </is>
       </c>
       <c r="F222" t="inlineStr"/>
@@ -18151,7 +18151,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>431</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18171,7 +18171,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-04-28 19:38:54</t>
+          <t>2026-04-28 19:27:32</t>
         </is>
       </c>
       <c r="F223" t="inlineStr"/>
@@ -18180,17 +18180,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>432</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -18200,7 +18200,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-04-28 18:59:52</t>
+          <t>2026-04-28 19:29:59</t>
         </is>
       </c>
       <c r="F224" t="inlineStr"/>
@@ -18209,7 +18209,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>438</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-04-28 19:05:38</t>
+          <t>2026-04-28 19:38:54</t>
         </is>
       </c>
       <c r="F225" t="inlineStr"/>
@@ -18238,17 +18238,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>413</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -18258,7 +18258,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-04-28 19:09:07</t>
+          <t>2026-04-28 18:59:52</t>
         </is>
       </c>
       <c r="F226" t="inlineStr"/>
@@ -18267,7 +18267,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>416</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18287,7 +18287,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-04-28 19:22:49</t>
+          <t>2026-04-28 19:05:38</t>
         </is>
       </c>
       <c r="F227" t="inlineStr"/>
@@ -18296,17 +18296,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>420</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -18316,7 +18316,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-04-28 19:46:42</t>
+          <t>2026-04-28 19:09:07</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
@@ -18325,7 +18325,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>429</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18345,7 +18345,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-04-29 15:54:41</t>
+          <t>2026-04-28 19:22:49</t>
         </is>
       </c>
       <c r="F229" t="inlineStr"/>
@@ -18354,17 +18354,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>439</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-04-29 15:56:41</t>
+          <t>2026-04-28 19:46:42</t>
         </is>
       </c>
       <c r="F230" t="inlineStr"/>
@@ -18383,17 +18383,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>440</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -18403,7 +18403,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-04-29 16:10:35</t>
+          <t>2026-04-29 15:54:41</t>
         </is>
       </c>
       <c r="F231" t="inlineStr"/>
@@ -18412,17 +18412,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>441</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -18432,7 +18432,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-04-29 16:13:57</t>
+          <t>2026-04-29 15:56:41</t>
         </is>
       </c>
       <c r="F232" t="inlineStr"/>
@@ -18441,17 +18441,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>442</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -18461,7 +18461,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-04-29 16:17:13</t>
+          <t>2026-04-29 16:10:35</t>
         </is>
       </c>
       <c r="F233" t="inlineStr"/>
@@ -18470,17 +18470,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>443</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -18490,7 +18490,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-04-29 16:21:56</t>
+          <t>2026-04-29 16:13:57</t>
         </is>
       </c>
       <c r="F234" t="inlineStr"/>
@@ -18499,7 +18499,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>444</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18519,7 +18519,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-04-29 16:26:19</t>
+          <t>2026-04-29 16:17:13</t>
         </is>
       </c>
       <c r="F235" t="inlineStr"/>
@@ -18528,7 +18528,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>445</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18548,7 +18548,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2026-04-30 11:56:22</t>
+          <t>2026-04-29 16:21:56</t>
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
@@ -18557,7 +18557,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>446</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18577,7 +18577,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-04-30 12:18:39</t>
+          <t>2026-04-29 16:26:19</t>
         </is>
       </c>
       <c r="F237" t="inlineStr"/>
@@ -18586,7 +18586,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>447</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18606,7 +18606,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-04-30 12:27:47</t>
+          <t>2026-04-30 11:56:22</t>
         </is>
       </c>
       <c r="F238" t="inlineStr"/>
@@ -18615,17 +18615,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>448</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -18635,7 +18635,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-04-30 14:33:48</t>
+          <t>2026-04-30 12:18:39</t>
         </is>
       </c>
       <c r="F239" t="inlineStr"/>
@@ -18644,17 +18644,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>449</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -18664,7 +18664,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-04-30 14:39:11</t>
+          <t>2026-04-30 12:27:47</t>
         </is>
       </c>
       <c r="F240" t="inlineStr"/>
@@ -18673,17 +18673,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>450</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-04-30 14:44:06</t>
+          <t>2026-04-30 14:33:48</t>
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
@@ -18702,17 +18702,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>452</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-04-30 14:50:48</t>
+          <t>2026-04-30 14:39:11</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
@@ -18731,7 +18731,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>453</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18751,7 +18751,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-04-30 15:03:19</t>
+          <t>2026-04-30 14:44:06</t>
         </is>
       </c>
       <c r="F243" t="inlineStr"/>
@@ -18760,17 +18760,17 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>454</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -18780,7 +18780,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-04-30 16:43:14</t>
+          <t>2026-04-30 14:50:48</t>
         </is>
       </c>
       <c r="F244" t="inlineStr"/>
@@ -18789,7 +18789,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>455</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -18809,7 +18809,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-04-30 16:49:38</t>
+          <t>2026-04-30 15:03:19</t>
         </is>
       </c>
       <c r="F245" t="inlineStr"/>
@@ -18818,17 +18818,17 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>456</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -18838,7 +18838,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-04-30 16:57:13</t>
+          <t>2026-04-30 16:43:14</t>
         </is>
       </c>
       <c r="F246" t="inlineStr"/>
@@ -18847,17 +18847,17 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>457</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -18867,7 +18867,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-04-30 16:59:14</t>
+          <t>2026-04-30 16:49:38</t>
         </is>
       </c>
       <c r="F247" t="inlineStr"/>
@@ -18876,17 +18876,17 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>458</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -18896,7 +18896,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-04-30 17:03:09</t>
+          <t>2026-04-30 16:57:13</t>
         </is>
       </c>
       <c r="F248" t="inlineStr"/>
@@ -18905,17 +18905,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>459</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -18925,7 +18925,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-04-30 17:07:20</t>
+          <t>2026-04-30 16:59:14</t>
         </is>
       </c>
       <c r="F249" t="inlineStr"/>
@@ -18934,7 +18934,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -18954,7 +18954,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-04-30 17:20:16</t>
+          <t>2026-04-30 17:03:09</t>
         </is>
       </c>
       <c r="F250" t="inlineStr"/>
@@ -18963,7 +18963,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>461</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-05-04 12:40:26</t>
+          <t>2026-04-30 17:07:20</t>
         </is>
       </c>
       <c r="F251" t="inlineStr"/>
@@ -18992,17 +18992,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>462</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-05-04 13:27:46</t>
+          <t>2026-04-30 17:20:16</t>
         </is>
       </c>
       <c r="F252" t="inlineStr"/>
@@ -19021,7 +19021,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>465</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19041,7 +19041,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-05-04 13:32:27</t>
+          <t>2026-05-04 12:40:26</t>
         </is>
       </c>
       <c r="F253" t="inlineStr"/>
@@ -19050,7 +19050,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>466</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19070,7 +19070,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-05-04 13:35:31</t>
+          <t>2026-05-04 13:27:46</t>
         </is>
       </c>
       <c r="F254" t="inlineStr"/>
@@ -19079,17 +19079,17 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>467</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -19099,7 +19099,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-05-04 13:52:33</t>
+          <t>2026-05-04 13:32:27</t>
         </is>
       </c>
       <c r="F255" t="inlineStr"/>
@@ -19108,17 +19108,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>468</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -19128,7 +19128,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2026-05-04 14:15:29</t>
+          <t>2026-05-04 13:35:31</t>
         </is>
       </c>
       <c r="F256" t="inlineStr"/>
@@ -19137,17 +19137,17 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>469</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -19157,7 +19157,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-05-04 14:21:26</t>
+          <t>2026-05-04 13:52:33</t>
         </is>
       </c>
       <c r="F257" t="inlineStr"/>
@@ -19166,7 +19166,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>470</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -19186,7 +19186,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-05-04 14:28:28</t>
+          <t>2026-05-04 14:15:29</t>
         </is>
       </c>
       <c r="F258" t="inlineStr"/>
@@ -19195,17 +19195,17 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>471</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -19215,7 +19215,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-05-05 12:33:28</t>
+          <t>2026-05-04 14:21:26</t>
         </is>
       </c>
       <c r="F259" t="inlineStr"/>
@@ -19224,17 +19224,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>472</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -19244,7 +19244,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-05-05 12:36:49</t>
+          <t>2026-05-04 14:28:28</t>
         </is>
       </c>
       <c r="F260" t="inlineStr"/>
@@ -19253,17 +19253,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>473</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -19273,7 +19273,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-05-05 13:16:10</t>
+          <t>2026-05-05 12:33:28</t>
         </is>
       </c>
       <c r="F261" t="inlineStr"/>
@@ -19282,17 +19282,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>474</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -19302,7 +19302,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-05-05 13:22:28</t>
+          <t>2026-05-05 12:36:49</t>
         </is>
       </c>
       <c r="F262" t="inlineStr"/>
@@ -19311,7 +19311,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>475</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -19331,7 +19331,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-05-05 15:49:32</t>
+          <t>2026-05-05 13:16:10</t>
         </is>
       </c>
       <c r="F263" t="inlineStr"/>
@@ -19340,7 +19340,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>476</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -19360,7 +19360,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-05-05 18:17:18</t>
+          <t>2026-05-05 13:22:28</t>
         </is>
       </c>
       <c r="F264" t="inlineStr"/>
@@ -19369,17 +19369,17 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>478</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-05-05 18:23:24</t>
+          <t>2026-05-05 15:49:32</t>
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
@@ -19398,17 +19398,17 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>484</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -19418,7 +19418,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-05-05 18:30:18</t>
+          <t>2026-05-05 18:17:18</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
@@ -19427,17 +19427,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>485</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -19447,7 +19447,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-05-05 19:24:36</t>
+          <t>2026-05-05 18:23:24</t>
         </is>
       </c>
       <c r="F267" t="inlineStr"/>
@@ -19456,17 +19456,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>486</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -19476,7 +19476,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-05-06 14:07:52</t>
+          <t>2026-05-05 18:30:18</t>
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
@@ -19485,17 +19485,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>487</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -19505,7 +19505,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-05-06 14:12:50</t>
+          <t>2026-05-05 19:24:36</t>
         </is>
       </c>
       <c r="F269" t="inlineStr"/>
@@ -19514,17 +19514,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>488</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -19534,7 +19534,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-05-06 14:15:34</t>
+          <t>2026-05-06 14:07:52</t>
         </is>
       </c>
       <c r="F270" t="inlineStr"/>
@@ -19543,7 +19543,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>489</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -19563,7 +19563,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-05-06 14:59:26</t>
+          <t>2026-05-06 14:12:50</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
@@ -19572,7 +19572,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>490</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -19592,7 +19592,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-05-06 15:04:52</t>
+          <t>2026-05-06 14:15:34</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
@@ -19601,17 +19601,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -19621,7 +19621,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-05-06 15:08:51</t>
+          <t>2026-05-06 14:59:26</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
@@ -19630,17 +19630,17 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>492</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Busy</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -19650,7 +19650,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-05-06 15:28:38</t>
+          <t>2026-05-06 15:04:52</t>
         </is>
       </c>
       <c r="F274" t="inlineStr"/>
@@ -19659,17 +19659,17 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>493</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -19679,7 +19679,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-05-06 15:31:36</t>
+          <t>2026-05-06 15:08:51</t>
         </is>
       </c>
       <c r="F275" t="inlineStr"/>
@@ -19688,17 +19688,17 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>494</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Busy</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -19708,7 +19708,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-05-06 17:53:50</t>
+          <t>2026-05-06 15:28:38</t>
         </is>
       </c>
       <c r="F276" t="inlineStr"/>
@@ -19717,17 +19717,17 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>495</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-05-06 17:59:31</t>
+          <t>2026-05-06 15:31:36</t>
         </is>
       </c>
       <c r="F277" t="inlineStr"/>
@@ -19746,17 +19746,17 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>501</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-05-06 19:18:14</t>
+          <t>2026-05-06 17:53:50</t>
         </is>
       </c>
       <c r="F278" t="inlineStr"/>
@@ -19775,7 +19775,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>502</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -19795,7 +19795,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-05-06 19:21:01</t>
+          <t>2026-05-06 17:59:31</t>
         </is>
       </c>
       <c r="F279" t="inlineStr"/>
@@ -19804,17 +19804,17 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>503</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-05-06 19:25:27</t>
+          <t>2026-05-06 19:18:14</t>
         </is>
       </c>
       <c r="F280" t="inlineStr"/>
@@ -19833,7 +19833,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>504</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -19853,7 +19853,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-05-06 19:27:23</t>
+          <t>2026-05-06 19:21:01</t>
         </is>
       </c>
       <c r="F281" t="inlineStr"/>
@@ -19862,17 +19862,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>505</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -19882,11 +19882,127 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-05-06 19:39:21</t>
+          <t>2026-05-06 19:25:27</t>
         </is>
       </c>
       <c r="F282" t="inlineStr"/>
       <c r="G282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>2026-05-06 19:27:23</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>2026-05-06 19:39:21</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>2026-05-06 20:09:52</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>2026-05-06 20:12:28</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -2777,7 +2777,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-04-01 14:22:42</t>
+          <t>2026-05-07 12:07:46</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-04-01 14:25:07</t>
+          <t>2026-05-07 12:12:23</t>
         </is>
       </c>
     </row>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-03-20 18:51:23</t>
+          <t>2026-05-07 12:25:15</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-04-01 14:13:12</t>
+          <t>2026-05-07 12:30:09</t>
         </is>
       </c>
     </row>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-04-01 14:37:17</t>
+          <t>2026-05-07 12:21:17</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-04-01 15:01:44</t>
+          <t>2026-05-07 12:22:45</t>
         </is>
       </c>
     </row>
@@ -11699,7 +11699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G286"/>
+  <dimension ref="A1:G299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13047,17 +13047,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>519</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -13067,7 +13067,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-03-20 18:49:21</t>
+          <t>2026-05-07 12:24:40</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -13076,17 +13076,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>185</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-04-28 19:34:30</t>
+          <t>2026-03-20 18:49:21</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -13105,17 +13105,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>434</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -13125,7 +13125,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-03-23 18:38:25</t>
+          <t>2026-04-28 19:34:30</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -13134,17 +13134,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>191</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -13154,7 +13154,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-03-23 18:47:52</t>
+          <t>2026-03-23 18:38:25</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -13163,17 +13163,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>193</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-03-23 18:54:34</t>
+          <t>2026-03-23 18:47:52</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -13192,7 +13192,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>194</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -13212,7 +13212,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-03-23 18:58:51</t>
+          <t>2026-03-23 18:54:34</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -13221,7 +13221,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>196</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>hot_lead</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-03-23 19:03:40</t>
+          <t>2026-03-23 18:58:51</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -13250,17 +13250,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>197</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>hot_lead</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -13270,7 +13270,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-03-24 15:48:39</t>
+          <t>2026-03-23 19:03:40</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -13279,17 +13279,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>202</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WRONG NUMBER -DNC</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>wrong_number__dnc</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-03-24 16:11:19</t>
+          <t>2026-03-24 15:48:39</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -13308,17 +13308,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>205</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>WRONG NUMBER -DNC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>wrong_number__dnc</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -13328,7 +13328,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-03-24 16:15:10</t>
+          <t>2026-03-24 16:11:19</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -13337,7 +13337,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>206</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -13357,7 +13357,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-03-24 16:23:12</t>
+          <t>2026-03-24 16:15:10</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -13366,17 +13366,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>207</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Follow Up</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-03-24 18:17:19</t>
+          <t>2026-03-24 16:23:12</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -13395,17 +13395,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>208</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Follow Up</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>follow_up</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -13415,7 +13415,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:48</t>
+          <t>2026-03-24 18:17:19</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -13424,7 +13424,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>369</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-04-27 16:40:16</t>
+          <t>2026-04-27 16:38:48</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -13453,7 +13453,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>372</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -13473,7 +13473,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-04-27 16:43:21</t>
+          <t>2026-04-27 16:40:16</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -13482,7 +13482,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>375</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -13502,7 +13502,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-04-27 16:47:15</t>
+          <t>2026-04-27 16:43:21</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -13511,7 +13511,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>380</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-04-27 16:50:20</t>
+          <t>2026-04-27 16:47:15</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -13540,17 +13540,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>385</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-03-24 18:57:44</t>
+          <t>2026-04-27 16:50:20</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -13569,7 +13569,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>209</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -13589,7 +13589,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-03-25 16:41:38</t>
+          <t>2026-03-24 18:57:44</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -13598,7 +13598,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>211</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-03-25 16:48:29</t>
+          <t>2026-03-25 16:41:38</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -13627,17 +13627,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>212</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13647,7 +13647,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-04-27 16:31:50</t>
+          <t>2026-03-25 16:48:29</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -13656,17 +13656,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>359</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-05-06 20:12:18</t>
+          <t>2026-04-27 16:31:50</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -13685,17 +13685,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>510</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13705,7 +13705,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-03-26 14:46:03</t>
+          <t>2026-05-06 20:12:18</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -13714,17 +13714,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>217</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-03-26 14:57:57</t>
+          <t>2026-03-26 14:46:03</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -13743,17 +13743,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>218</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -13763,7 +13763,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-03-26 15:12:09</t>
+          <t>2026-03-26 14:57:57</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -13772,17 +13772,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>220</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -13792,7 +13792,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-03-26 15:45:11</t>
+          <t>2026-03-26 15:12:09</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -13801,7 +13801,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>221</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-04-27 16:39:08</t>
+          <t>2026-03-26 15:45:11</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -13830,17 +13830,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>370</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -13850,7 +13850,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-03-27 18:06:04</t>
+          <t>2026-04-27 16:39:08</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -13859,17 +13859,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>228</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -13879,7 +13879,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-03-27 18:09:32</t>
+          <t>2026-03-27 18:06:04</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -13888,12 +13888,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>229</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Call on Monday</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-03-27 18:13:29</t>
+          <t>2026-03-27 18:09:32</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -13917,17 +13917,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>230</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call on Monday</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -13937,7 +13937,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-03-27 18:16:14</t>
+          <t>2026-03-27 18:13:29</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -13946,17 +13946,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>231</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -13966,7 +13966,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-03-27 18:28:41</t>
+          <t>2026-03-27 18:16:14</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -13975,17 +13975,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>232</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13995,7 +13995,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-04-23 18:46:03</t>
+          <t>2026-03-27 18:28:41</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -14004,7 +14004,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>319</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-04-27 16:34:45</t>
+          <t>2026-04-23 18:46:03</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -14033,17 +14033,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>363</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -14053,7 +14053,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-03-27 19:30:50</t>
+          <t>2026-04-27 16:34:45</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
@@ -14062,17 +14062,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>233</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-03-30 16:46:09</t>
+          <t>2026-03-27 19:30:50</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -14091,17 +14091,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>239</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Busy</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-05-06 20:09:36</t>
+          <t>2026-03-30 16:46:09</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
@@ -14120,17 +14120,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>508</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Busy</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -14140,7 +14140,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-03-31 13:50:49</t>
+          <t>2026-05-06 20:09:36</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -14149,17 +14149,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>245</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14169,7 +14169,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-03-31 13:57:09</t>
+          <t>2026-03-31 13:50:49</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -14178,17 +14178,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>246</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-03-31 14:01:39</t>
+          <t>2026-03-31 13:57:09</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -14207,17 +14207,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>247</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14227,7 +14227,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-03-31 14:09:41</t>
+          <t>2026-03-31 14:01:39</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
@@ -14236,7 +14236,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>248</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -14256,7 +14256,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-03-31 19:13:49</t>
+          <t>2026-03-31 14:09:41</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
@@ -14265,17 +14265,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>249</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-04-27 16:17:22</t>
+          <t>2026-03-31 19:13:49</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
@@ -14294,17 +14294,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>341</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14314,7 +14314,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-04-27 16:22:28</t>
+          <t>2026-04-27 16:17:22</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -14323,17 +14323,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>347</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-04-27 16:23:48</t>
+          <t>2026-04-27 16:22:28</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -14352,7 +14352,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>349</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -14372,7 +14372,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-04-27 16:26:16</t>
+          <t>2026-04-27 16:23:48</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -14381,7 +14381,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>352</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -14401,7 +14401,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-04-27 16:32:05</t>
+          <t>2026-04-27 16:26:16</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -14410,7 +14410,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-04-27 16:33:04</t>
+          <t>2026-04-27 16:32:05</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
@@ -14439,7 +14439,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>361</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -14459,7 +14459,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-04-27 16:34:57</t>
+          <t>2026-04-27 16:33:04</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -14468,7 +14468,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>364</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:15</t>
+          <t>2026-04-27 16:34:57</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -14497,7 +14497,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>390</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -14517,7 +14517,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-04-28 19:05:25</t>
+          <t>2026-04-27 18:05:15</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -14526,7 +14526,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>415</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-04-28 19:06:58</t>
+          <t>2026-04-28 19:05:25</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
@@ -14555,17 +14555,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>418</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-04-28 19:16:34</t>
+          <t>2026-04-28 19:06:58</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
@@ -14584,17 +14584,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>423</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -14604,7 +14604,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-04-28 19:34:42</t>
+          <t>2026-04-28 19:16:34</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -14613,17 +14613,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>435</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-03-31 19:22:45</t>
+          <t>2026-04-28 19:34:42</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
@@ -14642,7 +14642,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>250</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>follow_up</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -14662,7 +14662,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-03-31 19:37:10</t>
+          <t>2026-03-31 19:22:45</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -14671,17 +14671,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>251</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -14691,7 +14691,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-04-01 14:30:00</t>
+          <t>2026-03-31 19:37:10</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -14700,7 +14700,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>252</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-04-01 16:53:36</t>
+          <t>2026-04-01 14:30:00</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -14729,17 +14729,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>253</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-04-07 15:24:02</t>
+          <t>2026-04-01 16:53:36</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -14758,17 +14758,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>518</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14778,7 +14778,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-04-07 16:00:48</t>
+          <t>2026-05-07 12:22:45</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -14787,7 +14787,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>520</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -14807,7 +14807,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-04-24 11:55:32</t>
+          <t>2026-05-07 12:24:53</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
@@ -14816,7 +14816,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>523</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -14836,7 +14836,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-04-27 16:17:36</t>
+          <t>2026-05-07 12:30:02</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
@@ -14845,17 +14845,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>271</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14865,7 +14865,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-04-27 16:20:52</t>
+          <t>2026-04-07 15:24:02</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
@@ -14874,17 +14874,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>272</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-04-27 16:22:53</t>
+          <t>2026-04-07 16:00:48</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
@@ -14903,7 +14903,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>327</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-04-27 16:24:00</t>
+          <t>2026-04-24 11:55:32</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
@@ -14932,7 +14932,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>342</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-04-27 16:27:53</t>
+          <t>2026-04-27 16:17:36</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
@@ -14961,17 +14961,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>345</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-04-08 16:38:00</t>
+          <t>2026-04-27 16:20:52</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
@@ -14990,7 +14990,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>348</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -15010,7 +15010,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-04-08 18:21:03</t>
+          <t>2026-04-27 16:22:53</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -15019,7 +15019,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>350</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -15039,7 +15039,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-04-23 18:22:34</t>
+          <t>2026-04-27 16:24:00</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
@@ -15048,7 +15048,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>353</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -15068,7 +15068,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-04-23 18:24:52</t>
+          <t>2026-04-27 16:27:53</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
@@ -15077,17 +15077,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>274</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15097,7 +15097,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-04-27 16:43:32</t>
+          <t>2026-04-08 16:38:00</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
@@ -15106,17 +15106,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>275</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-04-27 16:44:32</t>
+          <t>2026-04-08 18:21:03</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
@@ -15135,7 +15135,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>308</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -15155,7 +15155,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-04-27 16:47:27</t>
+          <t>2026-04-23 18:22:34</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
@@ -15164,7 +15164,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>310</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -15184,7 +15184,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-04-27 16:48:30</t>
+          <t>2026-04-23 18:24:52</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
@@ -15193,17 +15193,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>376</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-04-27 16:49:41</t>
+          <t>2026-04-27 16:43:32</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
@@ -15222,17 +15222,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>378</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -15242,7 +15242,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-04-27 16:51:50</t>
+          <t>2026-04-27 16:44:32</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
@@ -15251,7 +15251,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>381</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -15271,7 +15271,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-04-28 19:34:54</t>
+          <t>2026-04-27 16:47:27</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
@@ -15280,17 +15280,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>383</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-04-09 14:38:33</t>
+          <t>2026-04-27 16:48:30</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
@@ -15309,17 +15309,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>384</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15329,7 +15329,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-04-09 14:50:24</t>
+          <t>2026-04-27 16:49:41</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -15338,7 +15338,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>386</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -15358,7 +15358,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-04-27 16:17:54</t>
+          <t>2026-04-27 16:51:50</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -15367,17 +15367,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>436</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15387,7 +15387,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-04-27 16:19:16</t>
+          <t>2026-04-28 19:34:54</t>
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
@@ -15396,7 +15396,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>276</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-04-27 16:21:26</t>
+          <t>2026-04-09 14:38:33</t>
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
@@ -15425,17 +15425,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>277</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15445,7 +15445,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-04-27 16:30:33</t>
+          <t>2026-04-09 14:50:24</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -15454,17 +15454,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>343</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15474,7 +15474,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-04-27 16:34:07</t>
+          <t>2026-04-27 16:17:54</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
@@ -15483,17 +15483,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>344</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>email</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15503,7 +15503,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-04-27 16:35:11</t>
+          <t>2026-04-27 16:19:16</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -15512,17 +15512,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>346</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -15532,7 +15532,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:29</t>
+          <t>2026-04-27 16:21:26</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
@@ -15541,17 +15541,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>357</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -15561,7 +15561,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-04-28 19:20:18</t>
+          <t>2026-04-27 16:30:33</t>
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
@@ -15570,17 +15570,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>362</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -15590,7 +15590,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-04-28 19:22:33</t>
+          <t>2026-04-27 16:34:07</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
@@ -15599,7 +15599,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>365</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -15619,7 +15619,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-04-28 19:27:09</t>
+          <t>2026-04-27 16:35:11</t>
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
@@ -15628,17 +15628,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>391</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -15648,7 +15648,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-04-13 15:45:27</t>
+          <t>2026-04-27 18:05:29</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
@@ -15657,17 +15657,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>426</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-04-13 15:46:25</t>
+          <t>2026-04-28 19:20:18</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
@@ -15686,17 +15686,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>428</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -15706,7 +15706,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-04-13 15:53:15</t>
+          <t>2026-04-28 19:22:33</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
@@ -15715,17 +15715,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>430</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-04-13 15:58:50</t>
+          <t>2026-04-28 19:27:09</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -15744,17 +15744,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>286</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-04-27 16:24:24</t>
+          <t>2026-04-13 15:45:27</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -15773,17 +15773,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>287</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-04-27 16:28:22</t>
+          <t>2026-04-13 15:46:25</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
@@ -15802,17 +15802,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>288</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -15822,7 +15822,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-04-27 16:35:40</t>
+          <t>2026-04-13 15:53:15</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
@@ -15831,17 +15831,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>289</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -15851,7 +15851,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-04-28 19:07:14</t>
+          <t>2026-04-13 15:58:50</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
@@ -15860,17 +15860,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>351</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-04-28 19:16:45</t>
+          <t>2026-04-27 16:24:24</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
@@ -15889,17 +15889,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>354</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -15909,7 +15909,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-04-27 16:29:25</t>
+          <t>2026-04-27 16:28:22</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
@@ -15918,17 +15918,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>366</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -15938,7 +15938,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-04-27 16:31:00</t>
+          <t>2026-04-27 16:35:40</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
@@ -15947,7 +15947,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>419</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -15967,7 +15967,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-04-27 16:39:21</t>
+          <t>2026-04-28 19:07:14</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
@@ -15976,7 +15976,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>424</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -15996,7 +15996,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-04-27 16:40:26</t>
+          <t>2026-04-28 19:16:45</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
@@ -16005,17 +16005,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>356</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -16025,7 +16025,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-04-27 16:42:47</t>
+          <t>2026-04-27 16:29:25</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
@@ -16034,17 +16034,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>358</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -16054,7 +16054,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-04-15 16:05:12</t>
+          <t>2026-04-27 16:31:00</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
@@ -16063,17 +16063,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>371</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -16083,7 +16083,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-04-15 18:17:17</t>
+          <t>2026-04-27 16:39:21</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
@@ -16092,7 +16092,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>373</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -16112,7 +16112,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-04-27 16:35:57</t>
+          <t>2026-04-27 16:40:26</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
@@ -16121,7 +16121,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>374</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -16141,7 +16141,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-04-27 16:52:02</t>
+          <t>2026-04-27 16:42:47</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -16150,17 +16150,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>294</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -16170,7 +16170,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-04-28 19:11:23</t>
+          <t>2026-04-15 16:05:12</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -16179,17 +16179,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>295</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -16199,7 +16199,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-04-30 14:38:42</t>
+          <t>2026-04-15 18:17:17</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -16208,17 +16208,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>367</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -16228,7 +16228,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-04-16 12:32:37</t>
+          <t>2026-04-27 16:35:57</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
@@ -16237,17 +16237,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>387</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -16257,7 +16257,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-04-16 12:52:16</t>
+          <t>2026-04-27 16:52:02</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -16266,17 +16266,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>421</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-04-27 16:37:49</t>
+          <t>2026-04-28 19:11:23</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
@@ -16295,17 +16295,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>451</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -16315,7 +16315,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-04-27 16:45:32</t>
+          <t>2026-04-30 14:38:42</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -16324,17 +16324,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>296</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -16344,7 +16344,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-04-27 16:47:40</t>
+          <t>2026-04-16 12:32:37</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
@@ -16353,17 +16353,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>297</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-04-16 18:41:52</t>
+          <t>2026-04-16 12:52:16</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
@@ -16382,7 +16382,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>368</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -16402,7 +16402,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-04-23 18:27:22</t>
+          <t>2026-04-27 16:37:49</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
@@ -16411,17 +16411,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>379</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -16431,7 +16431,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-04-23 18:30:25</t>
+          <t>2026-04-27 16:45:32</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -16440,7 +16440,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>382</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -16460,7 +16460,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-04-27 16:43:45</t>
+          <t>2026-04-27 16:47:40</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
@@ -16469,17 +16469,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>299</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -16489,7 +16489,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-04-23 18:40:56</t>
+          <t>2026-04-16 18:41:52</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
@@ -16498,17 +16498,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>312</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -16518,7 +16518,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-04-21 15:49:30</t>
+          <t>2026-04-23 18:27:22</t>
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
@@ -16527,17 +16527,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>314</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -16547,7 +16547,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-04-21 15:52:28</t>
+          <t>2026-04-23 18:30:25</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
@@ -16556,17 +16556,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>377</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -16576,7 +16576,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-04-21 17:03:38</t>
+          <t>2026-04-27 16:43:45</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
@@ -16585,17 +16585,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>317</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -16605,7 +16605,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-04-22 16:41:07</t>
+          <t>2026-04-23 18:40:56</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
@@ -16614,17 +16614,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -16634,7 +16634,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:41</t>
+          <t>2026-04-21 15:49:30</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
@@ -16643,17 +16643,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>301</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -16663,7 +16663,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-04-28 19:35:07</t>
+          <t>2026-04-21 15:52:28</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
@@ -16672,17 +16672,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>302</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-05-06 17:53:39</t>
+          <t>2026-04-21 17:03:38</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -16701,17 +16701,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>303</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-04-23 15:49:56</t>
+          <t>2026-04-22 16:41:07</t>
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
@@ -16730,7 +16730,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>392</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -16750,7 +16750,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-04-23 18:16:45</t>
+          <t>2026-04-27 18:05:41</t>
         </is>
       </c>
       <c r="F174" t="inlineStr"/>
@@ -16759,7 +16759,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>437</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -16779,7 +16779,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-04-23 18:22:46</t>
+          <t>2026-04-28 19:35:07</t>
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
@@ -16788,7 +16788,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>500</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-04-23 18:25:02</t>
+          <t>2026-05-06 17:53:39</t>
         </is>
       </c>
       <c r="F176" t="inlineStr"/>
@@ -16817,7 +16817,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>521</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -16837,7 +16837,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-04-23 18:27:36</t>
+          <t>2026-05-07 12:25:07</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -16846,17 +16846,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>306</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -16866,7 +16866,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-04-27 18:07:45</t>
+          <t>2026-04-23 15:49:56</t>
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
@@ -16875,7 +16875,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>307</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -16895,7 +16895,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-04-27 18:12:10</t>
+          <t>2026-04-23 18:16:45</t>
         </is>
       </c>
       <c r="F179" t="inlineStr"/>
@@ -16904,7 +16904,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>309</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -16924,7 +16924,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-04-23 18:30:34</t>
+          <t>2026-04-23 18:22:46</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
@@ -16933,17 +16933,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>311</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -16953,7 +16953,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-04-23 18:35:35</t>
+          <t>2026-04-23 18:25:02</t>
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
@@ -16962,17 +16962,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>313</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -16982,7 +16982,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2026-04-23 18:41:25</t>
+          <t>2026-04-23 18:27:36</t>
         </is>
       </c>
       <c r="F182" t="inlineStr"/>
@@ -16991,7 +16991,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>394</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -17011,7 +17011,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-04-23 18:46:12</t>
+          <t>2026-04-27 18:07:45</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
@@ -17020,17 +17020,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>397</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -17040,7 +17040,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-04-23 18:58:17</t>
+          <t>2026-04-27 18:12:10</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -17049,17 +17049,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>315</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -17069,7 +17069,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-04-23 19:09:01</t>
+          <t>2026-04-23 18:30:34</t>
         </is>
       </c>
       <c r="F185" t="inlineStr"/>
@@ -17078,17 +17078,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>316</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -17098,7 +17098,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-04-23 19:28:02</t>
+          <t>2026-04-23 18:35:35</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
@@ -17107,17 +17107,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>318</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -17127,7 +17127,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-04-23 19:33:02</t>
+          <t>2026-04-23 18:41:25</t>
         </is>
       </c>
       <c r="F187" t="inlineStr"/>
@@ -17136,17 +17136,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-04-23 19:35:57</t>
+          <t>2026-04-23 18:46:12</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
@@ -17165,17 +17165,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>321</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -17185,7 +17185,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-04-24 11:52:45</t>
+          <t>2026-04-23 18:58:17</t>
         </is>
       </c>
       <c r="F189" t="inlineStr"/>
@@ -17194,17 +17194,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>322</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -17214,7 +17214,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2026-04-24 11:55:39</t>
+          <t>2026-04-23 19:09:01</t>
         </is>
       </c>
       <c r="F190" t="inlineStr"/>
@@ -17223,17 +17223,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>323</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -17243,7 +17243,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-04-24 12:13:00</t>
+          <t>2026-04-23 19:28:02</t>
         </is>
       </c>
       <c r="F191" t="inlineStr"/>
@@ -17252,17 +17252,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>324</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -17272,7 +17272,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-04-24 12:17:05</t>
+          <t>2026-04-23 19:33:02</t>
         </is>
       </c>
       <c r="F192" t="inlineStr"/>
@@ -17281,17 +17281,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>325</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-04-24 12:19:39</t>
+          <t>2026-04-23 19:35:57</t>
         </is>
       </c>
       <c r="F193" t="inlineStr"/>
@@ -17310,17 +17310,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>326</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -17330,7 +17330,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-04-24 12:31:15</t>
+          <t>2026-04-24 11:52:45</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -17339,7 +17339,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>328</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -17359,7 +17359,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-04-24 12:33:01</t>
+          <t>2026-04-24 11:55:39</t>
         </is>
       </c>
       <c r="F195" t="inlineStr"/>
@@ -17368,7 +17368,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>329</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -17388,7 +17388,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2026-04-24 14:36:24</t>
+          <t>2026-04-24 12:13:00</t>
         </is>
       </c>
       <c r="F196" t="inlineStr"/>
@@ -17397,7 +17397,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>330</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-04-24 14:43:03</t>
+          <t>2026-04-24 12:17:05</t>
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
@@ -17426,7 +17426,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>331</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-04-24 14:58:00</t>
+          <t>2026-04-24 12:19:39</t>
         </is>
       </c>
       <c r="F198" t="inlineStr"/>
@@ -17455,17 +17455,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>332</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -17475,7 +17475,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-04-27 14:06:10</t>
+          <t>2026-04-24 12:31:15</t>
         </is>
       </c>
       <c r="F199" t="inlineStr"/>
@@ -17484,7 +17484,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>333</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -17504,7 +17504,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2026-04-27 14:10:21</t>
+          <t>2026-04-24 12:33:01</t>
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
@@ -17513,17 +17513,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>334</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -17533,7 +17533,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-04-27 14:13:06</t>
+          <t>2026-04-24 14:36:24</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -17542,17 +17542,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>335</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -17562,7 +17562,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-04-27 14:15:47</t>
+          <t>2026-04-24 14:43:03</t>
         </is>
       </c>
       <c r="F202" t="inlineStr"/>
@@ -17571,7 +17571,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>336</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -17591,7 +17591,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:51</t>
+          <t>2026-04-24 14:58:00</t>
         </is>
       </c>
       <c r="F203" t="inlineStr"/>
@@ -17600,7 +17600,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>337</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17620,7 +17620,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-04-27 18:08:12</t>
+          <t>2026-04-27 14:06:10</t>
         </is>
       </c>
       <c r="F204" t="inlineStr"/>
@@ -17629,7 +17629,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>338</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17649,7 +17649,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-04-27 18:10:09</t>
+          <t>2026-04-27 14:10:21</t>
         </is>
       </c>
       <c r="F205" t="inlineStr"/>
@@ -17658,17 +17658,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>339</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -17678,7 +17678,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-04-27 18:12:49</t>
+          <t>2026-04-27 14:13:06</t>
         </is>
       </c>
       <c r="F206" t="inlineStr"/>
@@ -17687,17 +17687,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>340</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -17707,7 +17707,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-04-27 18:25:23</t>
+          <t>2026-04-27 14:15:47</t>
         </is>
       </c>
       <c r="F207" t="inlineStr"/>
@@ -17716,7 +17716,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>393</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17736,7 +17736,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-04-27 18:26:29</t>
+          <t>2026-04-27 18:05:51</t>
         </is>
       </c>
       <c r="F208" t="inlineStr"/>
@@ -17745,17 +17745,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>395</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -17765,7 +17765,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-04-27 18:28:56</t>
+          <t>2026-04-27 18:08:12</t>
         </is>
       </c>
       <c r="F209" t="inlineStr"/>
@@ -17774,7 +17774,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>396</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2026-04-27 18:32:14</t>
+          <t>2026-04-27 18:10:09</t>
         </is>
       </c>
       <c r="F210" t="inlineStr"/>
@@ -17803,17 +17803,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>398</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -17823,7 +17823,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-04-27 19:10:16</t>
+          <t>2026-04-27 18:12:49</t>
         </is>
       </c>
       <c r="F211" t="inlineStr"/>
@@ -17832,17 +17832,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>399</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -17852,7 +17852,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-04-28 13:06:06</t>
+          <t>2026-04-27 18:25:23</t>
         </is>
       </c>
       <c r="F212" t="inlineStr"/>
@@ -17861,17 +17861,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>400</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -17881,7 +17881,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-04-28 13:09:10</t>
+          <t>2026-04-27 18:26:29</t>
         </is>
       </c>
       <c r="F213" t="inlineStr"/>
@@ -17890,17 +17890,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>401</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -17910,7 +17910,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-04-28 13:31:57</t>
+          <t>2026-04-27 18:28:56</t>
         </is>
       </c>
       <c r="F214" t="inlineStr"/>
@@ -17919,17 +17919,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>402</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -17939,7 +17939,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-04-28 16:36:52</t>
+          <t>2026-04-27 18:32:14</t>
         </is>
       </c>
       <c r="F215" t="inlineStr"/>
@@ -17948,7 +17948,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>403</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17968,7 +17968,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-04-28 16:41:55</t>
+          <t>2026-04-27 19:10:16</t>
         </is>
       </c>
       <c r="F216" t="inlineStr"/>
@@ -17977,7 +17977,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>404</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-04-28 16:45:43</t>
+          <t>2026-04-28 13:06:06</t>
         </is>
       </c>
       <c r="F217" t="inlineStr"/>
@@ -18006,17 +18006,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>405</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-04-28 16:50:41</t>
+          <t>2026-04-28 13:09:10</t>
         </is>
       </c>
       <c r="F218" t="inlineStr"/>
@@ -18035,17 +18035,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>406</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -18055,7 +18055,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-04-28 16:58:22</t>
+          <t>2026-04-28 13:31:57</t>
         </is>
       </c>
       <c r="F219" t="inlineStr"/>
@@ -18064,17 +18064,17 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>408</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -18084,7 +18084,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-04-28 19:11:43</t>
+          <t>2026-04-28 16:36:52</t>
         </is>
       </c>
       <c r="F220" t="inlineStr"/>
@@ -18093,17 +18093,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>409</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -18113,7 +18113,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-04-28 19:17:29</t>
+          <t>2026-04-28 16:41:55</t>
         </is>
       </c>
       <c r="F221" t="inlineStr"/>
@@ -18122,7 +18122,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>410</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18142,7 +18142,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-04-28 19:20:41</t>
+          <t>2026-04-28 16:45:43</t>
         </is>
       </c>
       <c r="F222" t="inlineStr"/>
@@ -18151,17 +18151,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>411</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -18171,7 +18171,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-04-28 19:27:32</t>
+          <t>2026-04-28 16:50:41</t>
         </is>
       </c>
       <c r="F223" t="inlineStr"/>
@@ -18180,17 +18180,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>412</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -18200,7 +18200,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-04-28 19:29:59</t>
+          <t>2026-04-28 16:58:22</t>
         </is>
       </c>
       <c r="F224" t="inlineStr"/>
@@ -18209,17 +18209,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>422</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-04-28 19:38:54</t>
+          <t>2026-04-28 19:11:43</t>
         </is>
       </c>
       <c r="F225" t="inlineStr"/>
@@ -18238,17 +18238,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>425</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -18258,7 +18258,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-04-28 18:59:52</t>
+          <t>2026-04-28 19:17:29</t>
         </is>
       </c>
       <c r="F226" t="inlineStr"/>
@@ -18267,7 +18267,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>427</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18287,7 +18287,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-04-28 19:05:38</t>
+          <t>2026-04-28 19:20:41</t>
         </is>
       </c>
       <c r="F227" t="inlineStr"/>
@@ -18296,7 +18296,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>431</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18316,7 +18316,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-04-28 19:09:07</t>
+          <t>2026-04-28 19:27:32</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
@@ -18325,17 +18325,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>432</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -18345,7 +18345,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-04-28 19:22:49</t>
+          <t>2026-04-28 19:29:59</t>
         </is>
       </c>
       <c r="F229" t="inlineStr"/>
@@ -18354,17 +18354,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>438</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-04-28 19:46:42</t>
+          <t>2026-04-28 19:38:54</t>
         </is>
       </c>
       <c r="F230" t="inlineStr"/>
@@ -18383,17 +18383,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>413</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -18403,7 +18403,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-04-29 15:54:41</t>
+          <t>2026-04-28 18:59:52</t>
         </is>
       </c>
       <c r="F231" t="inlineStr"/>
@@ -18412,7 +18412,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>416</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18432,7 +18432,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-04-29 15:56:41</t>
+          <t>2026-04-28 19:05:38</t>
         </is>
       </c>
       <c r="F232" t="inlineStr"/>
@@ -18441,17 +18441,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>420</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -18461,7 +18461,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-04-29 16:10:35</t>
+          <t>2026-04-28 19:09:07</t>
         </is>
       </c>
       <c r="F233" t="inlineStr"/>
@@ -18470,17 +18470,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>429</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -18490,7 +18490,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-04-29 16:13:57</t>
+          <t>2026-04-28 19:22:49</t>
         </is>
       </c>
       <c r="F234" t="inlineStr"/>
@@ -18499,17 +18499,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>439</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -18519,7 +18519,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-04-29 16:17:13</t>
+          <t>2026-04-28 19:46:42</t>
         </is>
       </c>
       <c r="F235" t="inlineStr"/>
@@ -18528,7 +18528,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>440</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18548,7 +18548,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2026-04-29 16:21:56</t>
+          <t>2026-04-29 15:54:41</t>
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
@@ -18557,7 +18557,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>441</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18577,7 +18577,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-04-29 16:26:19</t>
+          <t>2026-04-29 15:56:41</t>
         </is>
       </c>
       <c r="F237" t="inlineStr"/>
@@ -18586,17 +18586,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>442</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -18606,7 +18606,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-04-30 11:56:22</t>
+          <t>2026-04-29 16:10:35</t>
         </is>
       </c>
       <c r="F238" t="inlineStr"/>
@@ -18615,17 +18615,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>443</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -18635,7 +18635,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-04-30 12:18:39</t>
+          <t>2026-04-29 16:13:57</t>
         </is>
       </c>
       <c r="F239" t="inlineStr"/>
@@ -18644,7 +18644,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>444</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18664,7 +18664,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-04-30 12:27:47</t>
+          <t>2026-04-29 16:17:13</t>
         </is>
       </c>
       <c r="F240" t="inlineStr"/>
@@ -18673,17 +18673,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>445</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-04-30 14:33:48</t>
+          <t>2026-04-29 16:21:56</t>
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
@@ -18702,17 +18702,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>446</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-04-30 14:39:11</t>
+          <t>2026-04-29 16:26:19</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
@@ -18731,7 +18731,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>447</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18751,7 +18751,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-04-30 14:44:06</t>
+          <t>2026-04-30 11:56:22</t>
         </is>
       </c>
       <c r="F243" t="inlineStr"/>
@@ -18760,17 +18760,17 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>448</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -18780,7 +18780,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-04-30 14:50:48</t>
+          <t>2026-04-30 12:18:39</t>
         </is>
       </c>
       <c r="F244" t="inlineStr"/>
@@ -18789,7 +18789,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>449</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -18809,7 +18809,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-04-30 15:03:19</t>
+          <t>2026-04-30 12:27:47</t>
         </is>
       </c>
       <c r="F245" t="inlineStr"/>
@@ -18818,17 +18818,17 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>450</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -18838,7 +18838,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-04-30 16:43:14</t>
+          <t>2026-04-30 14:33:48</t>
         </is>
       </c>
       <c r="F246" t="inlineStr"/>
@@ -18847,17 +18847,17 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>452</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -18867,7 +18867,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-04-30 16:49:38</t>
+          <t>2026-04-30 14:39:11</t>
         </is>
       </c>
       <c r="F247" t="inlineStr"/>
@@ -18876,17 +18876,17 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>453</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -18896,7 +18896,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-04-30 16:57:13</t>
+          <t>2026-04-30 14:44:06</t>
         </is>
       </c>
       <c r="F248" t="inlineStr"/>
@@ -18905,17 +18905,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>454</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -18925,7 +18925,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-04-30 16:59:14</t>
+          <t>2026-04-30 14:50:48</t>
         </is>
       </c>
       <c r="F249" t="inlineStr"/>
@@ -18934,7 +18934,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>455</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -18954,7 +18954,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-04-30 17:03:09</t>
+          <t>2026-04-30 15:03:19</t>
         </is>
       </c>
       <c r="F250" t="inlineStr"/>
@@ -18963,7 +18963,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>456</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-04-30 17:07:20</t>
+          <t>2026-04-30 16:43:14</t>
         </is>
       </c>
       <c r="F251" t="inlineStr"/>
@@ -18992,7 +18992,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>457</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-04-30 17:20:16</t>
+          <t>2026-04-30 16:49:38</t>
         </is>
       </c>
       <c r="F252" t="inlineStr"/>
@@ -19021,17 +19021,17 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>458</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -19041,7 +19041,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-05-04 12:40:26</t>
+          <t>2026-04-30 16:57:13</t>
         </is>
       </c>
       <c r="F253" t="inlineStr"/>
@@ -19050,17 +19050,17 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>459</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -19070,7 +19070,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-05-04 13:27:46</t>
+          <t>2026-04-30 16:59:14</t>
         </is>
       </c>
       <c r="F254" t="inlineStr"/>
@@ -19079,7 +19079,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19099,7 +19099,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-05-04 13:32:27</t>
+          <t>2026-04-30 17:03:09</t>
         </is>
       </c>
       <c r="F255" t="inlineStr"/>
@@ -19108,17 +19108,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>461</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -19128,7 +19128,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2026-05-04 13:35:31</t>
+          <t>2026-04-30 17:07:20</t>
         </is>
       </c>
       <c r="F256" t="inlineStr"/>
@@ -19137,17 +19137,17 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>462</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -19157,7 +19157,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-05-04 13:52:33</t>
+          <t>2026-04-30 17:20:16</t>
         </is>
       </c>
       <c r="F257" t="inlineStr"/>
@@ -19166,7 +19166,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>465</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -19186,7 +19186,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-05-04 14:15:29</t>
+          <t>2026-05-04 12:40:26</t>
         </is>
       </c>
       <c r="F258" t="inlineStr"/>
@@ -19195,17 +19195,17 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>466</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -19215,7 +19215,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-05-04 14:21:26</t>
+          <t>2026-05-04 13:27:46</t>
         </is>
       </c>
       <c r="F259" t="inlineStr"/>
@@ -19224,7 +19224,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>467</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -19244,7 +19244,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-05-04 14:28:28</t>
+          <t>2026-05-04 13:32:27</t>
         </is>
       </c>
       <c r="F260" t="inlineStr"/>
@@ -19253,7 +19253,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>468</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -19273,7 +19273,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-05-05 12:33:28</t>
+          <t>2026-05-04 13:35:31</t>
         </is>
       </c>
       <c r="F261" t="inlineStr"/>
@@ -19282,17 +19282,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>469</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -19302,7 +19302,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-05-05 12:36:49</t>
+          <t>2026-05-04 13:52:33</t>
         </is>
       </c>
       <c r="F262" t="inlineStr"/>
@@ -19311,7 +19311,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>470</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -19331,7 +19331,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-05-05 13:16:10</t>
+          <t>2026-05-04 14:15:29</t>
         </is>
       </c>
       <c r="F263" t="inlineStr"/>
@@ -19340,7 +19340,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>471</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -19360,7 +19360,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-05-05 13:22:28</t>
+          <t>2026-05-04 14:21:26</t>
         </is>
       </c>
       <c r="F264" t="inlineStr"/>
@@ -19369,7 +19369,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>472</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-05-05 15:49:32</t>
+          <t>2026-05-04 14:28:28</t>
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
@@ -19398,17 +19398,17 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>473</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -19418,7 +19418,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-05-05 18:17:18</t>
+          <t>2026-05-05 12:33:28</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
@@ -19427,7 +19427,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>474</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -19447,7 +19447,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-05-05 18:23:24</t>
+          <t>2026-05-05 12:36:49</t>
         </is>
       </c>
       <c r="F267" t="inlineStr"/>
@@ -19456,17 +19456,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>475</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -19476,7 +19476,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-05-05 18:30:18</t>
+          <t>2026-05-05 13:16:10</t>
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
@@ -19485,7 +19485,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>476</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -19505,7 +19505,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-05-05 19:24:36</t>
+          <t>2026-05-05 13:22:28</t>
         </is>
       </c>
       <c r="F269" t="inlineStr"/>
@@ -19514,17 +19514,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>478</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -19534,7 +19534,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-05-06 14:07:52</t>
+          <t>2026-05-05 15:49:32</t>
         </is>
       </c>
       <c r="F270" t="inlineStr"/>
@@ -19543,17 +19543,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>484</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -19563,7 +19563,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-05-06 14:12:50</t>
+          <t>2026-05-05 18:17:18</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
@@ -19572,17 +19572,17 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>485</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -19592,7 +19592,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-05-06 14:15:34</t>
+          <t>2026-05-05 18:23:24</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
@@ -19601,17 +19601,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>486</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -19621,7 +19621,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-05-06 14:59:26</t>
+          <t>2026-05-05 18:30:18</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
@@ -19630,7 +19630,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>487</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -19650,7 +19650,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-05-06 15:04:52</t>
+          <t>2026-05-05 19:24:36</t>
         </is>
       </c>
       <c r="F274" t="inlineStr"/>
@@ -19659,17 +19659,17 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>488</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -19679,7 +19679,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-05-06 15:08:51</t>
+          <t>2026-05-06 14:07:52</t>
         </is>
       </c>
       <c r="F275" t="inlineStr"/>
@@ -19688,17 +19688,17 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>489</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Busy</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -19708,7 +19708,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-05-06 15:28:38</t>
+          <t>2026-05-06 14:12:50</t>
         </is>
       </c>
       <c r="F276" t="inlineStr"/>
@@ -19717,17 +19717,17 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>490</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-05-06 15:31:36</t>
+          <t>2026-05-06 14:15:34</t>
         </is>
       </c>
       <c r="F277" t="inlineStr"/>
@@ -19746,17 +19746,17 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-05-06 17:53:50</t>
+          <t>2026-05-06 14:59:26</t>
         </is>
       </c>
       <c r="F278" t="inlineStr"/>
@@ -19775,7 +19775,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>492</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -19795,7 +19795,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-05-06 17:59:31</t>
+          <t>2026-05-06 15:04:52</t>
         </is>
       </c>
       <c r="F279" t="inlineStr"/>
@@ -19804,17 +19804,17 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>493</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-05-06 19:18:14</t>
+          <t>2026-05-06 15:08:51</t>
         </is>
       </c>
       <c r="F280" t="inlineStr"/>
@@ -19833,17 +19833,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>494</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Busy</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -19853,7 +19853,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-05-06 19:21:01</t>
+          <t>2026-05-06 15:28:38</t>
         </is>
       </c>
       <c r="F281" t="inlineStr"/>
@@ -19862,17 +19862,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>495</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -19882,7 +19882,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-05-06 19:25:27</t>
+          <t>2026-05-06 15:31:36</t>
         </is>
       </c>
       <c r="F282" t="inlineStr"/>
@@ -19891,7 +19891,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>501</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -19911,7 +19911,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-05-06 19:27:23</t>
+          <t>2026-05-06 17:53:50</t>
         </is>
       </c>
       <c r="F283" t="inlineStr"/>
@@ -19920,17 +19920,17 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>502</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -19940,7 +19940,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-05-06 19:39:21</t>
+          <t>2026-05-06 17:59:31</t>
         </is>
       </c>
       <c r="F284" t="inlineStr"/>
@@ -19949,7 +19949,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>503</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -19969,7 +19969,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-05-06 20:09:52</t>
+          <t>2026-05-06 19:18:14</t>
         </is>
       </c>
       <c r="F285" t="inlineStr"/>
@@ -19978,7 +19978,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>504</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -19998,11 +19998,388 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-05-06 20:12:28</t>
+          <t>2026-05-06 19:21:01</t>
         </is>
       </c>
       <c r="F286" t="inlineStr"/>
       <c r="G286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>2026-05-06 19:25:27</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>2026-05-06 19:27:23</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>2026-05-06 19:39:21</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>2026-05-06 20:09:52</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>2026-05-06 20:12:28</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>2026-05-07 12:02:27</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>2026-05-07 12:05:31</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>514</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>2026-05-07 12:07:46</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>2026-05-07 12:12:23</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>2026-05-07 12:21:17</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>2026-05-07 12:22:26</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>2026-05-07 12:25:15</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>2026-05-07 12:30:09</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H270"/>
+  <dimension ref="A1:H271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-03-23 19:45:19</t>
+          <t>2026-05-07 18:31:47</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-03-17 17:51:06</t>
+          <t>2026-05-07 18:41:02</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-03-24 15:48:39</t>
+          <t>2026-05-07 19:12:07</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-04-23 19:09:01</t>
+          <t>2026-05-07 19:19:47</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-03-25 15:00:34</t>
+          <t>2026-05-07 18:11:26</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-03-27 19:35:26</t>
+          <t>2026-05-07 18:23:27</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-04-23 18:41:25</t>
+          <t>2026-05-07 18:21:05</t>
         </is>
       </c>
     </row>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-04-23 19:28:15</t>
+          <t>2026-05-07 19:35:25</t>
         </is>
       </c>
     </row>
@@ -11685,6 +11685,48 @@
       <c r="H270" t="inlineStr">
         <is>
           <t>2026-05-06 15:31:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>YURY RUDOVICH</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>info.esquiremoving@gmail.com</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>(617) 937-9567</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>esquiremoving</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>2026-05-07 19:04:03</t>
         </is>
       </c>
     </row>
@@ -11699,7 +11741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G299"/>
+  <dimension ref="A1:G308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20380,6 +20422,267 @@
       </c>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>2026-05-07 18:11:26</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>528</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>NO ANSWER</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>no_answer</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>2026-05-07 18:21:05</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>2026-05-07 18:23:27</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr"/>
+      <c r="G302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>NO ANSWER</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>no_answer</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>2026-05-07 18:31:47</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr"/>
+      <c r="G303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>2026-05-07 18:41:02</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr"/>
+      <c r="G304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>HUNG UP</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>hung_up</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>2026-05-07 19:04:03</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr"/>
+      <c r="G305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>533</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>2026-05-07 19:12:07</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>534</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>2026-05-07 19:19:47</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>2026-05-07 19:35:25</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr"/>
+      <c r="G308" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -11600,7 +11600,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>2026-05-06 15:04:52</t>
+          <t>2026-05-08 01:48:35</t>
         </is>
       </c>
     </row>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H271"/>
+  <dimension ref="A1:H274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-03-23 19:46:24</t>
+          <t>2026-05-08 12:36:57</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-04-10 16:24:20</t>
+          <t>2026-05-08 12:43:59</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-03-26 15:35:49</t>
+          <t>2026-05-08 13:16:49</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-04-13 18:46:14</t>
+          <t>2026-05-08 13:04:02</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-03-26 19:21:36</t>
+          <t>2026-05-08 13:22:02</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-04-23 18:58:16</t>
+          <t>2026-05-08 12:51:09</t>
         </is>
       </c>
     </row>
@@ -11727,6 +11727,132 @@
       <c r="H271" t="inlineStr">
         <is>
           <t>2026-05-07 19:04:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Steven Garrish</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>steven.garrish@odfl.com</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>336 822 5332</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OLD DOMINION FREIGHT LINE INC</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>2026-05-08 12:55:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Matthew Cann</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>mcann@braunsexpress.com</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>774-287-3233</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Braunsexpress</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>2026-05-08 12:57:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Bill Loyd</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>wloyd@amatrans.com</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>978-408-6578</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Amatrans</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>2026-05-08 13:09:59</t>
         </is>
       </c>
     </row>
@@ -11741,7 +11867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G308"/>
+  <dimension ref="A1:G318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20683,6 +20809,296 @@
       </c>
       <c r="F308" t="inlineStr"/>
       <c r="G308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>2026-05-08 12:36:57</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr"/>
+      <c r="G309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>537</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>2026-05-08 12:43:59</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr"/>
+      <c r="G310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>2026-05-08 12:51:09</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr"/>
+      <c r="G311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>539</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>2026-05-08 12:55:15</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr"/>
+      <c r="G312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>2026-05-08 12:57:14</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr"/>
+      <c r="G313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>2026-05-08 13:00:41</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr"/>
+      <c r="G314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>2026-05-08 13:04:02</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr"/>
+      <c r="G315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>2026-05-08 13:09:59</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr"/>
+      <c r="G316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>WARM LEAD</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>warm_lead</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>2026-05-08 13:16:49</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr"/>
+      <c r="G317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>2026-05-08 13:22:02</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H274"/>
+  <dimension ref="A1:H276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:51</t>
+          <t>2026-05-08 15:54:37</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-04-23 11:55:48</t>
+          <t>2026-05-08 15:50:51</t>
         </is>
       </c>
     </row>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-04-24 14:58:00</t>
+          <t>2026-05-08 15:59:34</t>
         </is>
       </c>
     </row>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>2026-04-27 18:32:13</t>
+          <t>2026-05-08 16:11:07</t>
         </is>
       </c>
     </row>
@@ -11853,6 +11853,90 @@
       <c r="H274" t="inlineStr">
         <is>
           <t>2026-05-08 13:09:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>David Wilson</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>deanwilson@intercitylines.com</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>(413) 531-1874</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Intercitylines</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>2026-05-08 16:19:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>John Sullivan</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>johns@richstrans.com</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>508-294-2021</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Richstrans</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>2026-05-08 16:24:03</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G318"/>
+  <dimension ref="A1:G324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21099,6 +21183,180 @@
       </c>
       <c r="F318" t="inlineStr"/>
       <c r="G318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>2026-05-08 15:50:51</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr"/>
+      <c r="G319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>NO ANSWER</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>no_answer</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>2026-05-08 15:54:37</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr"/>
+      <c r="G320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>2026-05-08 15:59:34</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr"/>
+      <c r="G321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>2026-05-08 16:11:07</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr"/>
+      <c r="G322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>2026-05-08 16:19:50</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr"/>
+      <c r="G323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>2026-05-08 16:24:03</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr"/>
+      <c r="G324" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -2254,7 +2254,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-04-02 19:52:54</t>
+          <t>2026-05-11 15:02:56</t>
         </is>
       </c>
     </row>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -6105,7 +6105,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Dave Winslow</t>
+          <t>NICHOLAS BRODEUR</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-04-27 16:19:30</t>
+          <t>2026-05-11 18:35:26</t>
         </is>
       </c>
     </row>
@@ -11951,7 +11951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G324"/>
+  <dimension ref="A1:G325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12110,27 +12110,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>552</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not Interested</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-02-12 20:19:12</t>
+          <t>2026-05-11 18:35:26</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -12139,17 +12139,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>not Interested</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-02-13 18:09:02</t>
+          <t>2026-02-12 20:19:12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -12168,7 +12168,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -12188,7 +12188,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-02-13 18:10:17</t>
+          <t>2026-02-13 18:09:02</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -12197,17 +12197,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Number Busy</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -12217,7 +12217,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-02-13 18:40:29</t>
+          <t>2026-02-13 18:10:17</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -12226,17 +12226,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Number Busy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-02-13 20:55:42</t>
+          <t>2026-02-13 18:40:29</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -12255,17 +12255,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>email</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-02-17 12:58:58</t>
+          <t>2026-02-13 20:55:42</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -12284,17 +12284,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Number not in service</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -12304,7 +12304,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-02-17 13:17:50</t>
+          <t>2026-02-17 12:58:58</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -12313,17 +12313,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Number not in service</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-02-18 13:35:13</t>
+          <t>2026-02-17 13:17:50</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -12342,12 +12342,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Left Voicemail</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -12362,7 +12362,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-02-18 19:14:30</t>
+          <t>2026-02-18 13:35:13</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -12371,19 +12371,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>Left Voicemail</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>voicemail</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>voicemail</t>
-        </is>
-      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>Done</t>
@@ -12391,7 +12391,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-02-20 16:16:15</t>
+          <t>2026-02-18 19:14:30</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -12400,12 +12400,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -12420,7 +12420,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-02-20 16:28:27</t>
+          <t>2026-02-20 16:16:15</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -12429,12 +12429,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Left Voicemail</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-02-20 16:40:56</t>
+          <t>2026-02-20 16:28:27</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -12458,17 +12458,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>98</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Left Voicemail</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12478,7 +12478,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-02-20 17:38:46</t>
+          <t>2026-02-20 16:40:56</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -12487,17 +12487,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Not Interested</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-02-20 17:51:33</t>
+          <t>2026-02-20 17:38:46</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -12516,17 +12516,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-02-20 17:51:57</t>
+          <t>2026-02-20 17:51:33</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -12545,17 +12545,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -12565,7 +12565,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-02-25 14:04:42</t>
+          <t>2026-02-20 17:51:57</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -12574,17 +12574,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-02-25 16:00:39</t>
+          <t>2026-02-25 14:04:42</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -12603,7 +12603,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -12623,7 +12623,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-03-04 19:53:23</t>
+          <t>2026-02-25 16:00:39</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -12632,17 +12632,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-03-13 11:44:50</t>
+          <t>2026-03-04 19:53:23</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -12661,17 +12661,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>157</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:38</t>
+          <t>2026-03-13 11:44:50</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -12690,17 +12690,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>158</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -12710,7 +12710,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-03-13 18:27:37</t>
+          <t>2026-03-13 18:22:38</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -12719,7 +12719,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>159</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -12739,7 +12739,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-03-16 13:12:26</t>
+          <t>2026-03-13 18:27:37</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -12748,7 +12748,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>160</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12768,7 +12768,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-03-16 13:13:55</t>
+          <t>2026-03-16 13:12:26</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -12777,17 +12777,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>161</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-03-17 15:47:45</t>
+          <t>2026-03-16 13:13:55</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -12806,17 +12806,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>167</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -12826,7 +12826,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-03-17 15:53:47</t>
+          <t>2026-03-17 15:47:45</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -12835,17 +12835,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>168</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-03-17 15:57:36</t>
+          <t>2026-03-17 15:53:47</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -12864,17 +12864,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>169</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>WRONG NUMBER -DNC</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>wrong_number__dnc</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-03-17 15:59:48</t>
+          <t>2026-03-17 15:57:36</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -12893,17 +12893,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>170</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>WRONG NUMBER -DNC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>wrong_number__dnc</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -12913,7 +12913,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-03-17 16:06:24</t>
+          <t>2026-03-17 15:59:48</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -12922,17 +12922,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>171</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-03-17 16:11:12</t>
+          <t>2026-03-17 16:06:24</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -12951,17 +12951,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>173</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-03-17 16:14:37</t>
+          <t>2026-03-17 16:11:12</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -12980,17 +12980,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>174</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-03-17 16:17:56</t>
+          <t>2026-03-17 16:14:37</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -13009,17 +13009,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>175</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-04-27 18:04:47</t>
+          <t>2026-03-17 16:17:56</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -13038,17 +13038,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>388</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-03-20 14:54:02</t>
+          <t>2026-04-27 18:04:47</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -13067,7 +13067,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>180</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -13087,7 +13087,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-03-20 14:57:56</t>
+          <t>2026-03-20 14:54:02</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -13096,7 +13096,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>181</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-03-20 18:07:00</t>
+          <t>2026-03-20 14:57:56</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -13125,17 +13125,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>183</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -13145,7 +13145,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-03-20 18:13:02</t>
+          <t>2026-03-20 18:07:00</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -13154,17 +13154,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>184</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-04-27 16:29:12</t>
+          <t>2026-03-20 18:13:02</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -13183,17 +13183,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>355</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -13203,7 +13203,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-04-27 18:04:59</t>
+          <t>2026-04-27 16:29:12</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -13212,7 +13212,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>389</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -13232,7 +13232,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-04-28 19:04:54</t>
+          <t>2026-04-27 18:04:59</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -13241,7 +13241,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>414</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -13261,7 +13261,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-04-28 19:06:45</t>
+          <t>2026-04-28 19:04:54</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -13270,7 +13270,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>417</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-04-28 19:34:15</t>
+          <t>2026-04-28 19:06:45</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -13299,7 +13299,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>433</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -13319,7 +13319,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-05-07 12:24:40</t>
+          <t>2026-04-28 19:34:15</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -13328,17 +13328,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>519</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -13348,7 +13348,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-03-20 18:49:21</t>
+          <t>2026-05-07 12:24:40</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -13357,17 +13357,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>185</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -13377,7 +13377,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-04-28 19:34:30</t>
+          <t>2026-03-20 18:49:21</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -13386,17 +13386,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>434</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-03-23 18:38:25</t>
+          <t>2026-04-28 19:34:30</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -13415,17 +13415,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>191</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -13435,7 +13435,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-03-23 18:47:52</t>
+          <t>2026-03-23 18:38:25</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -13444,17 +13444,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>193</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -13464,7 +13464,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-03-23 18:54:34</t>
+          <t>2026-03-23 18:47:52</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -13473,7 +13473,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>194</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -13493,7 +13493,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-03-23 18:58:51</t>
+          <t>2026-03-23 18:54:34</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -13502,7 +13502,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>196</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>hot_lead</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -13522,7 +13522,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-03-23 19:03:40</t>
+          <t>2026-03-23 18:58:51</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -13531,17 +13531,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>197</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>hot_lead</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-03-24 15:48:39</t>
+          <t>2026-03-23 19:03:40</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -13560,17 +13560,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>202</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WRONG NUMBER -DNC</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>wrong_number__dnc</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-03-24 16:11:19</t>
+          <t>2026-03-24 15:48:39</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -13589,17 +13589,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>205</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>WRONG NUMBER -DNC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>wrong_number__dnc</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-03-24 16:15:10</t>
+          <t>2026-03-24 16:11:19</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -13618,7 +13618,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>206</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -13638,7 +13638,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-03-24 16:23:12</t>
+          <t>2026-03-24 16:15:10</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -13647,17 +13647,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>207</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Follow Up</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -13667,7 +13667,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-03-24 18:17:19</t>
+          <t>2026-03-24 16:23:12</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -13676,17 +13676,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>208</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Follow Up</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>follow_up</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -13696,7 +13696,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:48</t>
+          <t>2026-03-24 18:17:19</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -13705,7 +13705,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>369</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-04-27 16:40:16</t>
+          <t>2026-04-27 16:38:48</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -13734,7 +13734,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>372</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -13754,7 +13754,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-04-27 16:43:21</t>
+          <t>2026-04-27 16:40:16</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -13763,7 +13763,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>375</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-04-27 16:47:15</t>
+          <t>2026-04-27 16:43:21</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -13792,7 +13792,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>380</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -13812,7 +13812,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-04-27 16:50:20</t>
+          <t>2026-04-27 16:47:15</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -13821,17 +13821,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>385</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-03-24 18:57:44</t>
+          <t>2026-04-27 16:50:20</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -13850,7 +13850,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>209</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-03-25 16:41:38</t>
+          <t>2026-03-24 18:57:44</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -13879,7 +13879,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>211</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -13899,7 +13899,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-03-25 16:48:29</t>
+          <t>2026-03-25 16:41:38</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -13908,17 +13908,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>212</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13928,7 +13928,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-04-27 16:31:50</t>
+          <t>2026-03-25 16:48:29</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -13937,17 +13937,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>359</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13957,7 +13957,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-05-06 20:12:18</t>
+          <t>2026-04-27 16:31:50</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -13966,17 +13966,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>510</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-03-26 14:46:03</t>
+          <t>2026-05-06 20:12:18</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -13995,17 +13995,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>217</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14015,7 +14015,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-03-26 14:57:57</t>
+          <t>2026-03-26 14:46:03</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -14024,17 +14024,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>218</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14044,7 +14044,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-03-26 15:12:09</t>
+          <t>2026-03-26 14:57:57</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -14053,17 +14053,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>220</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14073,7 +14073,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-03-26 15:45:11</t>
+          <t>2026-03-26 15:12:09</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -14082,7 +14082,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>221</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-04-27 16:39:08</t>
+          <t>2026-03-26 15:45:11</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -14111,17 +14111,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>370</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -14131,7 +14131,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-03-27 18:06:04</t>
+          <t>2026-04-27 16:39:08</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -14140,17 +14140,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>228</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-03-27 18:09:32</t>
+          <t>2026-03-27 18:06:04</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -14169,12 +14169,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>229</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Call on Monday</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-03-27 18:13:29</t>
+          <t>2026-03-27 18:09:32</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -14198,17 +14198,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>230</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call on Monday</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -14218,7 +14218,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-03-27 18:16:14</t>
+          <t>2026-03-27 18:13:29</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -14227,17 +14227,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>231</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -14247,7 +14247,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-03-27 18:28:41</t>
+          <t>2026-03-27 18:16:14</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -14256,17 +14256,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>232</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-04-23 18:46:03</t>
+          <t>2026-03-27 18:28:41</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -14285,7 +14285,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>319</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -14305,7 +14305,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-04-27 16:34:45</t>
+          <t>2026-04-23 18:46:03</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
@@ -14314,17 +14314,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>363</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-03-27 19:30:50</t>
+          <t>2026-04-27 16:34:45</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -14343,17 +14343,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>233</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-03-30 16:46:09</t>
+          <t>2026-03-27 19:30:50</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
@@ -14372,17 +14372,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>239</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Busy</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -14392,7 +14392,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-05-06 20:09:36</t>
+          <t>2026-03-30 16:46:09</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -14401,17 +14401,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>508</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Busy</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-03-31 13:50:49</t>
+          <t>2026-05-06 20:09:36</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -14430,17 +14430,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>245</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14450,7 +14450,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-03-31 13:57:09</t>
+          <t>2026-03-31 13:50:49</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -14459,17 +14459,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>246</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14479,7 +14479,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-03-31 14:01:39</t>
+          <t>2026-03-31 13:57:09</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
@@ -14488,17 +14488,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>247</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14508,7 +14508,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-03-31 14:09:41</t>
+          <t>2026-03-31 14:01:39</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
@@ -14517,7 +14517,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>248</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-03-31 19:13:49</t>
+          <t>2026-03-31 14:09:41</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
@@ -14546,17 +14546,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>249</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14566,7 +14566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-04-27 16:17:22</t>
+          <t>2026-03-31 19:13:49</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -14575,17 +14575,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>341</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14595,7 +14595,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-04-27 16:22:28</t>
+          <t>2026-04-27 16:17:22</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -14604,17 +14604,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>347</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -14624,7 +14624,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-04-27 16:23:48</t>
+          <t>2026-04-27 16:22:28</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -14633,7 +14633,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>349</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -14653,7 +14653,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-04-27 16:26:16</t>
+          <t>2026-04-27 16:23:48</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -14662,7 +14662,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>352</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -14682,7 +14682,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-04-27 16:32:05</t>
+          <t>2026-04-27 16:26:16</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
@@ -14691,7 +14691,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -14711,7 +14711,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-04-27 16:33:04</t>
+          <t>2026-04-27 16:32:05</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -14720,7 +14720,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>361</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-04-27 16:34:57</t>
+          <t>2026-04-27 16:33:04</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -14749,7 +14749,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>364</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -14769,7 +14769,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:15</t>
+          <t>2026-04-27 16:34:57</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -14778,7 +14778,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>390</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -14798,7 +14798,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-04-28 19:05:25</t>
+          <t>2026-04-27 18:05:15</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
@@ -14807,7 +14807,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>415</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -14827,7 +14827,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-04-28 19:06:58</t>
+          <t>2026-04-28 19:05:25</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
@@ -14836,17 +14836,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>418</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-04-28 19:16:34</t>
+          <t>2026-04-28 19:06:58</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -14865,17 +14865,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>423</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -14885,7 +14885,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-04-28 19:34:42</t>
+          <t>2026-04-28 19:16:34</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
@@ -14894,17 +14894,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>435</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-03-31 19:22:45</t>
+          <t>2026-04-28 19:34:42</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -14923,7 +14923,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>250</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -14933,7 +14933,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>follow_up</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -14943,7 +14943,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-03-31 19:37:10</t>
+          <t>2026-03-31 19:22:45</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -14952,17 +14952,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>251</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14972,7 +14972,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-04-01 14:30:00</t>
+          <t>2026-03-31 19:37:10</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -14981,7 +14981,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>252</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -15001,7 +15001,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-04-01 16:53:36</t>
+          <t>2026-04-01 14:30:00</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -15010,17 +15010,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>253</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -15030,7 +15030,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-05-07 12:22:45</t>
+          <t>2026-04-01 16:53:36</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -15039,7 +15039,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>518</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -15059,7 +15059,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-05-07 12:24:53</t>
+          <t>2026-05-07 12:22:45</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
@@ -15068,7 +15068,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>520</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -15088,7 +15088,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-05-07 12:30:02</t>
+          <t>2026-05-07 12:24:53</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
@@ -15097,17 +15097,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>523</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -15117,7 +15117,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-04-07 15:24:02</t>
+          <t>2026-05-07 12:30:02</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
@@ -15126,17 +15126,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>271</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -15146,7 +15146,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-04-07 16:00:48</t>
+          <t>2026-04-07 15:24:02</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
@@ -15155,17 +15155,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>272</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15175,7 +15175,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-04-24 11:55:32</t>
+          <t>2026-04-07 16:00:48</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
@@ -15184,7 +15184,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>327</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-04-27 16:17:36</t>
+          <t>2026-04-24 11:55:32</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
@@ -15213,7 +15213,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>342</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -15233,7 +15233,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-04-27 16:20:52</t>
+          <t>2026-04-27 16:17:36</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
@@ -15242,7 +15242,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>345</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -15262,7 +15262,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-04-27 16:22:53</t>
+          <t>2026-04-27 16:20:52</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -15271,7 +15271,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>348</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -15291,7 +15291,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-04-27 16:24:00</t>
+          <t>2026-04-27 16:22:53</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
@@ -15300,7 +15300,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>350</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-04-27 16:27:53</t>
+          <t>2026-04-27 16:24:00</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
@@ -15329,17 +15329,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>353</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15349,7 +15349,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-04-08 16:38:00</t>
+          <t>2026-04-27 16:27:53</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
@@ -15358,17 +15358,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>274</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15378,7 +15378,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-04-08 18:21:03</t>
+          <t>2026-04-08 16:38:00</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
@@ -15387,7 +15387,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>275</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -15407,7 +15407,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-04-23 18:22:34</t>
+          <t>2026-04-08 18:21:03</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
@@ -15416,7 +15416,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>308</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -15436,7 +15436,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-04-23 18:24:52</t>
+          <t>2026-04-23 18:22:34</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
@@ -15445,7 +15445,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>310</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -15465,7 +15465,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-04-27 16:43:32</t>
+          <t>2026-04-23 18:24:52</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
@@ -15474,17 +15474,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>376</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-04-27 16:44:32</t>
+          <t>2026-04-27 16:43:32</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
@@ -15503,17 +15503,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>378</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15523,7 +15523,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-04-27 16:47:27</t>
+          <t>2026-04-27 16:44:32</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
@@ -15532,7 +15532,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>381</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -15552,7 +15552,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-04-27 16:48:30</t>
+          <t>2026-04-27 16:47:27</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
@@ -15561,17 +15561,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>383</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15581,7 +15581,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-04-27 16:49:41</t>
+          <t>2026-04-27 16:48:30</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -15590,17 +15590,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>384</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15610,7 +15610,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-04-27 16:51:50</t>
+          <t>2026-04-27 16:49:41</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -15619,7 +15619,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>386</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-04-28 19:34:54</t>
+          <t>2026-04-27 16:51:50</t>
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
@@ -15648,17 +15648,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>436</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15668,7 +15668,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-04-09 14:38:33</t>
+          <t>2026-04-28 19:34:54</t>
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
@@ -15677,17 +15677,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>276</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15697,7 +15697,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-04-09 14:50:24</t>
+          <t>2026-04-09 14:38:33</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -15706,17 +15706,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>277</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-04-27 16:17:54</t>
+          <t>2026-04-09 14:50:24</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
@@ -15735,17 +15735,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>343</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15755,7 +15755,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-04-27 16:19:16</t>
+          <t>2026-04-27 16:17:54</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -15764,17 +15764,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>344</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>email</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-04-27 16:21:26</t>
+          <t>2026-04-27 16:19:16</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
@@ -15793,17 +15793,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>346</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -15813,7 +15813,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-04-27 16:30:33</t>
+          <t>2026-04-27 16:21:26</t>
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
@@ -15822,17 +15822,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>357</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -15842,7 +15842,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-04-27 16:34:07</t>
+          <t>2026-04-27 16:30:33</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
@@ -15851,17 +15851,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>362</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -15871,7 +15871,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-04-27 16:35:11</t>
+          <t>2026-04-27 16:34:07</t>
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
@@ -15880,7 +15880,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>365</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:29</t>
+          <t>2026-04-27 16:35:11</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
@@ -15909,7 +15909,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>391</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -15929,7 +15929,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-04-28 19:20:18</t>
+          <t>2026-04-27 18:05:29</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
@@ -15938,7 +15938,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>426</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -15958,7 +15958,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-04-28 19:22:33</t>
+          <t>2026-04-28 19:20:18</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
@@ -15967,7 +15967,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>428</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -15987,7 +15987,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-04-28 19:27:09</t>
+          <t>2026-04-28 19:22:33</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -15996,17 +15996,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>430</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -16016,7 +16016,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-04-13 15:45:27</t>
+          <t>2026-04-28 19:27:09</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -16025,7 +16025,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>286</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -16045,7 +16045,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-04-13 15:46:25</t>
+          <t>2026-04-13 15:45:27</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
@@ -16054,17 +16054,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>287</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-04-13 15:53:15</t>
+          <t>2026-04-13 15:46:25</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
@@ -16083,17 +16083,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>288</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -16103,7 +16103,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-04-13 15:58:50</t>
+          <t>2026-04-13 15:53:15</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
@@ -16112,17 +16112,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>289</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -16132,7 +16132,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-04-27 16:24:24</t>
+          <t>2026-04-13 15:58:50</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
@@ -16141,17 +16141,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>351</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -16161,7 +16161,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-04-27 16:28:22</t>
+          <t>2026-04-27 16:24:24</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
@@ -16170,17 +16170,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>354</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -16190,7 +16190,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-04-27 16:35:40</t>
+          <t>2026-04-27 16:28:22</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
@@ -16199,7 +16199,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>366</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -16219,7 +16219,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-04-28 19:07:14</t>
+          <t>2026-04-27 16:35:40</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
@@ -16228,7 +16228,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>419</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-04-28 19:16:45</t>
+          <t>2026-04-28 19:07:14</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
@@ -16257,17 +16257,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>424</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -16277,7 +16277,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-04-27 16:29:25</t>
+          <t>2026-04-28 19:16:45</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
@@ -16286,7 +16286,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>356</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -16306,7 +16306,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-04-27 16:31:00</t>
+          <t>2026-04-27 16:29:25</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
@@ -16315,17 +16315,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>358</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -16335,7 +16335,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-04-27 16:39:21</t>
+          <t>2026-04-27 16:31:00</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
@@ -16344,7 +16344,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>371</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -16364,7 +16364,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-04-27 16:40:26</t>
+          <t>2026-04-27 16:39:21</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
@@ -16373,7 +16373,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>373</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -16393,7 +16393,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-04-27 16:42:47</t>
+          <t>2026-04-27 16:40:26</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -16402,17 +16402,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>374</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-04-15 16:05:12</t>
+          <t>2026-04-27 16:42:47</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -16431,7 +16431,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>294</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -16451,7 +16451,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-04-15 18:17:17</t>
+          <t>2026-04-15 16:05:12</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -16460,17 +16460,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>295</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -16480,7 +16480,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-04-27 16:35:57</t>
+          <t>2026-04-15 18:17:17</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
@@ -16489,7 +16489,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>367</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-04-27 16:52:02</t>
+          <t>2026-04-27 16:35:57</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -16518,17 +16518,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>387</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -16538,7 +16538,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-04-28 19:11:23</t>
+          <t>2026-04-27 16:52:02</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
@@ -16547,17 +16547,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>421</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-04-30 14:38:42</t>
+          <t>2026-04-28 19:11:23</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -16576,17 +16576,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>451</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-04-16 12:32:37</t>
+          <t>2026-04-30 14:38:42</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
@@ -16605,17 +16605,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>296</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -16625,7 +16625,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-04-16 12:52:16</t>
+          <t>2026-04-16 12:32:37</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
@@ -16634,17 +16634,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>297</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -16654,7 +16654,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-04-27 16:37:49</t>
+          <t>2026-04-16 12:52:16</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
@@ -16663,17 +16663,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>368</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -16683,7 +16683,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-04-27 16:45:32</t>
+          <t>2026-04-27 16:37:49</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -16692,17 +16692,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>379</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -16712,7 +16712,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-04-27 16:47:40</t>
+          <t>2026-04-27 16:45:32</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
@@ -16721,17 +16721,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>382</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -16741,7 +16741,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-04-16 18:41:52</t>
+          <t>2026-04-27 16:47:40</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
@@ -16750,17 +16750,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>299</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -16770,7 +16770,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-04-23 18:27:22</t>
+          <t>2026-04-16 18:41:52</t>
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
@@ -16779,7 +16779,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>312</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -16799,7 +16799,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-04-23 18:30:25</t>
+          <t>2026-04-23 18:27:22</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
@@ -16808,7 +16808,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>314</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -16828,7 +16828,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-04-27 16:43:45</t>
+          <t>2026-04-23 18:30:25</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
@@ -16837,17 +16837,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>377</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -16857,7 +16857,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-04-23 18:40:56</t>
+          <t>2026-04-27 16:43:45</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
@@ -16866,17 +16866,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>317</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -16886,7 +16886,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-04-21 15:49:30</t>
+          <t>2026-04-23 18:40:56</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
@@ -16895,17 +16895,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -16915,7 +16915,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-04-21 15:52:28</t>
+          <t>2026-04-21 15:49:30</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
@@ -16924,17 +16924,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>301</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -16944,7 +16944,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-04-21 17:03:38</t>
+          <t>2026-04-21 15:52:28</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -16953,17 +16953,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>302</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -16973,7 +16973,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-04-22 16:41:07</t>
+          <t>2026-04-21 17:03:38</t>
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
@@ -16982,17 +16982,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>303</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:41</t>
+          <t>2026-04-22 16:41:07</t>
         </is>
       </c>
       <c r="F174" t="inlineStr"/>
@@ -17011,7 +17011,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>392</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -17031,7 +17031,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-04-28 19:35:07</t>
+          <t>2026-04-27 18:05:41</t>
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
@@ -17040,7 +17040,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>437</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-05-06 17:53:39</t>
+          <t>2026-04-28 19:35:07</t>
         </is>
       </c>
       <c r="F176" t="inlineStr"/>
@@ -17069,7 +17069,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>500</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-05-07 12:25:07</t>
+          <t>2026-05-06 17:53:39</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -17098,17 +17098,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>521</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -17118,7 +17118,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-04-23 15:49:56</t>
+          <t>2026-05-07 12:25:07</t>
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
@@ -17127,17 +17127,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>306</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -17147,7 +17147,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-04-23 18:16:45</t>
+          <t>2026-04-23 15:49:56</t>
         </is>
       </c>
       <c r="F179" t="inlineStr"/>
@@ -17156,7 +17156,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>307</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -17176,7 +17176,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-04-23 18:22:46</t>
+          <t>2026-04-23 18:16:45</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
@@ -17185,7 +17185,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>309</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -17205,7 +17205,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-04-23 18:25:02</t>
+          <t>2026-04-23 18:22:46</t>
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
@@ -17214,7 +17214,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>311</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2026-04-23 18:27:36</t>
+          <t>2026-04-23 18:25:02</t>
         </is>
       </c>
       <c r="F182" t="inlineStr"/>
@@ -17243,7 +17243,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>313</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -17263,7 +17263,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-04-27 18:07:45</t>
+          <t>2026-04-23 18:27:36</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
@@ -17272,7 +17272,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>394</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -17292,7 +17292,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-04-27 18:12:10</t>
+          <t>2026-04-27 18:07:45</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -17301,7 +17301,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>397</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-04-23 18:30:34</t>
+          <t>2026-04-27 18:12:10</t>
         </is>
       </c>
       <c r="F185" t="inlineStr"/>
@@ -17330,17 +17330,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>315</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -17350,7 +17350,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-04-23 18:35:35</t>
+          <t>2026-04-23 18:30:34</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
@@ -17359,17 +17359,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>316</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -17379,7 +17379,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-04-23 18:41:25</t>
+          <t>2026-04-23 18:35:35</t>
         </is>
       </c>
       <c r="F187" t="inlineStr"/>
@@ -17388,17 +17388,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>318</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -17408,7 +17408,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-04-23 18:46:12</t>
+          <t>2026-04-23 18:41:25</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
@@ -17417,17 +17417,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -17437,7 +17437,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-04-23 18:58:17</t>
+          <t>2026-04-23 18:46:12</t>
         </is>
       </c>
       <c r="F189" t="inlineStr"/>
@@ -17446,17 +17446,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>321</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -17466,7 +17466,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2026-04-23 19:09:01</t>
+          <t>2026-04-23 18:58:17</t>
         </is>
       </c>
       <c r="F190" t="inlineStr"/>
@@ -17475,17 +17475,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>322</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -17495,7 +17495,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-04-23 19:28:02</t>
+          <t>2026-04-23 19:09:01</t>
         </is>
       </c>
       <c r="F191" t="inlineStr"/>
@@ -17504,7 +17504,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>323</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -17524,7 +17524,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-04-23 19:33:02</t>
+          <t>2026-04-23 19:28:02</t>
         </is>
       </c>
       <c r="F192" t="inlineStr"/>
@@ -17533,17 +17533,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>324</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -17553,7 +17553,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-04-23 19:35:57</t>
+          <t>2026-04-23 19:33:02</t>
         </is>
       </c>
       <c r="F193" t="inlineStr"/>
@@ -17562,17 +17562,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>325</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -17582,7 +17582,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-04-24 11:52:45</t>
+          <t>2026-04-23 19:35:57</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -17591,17 +17591,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>326</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -17611,7 +17611,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-04-24 11:55:39</t>
+          <t>2026-04-24 11:52:45</t>
         </is>
       </c>
       <c r="F195" t="inlineStr"/>
@@ -17620,17 +17620,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>328</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2026-04-24 12:13:00</t>
+          <t>2026-04-24 11:55:39</t>
         </is>
       </c>
       <c r="F196" t="inlineStr"/>
@@ -17649,7 +17649,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>329</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -17669,7 +17669,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-04-24 12:17:05</t>
+          <t>2026-04-24 12:13:00</t>
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
@@ -17678,17 +17678,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>330</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -17698,7 +17698,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-04-24 12:19:39</t>
+          <t>2026-04-24 12:17:05</t>
         </is>
       </c>
       <c r="F198" t="inlineStr"/>
@@ -17707,17 +17707,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>331</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -17727,7 +17727,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-04-24 12:31:15</t>
+          <t>2026-04-24 12:19:39</t>
         </is>
       </c>
       <c r="F199" t="inlineStr"/>
@@ -17736,17 +17736,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>332</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -17756,7 +17756,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2026-04-24 12:33:01</t>
+          <t>2026-04-24 12:31:15</t>
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
@@ -17765,17 +17765,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>333</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -17785,7 +17785,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-04-24 14:36:24</t>
+          <t>2026-04-24 12:33:01</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -17794,7 +17794,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>334</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -17814,7 +17814,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-04-24 14:43:03</t>
+          <t>2026-04-24 14:36:24</t>
         </is>
       </c>
       <c r="F202" t="inlineStr"/>
@@ -17823,17 +17823,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>335</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -17843,7 +17843,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-04-24 14:58:00</t>
+          <t>2026-04-24 14:43:03</t>
         </is>
       </c>
       <c r="F203" t="inlineStr"/>
@@ -17852,17 +17852,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>336</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -17872,7 +17872,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-04-27 14:06:10</t>
+          <t>2026-04-24 14:58:00</t>
         </is>
       </c>
       <c r="F204" t="inlineStr"/>
@@ -17881,17 +17881,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>337</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -17901,7 +17901,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-04-27 14:10:21</t>
+          <t>2026-04-27 14:06:10</t>
         </is>
       </c>
       <c r="F205" t="inlineStr"/>
@@ -17910,17 +17910,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>338</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -17930,7 +17930,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-04-27 14:13:06</t>
+          <t>2026-04-27 14:10:21</t>
         </is>
       </c>
       <c r="F206" t="inlineStr"/>
@@ -17939,17 +17939,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>339</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -17959,7 +17959,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-04-27 14:15:47</t>
+          <t>2026-04-27 14:13:06</t>
         </is>
       </c>
       <c r="F207" t="inlineStr"/>
@@ -17968,17 +17968,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>340</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -17988,7 +17988,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:51</t>
+          <t>2026-04-27 14:15:47</t>
         </is>
       </c>
       <c r="F208" t="inlineStr"/>
@@ -17997,17 +17997,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>393</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-04-27 18:08:12</t>
+          <t>2026-04-27 18:05:51</t>
         </is>
       </c>
       <c r="F209" t="inlineStr"/>
@@ -18026,17 +18026,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>395</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -18046,7 +18046,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2026-04-27 18:10:09</t>
+          <t>2026-04-27 18:08:12</t>
         </is>
       </c>
       <c r="F210" t="inlineStr"/>
@@ -18055,17 +18055,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>396</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -18075,7 +18075,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-04-27 18:12:49</t>
+          <t>2026-04-27 18:10:09</t>
         </is>
       </c>
       <c r="F211" t="inlineStr"/>
@@ -18084,17 +18084,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>398</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -18104,7 +18104,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-04-27 18:25:23</t>
+          <t>2026-04-27 18:12:49</t>
         </is>
       </c>
       <c r="F212" t="inlineStr"/>
@@ -18113,17 +18113,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>399</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -18133,7 +18133,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-04-27 18:26:29</t>
+          <t>2026-04-27 18:25:23</t>
         </is>
       </c>
       <c r="F213" t="inlineStr"/>
@@ -18142,7 +18142,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>400</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -18162,7 +18162,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-04-27 18:28:56</t>
+          <t>2026-04-27 18:26:29</t>
         </is>
       </c>
       <c r="F214" t="inlineStr"/>
@@ -18171,7 +18171,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>401</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -18191,7 +18191,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-04-27 18:32:14</t>
+          <t>2026-04-27 18:28:56</t>
         </is>
       </c>
       <c r="F215" t="inlineStr"/>
@@ -18200,7 +18200,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>402</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -18220,7 +18220,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-04-27 19:10:16</t>
+          <t>2026-04-27 18:32:14</t>
         </is>
       </c>
       <c r="F216" t="inlineStr"/>
@@ -18229,7 +18229,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>403</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18249,7 +18249,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-04-28 13:06:06</t>
+          <t>2026-04-27 19:10:16</t>
         </is>
       </c>
       <c r="F217" t="inlineStr"/>
@@ -18258,17 +18258,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>404</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-04-28 13:09:10</t>
+          <t>2026-04-28 13:06:06</t>
         </is>
       </c>
       <c r="F218" t="inlineStr"/>
@@ -18287,17 +18287,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>405</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -18307,7 +18307,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-04-28 13:31:57</t>
+          <t>2026-04-28 13:09:10</t>
         </is>
       </c>
       <c r="F219" t="inlineStr"/>
@@ -18316,7 +18316,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>406</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18336,7 +18336,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-04-28 16:36:52</t>
+          <t>2026-04-28 13:31:57</t>
         </is>
       </c>
       <c r="F220" t="inlineStr"/>
@@ -18345,17 +18345,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>408</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -18365,7 +18365,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-04-28 16:41:55</t>
+          <t>2026-04-28 16:36:52</t>
         </is>
       </c>
       <c r="F221" t="inlineStr"/>
@@ -18374,7 +18374,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>409</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18394,7 +18394,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-04-28 16:45:43</t>
+          <t>2026-04-28 16:41:55</t>
         </is>
       </c>
       <c r="F222" t="inlineStr"/>
@@ -18403,17 +18403,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>410</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -18423,7 +18423,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-04-28 16:50:41</t>
+          <t>2026-04-28 16:45:43</t>
         </is>
       </c>
       <c r="F223" t="inlineStr"/>
@@ -18432,17 +18432,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>411</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -18452,7 +18452,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-04-28 16:58:22</t>
+          <t>2026-04-28 16:50:41</t>
         </is>
       </c>
       <c r="F224" t="inlineStr"/>
@@ -18461,17 +18461,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>412</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -18481,7 +18481,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-04-28 19:11:43</t>
+          <t>2026-04-28 16:58:22</t>
         </is>
       </c>
       <c r="F225" t="inlineStr"/>
@@ -18490,17 +18490,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>422</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -18510,7 +18510,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-04-28 19:17:29</t>
+          <t>2026-04-28 19:11:43</t>
         </is>
       </c>
       <c r="F226" t="inlineStr"/>
@@ -18519,17 +18519,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>425</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -18539,7 +18539,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-04-28 19:20:41</t>
+          <t>2026-04-28 19:17:29</t>
         </is>
       </c>
       <c r="F227" t="inlineStr"/>
@@ -18548,7 +18548,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>427</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18568,7 +18568,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-04-28 19:27:32</t>
+          <t>2026-04-28 19:20:41</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
@@ -18577,17 +18577,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>431</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -18597,7 +18597,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-04-28 19:29:59</t>
+          <t>2026-04-28 19:27:32</t>
         </is>
       </c>
       <c r="F229" t="inlineStr"/>
@@ -18606,17 +18606,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>432</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -18626,7 +18626,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-04-28 19:38:54</t>
+          <t>2026-04-28 19:29:59</t>
         </is>
       </c>
       <c r="F230" t="inlineStr"/>
@@ -18635,17 +18635,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>438</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -18655,7 +18655,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-04-28 18:59:52</t>
+          <t>2026-04-28 19:38:54</t>
         </is>
       </c>
       <c r="F231" t="inlineStr"/>
@@ -18664,17 +18664,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>413</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-04-28 19:05:38</t>
+          <t>2026-04-28 18:59:52</t>
         </is>
       </c>
       <c r="F232" t="inlineStr"/>
@@ -18693,7 +18693,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>416</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18713,7 +18713,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-04-28 19:09:07</t>
+          <t>2026-04-28 19:05:38</t>
         </is>
       </c>
       <c r="F233" t="inlineStr"/>
@@ -18722,7 +18722,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>420</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18742,7 +18742,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-04-28 19:22:49</t>
+          <t>2026-04-28 19:09:07</t>
         </is>
       </c>
       <c r="F234" t="inlineStr"/>
@@ -18751,17 +18751,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>429</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -18771,7 +18771,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-04-28 19:46:42</t>
+          <t>2026-04-28 19:22:49</t>
         </is>
       </c>
       <c r="F235" t="inlineStr"/>
@@ -18780,17 +18780,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>439</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -18800,7 +18800,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2026-04-29 15:54:41</t>
+          <t>2026-04-28 19:46:42</t>
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
@@ -18809,7 +18809,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>440</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18829,7 +18829,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-04-29 15:56:41</t>
+          <t>2026-04-29 15:54:41</t>
         </is>
       </c>
       <c r="F237" t="inlineStr"/>
@@ -18838,17 +18838,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>441</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -18858,7 +18858,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-04-29 16:10:35</t>
+          <t>2026-04-29 15:56:41</t>
         </is>
       </c>
       <c r="F238" t="inlineStr"/>
@@ -18867,17 +18867,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>442</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -18887,7 +18887,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-04-29 16:13:57</t>
+          <t>2026-04-29 16:10:35</t>
         </is>
       </c>
       <c r="F239" t="inlineStr"/>
@@ -18896,17 +18896,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>443</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -18916,7 +18916,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-04-29 16:17:13</t>
+          <t>2026-04-29 16:13:57</t>
         </is>
       </c>
       <c r="F240" t="inlineStr"/>
@@ -18925,7 +18925,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>444</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18945,7 +18945,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-04-29 16:21:56</t>
+          <t>2026-04-29 16:17:13</t>
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
@@ -18954,7 +18954,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>445</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-04-29 16:26:19</t>
+          <t>2026-04-29 16:21:56</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
@@ -18983,7 +18983,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>446</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19003,7 +19003,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-04-30 11:56:22</t>
+          <t>2026-04-29 16:26:19</t>
         </is>
       </c>
       <c r="F243" t="inlineStr"/>
@@ -19012,7 +19012,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>447</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-04-30 12:18:39</t>
+          <t>2026-04-30 11:56:22</t>
         </is>
       </c>
       <c r="F244" t="inlineStr"/>
@@ -19041,7 +19041,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>448</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19061,7 +19061,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-04-30 12:27:47</t>
+          <t>2026-04-30 12:18:39</t>
         </is>
       </c>
       <c r="F245" t="inlineStr"/>
@@ -19070,17 +19070,17 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>449</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -19090,7 +19090,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-04-30 14:33:48</t>
+          <t>2026-04-30 12:27:47</t>
         </is>
       </c>
       <c r="F246" t="inlineStr"/>
@@ -19099,17 +19099,17 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>450</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -19119,7 +19119,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-04-30 14:39:11</t>
+          <t>2026-04-30 14:33:48</t>
         </is>
       </c>
       <c r="F247" t="inlineStr"/>
@@ -19128,17 +19128,17 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>452</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -19148,7 +19148,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-04-30 14:44:06</t>
+          <t>2026-04-30 14:39:11</t>
         </is>
       </c>
       <c r="F248" t="inlineStr"/>
@@ -19157,17 +19157,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>453</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -19177,7 +19177,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-04-30 14:50:48</t>
+          <t>2026-04-30 14:44:06</t>
         </is>
       </c>
       <c r="F249" t="inlineStr"/>
@@ -19186,17 +19186,17 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>454</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -19206,7 +19206,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-04-30 15:03:19</t>
+          <t>2026-04-30 14:50:48</t>
         </is>
       </c>
       <c r="F250" t="inlineStr"/>
@@ -19215,7 +19215,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>455</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19235,7 +19235,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-04-30 16:43:14</t>
+          <t>2026-04-30 15:03:19</t>
         </is>
       </c>
       <c r="F251" t="inlineStr"/>
@@ -19244,7 +19244,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>456</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-04-30 16:49:38</t>
+          <t>2026-04-30 16:43:14</t>
         </is>
       </c>
       <c r="F252" t="inlineStr"/>
@@ -19273,17 +19273,17 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>457</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -19293,7 +19293,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-04-30 16:57:13</t>
+          <t>2026-04-30 16:49:38</t>
         </is>
       </c>
       <c r="F253" t="inlineStr"/>
@@ -19302,17 +19302,17 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>458</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -19322,7 +19322,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-04-30 16:59:14</t>
+          <t>2026-04-30 16:57:13</t>
         </is>
       </c>
       <c r="F254" t="inlineStr"/>
@@ -19331,17 +19331,17 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>459</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -19351,7 +19351,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-04-30 17:03:09</t>
+          <t>2026-04-30 16:59:14</t>
         </is>
       </c>
       <c r="F255" t="inlineStr"/>
@@ -19360,7 +19360,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -19380,7 +19380,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2026-04-30 17:07:20</t>
+          <t>2026-04-30 17:03:09</t>
         </is>
       </c>
       <c r="F256" t="inlineStr"/>
@@ -19389,7 +19389,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>461</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -19409,7 +19409,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-04-30 17:20:16</t>
+          <t>2026-04-30 17:07:20</t>
         </is>
       </c>
       <c r="F257" t="inlineStr"/>
@@ -19418,7 +19418,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>462</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -19438,7 +19438,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-05-04 12:40:26</t>
+          <t>2026-04-30 17:20:16</t>
         </is>
       </c>
       <c r="F258" t="inlineStr"/>
@@ -19447,17 +19447,17 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>465</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-05-04 13:27:46</t>
+          <t>2026-05-04 12:40:26</t>
         </is>
       </c>
       <c r="F259" t="inlineStr"/>
@@ -19476,17 +19476,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>466</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -19496,7 +19496,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-05-04 13:32:27</t>
+          <t>2026-05-04 13:27:46</t>
         </is>
       </c>
       <c r="F260" t="inlineStr"/>
@@ -19505,17 +19505,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>467</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -19525,7 +19525,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-05-04 13:35:31</t>
+          <t>2026-05-04 13:32:27</t>
         </is>
       </c>
       <c r="F261" t="inlineStr"/>
@@ -19534,7 +19534,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>468</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -19554,7 +19554,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-05-04 13:52:33</t>
+          <t>2026-05-04 13:35:31</t>
         </is>
       </c>
       <c r="F262" t="inlineStr"/>
@@ -19563,17 +19563,17 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>469</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -19583,7 +19583,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-05-04 14:15:29</t>
+          <t>2026-05-04 13:52:33</t>
         </is>
       </c>
       <c r="F263" t="inlineStr"/>
@@ -19592,7 +19592,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>470</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -19612,7 +19612,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-05-04 14:21:26</t>
+          <t>2026-05-04 14:15:29</t>
         </is>
       </c>
       <c r="F264" t="inlineStr"/>
@@ -19621,7 +19621,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>471</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-05-04 14:28:28</t>
+          <t>2026-05-04 14:21:26</t>
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
@@ -19650,17 +19650,17 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>472</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -19670,7 +19670,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-05-05 12:33:28</t>
+          <t>2026-05-04 14:28:28</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
@@ -19679,17 +19679,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>473</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -19699,7 +19699,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-05-05 12:36:49</t>
+          <t>2026-05-05 12:33:28</t>
         </is>
       </c>
       <c r="F267" t="inlineStr"/>
@@ -19708,17 +19708,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>474</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -19728,7 +19728,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-05-05 13:16:10</t>
+          <t>2026-05-05 12:36:49</t>
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
@@ -19737,7 +19737,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>475</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -19757,7 +19757,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-05-05 13:22:28</t>
+          <t>2026-05-05 13:16:10</t>
         </is>
       </c>
       <c r="F269" t="inlineStr"/>
@@ -19766,7 +19766,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>476</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -19786,7 +19786,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-05-05 15:49:32</t>
+          <t>2026-05-05 13:22:28</t>
         </is>
       </c>
       <c r="F270" t="inlineStr"/>
@@ -19795,7 +19795,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>478</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -19815,7 +19815,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-05-05 18:17:18</t>
+          <t>2026-05-05 15:49:32</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
@@ -19824,17 +19824,17 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>484</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -19844,7 +19844,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-05-05 18:23:24</t>
+          <t>2026-05-05 18:17:18</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
@@ -19853,17 +19853,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>485</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -19873,7 +19873,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-05-05 18:30:18</t>
+          <t>2026-05-05 18:23:24</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
@@ -19882,17 +19882,17 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>486</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -19902,7 +19902,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-05-05 19:24:36</t>
+          <t>2026-05-05 18:30:18</t>
         </is>
       </c>
       <c r="F274" t="inlineStr"/>
@@ -19911,17 +19911,17 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>487</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -19931,7 +19931,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-05-06 14:07:52</t>
+          <t>2026-05-05 19:24:36</t>
         </is>
       </c>
       <c r="F275" t="inlineStr"/>
@@ -19940,17 +19940,17 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>488</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -19960,7 +19960,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-05-06 14:12:50</t>
+          <t>2026-05-06 14:07:52</t>
         </is>
       </c>
       <c r="F276" t="inlineStr"/>
@@ -19969,17 +19969,17 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>489</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -19989,7 +19989,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-05-06 14:15:34</t>
+          <t>2026-05-06 14:12:50</t>
         </is>
       </c>
       <c r="F277" t="inlineStr"/>
@@ -19998,17 +19998,17 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>490</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -20018,7 +20018,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-05-06 14:59:26</t>
+          <t>2026-05-06 14:15:34</t>
         </is>
       </c>
       <c r="F278" t="inlineStr"/>
@@ -20027,17 +20027,17 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -20047,7 +20047,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-05-06 15:04:52</t>
+          <t>2026-05-06 14:59:26</t>
         </is>
       </c>
       <c r="F279" t="inlineStr"/>
@@ -20056,7 +20056,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>492</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -20076,7 +20076,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-05-06 15:08:51</t>
+          <t>2026-05-06 15:04:52</t>
         </is>
       </c>
       <c r="F280" t="inlineStr"/>
@@ -20085,17 +20085,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>493</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Busy</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -20105,7 +20105,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-05-06 15:28:38</t>
+          <t>2026-05-06 15:08:51</t>
         </is>
       </c>
       <c r="F281" t="inlineStr"/>
@@ -20114,17 +20114,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>494</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Busy</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -20134,7 +20134,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-05-06 15:31:36</t>
+          <t>2026-05-06 15:28:38</t>
         </is>
       </c>
       <c r="F282" t="inlineStr"/>
@@ -20143,17 +20143,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>495</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -20163,7 +20163,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-05-06 17:53:50</t>
+          <t>2026-05-06 15:31:36</t>
         </is>
       </c>
       <c r="F283" t="inlineStr"/>
@@ -20172,7 +20172,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>501</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -20192,7 +20192,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-05-06 17:59:31</t>
+          <t>2026-05-06 17:53:50</t>
         </is>
       </c>
       <c r="F284" t="inlineStr"/>
@@ -20201,17 +20201,17 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>502</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -20221,7 +20221,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-05-06 19:18:14</t>
+          <t>2026-05-06 17:59:31</t>
         </is>
       </c>
       <c r="F285" t="inlineStr"/>
@@ -20230,17 +20230,17 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>503</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -20250,7 +20250,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-05-06 19:21:01</t>
+          <t>2026-05-06 19:18:14</t>
         </is>
       </c>
       <c r="F286" t="inlineStr"/>
@@ -20259,7 +20259,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>504</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -20279,7 +20279,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-05-06 19:25:27</t>
+          <t>2026-05-06 19:21:01</t>
         </is>
       </c>
       <c r="F287" t="inlineStr"/>
@@ -20288,7 +20288,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>505</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -20308,7 +20308,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>2026-05-06 19:27:23</t>
+          <t>2026-05-06 19:25:27</t>
         </is>
       </c>
       <c r="F288" t="inlineStr"/>
@@ -20317,17 +20317,17 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>506</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -20337,7 +20337,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-05-06 19:39:21</t>
+          <t>2026-05-06 19:27:23</t>
         </is>
       </c>
       <c r="F289" t="inlineStr"/>
@@ -20346,17 +20346,17 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>507</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -20366,7 +20366,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-05-06 20:09:52</t>
+          <t>2026-05-06 19:39:21</t>
         </is>
       </c>
       <c r="F290" t="inlineStr"/>
@@ -20375,17 +20375,17 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>509</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -20395,7 +20395,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-05-06 20:12:28</t>
+          <t>2026-05-06 20:09:52</t>
         </is>
       </c>
       <c r="F291" t="inlineStr"/>
@@ -20404,7 +20404,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>511</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -20424,7 +20424,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-05-07 12:02:27</t>
+          <t>2026-05-06 20:12:28</t>
         </is>
       </c>
       <c r="F292" t="inlineStr"/>
@@ -20433,17 +20433,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>512</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-05-07 12:05:31</t>
+          <t>2026-05-07 12:02:27</t>
         </is>
       </c>
       <c r="F293" t="inlineStr"/>
@@ -20462,17 +20462,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>513</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -20482,7 +20482,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2026-05-07 12:07:46</t>
+          <t>2026-05-07 12:05:31</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
@@ -20491,17 +20491,17 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>514</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -20511,7 +20511,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-05-07 12:12:23</t>
+          <t>2026-05-07 12:07:46</t>
         </is>
       </c>
       <c r="F295" t="inlineStr"/>
@@ -20520,17 +20520,17 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>515</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -20540,7 +20540,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-05-07 12:21:17</t>
+          <t>2026-05-07 12:12:23</t>
         </is>
       </c>
       <c r="F296" t="inlineStr"/>
@@ -20549,7 +20549,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>516</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -20569,7 +20569,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-05-07 12:22:26</t>
+          <t>2026-05-07 12:21:17</t>
         </is>
       </c>
       <c r="F297" t="inlineStr"/>
@@ -20578,7 +20578,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>517</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -20598,7 +20598,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-05-07 12:25:15</t>
+          <t>2026-05-07 12:22:26</t>
         </is>
       </c>
       <c r="F298" t="inlineStr"/>
@@ -20607,7 +20607,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>522</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -20627,7 +20627,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-05-07 12:30:09</t>
+          <t>2026-05-07 12:25:15</t>
         </is>
       </c>
       <c r="F299" t="inlineStr"/>
@@ -20636,7 +20636,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>524</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -20656,7 +20656,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-05-07 18:11:26</t>
+          <t>2026-05-07 12:30:09</t>
         </is>
       </c>
       <c r="F300" t="inlineStr"/>
@@ -20665,17 +20665,17 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>527</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -20685,7 +20685,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-05-07 18:21:05</t>
+          <t>2026-05-07 18:11:26</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
@@ -20694,17 +20694,17 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>528</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -20714,7 +20714,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-05-07 18:23:27</t>
+          <t>2026-05-07 18:21:05</t>
         </is>
       </c>
       <c r="F302" t="inlineStr"/>
@@ -20723,17 +20723,17 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>529</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -20743,7 +20743,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-05-07 18:31:47</t>
+          <t>2026-05-07 18:23:27</t>
         </is>
       </c>
       <c r="F303" t="inlineStr"/>
@@ -20752,17 +20752,17 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>530</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -20772,7 +20772,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-05-07 18:41:02</t>
+          <t>2026-05-07 18:31:47</t>
         </is>
       </c>
       <c r="F304" t="inlineStr"/>
@@ -20781,17 +20781,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>531</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -20801,7 +20801,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-05-07 19:04:03</t>
+          <t>2026-05-07 18:41:02</t>
         </is>
       </c>
       <c r="F305" t="inlineStr"/>
@@ -20810,17 +20810,17 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>532</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -20830,7 +20830,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-05-07 19:12:07</t>
+          <t>2026-05-07 19:04:03</t>
         </is>
       </c>
       <c r="F306" t="inlineStr"/>
@@ -20839,17 +20839,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>533</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -20859,7 +20859,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-05-07 19:19:47</t>
+          <t>2026-05-07 19:12:07</t>
         </is>
       </c>
       <c r="F307" t="inlineStr"/>
@@ -20868,7 +20868,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>534</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -20888,7 +20888,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-05-07 19:35:25</t>
+          <t>2026-05-07 19:19:47</t>
         </is>
       </c>
       <c r="F308" t="inlineStr"/>
@@ -20897,7 +20897,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>535</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -20917,7 +20917,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-05-08 12:36:57</t>
+          <t>2026-05-07 19:35:25</t>
         </is>
       </c>
       <c r="F309" t="inlineStr"/>
@@ -20926,7 +20926,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>536</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -20946,7 +20946,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-05-08 12:43:59</t>
+          <t>2026-05-08 12:36:57</t>
         </is>
       </c>
       <c r="F310" t="inlineStr"/>
@@ -20955,17 +20955,17 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>537</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -20975,7 +20975,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-05-08 12:51:09</t>
+          <t>2026-05-08 12:43:59</t>
         </is>
       </c>
       <c r="F311" t="inlineStr"/>
@@ -20984,17 +20984,17 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>538</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -21004,7 +21004,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-05-08 12:55:15</t>
+          <t>2026-05-08 12:51:09</t>
         </is>
       </c>
       <c r="F312" t="inlineStr"/>
@@ -21013,7 +21013,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>539</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -21033,7 +21033,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-05-08 12:57:14</t>
+          <t>2026-05-08 12:55:15</t>
         </is>
       </c>
       <c r="F313" t="inlineStr"/>
@@ -21042,7 +21042,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>540</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -21062,7 +21062,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-05-08 13:00:41</t>
+          <t>2026-05-08 12:57:14</t>
         </is>
       </c>
       <c r="F314" t="inlineStr"/>
@@ -21071,17 +21071,17 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>541</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2026-05-08 13:04:02</t>
+          <t>2026-05-08 13:00:41</t>
         </is>
       </c>
       <c r="F315" t="inlineStr"/>
@@ -21100,17 +21100,17 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>542</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -21120,7 +21120,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-05-08 13:09:59</t>
+          <t>2026-05-08 13:04:02</t>
         </is>
       </c>
       <c r="F316" t="inlineStr"/>
@@ -21129,17 +21129,17 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>543</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>WARM LEAD</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>warm_lead</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -21149,7 +21149,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-05-08 13:16:49</t>
+          <t>2026-05-08 13:09:59</t>
         </is>
       </c>
       <c r="F317" t="inlineStr"/>
@@ -21158,17 +21158,17 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>544</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>WARM LEAD</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>warm_lead</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -21178,7 +21178,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-05-08 13:22:02</t>
+          <t>2026-05-08 13:16:49</t>
         </is>
       </c>
       <c r="F318" t="inlineStr"/>
@@ -21187,7 +21187,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>545</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -21207,7 +21207,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-05-08 15:50:51</t>
+          <t>2026-05-08 13:22:02</t>
         </is>
       </c>
       <c r="F319" t="inlineStr"/>
@@ -21216,17 +21216,17 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>546</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -21236,7 +21236,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-05-08 15:54:37</t>
+          <t>2026-05-08 15:50:51</t>
         </is>
       </c>
       <c r="F320" t="inlineStr"/>
@@ -21245,17 +21245,17 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>547</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -21265,7 +21265,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-05-08 15:59:34</t>
+          <t>2026-05-08 15:54:37</t>
         </is>
       </c>
       <c r="F321" t="inlineStr"/>
@@ -21274,7 +21274,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>548</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-05-08 16:11:07</t>
+          <t>2026-05-08 15:59:34</t>
         </is>
       </c>
       <c r="F322" t="inlineStr"/>
@@ -21303,17 +21303,17 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>549</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -21323,7 +21323,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-05-08 16:19:50</t>
+          <t>2026-05-08 16:11:07</t>
         </is>
       </c>
       <c r="F323" t="inlineStr"/>
@@ -21332,17 +21332,17 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>550</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -21352,11 +21352,40 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-05-08 16:24:03</t>
+          <t>2026-05-08 16:19:50</t>
         </is>
       </c>
       <c r="F324" t="inlineStr"/>
       <c r="G324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>2026-05-08 16:24:03</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr"/>
+      <c r="G325" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H276"/>
+  <dimension ref="A1:H279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>dwinslow@custominsulation.com</t>
+          <t>nbrodeur@custominsulation.com</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>(617) 839-7274</t>
+          <t>(774) 366-5225</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-05-11 18:35:26</t>
+          <t>2026-05-12 12:09:08</t>
         </is>
       </c>
     </row>
@@ -10508,7 +10508,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>2026-04-29 16:17:13</t>
+          <t>2026-05-12 12:12:48</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>2026-04-29 16:21:56</t>
+          <t>2026-05-12 12:22:04</t>
         </is>
       </c>
     </row>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>2026-05-04 12:40:26</t>
+          <t>2026-05-12 12:23:33</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>2026-05-04 13:27:46</t>
+          <t>2026-05-12 12:26:05</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>2026-05-05 13:16:10</t>
+          <t>2026-05-12 12:31:00</t>
         </is>
       </c>
     </row>
@@ -11432,7 +11432,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>2026-05-06 14:07:52</t>
+          <t>2026-05-12 12:33:59</t>
         </is>
       </c>
     </row>
@@ -11516,7 +11516,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>2026-05-06 14:15:34</t>
+          <t>2026-05-12 12:37:48</t>
         </is>
       </c>
     </row>
@@ -11937,6 +11937,132 @@
       <c r="H276" t="inlineStr">
         <is>
           <t>2026-05-08 16:24:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>DANTE VOLPE SR</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>danv@volpededicated.com</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>(610) 630-0700</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Volpededicated</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>2026-05-12 12:18:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>JOSEPH SPAUSE</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>jspause@danella.com</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>610) 828-6200</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Danella</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>2026-05-12 12:48:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>BENJAMIN MCLEAN</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>bmclean@ruan.com</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>(800) 678-3210</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Ruan</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>2026-05-12 12:51:08</t>
         </is>
       </c>
     </row>
@@ -11951,7 +12077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G325"/>
+  <dimension ref="A1:G335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21386,6 +21512,296 @@
       </c>
       <c r="F325" t="inlineStr"/>
       <c r="G325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>553</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>2026-05-12 12:12:48</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr"/>
+      <c r="G326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>2026-05-12 12:18:21</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr"/>
+      <c r="G327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>NO ANSWER</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>no_answer</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>2026-05-12 12:22:04</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>556</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Call disconnected</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>hung_up</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>2026-05-12 12:23:33</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>2026-05-12 12:26:05</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr"/>
+      <c r="G330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>2026-05-12 12:31:00</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr"/>
+      <c r="G331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>2026-05-12 12:33:59</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr"/>
+      <c r="G332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>2026-05-12 12:37:48</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr"/>
+      <c r="G333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>561</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>2026-05-12 12:48:40</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr"/>
+      <c r="G334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>2026-05-12 12:51:08</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr"/>
+      <c r="G335" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21398,7 +21814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21849,6 +22265,50 @@
       </c>
       <c r="J10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2a63ce30-4dfb-11f1-81fb-c748a87a03f2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Custominsulation</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Manually created</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-05-12T12:07:36.851Z</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>NICHOLAS BRODEUR</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Custominsulation</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H279"/>
+  <dimension ref="A1:H287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-04-28 19:20:41</t>
+          <t>2026-05-12 19:41:52</t>
         </is>
       </c>
     </row>
@@ -12063,6 +12063,342 @@
       <c r="H279" t="inlineStr">
         <is>
           <t>2026-05-12 12:51:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>CYNTHIA KLINE</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>ckline3568@comcast.net</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>(413) 596-3568</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OJS LANDSCAPE EXCAVATION INC</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>2026-05-12 18:19:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>John Papazoros</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>jpapazoros@iberiafood.com</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (413) 289-9809</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Iberiafood</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>2026-05-12 18:22:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>FAWAZ EL KHOURY</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>cmrk@cmrkne.com</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(508) 351-9000 </t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Cmrkne</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>2026-05-12 18:26:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Paul Bunn</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>pbunn@covenantlogistics.com</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>(423) 463-3473</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Covenantlogistics</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>2026-05-12 18:29:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Chris Ceausu</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>cceausu@whitearrow.com</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(800) 501-5589 </t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>White arrow</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>2026-05-12 18:38:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>JOHN FINDLEY</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>john@redlinefreightsystems.com</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>(781) 815-1028</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Redlinefreightsystems</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>2026-05-12 18:47:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>CHRISTOPHER DEVILLERS</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>chris@northerndrillservice.com</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(508) 393-6900 </t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Northerndrillservice</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>2026-05-12 18:54:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>ELMIRA KUTLAMBETOVA</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>impulselogisticsgroupinc@gmail.com</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(508) 981-7272 </t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>IMPULSE LOGISTICS GROUP INC</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>2026-05-12 19:03:54</t>
         </is>
       </c>
     </row>
@@ -12077,7 +12413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G335"/>
+  <dimension ref="A1:G343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21802,6 +22138,238 @@
       </c>
       <c r="F335" t="inlineStr"/>
       <c r="G335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>2026-05-12 18:19:14</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr"/>
+      <c r="G336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>2026-05-12 18:26:39</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr"/>
+      <c r="G337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>2026-05-12 18:29:28</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr"/>
+      <c r="G338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>2026-05-12 18:38:29</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr"/>
+      <c r="G339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>2026-05-12 18:47:34</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr"/>
+      <c r="G340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>2026-05-12 18:54:06</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr"/>
+      <c r="G341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>2026-05-12 19:03:54</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr"/>
+      <c r="G342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>2026-05-12 19:41:52</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr"/>
+      <c r="G343" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -5342,7 +5342,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-03-25 18:32:05</t>
+          <t>2026-05-13 12:23:52</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-05-08 13:22:02</t>
+          <t>2026-05-13 12:09:27</t>
         </is>
       </c>
     </row>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Meeting Booked</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-03-30 16:52:26</t>
+          <t>2026-05-13 12:20:22</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-03-30 17:02:38</t>
+          <t>2026-05-13 12:25:53</t>
         </is>
       </c>
     </row>
@@ -7400,7 +7400,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-04-08 18:06:17</t>
+          <t>2026-05-13 12:28:23</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-04-08 18:09:17</t>
+          <t>2026-05-13 12:32:52</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-04-30 17:20:16</t>
+          <t>2026-05-13 12:40:54</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-04-08 18:32:02</t>
+          <t>2026-05-13 12:43:27</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-04-23 11:55:47</t>
+          <t>2026-05-13 12:45:51</t>
         </is>
       </c>
     </row>
@@ -12413,7 +12413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G343"/>
+  <dimension ref="A1:G355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14892,17 +14892,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>578</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14912,7 +14912,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-03-31 13:50:49</t>
+          <t>2026-05-13 12:25:53</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -14921,17 +14921,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>245</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14941,7 +14941,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-03-31 13:57:09</t>
+          <t>2026-03-31 13:50:49</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
@@ -14950,17 +14950,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>246</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-03-31 14:01:39</t>
+          <t>2026-03-31 13:57:09</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
@@ -14979,17 +14979,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>247</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-03-31 14:09:41</t>
+          <t>2026-03-31 14:01:39</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
@@ -15008,7 +15008,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>248</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -15028,7 +15028,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-03-31 19:13:49</t>
+          <t>2026-03-31 14:09:41</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -15037,17 +15037,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>249</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-04-27 16:17:22</t>
+          <t>2026-03-31 19:13:49</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -15066,17 +15066,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>341</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-04-27 16:22:28</t>
+          <t>2026-04-27 16:17:22</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -15095,17 +15095,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>347</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15115,7 +15115,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-04-27 16:23:48</t>
+          <t>2026-04-27 16:22:28</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -15124,7 +15124,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>349</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -15144,7 +15144,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-04-27 16:26:16</t>
+          <t>2026-04-27 16:23:48</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
@@ -15153,7 +15153,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>352</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -15173,7 +15173,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-04-27 16:32:05</t>
+          <t>2026-04-27 16:26:16</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -15182,7 +15182,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -15202,7 +15202,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-04-27 16:33:04</t>
+          <t>2026-04-27 16:32:05</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -15211,7 +15211,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>361</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -15231,7 +15231,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-04-27 16:34:57</t>
+          <t>2026-04-27 16:33:04</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -15240,7 +15240,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>364</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:15</t>
+          <t>2026-04-27 16:34:57</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
@@ -15269,7 +15269,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>390</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-04-28 19:05:25</t>
+          <t>2026-04-27 18:05:15</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
@@ -15298,7 +15298,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>415</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -15318,7 +15318,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-04-28 19:06:58</t>
+          <t>2026-04-28 19:05:25</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -15327,17 +15327,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>418</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-04-28 19:16:34</t>
+          <t>2026-04-28 19:06:58</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
@@ -15356,17 +15356,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>423</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-04-28 19:34:42</t>
+          <t>2026-04-28 19:16:34</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -15385,17 +15385,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>435</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -15405,7 +15405,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-03-31 19:22:45</t>
+          <t>2026-04-28 19:34:42</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -15414,7 +15414,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>250</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -15424,7 +15424,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>follow_up</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -15434,7 +15434,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-03-31 19:37:10</t>
+          <t>2026-03-31 19:22:45</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -15443,17 +15443,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>251</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-04-01 14:30:00</t>
+          <t>2026-03-31 19:37:10</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -15472,7 +15472,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>252</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-04-01 16:53:36</t>
+          <t>2026-04-01 14:30:00</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -15501,17 +15501,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>253</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -15521,7 +15521,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-05-07 12:22:45</t>
+          <t>2026-04-01 16:53:36</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
@@ -15530,7 +15530,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>518</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-05-07 12:24:53</t>
+          <t>2026-05-07 12:22:45</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
@@ -15559,7 +15559,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>520</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -15579,7 +15579,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-05-07 12:30:02</t>
+          <t>2026-05-07 12:24:53</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
@@ -15588,17 +15588,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>523</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -15608,7 +15608,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-04-07 15:24:02</t>
+          <t>2026-05-07 12:30:02</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
@@ -15617,17 +15617,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>271</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15637,7 +15637,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-04-07 16:00:48</t>
+          <t>2026-04-07 15:24:02</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
@@ -15646,17 +15646,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>272</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -15666,7 +15666,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-04-24 11:55:32</t>
+          <t>2026-04-07 16:00:48</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
@@ -15675,7 +15675,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>327</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -15695,7 +15695,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-04-27 16:17:36</t>
+          <t>2026-04-24 11:55:32</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
@@ -15704,7 +15704,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>342</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -15724,7 +15724,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-04-27 16:20:52</t>
+          <t>2026-04-27 16:17:36</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -15733,7 +15733,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>345</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -15753,7 +15753,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-04-27 16:22:53</t>
+          <t>2026-04-27 16:20:52</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
@@ -15762,7 +15762,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>348</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -15782,7 +15782,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-04-27 16:24:00</t>
+          <t>2026-04-27 16:22:53</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
@@ -15791,7 +15791,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>350</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -15811,7 +15811,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-04-27 16:27:53</t>
+          <t>2026-04-27 16:24:00</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
@@ -15820,17 +15820,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>353</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15840,7 +15840,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-04-08 16:38:00</t>
+          <t>2026-04-27 16:27:53</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
@@ -15849,17 +15849,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>274</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15869,7 +15869,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-04-08 18:21:03</t>
+          <t>2026-04-08 16:38:00</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
@@ -15878,7 +15878,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>275</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -15898,7 +15898,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-04-23 18:22:34</t>
+          <t>2026-04-08 18:21:03</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
@@ -15907,7 +15907,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>308</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -15927,7 +15927,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-04-23 18:24:52</t>
+          <t>2026-04-23 18:22:34</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
@@ -15936,7 +15936,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>310</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -15956,7 +15956,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-04-27 16:43:32</t>
+          <t>2026-04-23 18:24:52</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
@@ -15965,17 +15965,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>376</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-04-27 16:44:32</t>
+          <t>2026-04-27 16:43:32</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
@@ -15994,17 +15994,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>378</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16014,7 +16014,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-04-27 16:47:27</t>
+          <t>2026-04-27 16:44:32</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
@@ -16023,7 +16023,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>381</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-04-27 16:48:30</t>
+          <t>2026-04-27 16:47:27</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -16052,17 +16052,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>383</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16072,7 +16072,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-04-27 16:49:41</t>
+          <t>2026-04-27 16:48:30</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -16081,17 +16081,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>384</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16101,7 +16101,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-04-27 16:51:50</t>
+          <t>2026-04-27 16:49:41</t>
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
@@ -16110,7 +16110,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>386</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -16130,7 +16130,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-04-28 19:34:54</t>
+          <t>2026-04-27 16:51:50</t>
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
@@ -16139,17 +16139,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>436</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -16159,7 +16159,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-04-09 14:38:33</t>
+          <t>2026-04-28 19:34:54</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -16168,17 +16168,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>579</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-04-09 14:50:24</t>
+          <t>2026-05-13 12:28:13</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
@@ -16197,7 +16197,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>581</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -16217,7 +16217,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-04-27 16:17:54</t>
+          <t>2026-05-13 12:32:44</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -16226,17 +16226,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>276</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16246,7 +16246,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-04-27 16:19:16</t>
+          <t>2026-04-09 14:38:33</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
@@ -16255,17 +16255,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>277</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16275,7 +16275,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-04-27 16:21:26</t>
+          <t>2026-04-09 14:50:24</t>
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
@@ -16284,17 +16284,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>343</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-04-27 16:30:33</t>
+          <t>2026-04-27 16:17:54</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
@@ -16313,17 +16313,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>344</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>email</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16333,7 +16333,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-04-27 16:34:07</t>
+          <t>2026-04-27 16:19:16</t>
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
@@ -16342,17 +16342,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>346</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16362,7 +16362,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-04-27 16:35:11</t>
+          <t>2026-04-27 16:21:26</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
@@ -16371,17 +16371,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>357</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:29</t>
+          <t>2026-04-27 16:30:33</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
@@ -16400,17 +16400,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>362</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16420,7 +16420,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-04-28 19:20:18</t>
+          <t>2026-04-27 16:34:07</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
@@ -16429,7 +16429,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>365</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -16449,7 +16449,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-04-28 19:22:33</t>
+          <t>2026-04-27 16:35:11</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -16458,7 +16458,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>391</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -16478,7 +16478,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-04-28 19:27:09</t>
+          <t>2026-04-27 18:05:29</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -16487,17 +16487,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>426</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -16507,7 +16507,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-04-13 15:45:27</t>
+          <t>2026-04-28 19:20:18</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
@@ -16516,17 +16516,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>428</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -16536,7 +16536,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-04-13 15:46:25</t>
+          <t>2026-04-28 19:22:33</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
@@ -16545,17 +16545,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>430</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -16565,7 +16565,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-04-13 15:53:15</t>
+          <t>2026-04-28 19:27:09</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
@@ -16574,17 +16574,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>286</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -16594,7 +16594,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-04-13 15:58:50</t>
+          <t>2026-04-13 15:45:27</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
@@ -16603,17 +16603,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>287</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -16623,7 +16623,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-04-27 16:24:24</t>
+          <t>2026-04-13 15:46:25</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
@@ -16632,17 +16632,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>288</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -16652,7 +16652,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-04-27 16:28:22</t>
+          <t>2026-04-13 15:53:15</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
@@ -16661,17 +16661,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>289</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -16681,7 +16681,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-04-27 16:35:40</t>
+          <t>2026-04-13 15:58:50</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
@@ -16690,17 +16690,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>351</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-04-28 19:07:14</t>
+          <t>2026-04-27 16:24:24</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
@@ -16719,17 +16719,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>354</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -16739,7 +16739,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-04-28 19:16:45</t>
+          <t>2026-04-27 16:28:22</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
@@ -16748,17 +16748,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>366</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -16768,7 +16768,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-04-27 16:29:25</t>
+          <t>2026-04-27 16:35:40</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
@@ -16777,17 +16777,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>419</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -16797,7 +16797,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-04-27 16:31:00</t>
+          <t>2026-04-28 19:07:14</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
@@ -16806,7 +16806,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>424</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -16826,7 +16826,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-04-27 16:39:21</t>
+          <t>2026-04-28 19:16:45</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
@@ -16835,17 +16835,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>356</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -16855,7 +16855,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-04-27 16:40:26</t>
+          <t>2026-04-27 16:29:25</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -16864,17 +16864,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>358</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-04-27 16:42:47</t>
+          <t>2026-04-27 16:31:00</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -16893,17 +16893,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>371</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -16913,7 +16913,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-04-15 16:05:12</t>
+          <t>2026-04-27 16:39:21</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -16922,17 +16922,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>373</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -16942,7 +16942,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-04-15 18:17:17</t>
+          <t>2026-04-27 16:40:26</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
@@ -16951,7 +16951,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>374</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -16971,7 +16971,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-04-27 16:35:57</t>
+          <t>2026-04-27 16:42:47</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -16980,17 +16980,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>294</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-04-27 16:52:02</t>
+          <t>2026-04-15 16:05:12</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
@@ -17009,17 +17009,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>295</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -17029,7 +17029,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-04-28 19:11:23</t>
+          <t>2026-04-15 18:17:17</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -17038,17 +17038,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>367</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -17058,7 +17058,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-04-30 14:38:42</t>
+          <t>2026-04-27 16:35:57</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
@@ -17067,17 +17067,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>387</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -17087,7 +17087,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-04-16 12:32:37</t>
+          <t>2026-04-27 16:52:02</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
@@ -17096,17 +17096,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>421</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -17116,7 +17116,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-04-16 12:52:16</t>
+          <t>2026-04-28 19:11:23</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
@@ -17125,17 +17125,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>451</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-04-27 16:37:49</t>
+          <t>2026-04-30 14:38:42</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -17154,7 +17154,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>296</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -17174,7 +17174,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-04-27 16:45:32</t>
+          <t>2026-04-16 12:32:37</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
@@ -17183,17 +17183,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>297</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-04-27 16:47:40</t>
+          <t>2026-04-16 12:52:16</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
@@ -17212,17 +17212,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>368</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -17232,7 +17232,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-04-16 18:41:52</t>
+          <t>2026-04-27 16:37:49</t>
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
@@ -17241,17 +17241,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>379</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -17261,7 +17261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-04-23 18:27:22</t>
+          <t>2026-04-27 16:45:32</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
@@ -17270,7 +17270,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>382</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -17290,7 +17290,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-04-23 18:30:25</t>
+          <t>2026-04-27 16:47:40</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
@@ -17299,17 +17299,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>299</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-04-27 16:43:45</t>
+          <t>2026-04-16 18:41:52</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
@@ -17328,17 +17328,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>312</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -17348,7 +17348,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-04-23 18:40:56</t>
+          <t>2026-04-23 18:27:22</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
@@ -17357,17 +17357,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>314</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -17377,7 +17377,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-04-21 15:49:30</t>
+          <t>2026-04-23 18:30:25</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
@@ -17386,17 +17386,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>377</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -17406,7 +17406,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-04-21 15:52:28</t>
+          <t>2026-04-27 16:43:45</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -17415,17 +17415,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>317</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -17435,7 +17435,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-04-21 17:03:38</t>
+          <t>2026-04-23 18:40:56</t>
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
@@ -17444,17 +17444,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -17464,7 +17464,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-04-22 16:41:07</t>
+          <t>2026-04-21 15:49:30</t>
         </is>
       </c>
       <c r="F174" t="inlineStr"/>
@@ -17473,17 +17473,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>301</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -17493,7 +17493,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:41</t>
+          <t>2026-04-21 15:52:28</t>
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
@@ -17502,17 +17502,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>302</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -17522,7 +17522,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-04-28 19:35:07</t>
+          <t>2026-04-21 17:03:38</t>
         </is>
       </c>
       <c r="F176" t="inlineStr"/>
@@ -17531,17 +17531,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>303</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -17551,7 +17551,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-05-06 17:53:39</t>
+          <t>2026-04-22 16:41:07</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -17560,7 +17560,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>392</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -17580,7 +17580,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-05-07 12:25:07</t>
+          <t>2026-04-27 18:05:41</t>
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
@@ -17589,17 +17589,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>437</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -17609,7 +17609,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-04-23 15:49:56</t>
+          <t>2026-04-28 19:35:07</t>
         </is>
       </c>
       <c r="F179" t="inlineStr"/>
@@ -17618,7 +17618,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>500</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -17638,7 +17638,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-04-23 18:16:45</t>
+          <t>2026-05-06 17:53:39</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
@@ -17647,7 +17647,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>521</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -17667,7 +17667,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-04-23 18:22:46</t>
+          <t>2026-05-07 12:25:07</t>
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
@@ -17676,17 +17676,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>306</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -17696,7 +17696,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2026-04-23 18:25:02</t>
+          <t>2026-04-23 15:49:56</t>
         </is>
       </c>
       <c r="F182" t="inlineStr"/>
@@ -17705,7 +17705,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>307</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -17725,7 +17725,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-04-23 18:27:36</t>
+          <t>2026-04-23 18:16:45</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
@@ -17734,7 +17734,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>309</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -17754,7 +17754,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-04-27 18:07:45</t>
+          <t>2026-04-23 18:22:46</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -17763,7 +17763,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>311</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -17783,7 +17783,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-04-27 18:12:10</t>
+          <t>2026-04-23 18:25:02</t>
         </is>
       </c>
       <c r="F185" t="inlineStr"/>
@@ -17792,7 +17792,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>313</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -17812,7 +17812,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-04-23 18:30:34</t>
+          <t>2026-04-23 18:27:36</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
@@ -17821,17 +17821,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>394</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -17841,7 +17841,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-04-23 18:35:35</t>
+          <t>2026-04-27 18:07:45</t>
         </is>
       </c>
       <c r="F187" t="inlineStr"/>
@@ -17850,17 +17850,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>397</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -17870,7 +17870,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-04-23 18:41:25</t>
+          <t>2026-04-27 18:12:10</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
@@ -17879,7 +17879,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>315</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -17899,7 +17899,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-04-23 18:46:12</t>
+          <t>2026-04-23 18:30:34</t>
         </is>
       </c>
       <c r="F189" t="inlineStr"/>
@@ -17908,17 +17908,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>316</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -17928,7 +17928,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2026-04-23 18:58:17</t>
+          <t>2026-04-23 18:35:35</t>
         </is>
       </c>
       <c r="F190" t="inlineStr"/>
@@ -17937,17 +17937,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>318</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -17957,7 +17957,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-04-23 19:09:01</t>
+          <t>2026-04-23 18:41:25</t>
         </is>
       </c>
       <c r="F191" t="inlineStr"/>
@@ -17966,7 +17966,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -17986,7 +17986,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-04-23 19:28:02</t>
+          <t>2026-04-23 18:46:12</t>
         </is>
       </c>
       <c r="F192" t="inlineStr"/>
@@ -17995,17 +17995,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>321</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -18015,7 +18015,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-04-23 19:33:02</t>
+          <t>2026-04-23 18:58:17</t>
         </is>
       </c>
       <c r="F193" t="inlineStr"/>
@@ -18024,17 +18024,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>322</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -18044,7 +18044,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-04-23 19:35:57</t>
+          <t>2026-04-23 19:09:01</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -18053,17 +18053,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>323</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -18073,7 +18073,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-04-24 11:52:45</t>
+          <t>2026-04-23 19:28:02</t>
         </is>
       </c>
       <c r="F195" t="inlineStr"/>
@@ -18082,7 +18082,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>324</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -18102,7 +18102,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2026-04-24 11:55:39</t>
+          <t>2026-04-23 19:33:02</t>
         </is>
       </c>
       <c r="F196" t="inlineStr"/>
@@ -18111,17 +18111,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>325</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-04-24 12:13:00</t>
+          <t>2026-04-23 19:35:57</t>
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
@@ -18140,7 +18140,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>326</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -18160,7 +18160,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-04-24 12:17:05</t>
+          <t>2026-04-24 11:52:45</t>
         </is>
       </c>
       <c r="F198" t="inlineStr"/>
@@ -18169,7 +18169,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>328</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -18189,7 +18189,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-04-24 12:19:39</t>
+          <t>2026-04-24 11:55:39</t>
         </is>
       </c>
       <c r="F199" t="inlineStr"/>
@@ -18198,17 +18198,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>329</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -18218,7 +18218,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2026-04-24 12:31:15</t>
+          <t>2026-04-24 12:13:00</t>
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
@@ -18227,17 +18227,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>330</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -18247,7 +18247,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-04-24 12:33:01</t>
+          <t>2026-04-24 12:17:05</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -18256,17 +18256,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>331</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -18276,7 +18276,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-04-24 14:36:24</t>
+          <t>2026-04-24 12:19:39</t>
         </is>
       </c>
       <c r="F202" t="inlineStr"/>
@@ -18285,17 +18285,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>332</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -18305,7 +18305,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-04-24 14:43:03</t>
+          <t>2026-04-24 12:31:15</t>
         </is>
       </c>
       <c r="F203" t="inlineStr"/>
@@ -18314,7 +18314,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>333</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -18334,7 +18334,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-04-24 14:58:00</t>
+          <t>2026-04-24 12:33:01</t>
         </is>
       </c>
       <c r="F204" t="inlineStr"/>
@@ -18343,17 +18343,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>334</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-04-27 14:06:10</t>
+          <t>2026-04-24 14:36:24</t>
         </is>
       </c>
       <c r="F205" t="inlineStr"/>
@@ -18372,17 +18372,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>335</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -18392,7 +18392,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-04-27 14:10:21</t>
+          <t>2026-04-24 14:43:03</t>
         </is>
       </c>
       <c r="F206" t="inlineStr"/>
@@ -18401,17 +18401,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>336</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -18421,7 +18421,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-04-27 14:13:06</t>
+          <t>2026-04-24 14:58:00</t>
         </is>
       </c>
       <c r="F207" t="inlineStr"/>
@@ -18430,7 +18430,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>337</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -18450,7 +18450,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-04-27 14:15:47</t>
+          <t>2026-04-27 14:06:10</t>
         </is>
       </c>
       <c r="F208" t="inlineStr"/>
@@ -18459,7 +18459,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>338</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -18479,7 +18479,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:51</t>
+          <t>2026-04-27 14:10:21</t>
         </is>
       </c>
       <c r="F209" t="inlineStr"/>
@@ -18488,17 +18488,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>339</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -18508,7 +18508,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2026-04-27 18:08:12</t>
+          <t>2026-04-27 14:13:06</t>
         </is>
       </c>
       <c r="F210" t="inlineStr"/>
@@ -18517,17 +18517,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>340</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -18537,7 +18537,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-04-27 18:10:09</t>
+          <t>2026-04-27 14:15:47</t>
         </is>
       </c>
       <c r="F211" t="inlineStr"/>
@@ -18546,17 +18546,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>393</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-04-27 18:12:49</t>
+          <t>2026-04-27 18:05:51</t>
         </is>
       </c>
       <c r="F212" t="inlineStr"/>
@@ -18575,17 +18575,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>395</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -18595,7 +18595,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-04-27 18:25:23</t>
+          <t>2026-04-27 18:08:12</t>
         </is>
       </c>
       <c r="F213" t="inlineStr"/>
@@ -18604,7 +18604,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>396</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -18624,7 +18624,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-04-27 18:26:29</t>
+          <t>2026-04-27 18:10:09</t>
         </is>
       </c>
       <c r="F214" t="inlineStr"/>
@@ -18633,17 +18633,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>398</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -18653,7 +18653,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-04-27 18:28:56</t>
+          <t>2026-04-27 18:12:49</t>
         </is>
       </c>
       <c r="F215" t="inlineStr"/>
@@ -18662,17 +18662,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>399</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -18682,7 +18682,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-04-27 18:32:14</t>
+          <t>2026-04-27 18:25:23</t>
         </is>
       </c>
       <c r="F216" t="inlineStr"/>
@@ -18691,7 +18691,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>400</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-04-27 19:10:16</t>
+          <t>2026-04-27 18:26:29</t>
         </is>
       </c>
       <c r="F217" t="inlineStr"/>
@@ -18720,7 +18720,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>401</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18740,7 +18740,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-04-28 13:06:06</t>
+          <t>2026-04-27 18:28:56</t>
         </is>
       </c>
       <c r="F218" t="inlineStr"/>
@@ -18749,17 +18749,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>402</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -18769,7 +18769,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-04-28 13:09:10</t>
+          <t>2026-04-27 18:32:14</t>
         </is>
       </c>
       <c r="F219" t="inlineStr"/>
@@ -18778,17 +18778,17 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>403</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -18798,7 +18798,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-04-28 13:31:57</t>
+          <t>2026-04-27 19:10:16</t>
         </is>
       </c>
       <c r="F220" t="inlineStr"/>
@@ -18807,17 +18807,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>404</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -18827,7 +18827,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-04-28 16:36:52</t>
+          <t>2026-04-28 13:06:06</t>
         </is>
       </c>
       <c r="F221" t="inlineStr"/>
@@ -18836,17 +18836,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>405</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -18856,7 +18856,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-04-28 16:41:55</t>
+          <t>2026-04-28 13:09:10</t>
         </is>
       </c>
       <c r="F222" t="inlineStr"/>
@@ -18865,17 +18865,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>406</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -18885,7 +18885,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-04-28 16:45:43</t>
+          <t>2026-04-28 13:31:57</t>
         </is>
       </c>
       <c r="F223" t="inlineStr"/>
@@ -18894,7 +18894,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>408</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-04-28 16:50:41</t>
+          <t>2026-04-28 16:36:52</t>
         </is>
       </c>
       <c r="F224" t="inlineStr"/>
@@ -18923,17 +18923,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>409</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -18943,7 +18943,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-04-28 16:58:22</t>
+          <t>2026-04-28 16:41:55</t>
         </is>
       </c>
       <c r="F225" t="inlineStr"/>
@@ -18952,17 +18952,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>410</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -18972,7 +18972,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-04-28 19:11:43</t>
+          <t>2026-04-28 16:45:43</t>
         </is>
       </c>
       <c r="F226" t="inlineStr"/>
@@ -18981,7 +18981,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>411</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -19001,7 +19001,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-04-28 19:17:29</t>
+          <t>2026-04-28 16:50:41</t>
         </is>
       </c>
       <c r="F227" t="inlineStr"/>
@@ -19010,17 +19010,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>412</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -19030,7 +19030,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-04-28 19:20:41</t>
+          <t>2026-04-28 16:58:22</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
@@ -19039,17 +19039,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>422</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -19059,7 +19059,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-04-28 19:27:32</t>
+          <t>2026-04-28 19:11:43</t>
         </is>
       </c>
       <c r="F229" t="inlineStr"/>
@@ -19068,17 +19068,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>425</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -19088,7 +19088,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-04-28 19:29:59</t>
+          <t>2026-04-28 19:17:29</t>
         </is>
       </c>
       <c r="F230" t="inlineStr"/>
@@ -19097,7 +19097,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>427</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -19117,7 +19117,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-04-28 19:38:54</t>
+          <t>2026-04-28 19:20:41</t>
         </is>
       </c>
       <c r="F231" t="inlineStr"/>
@@ -19126,17 +19126,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>431</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -19146,7 +19146,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-04-28 18:59:52</t>
+          <t>2026-04-28 19:27:32</t>
         </is>
       </c>
       <c r="F232" t="inlineStr"/>
@@ -19155,17 +19155,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>432</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -19175,7 +19175,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-04-28 19:05:38</t>
+          <t>2026-04-28 19:29:59</t>
         </is>
       </c>
       <c r="F233" t="inlineStr"/>
@@ -19184,7 +19184,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>438</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -19204,7 +19204,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-04-28 19:09:07</t>
+          <t>2026-04-28 19:38:54</t>
         </is>
       </c>
       <c r="F234" t="inlineStr"/>
@@ -19213,17 +19213,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>413</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -19233,7 +19233,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-04-28 19:22:49</t>
+          <t>2026-04-28 18:59:52</t>
         </is>
       </c>
       <c r="F235" t="inlineStr"/>
@@ -19242,17 +19242,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>416</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -19262,7 +19262,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2026-04-28 19:46:42</t>
+          <t>2026-04-28 19:05:38</t>
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
@@ -19271,7 +19271,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>420</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19291,7 +19291,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-04-29 15:54:41</t>
+          <t>2026-04-28 19:09:07</t>
         </is>
       </c>
       <c r="F237" t="inlineStr"/>
@@ -19300,7 +19300,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>429</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19320,7 +19320,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-04-29 15:56:41</t>
+          <t>2026-04-28 19:22:49</t>
         </is>
       </c>
       <c r="F238" t="inlineStr"/>
@@ -19329,17 +19329,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>439</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -19349,7 +19349,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-04-29 16:10:35</t>
+          <t>2026-04-28 19:46:42</t>
         </is>
       </c>
       <c r="F239" t="inlineStr"/>
@@ -19358,17 +19358,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>440</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -19378,7 +19378,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-04-29 16:13:57</t>
+          <t>2026-04-29 15:54:41</t>
         </is>
       </c>
       <c r="F240" t="inlineStr"/>
@@ -19387,7 +19387,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>441</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19407,7 +19407,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-04-29 16:17:13</t>
+          <t>2026-04-29 15:56:41</t>
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
@@ -19416,17 +19416,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>442</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -19436,7 +19436,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-04-29 16:21:56</t>
+          <t>2026-04-29 16:10:35</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
@@ -19445,17 +19445,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>443</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -19465,7 +19465,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-04-29 16:26:19</t>
+          <t>2026-04-29 16:13:57</t>
         </is>
       </c>
       <c r="F243" t="inlineStr"/>
@@ -19474,7 +19474,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>444</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19494,7 +19494,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-04-30 11:56:22</t>
+          <t>2026-04-29 16:17:13</t>
         </is>
       </c>
       <c r="F244" t="inlineStr"/>
@@ -19503,7 +19503,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>445</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19523,7 +19523,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-04-30 12:18:39</t>
+          <t>2026-04-29 16:21:56</t>
         </is>
       </c>
       <c r="F245" t="inlineStr"/>
@@ -19532,7 +19532,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>446</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19552,7 +19552,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-04-30 12:27:47</t>
+          <t>2026-04-29 16:26:19</t>
         </is>
       </c>
       <c r="F246" t="inlineStr"/>
@@ -19561,17 +19561,17 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>447</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -19581,7 +19581,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-04-30 14:33:48</t>
+          <t>2026-04-30 11:56:22</t>
         </is>
       </c>
       <c r="F247" t="inlineStr"/>
@@ -19590,17 +19590,17 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>448</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -19610,7 +19610,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-04-30 14:39:11</t>
+          <t>2026-04-30 12:18:39</t>
         </is>
       </c>
       <c r="F248" t="inlineStr"/>
@@ -19619,7 +19619,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>449</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19639,7 +19639,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-04-30 14:44:06</t>
+          <t>2026-04-30 12:27:47</t>
         </is>
       </c>
       <c r="F249" t="inlineStr"/>
@@ -19648,17 +19648,17 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>450</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -19668,7 +19668,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-04-30 14:50:48</t>
+          <t>2026-04-30 14:33:48</t>
         </is>
       </c>
       <c r="F250" t="inlineStr"/>
@@ -19677,17 +19677,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>452</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -19697,7 +19697,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-04-30 15:03:19</t>
+          <t>2026-04-30 14:39:11</t>
         </is>
       </c>
       <c r="F251" t="inlineStr"/>
@@ -19706,7 +19706,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>453</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19726,7 +19726,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-04-30 16:43:14</t>
+          <t>2026-04-30 14:44:06</t>
         </is>
       </c>
       <c r="F252" t="inlineStr"/>
@@ -19735,17 +19735,17 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>454</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -19755,7 +19755,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-04-30 16:49:38</t>
+          <t>2026-04-30 14:50:48</t>
         </is>
       </c>
       <c r="F253" t="inlineStr"/>
@@ -19764,17 +19764,17 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>455</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -19784,7 +19784,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-04-30 16:57:13</t>
+          <t>2026-04-30 15:03:19</t>
         </is>
       </c>
       <c r="F254" t="inlineStr"/>
@@ -19793,17 +19793,17 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>456</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -19813,7 +19813,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-04-30 16:59:14</t>
+          <t>2026-04-30 16:43:14</t>
         </is>
       </c>
       <c r="F255" t="inlineStr"/>
@@ -19822,7 +19822,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>457</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -19842,7 +19842,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2026-04-30 17:03:09</t>
+          <t>2026-04-30 16:49:38</t>
         </is>
       </c>
       <c r="F256" t="inlineStr"/>
@@ -19851,17 +19851,17 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>458</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -19871,7 +19871,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-04-30 17:07:20</t>
+          <t>2026-04-30 16:57:13</t>
         </is>
       </c>
       <c r="F257" t="inlineStr"/>
@@ -19880,17 +19880,17 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>459</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -19900,7 +19900,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-04-30 17:20:16</t>
+          <t>2026-04-30 16:59:14</t>
         </is>
       </c>
       <c r="F258" t="inlineStr"/>
@@ -19909,7 +19909,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-05-04 12:40:26</t>
+          <t>2026-04-30 17:03:09</t>
         </is>
       </c>
       <c r="F259" t="inlineStr"/>
@@ -19938,17 +19938,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>461</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -19958,7 +19958,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-05-04 13:27:46</t>
+          <t>2026-04-30 17:07:20</t>
         </is>
       </c>
       <c r="F260" t="inlineStr"/>
@@ -19967,7 +19967,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>462</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -19987,7 +19987,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-05-04 13:32:27</t>
+          <t>2026-04-30 17:20:16</t>
         </is>
       </c>
       <c r="F261" t="inlineStr"/>
@@ -19996,17 +19996,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>465</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -20016,7 +20016,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-05-04 13:35:31</t>
+          <t>2026-05-04 12:40:26</t>
         </is>
       </c>
       <c r="F262" t="inlineStr"/>
@@ -20025,7 +20025,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>466</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20045,7 +20045,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-05-04 13:52:33</t>
+          <t>2026-05-04 13:27:46</t>
         </is>
       </c>
       <c r="F263" t="inlineStr"/>
@@ -20054,7 +20054,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>467</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20074,7 +20074,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-05-04 14:15:29</t>
+          <t>2026-05-04 13:32:27</t>
         </is>
       </c>
       <c r="F264" t="inlineStr"/>
@@ -20083,17 +20083,17 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>468</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -20103,7 +20103,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-05-04 14:21:26</t>
+          <t>2026-05-04 13:35:31</t>
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
@@ -20112,17 +20112,17 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>469</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -20132,7 +20132,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-05-04 14:28:28</t>
+          <t>2026-05-04 13:52:33</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
@@ -20141,17 +20141,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>470</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -20161,7 +20161,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-05-05 12:33:28</t>
+          <t>2026-05-04 14:15:29</t>
         </is>
       </c>
       <c r="F267" t="inlineStr"/>
@@ -20170,17 +20170,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>471</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -20190,7 +20190,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-05-05 12:36:49</t>
+          <t>2026-05-04 14:21:26</t>
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
@@ -20199,7 +20199,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>472</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -20219,7 +20219,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-05-05 13:16:10</t>
+          <t>2026-05-04 14:28:28</t>
         </is>
       </c>
       <c r="F269" t="inlineStr"/>
@@ -20228,17 +20228,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>473</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -20248,7 +20248,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-05-05 13:22:28</t>
+          <t>2026-05-05 12:33:28</t>
         </is>
       </c>
       <c r="F270" t="inlineStr"/>
@@ -20257,17 +20257,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>474</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -20277,7 +20277,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-05-05 15:49:32</t>
+          <t>2026-05-05 12:36:49</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
@@ -20286,7 +20286,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>475</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-05-05 18:17:18</t>
+          <t>2026-05-05 13:16:10</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
@@ -20315,17 +20315,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>476</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -20335,7 +20335,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-05-05 18:23:24</t>
+          <t>2026-05-05 13:22:28</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
@@ -20344,17 +20344,17 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>478</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -20364,7 +20364,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-05-05 18:30:18</t>
+          <t>2026-05-05 15:49:32</t>
         </is>
       </c>
       <c r="F274" t="inlineStr"/>
@@ -20373,7 +20373,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>484</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-05-05 19:24:36</t>
+          <t>2026-05-05 18:17:18</t>
         </is>
       </c>
       <c r="F275" t="inlineStr"/>
@@ -20402,7 +20402,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>485</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -20422,7 +20422,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-05-06 14:07:52</t>
+          <t>2026-05-05 18:23:24</t>
         </is>
       </c>
       <c r="F276" t="inlineStr"/>
@@ -20431,17 +20431,17 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>486</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -20451,7 +20451,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-05-06 14:12:50</t>
+          <t>2026-05-05 18:30:18</t>
         </is>
       </c>
       <c r="F277" t="inlineStr"/>
@@ -20460,7 +20460,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>487</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -20480,7 +20480,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-05-06 14:15:34</t>
+          <t>2026-05-05 19:24:36</t>
         </is>
       </c>
       <c r="F278" t="inlineStr"/>
@@ -20489,17 +20489,17 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>488</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -20509,7 +20509,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-05-06 14:59:26</t>
+          <t>2026-05-06 14:07:52</t>
         </is>
       </c>
       <c r="F279" t="inlineStr"/>
@@ -20518,17 +20518,17 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>489</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -20538,7 +20538,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-05-06 15:04:52</t>
+          <t>2026-05-06 14:12:50</t>
         </is>
       </c>
       <c r="F280" t="inlineStr"/>
@@ -20547,7 +20547,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>490</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -20567,7 +20567,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-05-06 15:08:51</t>
+          <t>2026-05-06 14:15:34</t>
         </is>
       </c>
       <c r="F281" t="inlineStr"/>
@@ -20576,17 +20576,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Busy</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -20596,7 +20596,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-05-06 15:28:38</t>
+          <t>2026-05-06 14:59:26</t>
         </is>
       </c>
       <c r="F282" t="inlineStr"/>
@@ -20605,17 +20605,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>492</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -20625,7 +20625,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-05-06 15:31:36</t>
+          <t>2026-05-06 15:04:52</t>
         </is>
       </c>
       <c r="F283" t="inlineStr"/>
@@ -20634,7 +20634,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>493</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -20654,7 +20654,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-05-06 17:53:50</t>
+          <t>2026-05-06 15:08:51</t>
         </is>
       </c>
       <c r="F284" t="inlineStr"/>
@@ -20663,17 +20663,17 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>494</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Busy</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -20683,7 +20683,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-05-06 17:59:31</t>
+          <t>2026-05-06 15:28:38</t>
         </is>
       </c>
       <c r="F285" t="inlineStr"/>
@@ -20692,17 +20692,17 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>495</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -20712,7 +20712,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-05-06 19:18:14</t>
+          <t>2026-05-06 15:31:36</t>
         </is>
       </c>
       <c r="F286" t="inlineStr"/>
@@ -20721,7 +20721,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>501</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -20741,7 +20741,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-05-06 19:21:01</t>
+          <t>2026-05-06 17:53:50</t>
         </is>
       </c>
       <c r="F287" t="inlineStr"/>
@@ -20750,7 +20750,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>502</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -20770,7 +20770,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>2026-05-06 19:25:27</t>
+          <t>2026-05-06 17:59:31</t>
         </is>
       </c>
       <c r="F288" t="inlineStr"/>
@@ -20779,17 +20779,17 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>503</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -20799,7 +20799,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-05-06 19:27:23</t>
+          <t>2026-05-06 19:18:14</t>
         </is>
       </c>
       <c r="F289" t="inlineStr"/>
@@ -20808,17 +20808,17 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>504</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -20828,7 +20828,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-05-06 19:39:21</t>
+          <t>2026-05-06 19:21:01</t>
         </is>
       </c>
       <c r="F290" t="inlineStr"/>
@@ -20837,17 +20837,17 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>505</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -20857,7 +20857,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-05-06 20:09:52</t>
+          <t>2026-05-06 19:25:27</t>
         </is>
       </c>
       <c r="F291" t="inlineStr"/>
@@ -20866,7 +20866,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>506</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-05-06 20:12:28</t>
+          <t>2026-05-06 19:27:23</t>
         </is>
       </c>
       <c r="F292" t="inlineStr"/>
@@ -20895,17 +20895,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>507</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -20915,7 +20915,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-05-07 12:02:27</t>
+          <t>2026-05-06 19:39:21</t>
         </is>
       </c>
       <c r="F293" t="inlineStr"/>
@@ -20924,17 +20924,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>509</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2026-05-07 12:05:31</t>
+          <t>2026-05-06 20:09:52</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
@@ -20953,17 +20953,17 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>511</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -20973,7 +20973,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-05-07 12:07:46</t>
+          <t>2026-05-06 20:12:28</t>
         </is>
       </c>
       <c r="F295" t="inlineStr"/>
@@ -20982,17 +20982,17 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>512</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -21002,7 +21002,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-05-07 12:12:23</t>
+          <t>2026-05-07 12:02:27</t>
         </is>
       </c>
       <c r="F296" t="inlineStr"/>
@@ -21011,17 +21011,17 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>513</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -21031,7 +21031,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-05-07 12:21:17</t>
+          <t>2026-05-07 12:05:31</t>
         </is>
       </c>
       <c r="F297" t="inlineStr"/>
@@ -21040,17 +21040,17 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>514</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -21060,7 +21060,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-05-07 12:22:26</t>
+          <t>2026-05-07 12:07:46</t>
         </is>
       </c>
       <c r="F298" t="inlineStr"/>
@@ -21069,17 +21069,17 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>515</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -21089,7 +21089,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-05-07 12:25:15</t>
+          <t>2026-05-07 12:12:23</t>
         </is>
       </c>
       <c r="F299" t="inlineStr"/>
@@ -21098,7 +21098,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>516</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -21118,7 +21118,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-05-07 12:30:09</t>
+          <t>2026-05-07 12:21:17</t>
         </is>
       </c>
       <c r="F300" t="inlineStr"/>
@@ -21127,7 +21127,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>517</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -21147,7 +21147,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-05-07 18:11:26</t>
+          <t>2026-05-07 12:22:26</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
@@ -21156,17 +21156,17 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>522</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -21176,7 +21176,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-05-07 18:21:05</t>
+          <t>2026-05-07 12:25:15</t>
         </is>
       </c>
       <c r="F302" t="inlineStr"/>
@@ -21185,7 +21185,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>524</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -21205,7 +21205,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-05-07 18:23:27</t>
+          <t>2026-05-07 12:30:09</t>
         </is>
       </c>
       <c r="F303" t="inlineStr"/>
@@ -21214,17 +21214,17 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>527</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -21234,7 +21234,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-05-07 18:31:47</t>
+          <t>2026-05-07 18:11:26</t>
         </is>
       </c>
       <c r="F304" t="inlineStr"/>
@@ -21243,17 +21243,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>528</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -21263,7 +21263,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-05-07 18:41:02</t>
+          <t>2026-05-07 18:21:05</t>
         </is>
       </c>
       <c r="F305" t="inlineStr"/>
@@ -21272,17 +21272,17 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>529</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -21292,7 +21292,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-05-07 19:04:03</t>
+          <t>2026-05-07 18:23:27</t>
         </is>
       </c>
       <c r="F306" t="inlineStr"/>
@@ -21301,17 +21301,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>530</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -21321,7 +21321,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-05-07 19:12:07</t>
+          <t>2026-05-07 18:31:47</t>
         </is>
       </c>
       <c r="F307" t="inlineStr"/>
@@ -21330,17 +21330,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>531</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -21350,7 +21350,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-05-07 19:19:47</t>
+          <t>2026-05-07 18:41:02</t>
         </is>
       </c>
       <c r="F308" t="inlineStr"/>
@@ -21359,17 +21359,17 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>532</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -21379,7 +21379,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-05-07 19:35:25</t>
+          <t>2026-05-07 19:04:03</t>
         </is>
       </c>
       <c r="F309" t="inlineStr"/>
@@ -21388,17 +21388,17 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>533</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-05-08 12:36:57</t>
+          <t>2026-05-07 19:12:07</t>
         </is>
       </c>
       <c r="F310" t="inlineStr"/>
@@ -21417,7 +21417,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>534</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-05-08 12:43:59</t>
+          <t>2026-05-07 19:19:47</t>
         </is>
       </c>
       <c r="F311" t="inlineStr"/>
@@ -21446,17 +21446,17 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>535</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -21466,7 +21466,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-05-08 12:51:09</t>
+          <t>2026-05-07 19:35:25</t>
         </is>
       </c>
       <c r="F312" t="inlineStr"/>
@@ -21475,7 +21475,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>536</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -21495,7 +21495,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-05-08 12:55:15</t>
+          <t>2026-05-08 12:36:57</t>
         </is>
       </c>
       <c r="F313" t="inlineStr"/>
@@ -21504,7 +21504,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>537</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -21524,7 +21524,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-05-08 12:57:14</t>
+          <t>2026-05-08 12:43:59</t>
         </is>
       </c>
       <c r="F314" t="inlineStr"/>
@@ -21533,17 +21533,17 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>538</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -21553,7 +21553,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2026-05-08 13:00:41</t>
+          <t>2026-05-08 12:51:09</t>
         </is>
       </c>
       <c r="F315" t="inlineStr"/>
@@ -21562,17 +21562,17 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>539</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -21582,7 +21582,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-05-08 13:04:02</t>
+          <t>2026-05-08 12:55:15</t>
         </is>
       </c>
       <c r="F316" t="inlineStr"/>
@@ -21591,7 +21591,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>540</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -21611,7 +21611,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-05-08 13:09:59</t>
+          <t>2026-05-08 12:57:14</t>
         </is>
       </c>
       <c r="F317" t="inlineStr"/>
@@ -21620,17 +21620,17 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>541</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>WARM LEAD</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>warm_lead</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -21640,7 +21640,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-05-08 13:16:49</t>
+          <t>2026-05-08 13:00:41</t>
         </is>
       </c>
       <c r="F318" t="inlineStr"/>
@@ -21649,17 +21649,17 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>542</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -21669,7 +21669,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-05-08 13:22:02</t>
+          <t>2026-05-08 13:04:02</t>
         </is>
       </c>
       <c r="F319" t="inlineStr"/>
@@ -21678,7 +21678,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>543</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -21698,7 +21698,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-05-08 15:50:51</t>
+          <t>2026-05-08 13:09:59</t>
         </is>
       </c>
       <c r="F320" t="inlineStr"/>
@@ -21707,17 +21707,17 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>544</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>WARM LEAD</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>warm_lead</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -21727,7 +21727,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-05-08 15:54:37</t>
+          <t>2026-05-08 13:16:49</t>
         </is>
       </c>
       <c r="F321" t="inlineStr"/>
@@ -21736,7 +21736,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>545</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -21756,7 +21756,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-05-08 15:59:34</t>
+          <t>2026-05-08 13:22:02</t>
         </is>
       </c>
       <c r="F322" t="inlineStr"/>
@@ -21765,7 +21765,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>546</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -21785,7 +21785,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-05-08 16:11:07</t>
+          <t>2026-05-08 15:50:51</t>
         </is>
       </c>
       <c r="F323" t="inlineStr"/>
@@ -21794,17 +21794,17 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>547</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -21814,7 +21814,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-05-08 16:19:50</t>
+          <t>2026-05-08 15:54:37</t>
         </is>
       </c>
       <c r="F324" t="inlineStr"/>
@@ -21823,7 +21823,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>548</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -21843,7 +21843,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-05-08 16:24:03</t>
+          <t>2026-05-08 15:59:34</t>
         </is>
       </c>
       <c r="F325" t="inlineStr"/>
@@ -21852,7 +21852,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>549</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -21872,7 +21872,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-05-12 12:12:48</t>
+          <t>2026-05-08 16:11:07</t>
         </is>
       </c>
       <c r="F326" t="inlineStr"/>
@@ -21881,17 +21881,17 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>550</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -21901,7 +21901,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-05-12 12:18:21</t>
+          <t>2026-05-08 16:19:50</t>
         </is>
       </c>
       <c r="F327" t="inlineStr"/>
@@ -21910,17 +21910,17 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>551</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -21930,7 +21930,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-05-12 12:22:04</t>
+          <t>2026-05-08 16:24:03</t>
         </is>
       </c>
       <c r="F328" t="inlineStr"/>
@@ -21939,17 +21939,17 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>553</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Call disconnected</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -21959,7 +21959,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-05-12 12:23:33</t>
+          <t>2026-05-12 12:12:48</t>
         </is>
       </c>
       <c r="F329" t="inlineStr"/>
@@ -21968,17 +21968,17 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>554</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -21988,7 +21988,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-05-12 12:26:05</t>
+          <t>2026-05-12 12:18:21</t>
         </is>
       </c>
       <c r="F330" t="inlineStr"/>
@@ -21997,17 +21997,17 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>555</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -22017,7 +22017,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-05-12 12:31:00</t>
+          <t>2026-05-12 12:22:04</t>
         </is>
       </c>
       <c r="F331" t="inlineStr"/>
@@ -22026,17 +22026,17 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>556</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call disconnected</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -22046,7 +22046,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2026-05-12 12:33:59</t>
+          <t>2026-05-12 12:23:33</t>
         </is>
       </c>
       <c r="F332" t="inlineStr"/>
@@ -22055,7 +22055,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>557</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -22075,7 +22075,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-05-12 12:37:48</t>
+          <t>2026-05-12 12:26:05</t>
         </is>
       </c>
       <c r="F333" t="inlineStr"/>
@@ -22084,7 +22084,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>558</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -22104,7 +22104,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-05-12 12:48:40</t>
+          <t>2026-05-12 12:31:00</t>
         </is>
       </c>
       <c r="F334" t="inlineStr"/>
@@ -22113,17 +22113,17 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>559</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -22133,7 +22133,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-05-12 12:51:08</t>
+          <t>2026-05-12 12:33:59</t>
         </is>
       </c>
       <c r="F335" t="inlineStr"/>
@@ -22142,7 +22142,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>560</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-05-12 18:19:14</t>
+          <t>2026-05-12 12:37:48</t>
         </is>
       </c>
       <c r="F336" t="inlineStr"/>
@@ -22171,17 +22171,17 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -22191,7 +22191,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-05-12 18:26:39</t>
+          <t>2026-05-12 12:48:40</t>
         </is>
       </c>
       <c r="F337" t="inlineStr"/>
@@ -22200,7 +22200,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>562</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -22220,7 +22220,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-05-12 18:29:28</t>
+          <t>2026-05-12 12:51:08</t>
         </is>
       </c>
       <c r="F338" t="inlineStr"/>
@@ -22229,7 +22229,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>566</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -22249,7 +22249,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-05-12 18:38:29</t>
+          <t>2026-05-12 18:19:14</t>
         </is>
       </c>
       <c r="F339" t="inlineStr"/>
@@ -22258,17 +22258,17 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>567</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -22278,7 +22278,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-05-12 18:47:34</t>
+          <t>2026-05-12 18:26:39</t>
         </is>
       </c>
       <c r="F340" t="inlineStr"/>
@@ -22287,17 +22287,17 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>568</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -22307,7 +22307,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>2026-05-12 18:54:06</t>
+          <t>2026-05-12 18:29:28</t>
         </is>
       </c>
       <c r="F341" t="inlineStr"/>
@@ -22316,17 +22316,17 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>569</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -22336,7 +22336,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-05-12 19:03:54</t>
+          <t>2026-05-12 18:38:29</t>
         </is>
       </c>
       <c r="F342" t="inlineStr"/>
@@ -22345,17 +22345,17 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>570</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -22365,11 +22365,359 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>2026-05-12 19:41:52</t>
+          <t>2026-05-12 18:47:34</t>
         </is>
       </c>
       <c r="F343" t="inlineStr"/>
       <c r="G343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>2026-05-12 18:54:06</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr"/>
+      <c r="G344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>2026-05-12 19:03:54</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr"/>
+      <c r="G345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>2026-05-12 19:41:52</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr"/>
+      <c r="G346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:09:27</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr"/>
+      <c r="G347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:18:32</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr"/>
+      <c r="G348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:23:52</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr"/>
+      <c r="G349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>NO ANSWER</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>no_answer</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:25:37</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr"/>
+      <c r="G350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:28:23</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr"/>
+      <c r="G351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:32:52</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr"/>
+      <c r="G352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:40:54</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr"/>
+      <c r="G353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:43:27</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr"/>
+      <c r="G354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>585</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Busy</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>busy_call_back</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:45:51</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr"/>
+      <c r="G355" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22382,7 +22730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22877,6 +23225,50 @@
       </c>
       <c r="J11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>fcd86540-4ec5-11f1-8c7d-bb9573f02cba</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>mccarthybus</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Manually created</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-05-13T12:19:28.276Z</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>JOHN P. MCCARTHY</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>mccarthybus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H287"/>
+  <dimension ref="A1:H291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-05-12 12:09:08</t>
+          <t>2026-05-14 12:29:25</t>
         </is>
       </c>
     </row>
@@ -10172,7 +10172,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>2026-04-28 16:41:55</t>
+          <t>2026-05-14 12:57:05</t>
         </is>
       </c>
     </row>
@@ -12399,6 +12399,174 @@
       <c r="H287" t="inlineStr">
         <is>
           <t>2026-05-12 19:03:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>ANDREW CURTIS</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>info@curtisseptic.com</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(508) 393-7234 </t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Curtis septic</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>2026-05-14 12:31:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>DANIEL DEVANE</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>dandevane@devosstumpremoval.com</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>(508) 331-1192</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Devos stump removal</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>2026-05-14 12:34:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Peter Gordecki</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>peterg@bostonbattery.net</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (781) 647-7973</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Boston battery</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>2026-05-14 12:39:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>TIM PILATO</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>tpilato@premiertransportation.com</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(404) 675-1950 </t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Not Interested</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Premier transportation</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:04:59</t>
         </is>
       </c>
     </row>
@@ -12413,7 +12581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G355"/>
+  <dimension ref="A1:G362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12572,27 +12740,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>not Interested</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-05-11 18:35:26</t>
+          <t>2026-02-12 20:19:12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -12601,17 +12769,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not Interested</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -12621,7 +12789,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-02-12 20:19:12</t>
+          <t>2026-02-13 18:09:02</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -12630,7 +12798,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -12650,7 +12818,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-02-13 18:09:02</t>
+          <t>2026-02-13 18:10:17</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -12659,17 +12827,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Number Busy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -12679,7 +12847,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-02-13 18:10:17</t>
+          <t>2026-02-13 18:40:29</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -12688,17 +12856,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Number Busy</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>email</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -12708,7 +12876,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-02-13 18:40:29</t>
+          <t>2026-02-13 20:55:42</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -12717,17 +12885,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -12737,7 +12905,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-02-13 20:55:42</t>
+          <t>2026-02-17 12:58:58</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -12746,17 +12914,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Number not in service</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -12766,7 +12934,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-02-17 12:58:58</t>
+          <t>2026-02-17 13:17:50</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -12775,17 +12943,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Number not in service</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -12795,7 +12963,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-02-17 13:17:50</t>
+          <t>2026-02-18 13:35:13</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -12804,12 +12972,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Left Voicemail</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -12824,7 +12992,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-02-18 13:35:13</t>
+          <t>2026-02-18 19:14:30</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -12833,12 +13001,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Left Voicemail</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -12853,7 +13021,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-02-18 19:14:30</t>
+          <t>2026-02-20 16:16:15</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -12862,19 +13030,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>voicemail</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>voicemail</t>
-        </is>
-      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>Done</t>
@@ -12882,7 +13050,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-02-20 16:16:15</t>
+          <t>2026-02-20 16:28:27</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -12891,12 +13059,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>98</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Left Voicemail</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -12911,7 +13079,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-02-20 16:28:27</t>
+          <t>2026-02-20 16:40:56</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -12920,17 +13088,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Left Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12940,7 +13108,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-02-20 16:40:56</t>
+          <t>2026-02-20 17:38:46</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -12949,17 +13117,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>101</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -12969,7 +13137,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-02-20 17:38:46</t>
+          <t>2026-02-20 17:51:33</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -12978,17 +13146,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Not Interested</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -12998,7 +13166,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-02-20 17:51:33</t>
+          <t>2026-02-20 17:51:57</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -13007,17 +13175,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -13027,7 +13195,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-02-20 17:51:57</t>
+          <t>2026-02-25 14:04:42</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -13036,17 +13204,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -13056,7 +13224,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-02-25 14:04:42</t>
+          <t>2026-02-25 16:00:39</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -13065,7 +13233,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -13085,7 +13253,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-02-25 16:00:39</t>
+          <t>2026-03-04 19:53:23</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -13094,17 +13262,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>157</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -13114,7 +13282,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-03-04 19:53:23</t>
+          <t>2026-03-13 11:44:50</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -13123,17 +13291,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>158</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -13143,7 +13311,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-03-13 11:44:50</t>
+          <t>2026-03-13 18:22:38</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -13152,17 +13320,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>159</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -13172,7 +13340,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-03-13 18:22:38</t>
+          <t>2026-03-13 18:27:37</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -13181,7 +13349,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>160</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -13201,7 +13369,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-03-13 18:27:37</t>
+          <t>2026-03-16 13:12:26</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -13210,7 +13378,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>161</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -13230,7 +13398,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-03-16 13:12:26</t>
+          <t>2026-03-16 13:13:55</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -13239,17 +13407,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>167</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -13259,7 +13427,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-03-16 13:13:55</t>
+          <t>2026-03-17 15:47:45</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -13268,17 +13436,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>168</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -13288,7 +13456,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-03-17 15:47:45</t>
+          <t>2026-03-17 15:53:47</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -13297,17 +13465,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>169</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -13317,7 +13485,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-03-17 15:53:47</t>
+          <t>2026-03-17 15:57:36</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -13326,17 +13494,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>170</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>WRONG NUMBER -DNC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>wrong_number__dnc</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -13346,7 +13514,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-03-17 15:57:36</t>
+          <t>2026-03-17 15:59:48</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -13355,17 +13523,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>171</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>WRONG NUMBER -DNC</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>wrong_number__dnc</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -13375,7 +13543,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-03-17 15:59:48</t>
+          <t>2026-03-17 16:06:24</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -13384,17 +13552,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>173</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -13404,7 +13572,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-03-17 16:06:24</t>
+          <t>2026-03-17 16:11:12</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -13413,17 +13581,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>174</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -13433,7 +13601,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-03-17 16:11:12</t>
+          <t>2026-03-17 16:14:37</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -13442,17 +13610,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>175</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -13462,7 +13630,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-03-17 16:14:37</t>
+          <t>2026-03-17 16:17:56</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -13471,17 +13639,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>388</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -13491,7 +13659,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-03-17 16:17:56</t>
+          <t>2026-04-27 18:04:47</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -13500,17 +13668,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>180</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -13520,7 +13688,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-04-27 18:04:47</t>
+          <t>2026-03-20 14:54:02</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -13529,7 +13697,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>181</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -13549,7 +13717,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-03-20 14:54:02</t>
+          <t>2026-03-20 14:57:56</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -13558,7 +13726,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>183</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -13578,7 +13746,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-03-20 14:57:56</t>
+          <t>2026-03-20 18:07:00</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -13587,17 +13755,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>184</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -13607,7 +13775,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-03-20 18:07:00</t>
+          <t>2026-03-20 18:13:02</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -13616,17 +13784,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>355</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -13636,7 +13804,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-03-20 18:13:02</t>
+          <t>2026-04-27 16:29:12</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -13645,17 +13813,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>389</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -13665,7 +13833,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-04-27 16:29:12</t>
+          <t>2026-04-27 18:04:59</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -13674,7 +13842,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>414</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -13694,7 +13862,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-04-27 18:04:59</t>
+          <t>2026-04-28 19:04:54</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -13703,7 +13871,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>417</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -13723,7 +13891,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-04-28 19:04:54</t>
+          <t>2026-04-28 19:06:45</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -13732,7 +13900,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>433</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -13752,7 +13920,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-04-28 19:06:45</t>
+          <t>2026-04-28 19:34:15</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -13761,7 +13929,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>519</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -13781,7 +13949,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-04-28 19:34:15</t>
+          <t>2026-05-07 12:24:40</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -13790,17 +13958,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>185</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -13810,7 +13978,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-05-07 12:24:40</t>
+          <t>2026-03-20 18:49:21</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -13819,17 +13987,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>434</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -13839,7 +14007,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-03-20 18:49:21</t>
+          <t>2026-04-28 19:34:30</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -13848,17 +14016,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>191</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -13868,7 +14036,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-04-28 19:34:30</t>
+          <t>2026-03-23 18:38:25</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -13877,17 +14045,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>193</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -13897,7 +14065,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-03-23 18:38:25</t>
+          <t>2026-03-23 18:47:52</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -13906,17 +14074,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>194</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -13926,7 +14094,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-03-23 18:47:52</t>
+          <t>2026-03-23 18:54:34</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -13935,7 +14103,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>196</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -13955,7 +14123,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-03-23 18:54:34</t>
+          <t>2026-03-23 18:58:51</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -13964,7 +14132,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>197</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -13974,7 +14142,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>hot_lead</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -13984,7 +14152,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-03-23 18:58:51</t>
+          <t>2026-03-23 19:03:40</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -13993,17 +14161,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>202</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>hot_lead</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -14013,7 +14181,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-03-23 19:03:40</t>
+          <t>2026-03-24 15:48:39</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -14022,17 +14190,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>205</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>WRONG NUMBER -DNC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>wrong_number__dnc</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -14042,7 +14210,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-03-24 15:48:39</t>
+          <t>2026-03-24 16:11:19</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -14051,17 +14219,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>206</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WRONG NUMBER -DNC</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>wrong_number__dnc</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -14071,7 +14239,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-03-24 16:11:19</t>
+          <t>2026-03-24 16:15:10</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -14080,7 +14248,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>207</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -14100,7 +14268,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-03-24 16:15:10</t>
+          <t>2026-03-24 16:23:12</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -14109,17 +14277,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>208</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Follow Up</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>follow_up</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -14129,7 +14297,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-03-24 16:23:12</t>
+          <t>2026-03-24 18:17:19</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -14138,17 +14306,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>369</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Follow Up</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -14158,7 +14326,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-03-24 18:17:19</t>
+          <t>2026-04-27 16:38:48</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -14167,7 +14335,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>372</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -14187,7 +14355,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:48</t>
+          <t>2026-04-27 16:40:16</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -14196,7 +14364,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>375</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -14216,7 +14384,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-04-27 16:40:16</t>
+          <t>2026-04-27 16:43:21</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -14225,7 +14393,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>380</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -14245,7 +14413,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-04-27 16:43:21</t>
+          <t>2026-04-27 16:47:15</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -14254,7 +14422,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>385</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -14274,7 +14442,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-04-27 16:47:15</t>
+          <t>2026-04-27 16:50:20</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -14283,17 +14451,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>209</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -14303,7 +14471,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-04-27 16:50:20</t>
+          <t>2026-03-24 18:57:44</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -14312,7 +14480,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>211</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -14332,7 +14500,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-03-24 18:57:44</t>
+          <t>2026-03-25 16:41:38</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -14341,7 +14509,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>212</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -14361,7 +14529,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-03-25 16:41:38</t>
+          <t>2026-03-25 16:48:29</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -14370,17 +14538,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>359</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -14390,7 +14558,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-03-25 16:48:29</t>
+          <t>2026-04-27 16:31:50</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -14399,17 +14567,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>510</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -14419,7 +14587,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-04-27 16:31:50</t>
+          <t>2026-05-06 20:12:18</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -14428,17 +14596,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>217</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14448,7 +14616,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-05-06 20:12:18</t>
+          <t>2026-03-26 14:46:03</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -14457,17 +14625,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>218</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14477,7 +14645,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-03-26 14:46:03</t>
+          <t>2026-03-26 14:57:57</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -14486,17 +14654,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>220</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14506,7 +14674,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-03-26 14:57:57</t>
+          <t>2026-03-26 15:12:09</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -14515,17 +14683,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>221</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14535,7 +14703,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-03-26 15:12:09</t>
+          <t>2026-03-26 15:45:11</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -14544,7 +14712,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>370</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -14564,7 +14732,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-03-26 15:45:11</t>
+          <t>2026-04-27 16:39:08</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -14573,17 +14741,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>228</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -14593,7 +14761,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-04-27 16:39:08</t>
+          <t>2026-03-27 18:06:04</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -14602,17 +14770,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>229</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -14622,7 +14790,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-03-27 18:06:04</t>
+          <t>2026-03-27 18:09:32</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -14631,12 +14799,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>230</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Call on Monday</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -14651,7 +14819,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-03-27 18:09:32</t>
+          <t>2026-03-27 18:13:29</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -14660,17 +14828,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>231</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Call on Monday</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -14680,7 +14848,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-03-27 18:13:29</t>
+          <t>2026-03-27 18:16:14</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -14689,17 +14857,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>232</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -14709,7 +14877,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-03-27 18:16:14</t>
+          <t>2026-03-27 18:28:41</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -14718,17 +14886,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>319</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -14738,7 +14906,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-03-27 18:28:41</t>
+          <t>2026-04-23 18:46:03</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -14747,7 +14915,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>363</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -14767,7 +14935,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-04-23 18:46:03</t>
+          <t>2026-04-27 16:34:45</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
@@ -14776,17 +14944,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>233</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -14796,7 +14964,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-04-27 16:34:45</t>
+          <t>2026-03-27 19:30:50</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -14805,17 +14973,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>239</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -14825,7 +14993,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-03-27 19:30:50</t>
+          <t>2026-03-30 16:46:09</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
@@ -14834,17 +15002,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>508</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Busy</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -14854,7 +15022,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-03-30 16:46:09</t>
+          <t>2026-05-06 20:09:36</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -14863,17 +15031,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>578</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Busy</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14883,7 +15051,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-05-06 20:09:36</t>
+          <t>2026-05-13 12:25:53</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -14892,17 +15060,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>245</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14912,7 +15080,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-05-13 12:25:53</t>
+          <t>2026-03-31 13:50:49</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -14921,17 +15089,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>246</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14941,7 +15109,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-03-31 13:50:49</t>
+          <t>2026-03-31 13:57:09</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
@@ -14950,17 +15118,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>247</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14970,7 +15138,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-03-31 13:57:09</t>
+          <t>2026-03-31 14:01:39</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
@@ -14979,17 +15147,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>248</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14999,7 +15167,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-03-31 14:01:39</t>
+          <t>2026-03-31 14:09:41</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
@@ -15008,7 +15176,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>249</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -15028,7 +15196,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-03-31 14:09:41</t>
+          <t>2026-03-31 19:13:49</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -15037,17 +15205,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>341</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15057,7 +15225,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-03-31 19:13:49</t>
+          <t>2026-04-27 16:17:22</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -15066,17 +15234,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>347</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15086,7 +15254,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-04-27 16:17:22</t>
+          <t>2026-04-27 16:22:28</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -15095,17 +15263,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>349</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15115,7 +15283,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-04-27 16:22:28</t>
+          <t>2026-04-27 16:23:48</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -15124,7 +15292,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>352</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -15144,7 +15312,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-04-27 16:23:48</t>
+          <t>2026-04-27 16:26:16</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
@@ -15153,7 +15321,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -15173,7 +15341,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-04-27 16:26:16</t>
+          <t>2026-04-27 16:32:05</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -15182,7 +15350,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>361</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -15202,7 +15370,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-04-27 16:32:05</t>
+          <t>2026-04-27 16:33:04</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -15211,7 +15379,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>364</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -15231,7 +15399,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-04-27 16:33:04</t>
+          <t>2026-04-27 16:34:57</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -15240,7 +15408,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>390</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -15260,7 +15428,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-04-27 16:34:57</t>
+          <t>2026-04-27 18:05:15</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
@@ -15269,7 +15437,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>415</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -15289,7 +15457,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:15</t>
+          <t>2026-04-28 19:05:25</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
@@ -15298,7 +15466,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>418</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -15318,7 +15486,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-04-28 19:05:25</t>
+          <t>2026-04-28 19:06:58</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -15327,17 +15495,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>423</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -15347,7 +15515,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-04-28 19:06:58</t>
+          <t>2026-04-28 19:16:34</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
@@ -15356,17 +15524,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>435</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -15376,7 +15544,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-04-28 19:16:34</t>
+          <t>2026-04-28 19:34:42</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -15385,17 +15553,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>250</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>follow_up</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -15405,7 +15573,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-04-28 19:34:42</t>
+          <t>2026-03-31 19:22:45</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -15414,7 +15582,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>251</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -15424,7 +15592,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -15434,7 +15602,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-03-31 19:22:45</t>
+          <t>2026-03-31 19:37:10</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -15443,17 +15611,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>252</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -15463,7 +15631,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-03-31 19:37:10</t>
+          <t>2026-04-01 14:30:00</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -15472,7 +15640,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>253</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -15492,7 +15660,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-04-01 14:30:00</t>
+          <t>2026-04-01 16:53:36</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -15501,17 +15669,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>518</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -15521,7 +15689,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-04-01 16:53:36</t>
+          <t>2026-05-07 12:22:45</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
@@ -15530,7 +15698,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>520</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -15550,7 +15718,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-05-07 12:22:45</t>
+          <t>2026-05-07 12:24:53</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
@@ -15559,7 +15727,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>523</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -15579,7 +15747,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-05-07 12:24:53</t>
+          <t>2026-05-07 12:30:02</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
@@ -15588,17 +15756,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>271</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -15608,7 +15776,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-05-07 12:30:02</t>
+          <t>2026-04-07 15:24:02</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
@@ -15617,17 +15785,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>272</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15637,7 +15805,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-04-07 15:24:02</t>
+          <t>2026-04-07 16:00:48</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
@@ -15646,17 +15814,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>327</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -15666,7 +15834,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-04-07 16:00:48</t>
+          <t>2026-04-24 11:55:32</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
@@ -15675,7 +15843,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>342</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -15695,7 +15863,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-04-24 11:55:32</t>
+          <t>2026-04-27 16:17:36</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
@@ -15704,7 +15872,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>345</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -15724,7 +15892,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-04-27 16:17:36</t>
+          <t>2026-04-27 16:20:52</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -15733,7 +15901,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>348</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -15753,7 +15921,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-04-27 16:20:52</t>
+          <t>2026-04-27 16:22:53</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
@@ -15762,7 +15930,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>350</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -15782,7 +15950,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-04-27 16:22:53</t>
+          <t>2026-04-27 16:24:00</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
@@ -15791,7 +15959,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>353</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -15811,7 +15979,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-04-27 16:24:00</t>
+          <t>2026-04-27 16:27:53</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
@@ -15820,17 +15988,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>274</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15840,7 +16008,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-04-27 16:27:53</t>
+          <t>2026-04-08 16:38:00</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
@@ -15849,17 +16017,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>275</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15869,7 +16037,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-04-08 16:38:00</t>
+          <t>2026-04-08 18:21:03</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
@@ -15878,7 +16046,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>308</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -15898,7 +16066,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-04-08 18:21:03</t>
+          <t>2026-04-23 18:22:34</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
@@ -15907,7 +16075,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>310</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -15927,7 +16095,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-04-23 18:22:34</t>
+          <t>2026-04-23 18:24:52</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
@@ -15936,7 +16104,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>376</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -15956,7 +16124,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-04-23 18:24:52</t>
+          <t>2026-04-27 16:43:32</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
@@ -15965,17 +16133,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>378</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15985,7 +16153,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-04-27 16:43:32</t>
+          <t>2026-04-27 16:44:32</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
@@ -15994,17 +16162,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>381</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16014,7 +16182,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-04-27 16:44:32</t>
+          <t>2026-04-27 16:47:27</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
@@ -16023,7 +16191,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>383</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -16043,7 +16211,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-04-27 16:47:27</t>
+          <t>2026-04-27 16:48:30</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -16052,17 +16220,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>384</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16072,7 +16240,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-04-27 16:48:30</t>
+          <t>2026-04-27 16:49:41</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -16081,17 +16249,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>386</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16101,7 +16269,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-04-27 16:49:41</t>
+          <t>2026-04-27 16:51:50</t>
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
@@ -16110,7 +16278,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>436</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -16130,7 +16298,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-04-27 16:51:50</t>
+          <t>2026-04-28 19:34:54</t>
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
@@ -16139,7 +16307,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>579</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -16159,7 +16327,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-04-28 19:34:54</t>
+          <t>2026-05-13 12:28:13</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -16168,7 +16336,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>581</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -16188,7 +16356,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-05-13 12:28:13</t>
+          <t>2026-05-13 12:32:44</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
@@ -16197,17 +16365,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>276</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -16217,7 +16385,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-05-13 12:32:44</t>
+          <t>2026-04-09 14:38:33</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -16226,17 +16394,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>277</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16246,7 +16414,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-04-09 14:38:33</t>
+          <t>2026-04-09 14:50:24</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
@@ -16255,17 +16423,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>343</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16275,7 +16443,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-04-09 14:50:24</t>
+          <t>2026-04-27 16:17:54</t>
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
@@ -16284,17 +16452,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>344</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>email</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16304,7 +16472,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-04-27 16:17:54</t>
+          <t>2026-04-27 16:19:16</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
@@ -16313,17 +16481,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>346</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16333,7 +16501,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-04-27 16:19:16</t>
+          <t>2026-04-27 16:21:26</t>
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
@@ -16342,17 +16510,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>357</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16362,7 +16530,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-04-27 16:21:26</t>
+          <t>2026-04-27 16:30:33</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
@@ -16371,17 +16539,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>362</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16391,7 +16559,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-04-27 16:30:33</t>
+          <t>2026-04-27 16:34:07</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
@@ -16400,17 +16568,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>365</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16420,7 +16588,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-04-27 16:34:07</t>
+          <t>2026-04-27 16:35:11</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
@@ -16429,7 +16597,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>391</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -16449,7 +16617,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-04-27 16:35:11</t>
+          <t>2026-04-27 18:05:29</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -16458,7 +16626,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>426</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -16478,7 +16646,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:29</t>
+          <t>2026-04-28 19:20:18</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -16487,7 +16655,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>428</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -16507,7 +16675,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-04-28 19:20:18</t>
+          <t>2026-04-28 19:22:33</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
@@ -16516,7 +16684,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>430</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -16536,7 +16704,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-04-28 19:22:33</t>
+          <t>2026-04-28 19:27:09</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
@@ -16545,17 +16713,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>286</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -16565,7 +16733,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-04-28 19:27:09</t>
+          <t>2026-04-13 15:45:27</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
@@ -16574,7 +16742,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>287</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -16594,7 +16762,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-04-13 15:45:27</t>
+          <t>2026-04-13 15:46:25</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
@@ -16603,17 +16771,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>288</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -16623,7 +16791,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-04-13 15:46:25</t>
+          <t>2026-04-13 15:53:15</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
@@ -16632,17 +16800,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>289</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -16652,7 +16820,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-04-13 15:53:15</t>
+          <t>2026-04-13 15:58:50</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
@@ -16661,17 +16829,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>351</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -16681,7 +16849,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-04-13 15:58:50</t>
+          <t>2026-04-27 16:24:24</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
@@ -16690,17 +16858,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>354</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -16710,7 +16878,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-04-27 16:24:24</t>
+          <t>2026-04-27 16:28:22</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
@@ -16719,17 +16887,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>366</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -16739,7 +16907,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-04-27 16:28:22</t>
+          <t>2026-04-27 16:35:40</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
@@ -16748,7 +16916,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>419</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -16768,7 +16936,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-04-27 16:35:40</t>
+          <t>2026-04-28 19:07:14</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
@@ -16777,7 +16945,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>424</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -16797,7 +16965,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-04-28 19:07:14</t>
+          <t>2026-04-28 19:16:45</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
@@ -16806,17 +16974,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>356</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -16826,7 +16994,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-04-28 19:16:45</t>
+          <t>2026-04-27 16:29:25</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
@@ -16835,7 +17003,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>358</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -16855,7 +17023,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-04-27 16:29:25</t>
+          <t>2026-04-27 16:31:00</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -16864,17 +17032,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>371</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -16884,7 +17052,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-04-27 16:31:00</t>
+          <t>2026-04-27 16:39:21</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -16893,7 +17061,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>373</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -16913,7 +17081,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-04-27 16:39:21</t>
+          <t>2026-04-27 16:40:26</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -16922,7 +17090,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>374</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -16942,7 +17110,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-04-27 16:40:26</t>
+          <t>2026-04-27 16:42:47</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
@@ -16951,17 +17119,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>294</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -16971,7 +17139,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-04-27 16:42:47</t>
+          <t>2026-04-15 16:05:12</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -16980,7 +17148,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>295</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -17000,7 +17168,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-04-15 16:05:12</t>
+          <t>2026-04-15 18:17:17</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
@@ -17009,17 +17177,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>367</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -17029,7 +17197,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-04-15 18:17:17</t>
+          <t>2026-04-27 16:35:57</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -17038,7 +17206,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>387</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -17058,7 +17226,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-04-27 16:35:57</t>
+          <t>2026-04-27 16:52:02</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
@@ -17067,17 +17235,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>421</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -17087,7 +17255,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-04-27 16:52:02</t>
+          <t>2026-04-28 19:11:23</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
@@ -17096,17 +17264,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>451</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -17116,7 +17284,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-04-28 19:11:23</t>
+          <t>2026-04-30 14:38:42</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
@@ -17125,17 +17293,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>296</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -17145,7 +17313,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-04-30 14:38:42</t>
+          <t>2026-04-16 12:32:37</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -17154,17 +17322,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>297</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -17174,7 +17342,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-04-16 12:32:37</t>
+          <t>2026-04-16 12:52:16</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
@@ -17183,17 +17351,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>368</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -17203,7 +17371,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-04-16 12:52:16</t>
+          <t>2026-04-27 16:37:49</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
@@ -17212,17 +17380,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>379</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -17232,7 +17400,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-04-27 16:37:49</t>
+          <t>2026-04-27 16:45:32</t>
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
@@ -17241,17 +17409,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>382</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -17261,7 +17429,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-04-27 16:45:32</t>
+          <t>2026-04-27 16:47:40</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
@@ -17270,17 +17438,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>299</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -17290,7 +17458,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-04-27 16:47:40</t>
+          <t>2026-04-16 18:41:52</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
@@ -17299,17 +17467,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>312</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -17319,7 +17487,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-04-16 18:41:52</t>
+          <t>2026-04-23 18:27:22</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
@@ -17328,7 +17496,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>314</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -17348,7 +17516,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-04-23 18:27:22</t>
+          <t>2026-04-23 18:30:25</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
@@ -17357,7 +17525,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>377</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -17377,7 +17545,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-04-23 18:30:25</t>
+          <t>2026-04-27 16:43:45</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
@@ -17386,17 +17554,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>317</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -17406,7 +17574,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-04-27 16:43:45</t>
+          <t>2026-04-23 18:40:56</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -17415,17 +17583,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -17435,7 +17603,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-04-23 18:40:56</t>
+          <t>2026-04-21 15:49:30</t>
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
@@ -17444,17 +17612,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>301</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -17464,7 +17632,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-04-21 15:49:30</t>
+          <t>2026-04-21 15:52:28</t>
         </is>
       </c>
       <c r="F174" t="inlineStr"/>
@@ -17473,17 +17641,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>302</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -17493,7 +17661,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-04-21 15:52:28</t>
+          <t>2026-04-21 17:03:38</t>
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
@@ -17502,17 +17670,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>303</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -17522,7 +17690,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-04-21 17:03:38</t>
+          <t>2026-04-22 16:41:07</t>
         </is>
       </c>
       <c r="F176" t="inlineStr"/>
@@ -17531,17 +17699,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>392</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -17551,7 +17719,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-04-22 16:41:07</t>
+          <t>2026-04-27 18:05:41</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -17560,7 +17728,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>437</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -17580,7 +17748,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:41</t>
+          <t>2026-04-28 19:35:07</t>
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
@@ -17589,7 +17757,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>500</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -17609,7 +17777,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-04-28 19:35:07</t>
+          <t>2026-05-06 17:53:39</t>
         </is>
       </c>
       <c r="F179" t="inlineStr"/>
@@ -17618,7 +17786,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>521</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -17638,7 +17806,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-05-06 17:53:39</t>
+          <t>2026-05-07 12:25:07</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
@@ -17647,17 +17815,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>306</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -17667,7 +17835,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-05-07 12:25:07</t>
+          <t>2026-04-23 15:49:56</t>
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
@@ -17676,17 +17844,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>307</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -17696,7 +17864,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2026-04-23 15:49:56</t>
+          <t>2026-04-23 18:16:45</t>
         </is>
       </c>
       <c r="F182" t="inlineStr"/>
@@ -17705,7 +17873,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>309</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -17725,7 +17893,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-04-23 18:16:45</t>
+          <t>2026-04-23 18:22:46</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
@@ -17734,7 +17902,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>311</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -17754,7 +17922,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-04-23 18:22:46</t>
+          <t>2026-04-23 18:25:02</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -17763,7 +17931,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>313</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -17783,7 +17951,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-04-23 18:25:02</t>
+          <t>2026-04-23 18:27:36</t>
         </is>
       </c>
       <c r="F185" t="inlineStr"/>
@@ -17792,7 +17960,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>394</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -17812,7 +17980,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-04-23 18:27:36</t>
+          <t>2026-04-27 18:07:45</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
@@ -17821,7 +17989,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>397</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -17841,7 +18009,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-04-27 18:07:45</t>
+          <t>2026-04-27 18:12:10</t>
         </is>
       </c>
       <c r="F187" t="inlineStr"/>
@@ -17850,7 +18018,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>315</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -17870,7 +18038,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-04-27 18:12:10</t>
+          <t>2026-04-23 18:30:34</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
@@ -17879,17 +18047,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>316</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -17899,7 +18067,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-04-23 18:30:34</t>
+          <t>2026-04-23 18:35:35</t>
         </is>
       </c>
       <c r="F189" t="inlineStr"/>
@@ -17908,17 +18076,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>318</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -17928,7 +18096,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2026-04-23 18:35:35</t>
+          <t>2026-04-23 18:41:25</t>
         </is>
       </c>
       <c r="F190" t="inlineStr"/>
@@ -17937,17 +18105,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -17957,7 +18125,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-04-23 18:41:25</t>
+          <t>2026-04-23 18:46:12</t>
         </is>
       </c>
       <c r="F191" t="inlineStr"/>
@@ -17966,17 +18134,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>321</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -17986,7 +18154,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-04-23 18:46:12</t>
+          <t>2026-04-23 18:58:17</t>
         </is>
       </c>
       <c r="F192" t="inlineStr"/>
@@ -17995,17 +18163,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>322</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -18015,7 +18183,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-04-23 18:58:17</t>
+          <t>2026-04-23 19:09:01</t>
         </is>
       </c>
       <c r="F193" t="inlineStr"/>
@@ -18024,17 +18192,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>323</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -18044,7 +18212,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-04-23 19:09:01</t>
+          <t>2026-04-23 19:28:02</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -18053,7 +18221,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>324</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -18073,7 +18241,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-04-23 19:28:02</t>
+          <t>2026-04-23 19:33:02</t>
         </is>
       </c>
       <c r="F195" t="inlineStr"/>
@@ -18082,17 +18250,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>325</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -18102,7 +18270,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2026-04-23 19:33:02</t>
+          <t>2026-04-23 19:35:57</t>
         </is>
       </c>
       <c r="F196" t="inlineStr"/>
@@ -18111,17 +18279,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>326</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -18131,7 +18299,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-04-23 19:35:57</t>
+          <t>2026-04-24 11:52:45</t>
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
@@ -18140,17 +18308,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>328</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -18160,7 +18328,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-04-24 11:52:45</t>
+          <t>2026-04-24 11:55:39</t>
         </is>
       </c>
       <c r="F198" t="inlineStr"/>
@@ -18169,17 +18337,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>329</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -18189,7 +18357,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-04-24 11:55:39</t>
+          <t>2026-04-24 12:13:00</t>
         </is>
       </c>
       <c r="F199" t="inlineStr"/>
@@ -18198,7 +18366,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>330</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -18218,7 +18386,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2026-04-24 12:13:00</t>
+          <t>2026-04-24 12:17:05</t>
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
@@ -18227,17 +18395,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>331</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -18247,7 +18415,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-04-24 12:17:05</t>
+          <t>2026-04-24 12:19:39</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -18256,17 +18424,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>332</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -18276,7 +18444,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-04-24 12:19:39</t>
+          <t>2026-04-24 12:31:15</t>
         </is>
       </c>
       <c r="F202" t="inlineStr"/>
@@ -18285,17 +18453,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>333</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -18305,7 +18473,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-04-24 12:31:15</t>
+          <t>2026-04-24 12:33:01</t>
         </is>
       </c>
       <c r="F203" t="inlineStr"/>
@@ -18314,17 +18482,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>334</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -18334,7 +18502,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-04-24 12:33:01</t>
+          <t>2026-04-24 14:36:24</t>
         </is>
       </c>
       <c r="F204" t="inlineStr"/>
@@ -18343,7 +18511,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>335</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -18363,7 +18531,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-04-24 14:36:24</t>
+          <t>2026-04-24 14:43:03</t>
         </is>
       </c>
       <c r="F205" t="inlineStr"/>
@@ -18372,17 +18540,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>336</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -18392,7 +18560,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-04-24 14:43:03</t>
+          <t>2026-04-24 14:58:00</t>
         </is>
       </c>
       <c r="F206" t="inlineStr"/>
@@ -18401,17 +18569,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>337</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -18421,7 +18589,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-04-24 14:58:00</t>
+          <t>2026-04-27 14:06:10</t>
         </is>
       </c>
       <c r="F207" t="inlineStr"/>
@@ -18430,17 +18598,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>338</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -18450,7 +18618,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-04-27 14:06:10</t>
+          <t>2026-04-27 14:10:21</t>
         </is>
       </c>
       <c r="F208" t="inlineStr"/>
@@ -18459,17 +18627,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>339</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -18479,7 +18647,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-04-27 14:10:21</t>
+          <t>2026-04-27 14:13:06</t>
         </is>
       </c>
       <c r="F209" t="inlineStr"/>
@@ -18488,17 +18656,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>340</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -18508,7 +18676,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2026-04-27 14:13:06</t>
+          <t>2026-04-27 14:15:47</t>
         </is>
       </c>
       <c r="F210" t="inlineStr"/>
@@ -18517,17 +18685,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>393</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -18537,7 +18705,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-04-27 14:15:47</t>
+          <t>2026-04-27 18:05:51</t>
         </is>
       </c>
       <c r="F211" t="inlineStr"/>
@@ -18546,17 +18714,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>395</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -18566,7 +18734,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:51</t>
+          <t>2026-04-27 18:08:12</t>
         </is>
       </c>
       <c r="F212" t="inlineStr"/>
@@ -18575,17 +18743,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>396</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -18595,7 +18763,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-04-27 18:08:12</t>
+          <t>2026-04-27 18:10:09</t>
         </is>
       </c>
       <c r="F213" t="inlineStr"/>
@@ -18604,17 +18772,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>398</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -18624,7 +18792,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-04-27 18:10:09</t>
+          <t>2026-04-27 18:12:49</t>
         </is>
       </c>
       <c r="F214" t="inlineStr"/>
@@ -18633,17 +18801,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>399</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -18653,7 +18821,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-04-27 18:12:49</t>
+          <t>2026-04-27 18:25:23</t>
         </is>
       </c>
       <c r="F215" t="inlineStr"/>
@@ -18662,17 +18830,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>400</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -18682,7 +18850,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-04-27 18:25:23</t>
+          <t>2026-04-27 18:26:29</t>
         </is>
       </c>
       <c r="F216" t="inlineStr"/>
@@ -18691,7 +18859,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>401</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18711,7 +18879,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-04-27 18:26:29</t>
+          <t>2026-04-27 18:28:56</t>
         </is>
       </c>
       <c r="F217" t="inlineStr"/>
@@ -18720,7 +18888,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>402</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18740,7 +18908,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-04-27 18:28:56</t>
+          <t>2026-04-27 18:32:14</t>
         </is>
       </c>
       <c r="F218" t="inlineStr"/>
@@ -18749,7 +18917,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>403</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18769,7 +18937,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-04-27 18:32:14</t>
+          <t>2026-04-27 19:10:16</t>
         </is>
       </c>
       <c r="F219" t="inlineStr"/>
@@ -18778,7 +18946,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>404</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18798,7 +18966,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-04-27 19:10:16</t>
+          <t>2026-04-28 13:06:06</t>
         </is>
       </c>
       <c r="F220" t="inlineStr"/>
@@ -18807,17 +18975,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>405</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -18827,7 +18995,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-04-28 13:06:06</t>
+          <t>2026-04-28 13:09:10</t>
         </is>
       </c>
       <c r="F221" t="inlineStr"/>
@@ -18836,17 +19004,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>406</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -18856,7 +19024,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-04-28 13:09:10</t>
+          <t>2026-04-28 13:31:57</t>
         </is>
       </c>
       <c r="F222" t="inlineStr"/>
@@ -18865,7 +19033,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>408</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18885,7 +19053,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-04-28 13:31:57</t>
+          <t>2026-04-28 16:36:52</t>
         </is>
       </c>
       <c r="F223" t="inlineStr"/>
@@ -18894,17 +19062,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>409</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -18914,7 +19082,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-04-28 16:36:52</t>
+          <t>2026-04-28 16:41:55</t>
         </is>
       </c>
       <c r="F224" t="inlineStr"/>
@@ -18923,7 +19091,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>410</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18943,7 +19111,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-04-28 16:41:55</t>
+          <t>2026-04-28 16:45:43</t>
         </is>
       </c>
       <c r="F225" t="inlineStr"/>
@@ -18952,17 +19120,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>411</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -18972,7 +19140,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-04-28 16:45:43</t>
+          <t>2026-04-28 16:50:41</t>
         </is>
       </c>
       <c r="F226" t="inlineStr"/>
@@ -18981,17 +19149,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>412</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -19001,7 +19169,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-04-28 16:50:41</t>
+          <t>2026-04-28 16:58:22</t>
         </is>
       </c>
       <c r="F227" t="inlineStr"/>
@@ -19010,17 +19178,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>422</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -19030,7 +19198,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-04-28 16:58:22</t>
+          <t>2026-04-28 19:11:43</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
@@ -19039,17 +19207,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>425</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -19059,7 +19227,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-04-28 19:11:43</t>
+          <t>2026-04-28 19:17:29</t>
         </is>
       </c>
       <c r="F229" t="inlineStr"/>
@@ -19068,17 +19236,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>427</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -19088,7 +19256,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-04-28 19:17:29</t>
+          <t>2026-04-28 19:20:41</t>
         </is>
       </c>
       <c r="F230" t="inlineStr"/>
@@ -19097,7 +19265,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>431</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -19117,7 +19285,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-04-28 19:20:41</t>
+          <t>2026-04-28 19:27:32</t>
         </is>
       </c>
       <c r="F231" t="inlineStr"/>
@@ -19126,17 +19294,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>432</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -19146,7 +19314,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-04-28 19:27:32</t>
+          <t>2026-04-28 19:29:59</t>
         </is>
       </c>
       <c r="F232" t="inlineStr"/>
@@ -19155,17 +19323,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>438</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -19175,7 +19343,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-04-28 19:29:59</t>
+          <t>2026-04-28 19:38:54</t>
         </is>
       </c>
       <c r="F233" t="inlineStr"/>
@@ -19184,17 +19352,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>413</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -19204,7 +19372,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-04-28 19:38:54</t>
+          <t>2026-04-28 18:59:52</t>
         </is>
       </c>
       <c r="F234" t="inlineStr"/>
@@ -19213,17 +19381,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>416</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -19233,7 +19401,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-04-28 18:59:52</t>
+          <t>2026-04-28 19:05:38</t>
         </is>
       </c>
       <c r="F235" t="inlineStr"/>
@@ -19242,7 +19410,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>420</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -19262,7 +19430,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2026-04-28 19:05:38</t>
+          <t>2026-04-28 19:09:07</t>
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
@@ -19271,7 +19439,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>429</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19291,7 +19459,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-04-28 19:09:07</t>
+          <t>2026-04-28 19:22:49</t>
         </is>
       </c>
       <c r="F237" t="inlineStr"/>
@@ -19300,17 +19468,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>439</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -19320,7 +19488,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-04-28 19:22:49</t>
+          <t>2026-04-28 19:46:42</t>
         </is>
       </c>
       <c r="F238" t="inlineStr"/>
@@ -19329,17 +19497,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>440</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -19349,7 +19517,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-04-28 19:46:42</t>
+          <t>2026-04-29 15:54:41</t>
         </is>
       </c>
       <c r="F239" t="inlineStr"/>
@@ -19358,7 +19526,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>441</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19378,7 +19546,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-04-29 15:54:41</t>
+          <t>2026-04-29 15:56:41</t>
         </is>
       </c>
       <c r="F240" t="inlineStr"/>
@@ -19387,17 +19555,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>442</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -19407,7 +19575,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-04-29 15:56:41</t>
+          <t>2026-04-29 16:10:35</t>
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
@@ -19416,17 +19584,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>443</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -19436,7 +19604,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-04-29 16:10:35</t>
+          <t>2026-04-29 16:13:57</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
@@ -19445,17 +19613,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>444</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -19465,7 +19633,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-04-29 16:13:57</t>
+          <t>2026-04-29 16:17:13</t>
         </is>
       </c>
       <c r="F243" t="inlineStr"/>
@@ -19474,7 +19642,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>445</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19494,7 +19662,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-04-29 16:17:13</t>
+          <t>2026-04-29 16:21:56</t>
         </is>
       </c>
       <c r="F244" t="inlineStr"/>
@@ -19503,7 +19671,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>446</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19523,7 +19691,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-04-29 16:21:56</t>
+          <t>2026-04-29 16:26:19</t>
         </is>
       </c>
       <c r="F245" t="inlineStr"/>
@@ -19532,7 +19700,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>447</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19552,7 +19720,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-04-29 16:26:19</t>
+          <t>2026-04-30 11:56:22</t>
         </is>
       </c>
       <c r="F246" t="inlineStr"/>
@@ -19561,7 +19729,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>448</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19581,7 +19749,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-04-30 11:56:22</t>
+          <t>2026-04-30 12:18:39</t>
         </is>
       </c>
       <c r="F247" t="inlineStr"/>
@@ -19590,7 +19758,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>449</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19610,7 +19778,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-04-30 12:18:39</t>
+          <t>2026-04-30 12:27:47</t>
         </is>
       </c>
       <c r="F248" t="inlineStr"/>
@@ -19619,17 +19787,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>450</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -19639,7 +19807,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-04-30 12:27:47</t>
+          <t>2026-04-30 14:33:48</t>
         </is>
       </c>
       <c r="F249" t="inlineStr"/>
@@ -19648,17 +19816,17 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>452</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -19668,7 +19836,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-04-30 14:33:48</t>
+          <t>2026-04-30 14:39:11</t>
         </is>
       </c>
       <c r="F250" t="inlineStr"/>
@@ -19677,17 +19845,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>453</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -19697,7 +19865,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-04-30 14:39:11</t>
+          <t>2026-04-30 14:44:06</t>
         </is>
       </c>
       <c r="F251" t="inlineStr"/>
@@ -19706,17 +19874,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>454</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -19726,7 +19894,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-04-30 14:44:06</t>
+          <t>2026-04-30 14:50:48</t>
         </is>
       </c>
       <c r="F252" t="inlineStr"/>
@@ -19735,17 +19903,17 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>455</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -19755,7 +19923,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-04-30 14:50:48</t>
+          <t>2026-04-30 15:03:19</t>
         </is>
       </c>
       <c r="F253" t="inlineStr"/>
@@ -19764,7 +19932,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>456</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19784,7 +19952,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-04-30 15:03:19</t>
+          <t>2026-04-30 16:43:14</t>
         </is>
       </c>
       <c r="F254" t="inlineStr"/>
@@ -19793,7 +19961,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>457</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19813,7 +19981,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-04-30 16:43:14</t>
+          <t>2026-04-30 16:49:38</t>
         </is>
       </c>
       <c r="F255" t="inlineStr"/>
@@ -19822,17 +19990,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>458</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -19842,7 +20010,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2026-04-30 16:49:38</t>
+          <t>2026-04-30 16:57:13</t>
         </is>
       </c>
       <c r="F256" t="inlineStr"/>
@@ -19851,17 +20019,17 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>459</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -19871,7 +20039,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-04-30 16:57:13</t>
+          <t>2026-04-30 16:59:14</t>
         </is>
       </c>
       <c r="F257" t="inlineStr"/>
@@ -19880,17 +20048,17 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -19900,7 +20068,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-04-30 16:59:14</t>
+          <t>2026-04-30 17:03:09</t>
         </is>
       </c>
       <c r="F258" t="inlineStr"/>
@@ -19909,7 +20077,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>461</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -19929,7 +20097,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-04-30 17:03:09</t>
+          <t>2026-04-30 17:07:20</t>
         </is>
       </c>
       <c r="F259" t="inlineStr"/>
@@ -19938,7 +20106,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>462</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -19958,7 +20126,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-04-30 17:07:20</t>
+          <t>2026-04-30 17:20:16</t>
         </is>
       </c>
       <c r="F260" t="inlineStr"/>
@@ -19967,7 +20135,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>465</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -19987,7 +20155,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-04-30 17:20:16</t>
+          <t>2026-05-04 12:40:26</t>
         </is>
       </c>
       <c r="F261" t="inlineStr"/>
@@ -19996,17 +20164,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>466</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -20016,7 +20184,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-05-04 12:40:26</t>
+          <t>2026-05-04 13:27:46</t>
         </is>
       </c>
       <c r="F262" t="inlineStr"/>
@@ -20025,17 +20193,17 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>467</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -20045,7 +20213,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-05-04 13:27:46</t>
+          <t>2026-05-04 13:32:27</t>
         </is>
       </c>
       <c r="F263" t="inlineStr"/>
@@ -20054,17 +20222,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>468</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -20074,7 +20242,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-05-04 13:32:27</t>
+          <t>2026-05-04 13:35:31</t>
         </is>
       </c>
       <c r="F264" t="inlineStr"/>
@@ -20083,7 +20251,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>469</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20103,7 +20271,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-05-04 13:35:31</t>
+          <t>2026-05-04 13:52:33</t>
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
@@ -20112,17 +20280,17 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>470</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -20132,7 +20300,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-05-04 13:52:33</t>
+          <t>2026-05-04 14:15:29</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
@@ -20141,7 +20309,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>471</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20161,7 +20329,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-05-04 14:15:29</t>
+          <t>2026-05-04 14:21:26</t>
         </is>
       </c>
       <c r="F267" t="inlineStr"/>
@@ -20170,7 +20338,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>472</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -20190,7 +20358,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-05-04 14:21:26</t>
+          <t>2026-05-04 14:28:28</t>
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
@@ -20199,17 +20367,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>473</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -20219,7 +20387,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-05-04 14:28:28</t>
+          <t>2026-05-05 12:33:28</t>
         </is>
       </c>
       <c r="F269" t="inlineStr"/>
@@ -20228,17 +20396,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>474</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -20248,7 +20416,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-05-05 12:33:28</t>
+          <t>2026-05-05 12:36:49</t>
         </is>
       </c>
       <c r="F270" t="inlineStr"/>
@@ -20257,17 +20425,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>475</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -20277,7 +20445,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-05-05 12:36:49</t>
+          <t>2026-05-05 13:16:10</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
@@ -20286,7 +20454,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>476</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -20306,7 +20474,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-05-05 13:16:10</t>
+          <t>2026-05-05 13:22:28</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
@@ -20315,7 +20483,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>478</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -20335,7 +20503,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-05-05 13:22:28</t>
+          <t>2026-05-05 15:49:32</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
@@ -20344,7 +20512,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>484</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -20364,7 +20532,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-05-05 15:49:32</t>
+          <t>2026-05-05 18:17:18</t>
         </is>
       </c>
       <c r="F274" t="inlineStr"/>
@@ -20373,17 +20541,17 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>485</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -20393,7 +20561,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-05-05 18:17:18</t>
+          <t>2026-05-05 18:23:24</t>
         </is>
       </c>
       <c r="F275" t="inlineStr"/>
@@ -20402,17 +20570,17 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>486</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -20422,7 +20590,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-05-05 18:23:24</t>
+          <t>2026-05-05 18:30:18</t>
         </is>
       </c>
       <c r="F276" t="inlineStr"/>
@@ -20431,17 +20599,17 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>487</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -20451,7 +20619,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-05-05 18:30:18</t>
+          <t>2026-05-05 19:24:36</t>
         </is>
       </c>
       <c r="F277" t="inlineStr"/>
@@ -20460,17 +20628,17 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>488</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -20480,7 +20648,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-05-05 19:24:36</t>
+          <t>2026-05-06 14:07:52</t>
         </is>
       </c>
       <c r="F278" t="inlineStr"/>
@@ -20489,17 +20657,17 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>489</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -20509,7 +20677,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-05-06 14:07:52</t>
+          <t>2026-05-06 14:12:50</t>
         </is>
       </c>
       <c r="F279" t="inlineStr"/>
@@ -20518,17 +20686,17 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>490</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -20538,7 +20706,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-05-06 14:12:50</t>
+          <t>2026-05-06 14:15:34</t>
         </is>
       </c>
       <c r="F280" t="inlineStr"/>
@@ -20547,17 +20715,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -20567,7 +20735,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-05-06 14:15:34</t>
+          <t>2026-05-06 14:59:26</t>
         </is>
       </c>
       <c r="F281" t="inlineStr"/>
@@ -20576,17 +20744,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>492</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -20596,7 +20764,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-05-06 14:59:26</t>
+          <t>2026-05-06 15:04:52</t>
         </is>
       </c>
       <c r="F282" t="inlineStr"/>
@@ -20605,7 +20773,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>493</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -20625,7 +20793,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-05-06 15:04:52</t>
+          <t>2026-05-06 15:08:51</t>
         </is>
       </c>
       <c r="F283" t="inlineStr"/>
@@ -20634,17 +20802,17 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>494</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Busy</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -20654,7 +20822,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-05-06 15:08:51</t>
+          <t>2026-05-06 15:28:38</t>
         </is>
       </c>
       <c r="F284" t="inlineStr"/>
@@ -20663,17 +20831,17 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>495</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Busy</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -20683,7 +20851,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-05-06 15:28:38</t>
+          <t>2026-05-06 15:31:36</t>
         </is>
       </c>
       <c r="F285" t="inlineStr"/>
@@ -20692,17 +20860,17 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>501</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -20712,7 +20880,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-05-06 15:31:36</t>
+          <t>2026-05-06 17:53:50</t>
         </is>
       </c>
       <c r="F286" t="inlineStr"/>
@@ -20721,7 +20889,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>502</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -20741,7 +20909,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-05-06 17:53:50</t>
+          <t>2026-05-06 17:59:31</t>
         </is>
       </c>
       <c r="F287" t="inlineStr"/>
@@ -20750,17 +20918,17 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>503</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -20770,7 +20938,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>2026-05-06 17:59:31</t>
+          <t>2026-05-06 19:18:14</t>
         </is>
       </c>
       <c r="F288" t="inlineStr"/>
@@ -20779,17 +20947,17 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>504</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -20799,7 +20967,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-05-06 19:18:14</t>
+          <t>2026-05-06 19:21:01</t>
         </is>
       </c>
       <c r="F289" t="inlineStr"/>
@@ -20808,7 +20976,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>505</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -20828,7 +20996,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-05-06 19:21:01</t>
+          <t>2026-05-06 19:25:27</t>
         </is>
       </c>
       <c r="F290" t="inlineStr"/>
@@ -20837,7 +21005,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>506</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -20857,7 +21025,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-05-06 19:25:27</t>
+          <t>2026-05-06 19:27:23</t>
         </is>
       </c>
       <c r="F291" t="inlineStr"/>
@@ -20866,17 +21034,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>507</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -20886,7 +21054,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-05-06 19:27:23</t>
+          <t>2026-05-06 19:39:21</t>
         </is>
       </c>
       <c r="F292" t="inlineStr"/>
@@ -20895,17 +21063,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>509</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -20915,7 +21083,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-05-06 19:39:21</t>
+          <t>2026-05-06 20:09:52</t>
         </is>
       </c>
       <c r="F293" t="inlineStr"/>
@@ -20924,17 +21092,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>511</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -20944,7 +21112,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2026-05-06 20:09:52</t>
+          <t>2026-05-06 20:12:28</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
@@ -20953,7 +21121,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>512</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -20973,7 +21141,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-05-06 20:12:28</t>
+          <t>2026-05-07 12:02:27</t>
         </is>
       </c>
       <c r="F295" t="inlineStr"/>
@@ -20982,17 +21150,17 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>513</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -21002,7 +21170,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-05-07 12:02:27</t>
+          <t>2026-05-07 12:05:31</t>
         </is>
       </c>
       <c r="F296" t="inlineStr"/>
@@ -21011,17 +21179,17 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>514</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -21031,7 +21199,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-05-07 12:05:31</t>
+          <t>2026-05-07 12:07:46</t>
         </is>
       </c>
       <c r="F297" t="inlineStr"/>
@@ -21040,17 +21208,17 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>515</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -21060,7 +21228,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-05-07 12:07:46</t>
+          <t>2026-05-07 12:12:23</t>
         </is>
       </c>
       <c r="F298" t="inlineStr"/>
@@ -21069,17 +21237,17 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>516</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -21089,7 +21257,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-05-07 12:12:23</t>
+          <t>2026-05-07 12:21:17</t>
         </is>
       </c>
       <c r="F299" t="inlineStr"/>
@@ -21098,7 +21266,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>517</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -21118,7 +21286,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-05-07 12:21:17</t>
+          <t>2026-05-07 12:22:26</t>
         </is>
       </c>
       <c r="F300" t="inlineStr"/>
@@ -21127,7 +21295,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>522</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -21147,7 +21315,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-05-07 12:22:26</t>
+          <t>2026-05-07 12:25:15</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
@@ -21156,7 +21324,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>524</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -21176,7 +21344,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-05-07 12:25:15</t>
+          <t>2026-05-07 12:30:09</t>
         </is>
       </c>
       <c r="F302" t="inlineStr"/>
@@ -21185,7 +21353,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>527</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -21205,7 +21373,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-05-07 12:30:09</t>
+          <t>2026-05-07 18:11:26</t>
         </is>
       </c>
       <c r="F303" t="inlineStr"/>
@@ -21214,17 +21382,17 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>528</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -21234,7 +21402,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-05-07 18:11:26</t>
+          <t>2026-05-07 18:21:05</t>
         </is>
       </c>
       <c r="F304" t="inlineStr"/>
@@ -21243,17 +21411,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>529</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -21263,7 +21431,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-05-07 18:21:05</t>
+          <t>2026-05-07 18:23:27</t>
         </is>
       </c>
       <c r="F305" t="inlineStr"/>
@@ -21272,17 +21440,17 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>530</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -21292,7 +21460,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-05-07 18:23:27</t>
+          <t>2026-05-07 18:31:47</t>
         </is>
       </c>
       <c r="F306" t="inlineStr"/>
@@ -21301,17 +21469,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>531</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -21321,7 +21489,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-05-07 18:31:47</t>
+          <t>2026-05-07 18:41:02</t>
         </is>
       </c>
       <c r="F307" t="inlineStr"/>
@@ -21330,17 +21498,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>532</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -21350,7 +21518,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-05-07 18:41:02</t>
+          <t>2026-05-07 19:04:03</t>
         </is>
       </c>
       <c r="F308" t="inlineStr"/>
@@ -21359,17 +21527,17 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>533</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -21379,7 +21547,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-05-07 19:04:03</t>
+          <t>2026-05-07 19:12:07</t>
         </is>
       </c>
       <c r="F309" t="inlineStr"/>
@@ -21388,17 +21556,17 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>534</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -21408,7 +21576,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-05-07 19:12:07</t>
+          <t>2026-05-07 19:19:47</t>
         </is>
       </c>
       <c r="F310" t="inlineStr"/>
@@ -21417,7 +21585,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>535</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -21437,7 +21605,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-05-07 19:19:47</t>
+          <t>2026-05-07 19:35:25</t>
         </is>
       </c>
       <c r="F311" t="inlineStr"/>
@@ -21446,7 +21614,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>536</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -21466,7 +21634,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-05-07 19:35:25</t>
+          <t>2026-05-08 12:36:57</t>
         </is>
       </c>
       <c r="F312" t="inlineStr"/>
@@ -21475,7 +21643,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>537</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -21495,7 +21663,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-05-08 12:36:57</t>
+          <t>2026-05-08 12:43:59</t>
         </is>
       </c>
       <c r="F313" t="inlineStr"/>
@@ -21504,17 +21672,17 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>538</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -21524,7 +21692,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-05-08 12:43:59</t>
+          <t>2026-05-08 12:51:09</t>
         </is>
       </c>
       <c r="F314" t="inlineStr"/>
@@ -21533,17 +21701,17 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>539</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -21553,7 +21721,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2026-05-08 12:51:09</t>
+          <t>2026-05-08 12:55:15</t>
         </is>
       </c>
       <c r="F315" t="inlineStr"/>
@@ -21562,7 +21730,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>540</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -21582,7 +21750,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-05-08 12:55:15</t>
+          <t>2026-05-08 12:57:14</t>
         </is>
       </c>
       <c r="F316" t="inlineStr"/>
@@ -21591,7 +21759,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>541</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -21611,7 +21779,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-05-08 12:57:14</t>
+          <t>2026-05-08 13:00:41</t>
         </is>
       </c>
       <c r="F317" t="inlineStr"/>
@@ -21620,17 +21788,17 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>542</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -21640,7 +21808,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-05-08 13:00:41</t>
+          <t>2026-05-08 13:04:02</t>
         </is>
       </c>
       <c r="F318" t="inlineStr"/>
@@ -21649,17 +21817,17 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>543</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -21669,7 +21837,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-05-08 13:04:02</t>
+          <t>2026-05-08 13:09:59</t>
         </is>
       </c>
       <c r="F319" t="inlineStr"/>
@@ -21678,17 +21846,17 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>544</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>WARM LEAD</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>warm_lead</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -21698,7 +21866,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-05-08 13:09:59</t>
+          <t>2026-05-08 13:16:49</t>
         </is>
       </c>
       <c r="F320" t="inlineStr"/>
@@ -21707,17 +21875,17 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>545</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>WARM LEAD</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>warm_lead</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -21727,7 +21895,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-05-08 13:16:49</t>
+          <t>2026-05-08 13:22:02</t>
         </is>
       </c>
       <c r="F321" t="inlineStr"/>
@@ -21736,7 +21904,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>546</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -21756,7 +21924,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-05-08 13:22:02</t>
+          <t>2026-05-08 15:50:51</t>
         </is>
       </c>
       <c r="F322" t="inlineStr"/>
@@ -21765,17 +21933,17 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>547</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -21785,7 +21953,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-05-08 15:50:51</t>
+          <t>2026-05-08 15:54:37</t>
         </is>
       </c>
       <c r="F323" t="inlineStr"/>
@@ -21794,17 +21962,17 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>548</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -21814,7 +21982,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-05-08 15:54:37</t>
+          <t>2026-05-08 15:59:34</t>
         </is>
       </c>
       <c r="F324" t="inlineStr"/>
@@ -21823,7 +21991,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>549</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -21843,7 +22011,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-05-08 15:59:34</t>
+          <t>2026-05-08 16:11:07</t>
         </is>
       </c>
       <c r="F325" t="inlineStr"/>
@@ -21852,17 +22020,17 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>550</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -21872,7 +22040,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-05-08 16:11:07</t>
+          <t>2026-05-08 16:19:50</t>
         </is>
       </c>
       <c r="F326" t="inlineStr"/>
@@ -21881,17 +22049,17 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>551</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -21901,7 +22069,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-05-08 16:19:50</t>
+          <t>2026-05-08 16:24:03</t>
         </is>
       </c>
       <c r="F327" t="inlineStr"/>
@@ -21910,17 +22078,17 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>552</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -21930,7 +22098,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-05-08 16:24:03</t>
+          <t>2026-05-11 18:35:26</t>
         </is>
       </c>
       <c r="F328" t="inlineStr"/>
@@ -22718,6 +22886,209 @@
       </c>
       <c r="F355" t="inlineStr"/>
       <c r="G355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>2026-05-14 12:29:10</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr"/>
+      <c r="G356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>2026-05-14 12:31:42</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr"/>
+      <c r="G357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>2026-05-14 12:34:26</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr"/>
+      <c r="G358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>2026-05-14 12:39:18</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr"/>
+      <c r="G359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Busy</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>busy_call_back</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>2026-05-14 12:53:07</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr"/>
+      <c r="G360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>591</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>2026-05-14 12:57:05</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr"/>
+      <c r="G361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:04:59</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr"/>
+      <c r="G362" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H291"/>
+  <dimension ref="A1:H292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-27 18:02:28</t>
+          <t>2026-05-14 17:58:21</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-04-30 16:43:14</t>
+          <t>2026-05-14 18:00:32</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-04-30 16:49:38</t>
+          <t>2026-05-14 18:07:31</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-04-23 18:25:02</t>
+          <t>2026-05-14 18:16:47</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-04-23 18:27:36</t>
+          <t>2026-05-14 18:23:35</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-03-27 15:05:33</t>
+          <t>2026-05-14 18:35:02</t>
         </is>
       </c>
     </row>
@@ -12567,6 +12567,48 @@
       <c r="H291" t="inlineStr">
         <is>
           <t>2026-05-14 13:04:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>JOE P CURRIER</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>joejrdb@gmail.com</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>(617) 686-6075</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>JR &amp; RJ LLC</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:29:03</t>
         </is>
       </c>
     </row>
@@ -12581,7 +12623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G362"/>
+  <dimension ref="A1:G369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23089,6 +23131,209 @@
       </c>
       <c r="F362" t="inlineStr"/>
       <c r="G362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>2026-05-14 17:58:21</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr"/>
+      <c r="G363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:00:32</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr"/>
+      <c r="G364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:07:31</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:16:47</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr"/>
+      <c r="G366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:23:35</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr"/>
+      <c r="G367" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Not Connecting</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:29:03</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr"/>
+      <c r="G368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:35:02</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr"/>
+      <c r="G369" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H292"/>
+  <dimension ref="A1:H299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12609,6 +12609,300 @@
       <c r="H292" t="inlineStr">
         <is>
           <t>2026-05-14 18:29:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Tony Gallo</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>tgallo@gallomoving.com</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>(508) 422-4400</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Gallo moving</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>2026-05-15 12:51:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>BRUNO MOREIRA</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>rightwaytransporters@gmail.com</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>774) 249-4400</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>RIGHT WAY TRANSPORTERS INC</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>2026-05-15 12:54:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>MICHAEL MANCINI SR</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>mikem@brazamancini.com</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(508) 478-8808 </t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Brazamancini</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>2026-05-15 12:55:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Fatima Afonso</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>afonsorealestate@afonsore.com</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>(508) 478-7286</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>afonso real estate</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>2026-05-15 12:58:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>RAVI VARANASI</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>thedailyloafbread@gmail.com</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>(508) 473-1175</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>THE DAILY LOAF LLC</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:01:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Mr. Paul C. Tremblay</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>camsoil@yahoo.com</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(508) 943-0415 </t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Cam's Oil Service Inc</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:04:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>SARDOR SAFAROV</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>highway@truckingservicesinc.net</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>(800) 610-1881</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Trucking services inc</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:09:25</t>
         </is>
       </c>
     </row>
@@ -12623,7 +12917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G369"/>
+  <dimension ref="A1:G376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23334,6 +23628,209 @@
       </c>
       <c r="F369" t="inlineStr"/>
       <c r="G369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>2026-05-15 12:51:19</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr"/>
+      <c r="G370" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>2026-05-15 12:54:10</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr"/>
+      <c r="G371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>2026-05-15 12:55:59</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr"/>
+      <c r="G372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>2026-05-15 12:58:34</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr"/>
+      <c r="G373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:01:15</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr"/>
+      <c r="G374" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:04:37</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr"/>
+      <c r="G375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Busy</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>busy_call_back</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:09:25</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr"/>
+      <c r="G376" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H299"/>
+  <dimension ref="A1:H300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-04-07 14:53:07</t>
+          <t>2026-05-18 12:22:29</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-04-09 15:25:34</t>
+          <t>2026-05-18 12:14:14</t>
         </is>
       </c>
     </row>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-04-14 18:12:14</t>
+          <t>2026-05-18 12:10:32</t>
         </is>
       </c>
     </row>
@@ -12903,6 +12903,48 @@
       <c r="H299" t="inlineStr">
         <is>
           <t>2026-05-15 13:09:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Mark HEALEY</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>mark@healeybus.com</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>(781) 389-5296</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Healeybus</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:07:32</t>
         </is>
       </c>
     </row>
@@ -12917,7 +12959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G376"/>
+  <dimension ref="A1:G380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23831,6 +23873,122 @@
       </c>
       <c r="F376" t="inlineStr"/>
       <c r="G376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:07:32</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr"/>
+      <c r="G377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:10:32</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr"/>
+      <c r="G378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:14:14</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr"/>
+      <c r="G379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>NO ANSWER</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>no_answer</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:22:29</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr"/>
+      <c r="G380" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H300"/>
+  <dimension ref="A1:H301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-04-07 15:34:09</t>
+          <t>2026-05-18 15:20:57</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-04-07 15:42:11</t>
+          <t>2026-05-18 15:36:40</t>
         </is>
       </c>
     </row>
@@ -12945,6 +12945,48 @@
       <c r="H300" t="inlineStr">
         <is>
           <t>2026-05-18 12:07:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>MARK STRAZDAS</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>mstrazdassslobster@gmail.com</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>(978) 490-4415</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>ss lobster fitchburg</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:29:00</t>
         </is>
       </c>
     </row>
@@ -12959,7 +13001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G380"/>
+  <dimension ref="A1:G384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16366,17 +16408,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>611</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -16386,7 +16428,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-04-08 16:38:00</t>
+          <t>2026-05-18 15:20:49</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
@@ -16395,17 +16437,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>274</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16415,7 +16457,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-04-08 18:21:03</t>
+          <t>2026-04-08 16:38:00</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
@@ -16424,7 +16466,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>275</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -16444,7 +16486,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-04-23 18:22:34</t>
+          <t>2026-04-08 18:21:03</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
@@ -16453,7 +16495,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>308</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -16473,7 +16515,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-04-23 18:24:52</t>
+          <t>2026-04-23 18:22:34</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
@@ -16482,7 +16524,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>310</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -16502,7 +16544,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-04-27 16:43:32</t>
+          <t>2026-04-23 18:24:52</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
@@ -16511,17 +16553,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>376</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16531,7 +16573,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-04-27 16:44:32</t>
+          <t>2026-04-27 16:43:32</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
@@ -16540,17 +16582,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>378</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16560,7 +16602,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-04-27 16:47:27</t>
+          <t>2026-04-27 16:44:32</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
@@ -16569,7 +16611,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>381</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -16589,7 +16631,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-04-27 16:48:30</t>
+          <t>2026-04-27 16:47:27</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -16598,17 +16640,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>383</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16618,7 +16660,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-04-27 16:49:41</t>
+          <t>2026-04-27 16:48:30</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -16627,17 +16669,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>384</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16647,7 +16689,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-04-27 16:51:50</t>
+          <t>2026-04-27 16:49:41</t>
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
@@ -16656,7 +16698,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>386</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -16676,7 +16718,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-04-28 19:34:54</t>
+          <t>2026-04-27 16:51:50</t>
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
@@ -16685,7 +16727,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>436</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -16705,7 +16747,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-05-13 12:28:13</t>
+          <t>2026-04-28 19:34:54</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -16714,7 +16756,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>579</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -16734,7 +16776,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-05-13 12:32:44</t>
+          <t>2026-05-13 12:28:13</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
@@ -16743,17 +16785,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>581</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -16763,7 +16805,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-04-09 14:38:33</t>
+          <t>2026-05-13 12:32:44</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -16772,17 +16814,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>276</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16792,7 +16834,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-04-09 14:50:24</t>
+          <t>2026-04-09 14:38:33</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
@@ -16801,17 +16843,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>277</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16821,7 +16863,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-04-27 16:17:54</t>
+          <t>2026-04-09 14:50:24</t>
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
@@ -16830,17 +16872,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>343</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16850,7 +16892,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-04-27 16:19:16</t>
+          <t>2026-04-27 16:17:54</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
@@ -16859,17 +16901,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>344</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>email</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16879,7 +16921,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-04-27 16:21:26</t>
+          <t>2026-04-27 16:19:16</t>
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
@@ -16888,17 +16930,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>346</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16908,7 +16950,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-04-27 16:30:33</t>
+          <t>2026-04-27 16:21:26</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
@@ -16917,17 +16959,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>357</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16937,7 +16979,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-04-27 16:34:07</t>
+          <t>2026-04-27 16:30:33</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
@@ -16946,17 +16988,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>362</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16966,7 +17008,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-04-27 16:35:11</t>
+          <t>2026-04-27 16:34:07</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
@@ -16975,7 +17017,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>365</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -16995,7 +17037,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:29</t>
+          <t>2026-04-27 16:35:11</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -17004,7 +17046,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>391</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -17024,7 +17066,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-04-28 19:20:18</t>
+          <t>2026-04-27 18:05:29</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -17033,7 +17075,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>426</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -17053,7 +17095,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-04-28 19:22:33</t>
+          <t>2026-04-28 19:20:18</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
@@ -17062,7 +17104,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>428</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -17082,7 +17124,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-04-28 19:27:09</t>
+          <t>2026-04-28 19:22:33</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
@@ -17091,17 +17133,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>430</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17111,7 +17153,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-04-13 15:45:27</t>
+          <t>2026-04-28 19:27:09</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
@@ -17120,7 +17162,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>286</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -17140,7 +17182,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-04-13 15:46:25</t>
+          <t>2026-04-13 15:45:27</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
@@ -17149,17 +17191,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>287</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17169,7 +17211,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-04-13 15:53:15</t>
+          <t>2026-04-13 15:46:25</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
@@ -17178,17 +17220,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>288</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17198,7 +17240,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-04-13 15:58:50</t>
+          <t>2026-04-13 15:53:15</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
@@ -17207,17 +17249,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>289</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17227,7 +17269,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-04-27 16:24:24</t>
+          <t>2026-04-13 15:58:50</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
@@ -17236,17 +17278,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>351</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -17256,7 +17298,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-04-27 16:28:22</t>
+          <t>2026-04-27 16:24:24</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
@@ -17265,17 +17307,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>354</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -17285,7 +17327,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-04-27 16:35:40</t>
+          <t>2026-04-27 16:28:22</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
@@ -17294,7 +17336,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>366</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -17314,7 +17356,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-04-28 19:07:14</t>
+          <t>2026-04-27 16:35:40</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
@@ -17323,7 +17365,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>419</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -17343,7 +17385,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-04-28 19:16:45</t>
+          <t>2026-04-28 19:07:14</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
@@ -17352,17 +17394,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>424</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -17372,7 +17414,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-04-27 16:29:25</t>
+          <t>2026-04-28 19:16:45</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
@@ -17381,7 +17423,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>356</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -17401,7 +17443,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-04-27 16:31:00</t>
+          <t>2026-04-27 16:29:25</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -17410,17 +17452,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>358</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -17430,7 +17472,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-04-27 16:39:21</t>
+          <t>2026-04-27 16:31:00</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -17439,7 +17481,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>371</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -17459,7 +17501,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-04-27 16:40:26</t>
+          <t>2026-04-27 16:39:21</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -17468,7 +17510,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>373</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -17488,7 +17530,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-04-27 16:42:47</t>
+          <t>2026-04-27 16:40:26</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
@@ -17497,17 +17539,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>374</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -17517,7 +17559,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-04-15 16:05:12</t>
+          <t>2026-04-27 16:42:47</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -17526,7 +17568,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>294</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -17546,7 +17588,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-04-15 18:17:17</t>
+          <t>2026-04-15 16:05:12</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
@@ -17555,17 +17597,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>295</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -17575,7 +17617,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-04-27 16:35:57</t>
+          <t>2026-04-15 18:17:17</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -17584,7 +17626,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>367</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -17604,7 +17646,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-04-27 16:52:02</t>
+          <t>2026-04-27 16:35:57</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
@@ -17613,17 +17655,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>387</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -17633,7 +17675,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-04-28 19:11:23</t>
+          <t>2026-04-27 16:52:02</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
@@ -17642,17 +17684,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>421</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -17662,7 +17704,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-04-30 14:38:42</t>
+          <t>2026-04-28 19:11:23</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
@@ -17671,17 +17713,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>451</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -17691,7 +17733,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-04-16 12:32:37</t>
+          <t>2026-04-30 14:38:42</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -17700,17 +17742,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>296</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -17720,7 +17762,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-04-16 12:52:16</t>
+          <t>2026-04-16 12:32:37</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
@@ -17729,17 +17771,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>297</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -17749,7 +17791,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-04-27 16:37:49</t>
+          <t>2026-04-16 12:52:16</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
@@ -17758,17 +17800,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>368</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -17778,7 +17820,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-04-27 16:45:32</t>
+          <t>2026-04-27 16:37:49</t>
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
@@ -17787,17 +17829,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>379</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -17807,7 +17849,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-04-27 16:47:40</t>
+          <t>2026-04-27 16:45:32</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
@@ -17816,17 +17858,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>382</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -17836,7 +17878,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-04-16 18:41:52</t>
+          <t>2026-04-27 16:47:40</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
@@ -17845,17 +17887,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>299</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -17865,7 +17907,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-04-23 18:27:22</t>
+          <t>2026-04-16 18:41:52</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
@@ -17874,7 +17916,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>312</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -17894,7 +17936,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-04-23 18:30:25</t>
+          <t>2026-04-23 18:27:22</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
@@ -17903,7 +17945,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>314</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -17923,7 +17965,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-04-27 16:43:45</t>
+          <t>2026-04-23 18:30:25</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
@@ -17932,17 +17974,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>377</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -17952,7 +17994,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-04-23 18:40:56</t>
+          <t>2026-04-27 16:43:45</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -17961,17 +18003,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>317</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -17981,7 +18023,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-04-21 15:49:30</t>
+          <t>2026-04-23 18:40:56</t>
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
@@ -17990,17 +18032,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -18010,7 +18052,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-04-21 15:52:28</t>
+          <t>2026-04-21 15:49:30</t>
         </is>
       </c>
       <c r="F174" t="inlineStr"/>
@@ -18019,17 +18061,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>301</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -18039,7 +18081,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-04-21 17:03:38</t>
+          <t>2026-04-21 15:52:28</t>
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
@@ -18048,17 +18090,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>302</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -18068,7 +18110,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-04-22 16:41:07</t>
+          <t>2026-04-21 17:03:38</t>
         </is>
       </c>
       <c r="F176" t="inlineStr"/>
@@ -18077,17 +18119,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>303</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -18097,7 +18139,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:41</t>
+          <t>2026-04-22 16:41:07</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -18106,7 +18148,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>392</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -18126,7 +18168,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-04-28 19:35:07</t>
+          <t>2026-04-27 18:05:41</t>
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
@@ -18135,7 +18177,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>437</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -18155,7 +18197,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-05-06 17:53:39</t>
+          <t>2026-04-28 19:35:07</t>
         </is>
       </c>
       <c r="F179" t="inlineStr"/>
@@ -18164,7 +18206,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>500</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -18184,7 +18226,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-05-07 12:25:07</t>
+          <t>2026-05-06 17:53:39</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
@@ -18193,17 +18235,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>521</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -18213,7 +18255,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-04-23 15:49:56</t>
+          <t>2026-05-07 12:25:07</t>
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
@@ -18222,17 +18264,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>306</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -18242,7 +18284,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2026-04-23 18:16:45</t>
+          <t>2026-04-23 15:49:56</t>
         </is>
       </c>
       <c r="F182" t="inlineStr"/>
@@ -18251,7 +18293,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>307</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -18271,7 +18313,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-04-23 18:22:46</t>
+          <t>2026-04-23 18:16:45</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
@@ -18280,7 +18322,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>309</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -18300,7 +18342,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-04-23 18:25:02</t>
+          <t>2026-04-23 18:22:46</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -18309,7 +18351,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>311</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -18329,7 +18371,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-04-23 18:27:36</t>
+          <t>2026-04-23 18:25:02</t>
         </is>
       </c>
       <c r="F185" t="inlineStr"/>
@@ -18338,7 +18380,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>313</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -18358,7 +18400,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-04-27 18:07:45</t>
+          <t>2026-04-23 18:27:36</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
@@ -18367,7 +18409,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>394</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -18387,7 +18429,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-04-27 18:12:10</t>
+          <t>2026-04-27 18:07:45</t>
         </is>
       </c>
       <c r="F187" t="inlineStr"/>
@@ -18396,7 +18438,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>397</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -18416,7 +18458,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-04-23 18:30:34</t>
+          <t>2026-04-27 18:12:10</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
@@ -18425,17 +18467,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>315</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -18445,7 +18487,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-04-23 18:35:35</t>
+          <t>2026-04-23 18:30:34</t>
         </is>
       </c>
       <c r="F189" t="inlineStr"/>
@@ -18454,17 +18496,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>316</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -18474,7 +18516,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2026-04-23 18:41:25</t>
+          <t>2026-04-23 18:35:35</t>
         </is>
       </c>
       <c r="F190" t="inlineStr"/>
@@ -18483,17 +18525,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>318</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -18503,7 +18545,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-04-23 18:46:12</t>
+          <t>2026-04-23 18:41:25</t>
         </is>
       </c>
       <c r="F191" t="inlineStr"/>
@@ -18512,17 +18554,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -18532,7 +18574,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-04-23 18:58:17</t>
+          <t>2026-04-23 18:46:12</t>
         </is>
       </c>
       <c r="F192" t="inlineStr"/>
@@ -18541,17 +18583,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>321</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -18561,7 +18603,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-04-23 19:09:01</t>
+          <t>2026-04-23 18:58:17</t>
         </is>
       </c>
       <c r="F193" t="inlineStr"/>
@@ -18570,17 +18612,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>322</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -18590,7 +18632,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-04-23 19:28:02</t>
+          <t>2026-04-23 19:09:01</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -18599,7 +18641,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>323</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -18619,7 +18661,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-04-23 19:33:02</t>
+          <t>2026-04-23 19:28:02</t>
         </is>
       </c>
       <c r="F195" t="inlineStr"/>
@@ -18628,17 +18670,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>324</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -18648,7 +18690,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2026-04-23 19:35:57</t>
+          <t>2026-04-23 19:33:02</t>
         </is>
       </c>
       <c r="F196" t="inlineStr"/>
@@ -18657,17 +18699,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>325</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -18677,7 +18719,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-04-24 11:52:45</t>
+          <t>2026-04-23 19:35:57</t>
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
@@ -18686,17 +18728,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>326</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -18706,7 +18748,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-04-24 11:55:39</t>
+          <t>2026-04-24 11:52:45</t>
         </is>
       </c>
       <c r="F198" t="inlineStr"/>
@@ -18715,17 +18757,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>328</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -18735,7 +18777,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-04-24 12:13:00</t>
+          <t>2026-04-24 11:55:39</t>
         </is>
       </c>
       <c r="F199" t="inlineStr"/>
@@ -18744,7 +18786,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>329</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -18764,7 +18806,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2026-04-24 12:17:05</t>
+          <t>2026-04-24 12:13:00</t>
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
@@ -18773,17 +18815,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>330</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -18793,7 +18835,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-04-24 12:19:39</t>
+          <t>2026-04-24 12:17:05</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -18802,17 +18844,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>331</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -18822,7 +18864,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-04-24 12:31:15</t>
+          <t>2026-04-24 12:19:39</t>
         </is>
       </c>
       <c r="F202" t="inlineStr"/>
@@ -18831,17 +18873,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>332</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -18851,7 +18893,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-04-24 12:33:01</t>
+          <t>2026-04-24 12:31:15</t>
         </is>
       </c>
       <c r="F203" t="inlineStr"/>
@@ -18860,17 +18902,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>333</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -18880,7 +18922,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-04-24 14:36:24</t>
+          <t>2026-04-24 12:33:01</t>
         </is>
       </c>
       <c r="F204" t="inlineStr"/>
@@ -18889,7 +18931,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>334</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -18909,7 +18951,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-04-24 14:43:03</t>
+          <t>2026-04-24 14:36:24</t>
         </is>
       </c>
       <c r="F205" t="inlineStr"/>
@@ -18918,17 +18960,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>335</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -18938,7 +18980,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-04-24 14:58:00</t>
+          <t>2026-04-24 14:43:03</t>
         </is>
       </c>
       <c r="F206" t="inlineStr"/>
@@ -18947,17 +18989,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>336</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -18967,7 +19009,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-04-27 14:06:10</t>
+          <t>2026-04-24 14:58:00</t>
         </is>
       </c>
       <c r="F207" t="inlineStr"/>
@@ -18976,17 +19018,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>337</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -18996,7 +19038,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-04-27 14:10:21</t>
+          <t>2026-04-27 14:06:10</t>
         </is>
       </c>
       <c r="F208" t="inlineStr"/>
@@ -19005,17 +19047,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>338</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -19025,7 +19067,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-04-27 14:13:06</t>
+          <t>2026-04-27 14:10:21</t>
         </is>
       </c>
       <c r="F209" t="inlineStr"/>
@@ -19034,17 +19076,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>339</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -19054,7 +19096,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2026-04-27 14:15:47</t>
+          <t>2026-04-27 14:13:06</t>
         </is>
       </c>
       <c r="F210" t="inlineStr"/>
@@ -19063,17 +19105,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>340</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -19083,7 +19125,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:51</t>
+          <t>2026-04-27 14:15:47</t>
         </is>
       </c>
       <c r="F211" t="inlineStr"/>
@@ -19092,17 +19134,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>393</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -19112,7 +19154,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-04-27 18:08:12</t>
+          <t>2026-04-27 18:05:51</t>
         </is>
       </c>
       <c r="F212" t="inlineStr"/>
@@ -19121,17 +19163,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>395</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -19141,7 +19183,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-04-27 18:10:09</t>
+          <t>2026-04-27 18:08:12</t>
         </is>
       </c>
       <c r="F213" t="inlineStr"/>
@@ -19150,17 +19192,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>396</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -19170,7 +19212,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-04-27 18:12:49</t>
+          <t>2026-04-27 18:10:09</t>
         </is>
       </c>
       <c r="F214" t="inlineStr"/>
@@ -19179,17 +19221,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>398</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -19199,7 +19241,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-04-27 18:25:23</t>
+          <t>2026-04-27 18:12:49</t>
         </is>
       </c>
       <c r="F215" t="inlineStr"/>
@@ -19208,17 +19250,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>399</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -19228,7 +19270,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-04-27 18:26:29</t>
+          <t>2026-04-27 18:25:23</t>
         </is>
       </c>
       <c r="F216" t="inlineStr"/>
@@ -19237,7 +19279,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>400</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -19257,7 +19299,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-04-27 18:28:56</t>
+          <t>2026-04-27 18:26:29</t>
         </is>
       </c>
       <c r="F217" t="inlineStr"/>
@@ -19266,7 +19308,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>401</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -19286,7 +19328,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-04-27 18:32:14</t>
+          <t>2026-04-27 18:28:56</t>
         </is>
       </c>
       <c r="F218" t="inlineStr"/>
@@ -19295,7 +19337,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>402</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -19315,7 +19357,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-04-27 19:10:16</t>
+          <t>2026-04-27 18:32:14</t>
         </is>
       </c>
       <c r="F219" t="inlineStr"/>
@@ -19324,7 +19366,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>403</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -19344,7 +19386,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-04-28 13:06:06</t>
+          <t>2026-04-27 19:10:16</t>
         </is>
       </c>
       <c r="F220" t="inlineStr"/>
@@ -19353,17 +19395,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>404</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -19373,7 +19415,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-04-28 13:09:10</t>
+          <t>2026-04-28 13:06:06</t>
         </is>
       </c>
       <c r="F221" t="inlineStr"/>
@@ -19382,17 +19424,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>405</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -19402,7 +19444,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-04-28 13:31:57</t>
+          <t>2026-04-28 13:09:10</t>
         </is>
       </c>
       <c r="F222" t="inlineStr"/>
@@ -19411,7 +19453,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>406</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -19431,7 +19473,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-04-28 16:36:52</t>
+          <t>2026-04-28 13:31:57</t>
         </is>
       </c>
       <c r="F223" t="inlineStr"/>
@@ -19440,17 +19482,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>408</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -19460,7 +19502,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-04-28 16:41:55</t>
+          <t>2026-04-28 16:36:52</t>
         </is>
       </c>
       <c r="F224" t="inlineStr"/>
@@ -19469,7 +19511,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>409</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -19489,7 +19531,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-04-28 16:45:43</t>
+          <t>2026-04-28 16:41:55</t>
         </is>
       </c>
       <c r="F225" t="inlineStr"/>
@@ -19498,17 +19540,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>410</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -19518,7 +19560,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-04-28 16:50:41</t>
+          <t>2026-04-28 16:45:43</t>
         </is>
       </c>
       <c r="F226" t="inlineStr"/>
@@ -19527,17 +19569,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>411</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -19547,7 +19589,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-04-28 16:58:22</t>
+          <t>2026-04-28 16:50:41</t>
         </is>
       </c>
       <c r="F227" t="inlineStr"/>
@@ -19556,17 +19598,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>412</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -19576,7 +19618,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-04-28 19:11:43</t>
+          <t>2026-04-28 16:58:22</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
@@ -19585,17 +19627,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>422</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -19605,7 +19647,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-04-28 19:17:29</t>
+          <t>2026-04-28 19:11:43</t>
         </is>
       </c>
       <c r="F229" t="inlineStr"/>
@@ -19614,17 +19656,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>425</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -19634,7 +19676,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-04-28 19:20:41</t>
+          <t>2026-04-28 19:17:29</t>
         </is>
       </c>
       <c r="F230" t="inlineStr"/>
@@ -19643,7 +19685,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>427</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -19663,7 +19705,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-04-28 19:27:32</t>
+          <t>2026-04-28 19:20:41</t>
         </is>
       </c>
       <c r="F231" t="inlineStr"/>
@@ -19672,17 +19714,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>431</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -19692,7 +19734,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-04-28 19:29:59</t>
+          <t>2026-04-28 19:27:32</t>
         </is>
       </c>
       <c r="F232" t="inlineStr"/>
@@ -19701,17 +19743,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>432</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -19721,7 +19763,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-04-28 19:38:54</t>
+          <t>2026-04-28 19:29:59</t>
         </is>
       </c>
       <c r="F233" t="inlineStr"/>
@@ -19730,17 +19772,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>438</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -19750,7 +19792,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-04-28 18:59:52</t>
+          <t>2026-04-28 19:38:54</t>
         </is>
       </c>
       <c r="F234" t="inlineStr"/>
@@ -19759,17 +19801,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>413</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -19779,7 +19821,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-04-28 19:05:38</t>
+          <t>2026-04-28 18:59:52</t>
         </is>
       </c>
       <c r="F235" t="inlineStr"/>
@@ -19788,7 +19830,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>416</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -19808,7 +19850,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2026-04-28 19:09:07</t>
+          <t>2026-04-28 19:05:38</t>
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
@@ -19817,7 +19859,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>420</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19837,7 +19879,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-04-28 19:22:49</t>
+          <t>2026-04-28 19:09:07</t>
         </is>
       </c>
       <c r="F237" t="inlineStr"/>
@@ -19846,17 +19888,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>429</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -19866,7 +19908,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-04-28 19:46:42</t>
+          <t>2026-04-28 19:22:49</t>
         </is>
       </c>
       <c r="F238" t="inlineStr"/>
@@ -19875,17 +19917,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>439</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -19895,7 +19937,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-04-29 15:54:41</t>
+          <t>2026-04-28 19:46:42</t>
         </is>
       </c>
       <c r="F239" t="inlineStr"/>
@@ -19904,7 +19946,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>440</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19924,7 +19966,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-04-29 15:56:41</t>
+          <t>2026-04-29 15:54:41</t>
         </is>
       </c>
       <c r="F240" t="inlineStr"/>
@@ -19933,17 +19975,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>441</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -19953,7 +19995,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-04-29 16:10:35</t>
+          <t>2026-04-29 15:56:41</t>
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
@@ -19962,17 +20004,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>442</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -19982,7 +20024,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-04-29 16:13:57</t>
+          <t>2026-04-29 16:10:35</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
@@ -19991,17 +20033,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>443</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -20011,7 +20053,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-04-29 16:17:13</t>
+          <t>2026-04-29 16:13:57</t>
         </is>
       </c>
       <c r="F243" t="inlineStr"/>
@@ -20020,7 +20062,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>444</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -20040,7 +20082,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-04-29 16:21:56</t>
+          <t>2026-04-29 16:17:13</t>
         </is>
       </c>
       <c r="F244" t="inlineStr"/>
@@ -20049,7 +20091,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>445</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -20069,7 +20111,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-04-29 16:26:19</t>
+          <t>2026-04-29 16:21:56</t>
         </is>
       </c>
       <c r="F245" t="inlineStr"/>
@@ -20078,7 +20120,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>446</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -20098,7 +20140,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-04-30 11:56:22</t>
+          <t>2026-04-29 16:26:19</t>
         </is>
       </c>
       <c r="F246" t="inlineStr"/>
@@ -20107,7 +20149,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>447</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -20127,7 +20169,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-04-30 12:18:39</t>
+          <t>2026-04-30 11:56:22</t>
         </is>
       </c>
       <c r="F247" t="inlineStr"/>
@@ -20136,7 +20178,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>448</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -20156,7 +20198,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-04-30 12:27:47</t>
+          <t>2026-04-30 12:18:39</t>
         </is>
       </c>
       <c r="F248" t="inlineStr"/>
@@ -20165,17 +20207,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>449</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -20185,7 +20227,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-04-30 14:33:48</t>
+          <t>2026-04-30 12:27:47</t>
         </is>
       </c>
       <c r="F249" t="inlineStr"/>
@@ -20194,17 +20236,17 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>450</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -20214,7 +20256,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-04-30 14:39:11</t>
+          <t>2026-04-30 14:33:48</t>
         </is>
       </c>
       <c r="F250" t="inlineStr"/>
@@ -20223,17 +20265,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>452</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -20243,7 +20285,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-04-30 14:44:06</t>
+          <t>2026-04-30 14:39:11</t>
         </is>
       </c>
       <c r="F251" t="inlineStr"/>
@@ -20252,17 +20294,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>453</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -20272,7 +20314,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-04-30 14:50:48</t>
+          <t>2026-04-30 14:44:06</t>
         </is>
       </c>
       <c r="F252" t="inlineStr"/>
@@ -20281,17 +20323,17 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>454</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -20301,7 +20343,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-04-30 15:03:19</t>
+          <t>2026-04-30 14:50:48</t>
         </is>
       </c>
       <c r="F253" t="inlineStr"/>
@@ -20310,7 +20352,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>455</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20330,7 +20372,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-04-30 16:43:14</t>
+          <t>2026-04-30 15:03:19</t>
         </is>
       </c>
       <c r="F254" t="inlineStr"/>
@@ -20339,7 +20381,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>456</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20359,7 +20401,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-04-30 16:49:38</t>
+          <t>2026-04-30 16:43:14</t>
         </is>
       </c>
       <c r="F255" t="inlineStr"/>
@@ -20368,17 +20410,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>457</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -20388,7 +20430,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2026-04-30 16:57:13</t>
+          <t>2026-04-30 16:49:38</t>
         </is>
       </c>
       <c r="F256" t="inlineStr"/>
@@ -20397,17 +20439,17 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>458</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -20417,7 +20459,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-04-30 16:59:14</t>
+          <t>2026-04-30 16:57:13</t>
         </is>
       </c>
       <c r="F257" t="inlineStr"/>
@@ -20426,17 +20468,17 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>459</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -20446,7 +20488,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-04-30 17:03:09</t>
+          <t>2026-04-30 16:59:14</t>
         </is>
       </c>
       <c r="F258" t="inlineStr"/>
@@ -20455,7 +20497,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20475,7 +20517,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-04-30 17:07:20</t>
+          <t>2026-04-30 17:03:09</t>
         </is>
       </c>
       <c r="F259" t="inlineStr"/>
@@ -20484,7 +20526,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>461</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20504,7 +20546,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-04-30 17:20:16</t>
+          <t>2026-04-30 17:07:20</t>
         </is>
       </c>
       <c r="F260" t="inlineStr"/>
@@ -20513,7 +20555,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>462</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20533,7 +20575,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-05-04 12:40:26</t>
+          <t>2026-04-30 17:20:16</t>
         </is>
       </c>
       <c r="F261" t="inlineStr"/>
@@ -20542,17 +20584,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>465</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -20562,7 +20604,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-05-04 13:27:46</t>
+          <t>2026-05-04 12:40:26</t>
         </is>
       </c>
       <c r="F262" t="inlineStr"/>
@@ -20571,17 +20613,17 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>466</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -20591,7 +20633,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-05-04 13:32:27</t>
+          <t>2026-05-04 13:27:46</t>
         </is>
       </c>
       <c r="F263" t="inlineStr"/>
@@ -20600,17 +20642,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>467</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -20620,7 +20662,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-05-04 13:35:31</t>
+          <t>2026-05-04 13:32:27</t>
         </is>
       </c>
       <c r="F264" t="inlineStr"/>
@@ -20629,7 +20671,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>468</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20649,7 +20691,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-05-04 13:52:33</t>
+          <t>2026-05-04 13:35:31</t>
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
@@ -20658,17 +20700,17 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>469</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -20678,7 +20720,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-05-04 14:15:29</t>
+          <t>2026-05-04 13:52:33</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
@@ -20687,7 +20729,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>470</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20707,7 +20749,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-05-04 14:21:26</t>
+          <t>2026-05-04 14:15:29</t>
         </is>
       </c>
       <c r="F267" t="inlineStr"/>
@@ -20716,7 +20758,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>471</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -20736,7 +20778,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-05-04 14:28:28</t>
+          <t>2026-05-04 14:21:26</t>
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
@@ -20745,17 +20787,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>472</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -20765,7 +20807,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-05-05 12:33:28</t>
+          <t>2026-05-04 14:28:28</t>
         </is>
       </c>
       <c r="F269" t="inlineStr"/>
@@ -20774,17 +20816,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>473</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -20794,7 +20836,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-05-05 12:36:49</t>
+          <t>2026-05-05 12:33:28</t>
         </is>
       </c>
       <c r="F270" t="inlineStr"/>
@@ -20803,17 +20845,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>474</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -20823,7 +20865,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-05-05 13:16:10</t>
+          <t>2026-05-05 12:36:49</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
@@ -20832,7 +20874,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>475</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -20852,7 +20894,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-05-05 13:22:28</t>
+          <t>2026-05-05 13:16:10</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
@@ -20861,7 +20903,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>476</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -20881,7 +20923,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-05-05 15:49:32</t>
+          <t>2026-05-05 13:22:28</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
@@ -20890,7 +20932,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>478</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -20910,7 +20952,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-05-05 18:17:18</t>
+          <t>2026-05-05 15:49:32</t>
         </is>
       </c>
       <c r="F274" t="inlineStr"/>
@@ -20919,17 +20961,17 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>484</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -20939,7 +20981,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-05-05 18:23:24</t>
+          <t>2026-05-05 18:17:18</t>
         </is>
       </c>
       <c r="F275" t="inlineStr"/>
@@ -20948,17 +20990,17 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>485</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -20968,7 +21010,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-05-05 18:30:18</t>
+          <t>2026-05-05 18:23:24</t>
         </is>
       </c>
       <c r="F276" t="inlineStr"/>
@@ -20977,17 +21019,17 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>486</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -20997,7 +21039,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-05-05 19:24:36</t>
+          <t>2026-05-05 18:30:18</t>
         </is>
       </c>
       <c r="F277" t="inlineStr"/>
@@ -21006,17 +21048,17 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>487</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -21026,7 +21068,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-05-06 14:07:52</t>
+          <t>2026-05-05 19:24:36</t>
         </is>
       </c>
       <c r="F278" t="inlineStr"/>
@@ -21035,17 +21077,17 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>488</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -21055,7 +21097,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-05-06 14:12:50</t>
+          <t>2026-05-06 14:07:52</t>
         </is>
       </c>
       <c r="F279" t="inlineStr"/>
@@ -21064,17 +21106,17 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>489</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -21084,7 +21126,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-05-06 14:15:34</t>
+          <t>2026-05-06 14:12:50</t>
         </is>
       </c>
       <c r="F280" t="inlineStr"/>
@@ -21093,17 +21135,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>490</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -21113,7 +21155,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-05-06 14:59:26</t>
+          <t>2026-05-06 14:15:34</t>
         </is>
       </c>
       <c r="F281" t="inlineStr"/>
@@ -21122,17 +21164,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -21142,7 +21184,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-05-06 15:04:52</t>
+          <t>2026-05-06 14:59:26</t>
         </is>
       </c>
       <c r="F282" t="inlineStr"/>
@@ -21151,7 +21193,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>492</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -21171,7 +21213,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-05-06 15:08:51</t>
+          <t>2026-05-06 15:04:52</t>
         </is>
       </c>
       <c r="F283" t="inlineStr"/>
@@ -21180,17 +21222,17 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>493</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Busy</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -21200,7 +21242,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-05-06 15:28:38</t>
+          <t>2026-05-06 15:08:51</t>
         </is>
       </c>
       <c r="F284" t="inlineStr"/>
@@ -21209,17 +21251,17 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>494</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Busy</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -21229,7 +21271,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-05-06 15:31:36</t>
+          <t>2026-05-06 15:28:38</t>
         </is>
       </c>
       <c r="F285" t="inlineStr"/>
@@ -21238,17 +21280,17 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>495</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -21258,7 +21300,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-05-06 17:53:50</t>
+          <t>2026-05-06 15:31:36</t>
         </is>
       </c>
       <c r="F286" t="inlineStr"/>
@@ -21267,7 +21309,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>501</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -21287,7 +21329,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-05-06 17:59:31</t>
+          <t>2026-05-06 17:53:50</t>
         </is>
       </c>
       <c r="F287" t="inlineStr"/>
@@ -21296,17 +21338,17 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>502</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -21316,7 +21358,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>2026-05-06 19:18:14</t>
+          <t>2026-05-06 17:59:31</t>
         </is>
       </c>
       <c r="F288" t="inlineStr"/>
@@ -21325,17 +21367,17 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>503</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -21345,7 +21387,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-05-06 19:21:01</t>
+          <t>2026-05-06 19:18:14</t>
         </is>
       </c>
       <c r="F289" t="inlineStr"/>
@@ -21354,7 +21396,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>504</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -21374,7 +21416,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-05-06 19:25:27</t>
+          <t>2026-05-06 19:21:01</t>
         </is>
       </c>
       <c r="F290" t="inlineStr"/>
@@ -21383,7 +21425,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>505</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -21403,7 +21445,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-05-06 19:27:23</t>
+          <t>2026-05-06 19:25:27</t>
         </is>
       </c>
       <c r="F291" t="inlineStr"/>
@@ -21412,17 +21454,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>506</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -21432,7 +21474,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-05-06 19:39:21</t>
+          <t>2026-05-06 19:27:23</t>
         </is>
       </c>
       <c r="F292" t="inlineStr"/>
@@ -21441,17 +21483,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>507</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -21461,7 +21503,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-05-06 20:09:52</t>
+          <t>2026-05-06 19:39:21</t>
         </is>
       </c>
       <c r="F293" t="inlineStr"/>
@@ -21470,17 +21512,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>509</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -21490,7 +21532,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2026-05-06 20:12:28</t>
+          <t>2026-05-06 20:09:52</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
@@ -21499,7 +21541,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>511</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -21519,7 +21561,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-05-07 12:02:27</t>
+          <t>2026-05-06 20:12:28</t>
         </is>
       </c>
       <c r="F295" t="inlineStr"/>
@@ -21528,17 +21570,17 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>512</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -21548,7 +21590,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-05-07 12:05:31</t>
+          <t>2026-05-07 12:02:27</t>
         </is>
       </c>
       <c r="F296" t="inlineStr"/>
@@ -21557,17 +21599,17 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>513</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -21577,7 +21619,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-05-07 12:07:46</t>
+          <t>2026-05-07 12:05:31</t>
         </is>
       </c>
       <c r="F297" t="inlineStr"/>
@@ -21586,17 +21628,17 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>514</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -21606,7 +21648,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-05-07 12:12:23</t>
+          <t>2026-05-07 12:07:46</t>
         </is>
       </c>
       <c r="F298" t="inlineStr"/>
@@ -21615,17 +21657,17 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>515</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -21635,7 +21677,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-05-07 12:21:17</t>
+          <t>2026-05-07 12:12:23</t>
         </is>
       </c>
       <c r="F299" t="inlineStr"/>
@@ -21644,7 +21686,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>516</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -21664,7 +21706,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-05-07 12:22:26</t>
+          <t>2026-05-07 12:21:17</t>
         </is>
       </c>
       <c r="F300" t="inlineStr"/>
@@ -21673,7 +21715,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>517</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -21693,7 +21735,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-05-07 12:25:15</t>
+          <t>2026-05-07 12:22:26</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
@@ -21702,7 +21744,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>522</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -21722,7 +21764,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-05-07 12:30:09</t>
+          <t>2026-05-07 12:25:15</t>
         </is>
       </c>
       <c r="F302" t="inlineStr"/>
@@ -21731,7 +21773,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>524</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -21751,7 +21793,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-05-07 18:11:26</t>
+          <t>2026-05-07 12:30:09</t>
         </is>
       </c>
       <c r="F303" t="inlineStr"/>
@@ -21760,17 +21802,17 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>527</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -21780,7 +21822,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-05-07 18:21:05</t>
+          <t>2026-05-07 18:11:26</t>
         </is>
       </c>
       <c r="F304" t="inlineStr"/>
@@ -21789,17 +21831,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>528</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -21809,7 +21851,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-05-07 18:23:27</t>
+          <t>2026-05-07 18:21:05</t>
         </is>
       </c>
       <c r="F305" t="inlineStr"/>
@@ -21818,17 +21860,17 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>529</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -21838,7 +21880,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-05-07 18:31:47</t>
+          <t>2026-05-07 18:23:27</t>
         </is>
       </c>
       <c r="F306" t="inlineStr"/>
@@ -21847,17 +21889,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>530</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -21867,7 +21909,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-05-07 18:41:02</t>
+          <t>2026-05-07 18:31:47</t>
         </is>
       </c>
       <c r="F307" t="inlineStr"/>
@@ -21876,17 +21918,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>531</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -21896,7 +21938,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-05-07 19:04:03</t>
+          <t>2026-05-07 18:41:02</t>
         </is>
       </c>
       <c r="F308" t="inlineStr"/>
@@ -21905,17 +21947,17 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>532</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -21925,7 +21967,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-05-07 19:12:07</t>
+          <t>2026-05-07 19:04:03</t>
         </is>
       </c>
       <c r="F309" t="inlineStr"/>
@@ -21934,17 +21976,17 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>533</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -21954,7 +21996,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-05-07 19:19:47</t>
+          <t>2026-05-07 19:12:07</t>
         </is>
       </c>
       <c r="F310" t="inlineStr"/>
@@ -21963,7 +22005,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>534</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -21983,7 +22025,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-05-07 19:35:25</t>
+          <t>2026-05-07 19:19:47</t>
         </is>
       </c>
       <c r="F311" t="inlineStr"/>
@@ -21992,7 +22034,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>535</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -22012,7 +22054,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-05-08 12:36:57</t>
+          <t>2026-05-07 19:35:25</t>
         </is>
       </c>
       <c r="F312" t="inlineStr"/>
@@ -22021,7 +22063,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>536</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -22041,7 +22083,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-05-08 12:43:59</t>
+          <t>2026-05-08 12:36:57</t>
         </is>
       </c>
       <c r="F313" t="inlineStr"/>
@@ -22050,17 +22092,17 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>537</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -22070,7 +22112,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-05-08 12:51:09</t>
+          <t>2026-05-08 12:43:59</t>
         </is>
       </c>
       <c r="F314" t="inlineStr"/>
@@ -22079,17 +22121,17 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>538</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -22099,7 +22141,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2026-05-08 12:55:15</t>
+          <t>2026-05-08 12:51:09</t>
         </is>
       </c>
       <c r="F315" t="inlineStr"/>
@@ -22108,7 +22150,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>539</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -22128,7 +22170,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-05-08 12:57:14</t>
+          <t>2026-05-08 12:55:15</t>
         </is>
       </c>
       <c r="F316" t="inlineStr"/>
@@ -22137,7 +22179,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>540</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -22157,7 +22199,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-05-08 13:00:41</t>
+          <t>2026-05-08 12:57:14</t>
         </is>
       </c>
       <c r="F317" t="inlineStr"/>
@@ -22166,17 +22208,17 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>541</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -22186,7 +22228,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-05-08 13:04:02</t>
+          <t>2026-05-08 13:00:41</t>
         </is>
       </c>
       <c r="F318" t="inlineStr"/>
@@ -22195,17 +22237,17 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>542</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -22215,7 +22257,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-05-08 13:09:59</t>
+          <t>2026-05-08 13:04:02</t>
         </is>
       </c>
       <c r="F319" t="inlineStr"/>
@@ -22224,17 +22266,17 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>543</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>WARM LEAD</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>warm_lead</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -22244,7 +22286,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-05-08 13:16:49</t>
+          <t>2026-05-08 13:09:59</t>
         </is>
       </c>
       <c r="F320" t="inlineStr"/>
@@ -22253,17 +22295,17 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>544</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>WARM LEAD</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>warm_lead</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -22273,7 +22315,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-05-08 13:22:02</t>
+          <t>2026-05-08 13:16:49</t>
         </is>
       </c>
       <c r="F321" t="inlineStr"/>
@@ -22282,7 +22324,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>545</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -22302,7 +22344,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-05-08 15:50:51</t>
+          <t>2026-05-08 13:22:02</t>
         </is>
       </c>
       <c r="F322" t="inlineStr"/>
@@ -22311,17 +22353,17 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>546</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -22331,7 +22373,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-05-08 15:54:37</t>
+          <t>2026-05-08 15:50:51</t>
         </is>
       </c>
       <c r="F323" t="inlineStr"/>
@@ -22340,17 +22382,17 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>547</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -22360,7 +22402,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-05-08 15:59:34</t>
+          <t>2026-05-08 15:54:37</t>
         </is>
       </c>
       <c r="F324" t="inlineStr"/>
@@ -22369,7 +22411,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>548</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -22389,7 +22431,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-05-08 16:11:07</t>
+          <t>2026-05-08 15:59:34</t>
         </is>
       </c>
       <c r="F325" t="inlineStr"/>
@@ -22398,17 +22440,17 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>549</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -22418,7 +22460,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-05-08 16:19:50</t>
+          <t>2026-05-08 16:11:07</t>
         </is>
       </c>
       <c r="F326" t="inlineStr"/>
@@ -22427,17 +22469,17 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>550</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -22447,7 +22489,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-05-08 16:24:03</t>
+          <t>2026-05-08 16:19:50</t>
         </is>
       </c>
       <c r="F327" t="inlineStr"/>
@@ -22456,17 +22498,17 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>551</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -22476,7 +22518,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-05-11 18:35:26</t>
+          <t>2026-05-08 16:24:03</t>
         </is>
       </c>
       <c r="F328" t="inlineStr"/>
@@ -22485,17 +22527,17 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>552</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -22505,7 +22547,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-05-12 12:12:48</t>
+          <t>2026-05-11 18:35:26</t>
         </is>
       </c>
       <c r="F329" t="inlineStr"/>
@@ -22514,17 +22556,17 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>553</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -22534,7 +22576,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-05-12 12:18:21</t>
+          <t>2026-05-12 12:12:48</t>
         </is>
       </c>
       <c r="F330" t="inlineStr"/>
@@ -22543,17 +22585,17 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>554</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -22563,7 +22605,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-05-12 12:22:04</t>
+          <t>2026-05-12 12:18:21</t>
         </is>
       </c>
       <c r="F331" t="inlineStr"/>
@@ -22572,17 +22614,17 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>555</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Call disconnected</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -22592,7 +22634,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2026-05-12 12:23:33</t>
+          <t>2026-05-12 12:22:04</t>
         </is>
       </c>
       <c r="F332" t="inlineStr"/>
@@ -22601,17 +22643,17 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>556</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call disconnected</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -22621,7 +22663,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-05-12 12:26:05</t>
+          <t>2026-05-12 12:23:33</t>
         </is>
       </c>
       <c r="F333" t="inlineStr"/>
@@ -22630,7 +22672,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>557</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -22650,7 +22692,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-05-12 12:31:00</t>
+          <t>2026-05-12 12:26:05</t>
         </is>
       </c>
       <c r="F334" t="inlineStr"/>
@@ -22659,17 +22701,17 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>558</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -22679,7 +22721,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-05-12 12:33:59</t>
+          <t>2026-05-12 12:31:00</t>
         </is>
       </c>
       <c r="F335" t="inlineStr"/>
@@ -22688,17 +22730,17 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>559</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -22708,7 +22750,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-05-12 12:37:48</t>
+          <t>2026-05-12 12:33:59</t>
         </is>
       </c>
       <c r="F336" t="inlineStr"/>
@@ -22717,7 +22759,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>560</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -22737,7 +22779,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-05-12 12:48:40</t>
+          <t>2026-05-12 12:37:48</t>
         </is>
       </c>
       <c r="F337" t="inlineStr"/>
@@ -22746,7 +22788,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -22766,7 +22808,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-05-12 12:51:08</t>
+          <t>2026-05-12 12:48:40</t>
         </is>
       </c>
       <c r="F338" t="inlineStr"/>
@@ -22775,7 +22817,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>562</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -22795,7 +22837,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-05-12 18:19:14</t>
+          <t>2026-05-12 12:51:08</t>
         </is>
       </c>
       <c r="F339" t="inlineStr"/>
@@ -22804,17 +22846,17 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>566</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -22824,7 +22866,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-05-12 18:26:39</t>
+          <t>2026-05-12 18:19:14</t>
         </is>
       </c>
       <c r="F340" t="inlineStr"/>
@@ -22833,17 +22875,17 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>567</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -22853,7 +22895,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>2026-05-12 18:29:28</t>
+          <t>2026-05-12 18:26:39</t>
         </is>
       </c>
       <c r="F341" t="inlineStr"/>
@@ -22862,7 +22904,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>568</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22882,7 +22924,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-05-12 18:38:29</t>
+          <t>2026-05-12 18:29:28</t>
         </is>
       </c>
       <c r="F342" t="inlineStr"/>
@@ -22891,17 +22933,17 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>569</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -22911,7 +22953,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>2026-05-12 18:47:34</t>
+          <t>2026-05-12 18:38:29</t>
         </is>
       </c>
       <c r="F343" t="inlineStr"/>
@@ -22920,17 +22962,17 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>570</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -22940,7 +22982,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>2026-05-12 18:54:06</t>
+          <t>2026-05-12 18:47:34</t>
         </is>
       </c>
       <c r="F344" t="inlineStr"/>
@@ -22949,7 +22991,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>571</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -22969,7 +23011,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-05-12 19:03:54</t>
+          <t>2026-05-12 18:54:06</t>
         </is>
       </c>
       <c r="F345" t="inlineStr"/>
@@ -22978,17 +23020,17 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>572</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -22998,7 +23040,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-05-12 19:41:52</t>
+          <t>2026-05-12 19:03:54</t>
         </is>
       </c>
       <c r="F346" t="inlineStr"/>
@@ -23007,7 +23049,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>573</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -23027,7 +23069,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-05-13 12:09:27</t>
+          <t>2026-05-12 19:41:52</t>
         </is>
       </c>
       <c r="F347" t="inlineStr"/>
@@ -23036,17 +23078,17 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>574</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -23056,7 +23098,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-05-13 12:18:32</t>
+          <t>2026-05-13 12:09:27</t>
         </is>
       </c>
       <c r="F348" t="inlineStr"/>
@@ -23065,17 +23107,17 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>575</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -23085,7 +23127,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-05-13 12:23:52</t>
+          <t>2026-05-13 12:18:32</t>
         </is>
       </c>
       <c r="F349" t="inlineStr"/>
@@ -23094,17 +23136,17 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>576</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -23114,7 +23156,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-05-13 12:25:37</t>
+          <t>2026-05-13 12:23:52</t>
         </is>
       </c>
       <c r="F350" t="inlineStr"/>
@@ -23123,17 +23165,17 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>577</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -23143,7 +23185,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-05-13 12:28:23</t>
+          <t>2026-05-13 12:25:37</t>
         </is>
       </c>
       <c r="F351" t="inlineStr"/>
@@ -23152,7 +23194,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>580</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -23172,7 +23214,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-05-13 12:32:52</t>
+          <t>2026-05-13 12:28:23</t>
         </is>
       </c>
       <c r="F352" t="inlineStr"/>
@@ -23181,17 +23223,17 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>582</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -23201,7 +23243,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-05-13 12:40:54</t>
+          <t>2026-05-13 12:32:52</t>
         </is>
       </c>
       <c r="F353" t="inlineStr"/>
@@ -23210,17 +23252,17 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>583</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -23230,7 +23272,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-05-13 12:43:27</t>
+          <t>2026-05-13 12:40:54</t>
         </is>
       </c>
       <c r="F354" t="inlineStr"/>
@@ -23239,17 +23281,17 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>584</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Busy</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -23259,7 +23301,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-05-13 12:45:51</t>
+          <t>2026-05-13 12:43:27</t>
         </is>
       </c>
       <c r="F355" t="inlineStr"/>
@@ -23268,17 +23310,17 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>585</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Busy</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -23288,7 +23330,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>2026-05-14 12:29:10</t>
+          <t>2026-05-13 12:45:51</t>
         </is>
       </c>
       <c r="F356" t="inlineStr"/>
@@ -23297,17 +23339,17 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>586</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -23317,7 +23359,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>2026-05-14 12:31:42</t>
+          <t>2026-05-14 12:29:10</t>
         </is>
       </c>
       <c r="F357" t="inlineStr"/>
@@ -23326,7 +23368,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>587</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -23346,7 +23388,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>2026-05-14 12:34:26</t>
+          <t>2026-05-14 12:31:42</t>
         </is>
       </c>
       <c r="F358" t="inlineStr"/>
@@ -23355,7 +23397,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>588</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23375,7 +23417,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>2026-05-14 12:39:18</t>
+          <t>2026-05-14 12:34:26</t>
         </is>
       </c>
       <c r="F359" t="inlineStr"/>
@@ -23384,17 +23426,17 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>589</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Busy</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -23404,7 +23446,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>2026-05-14 12:53:07</t>
+          <t>2026-05-14 12:39:18</t>
         </is>
       </c>
       <c r="F360" t="inlineStr"/>
@@ -23413,17 +23455,17 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>590</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Busy</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -23433,7 +23475,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>2026-05-14 12:57:05</t>
+          <t>2026-05-14 12:53:07</t>
         </is>
       </c>
       <c r="F361" t="inlineStr"/>
@@ -23442,17 +23484,17 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>591</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -23462,7 +23504,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>2026-05-14 13:04:59</t>
+          <t>2026-05-14 12:57:05</t>
         </is>
       </c>
       <c r="F362" t="inlineStr"/>
@@ -23471,17 +23513,17 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>592</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -23491,7 +23533,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>2026-05-14 17:58:21</t>
+          <t>2026-05-14 13:04:59</t>
         </is>
       </c>
       <c r="F363" t="inlineStr"/>
@@ -23500,7 +23542,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>593</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -23520,7 +23562,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>2026-05-14 18:00:32</t>
+          <t>2026-05-14 17:58:21</t>
         </is>
       </c>
       <c r="F364" t="inlineStr"/>
@@ -23529,17 +23571,17 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>594</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -23549,7 +23591,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>2026-05-14 18:07:31</t>
+          <t>2026-05-14 18:00:32</t>
         </is>
       </c>
       <c r="F365" t="inlineStr"/>
@@ -23558,17 +23600,17 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>595</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -23578,7 +23620,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>2026-05-14 18:16:47</t>
+          <t>2026-05-14 18:07:31</t>
         </is>
       </c>
       <c r="F366" t="inlineStr"/>
@@ -23587,7 +23629,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>596</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -23607,7 +23649,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>2026-05-14 18:23:35</t>
+          <t>2026-05-14 18:16:47</t>
         </is>
       </c>
       <c r="F367" t="inlineStr"/>
@@ -23616,17 +23658,17 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>597</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Not Connecting</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -23636,7 +23678,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>2026-05-14 18:29:03</t>
+          <t>2026-05-14 18:23:35</t>
         </is>
       </c>
       <c r="F368" t="inlineStr"/>
@@ -23645,17 +23687,17 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>598</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Not Connecting</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -23665,7 +23707,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>2026-05-14 18:35:02</t>
+          <t>2026-05-14 18:29:03</t>
         </is>
       </c>
       <c r="F369" t="inlineStr"/>
@@ -23674,7 +23716,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>599</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -23694,7 +23736,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>2026-05-15 12:51:19</t>
+          <t>2026-05-14 18:35:02</t>
         </is>
       </c>
       <c r="F370" t="inlineStr"/>
@@ -23703,17 +23745,17 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>600</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -23723,7 +23765,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>2026-05-15 12:54:10</t>
+          <t>2026-05-15 12:51:19</t>
         </is>
       </c>
       <c r="F371" t="inlineStr"/>
@@ -23732,17 +23774,17 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>601</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -23752,7 +23794,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>2026-05-15 12:55:59</t>
+          <t>2026-05-15 12:54:10</t>
         </is>
       </c>
       <c r="F372" t="inlineStr"/>
@@ -23761,17 +23803,17 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>602</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -23781,7 +23823,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>2026-05-15 12:58:34</t>
+          <t>2026-05-15 12:55:59</t>
         </is>
       </c>
       <c r="F373" t="inlineStr"/>
@@ -23790,7 +23832,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>603</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -23810,7 +23852,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>2026-05-15 13:01:15</t>
+          <t>2026-05-15 12:58:34</t>
         </is>
       </c>
       <c r="F374" t="inlineStr"/>
@@ -23819,7 +23861,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>604</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -23839,7 +23881,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>2026-05-15 13:04:37</t>
+          <t>2026-05-15 13:01:15</t>
         </is>
       </c>
       <c r="F375" t="inlineStr"/>
@@ -23848,17 +23890,17 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>605</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Busy</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -23868,7 +23910,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>2026-05-15 13:09:25</t>
+          <t>2026-05-15 13:04:37</t>
         </is>
       </c>
       <c r="F376" t="inlineStr"/>
@@ -23877,17 +23919,17 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>606</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Busy</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -23897,7 +23939,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>2026-05-18 12:07:32</t>
+          <t>2026-05-15 13:09:25</t>
         </is>
       </c>
       <c r="F377" t="inlineStr"/>
@@ -23906,7 +23948,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>607</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -23926,7 +23968,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>2026-05-18 12:10:32</t>
+          <t>2026-05-18 12:07:32</t>
         </is>
       </c>
       <c r="F378" t="inlineStr"/>
@@ -23935,17 +23977,17 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>608</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -23955,7 +23997,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>2026-05-18 12:14:14</t>
+          <t>2026-05-18 12:10:32</t>
         </is>
       </c>
       <c r="F379" t="inlineStr"/>
@@ -23964,17 +24006,17 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>609</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -23984,11 +24026,127 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>2026-05-18 12:22:29</t>
+          <t>2026-05-18 12:14:14</t>
         </is>
       </c>
       <c r="F380" t="inlineStr"/>
       <c r="G380" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>NO ANSWER</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>no_answer</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:22:29</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr"/>
+      <c r="G381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:20:57</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr"/>
+      <c r="G382" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:29:00</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr"/>
+      <c r="G383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:36:40</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr"/>
+      <c r="G384" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H301"/>
+  <dimension ref="A1:H302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-03-27 18:24:47</t>
+          <t>2026-05-18 19:14:00</t>
         </is>
       </c>
     </row>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-04-23 18:46:12</t>
+          <t>2026-05-18 19:05:01</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-05-07 18:23:27</t>
+          <t>2026-05-18 19:20:23</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-05-07 18:21:05</t>
+          <t>2026-05-18 19:00:07</t>
         </is>
       </c>
     </row>
@@ -12987,6 +12987,48 @@
       <c r="H301" t="inlineStr">
         <is>
           <t>2026-05-18 15:29:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>JEAN CARRIER</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>jcarrier@materiauxblanchet.ca</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>(418) 871-2626</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Materiaux blanchet</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>2026-05-18 19:25:32</t>
         </is>
       </c>
     </row>
@@ -13001,7 +13043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G384"/>
+  <dimension ref="A1:G389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24147,6 +24189,151 @@
       </c>
       <c r="F384" t="inlineStr"/>
       <c r="G384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Number busy</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>busy_call_back</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>2026-05-18 19:00:07</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr"/>
+      <c r="G385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>2026-05-18 19:05:01</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr"/>
+      <c r="G386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>2026-05-18 19:14:00</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr"/>
+      <c r="G387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>2026-05-18 19:20:23</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>2026-05-18 19:25:32</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr"/>
+      <c r="G389" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H302"/>
+  <dimension ref="A1:H307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13029,6 +13029,216 @@
       <c r="H302" t="inlineStr">
         <is>
           <t>2026-05-18 19:25:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Harry Leo III</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>leocraneservice@yahoo.com</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>(774) 321-0199</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Ha Leo Crane Service Llc</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>2026-05-19 12:18:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>CAROLYN LEARY</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>cel4242@gmail.com</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>(978) 333-2666</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>TJ TRANSPORT SERVICE INC</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>2026-05-19 12:20:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>DAVID M. CARLSTROM</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>david@carlstrompm.com</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>508 - 366 - 4472</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Carlstrompm</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>2026-05-19 12:29:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Patrick Cassidy</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>patrick@cassidylandscaping.com</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(781) 850-4530 </t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Cassidy landscaping</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>2026-05-19 12:32:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>PAUL CAVICCHIO</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>paul@cavicchio.com</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(978) 443-7177 </t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>cavicchio</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>2026-05-19 12:39:56</t>
         </is>
       </c>
     </row>
@@ -13043,7 +13253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G389"/>
+  <dimension ref="A1:G394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24334,6 +24544,151 @@
       </c>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>2026-05-19 12:18:19</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr"/>
+      <c r="G390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>2026-05-19 12:20:25</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>2026-05-19 12:29:41</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr"/>
+      <c r="G392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>2026-05-19 12:32:34</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>2026-05-19 12:39:56</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr"/>
+      <c r="G394" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H307"/>
+  <dimension ref="A1:H312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-05-06 19:25:27</t>
+          <t>2026-05-19 18:28:23</t>
         </is>
       </c>
     </row>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-05-06 19:27:23</t>
+          <t>2026-05-19 18:29:34</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-05-07 18:11:26</t>
+          <t>2026-05-19 20:15:45</t>
         </is>
       </c>
     </row>
@@ -9710,7 +9710,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-05-06 19:21:01</t>
+          <t>2026-05-19 18:22:09</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>2026-05-12 18:29:28</t>
+          <t>2026-05-19 19:59:33</t>
         </is>
       </c>
     </row>
@@ -12734,7 +12734,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>2026-05-15 12:55:59</t>
+          <t>2026-05-19 18:04:37</t>
         </is>
       </c>
     </row>
@@ -12776,7 +12776,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>2026-05-15 12:58:34</t>
+          <t>2026-05-19 20:02:58</t>
         </is>
       </c>
     </row>
@@ -13239,6 +13239,216 @@
       <c r="H307" t="inlineStr">
         <is>
           <t>2026-05-19 12:39:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>DARREL HOPKINS</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>dhopkins@primeinc.com</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>(417) 866-0001</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>Primeinc</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>2026-05-19 18:09:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Randy Marten</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>randy.marten@marten.com</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>(715) 926-4216</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>MARTEN TRANSPORT LTD</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>2026-05-19 18:13:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>CHARLES HAMMEL III</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>chammel@pittohio.com</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>(412) 232-3015</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>Pitt ohio</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>2026-05-19 18:18:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>ANTHONY DE ANGELIS</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>mammaromeo2@aol.com</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>(508) 889-6590</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>DE ANGELIS RAILROAD CONTRACTORS INC</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>2026-05-19 20:10:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>RICHARD CAPPELLO</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>dispatch@cappelloheavytransport.com</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (508) 958-6026</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>CAPPELLO HEAVY TRANSPORT LLC</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>2026-05-19 20:19:00</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G394"/>
+  <dimension ref="A1:G406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24689,6 +24899,354 @@
       </c>
       <c r="F394" t="inlineStr"/>
       <c r="G394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>2026-05-19 18:04:37</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr"/>
+      <c r="G395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>2026-05-19 18:09:24</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr"/>
+      <c r="G396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>2026-05-19 18:13:58</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr"/>
+      <c r="G397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>2026-05-19 18:18:09</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr"/>
+      <c r="G398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>2026-05-19 18:22:09</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>2026-05-19 18:28:23</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>2026-05-19 18:29:34</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr"/>
+      <c r="G401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>2026-05-19 19:59:33</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr"/>
+      <c r="G402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>2026-05-19 20:02:58</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr"/>
+      <c r="G403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>2026-05-19 20:10:47</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr"/>
+      <c r="G404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>2026-05-19 20:15:45</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr"/>
+      <c r="G405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>2026-05-19 20:19:00</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr"/>
+      <c r="G406" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -4292,7 +4292,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-04-28 19:09:07</t>
+          <t>2026-05-20 12:12:34</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-04-28 19:05:38</t>
+          <t>2026-05-20 12:07:44</t>
         </is>
       </c>
     </row>
@@ -6315,7 +6315,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Maureen Dowling</t>
+          <t>Stephen Dowling</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-04-28 19:17:29</t>
+          <t>2026-05-20 12:22:22</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-04-28 19:11:43</t>
+          <t>2026-05-20 12:16:25</t>
         </is>
       </c>
     </row>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-04-28 19:22:48</t>
+          <t>2026-05-20 12:28:53</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-04-10 13:20:44</t>
+          <t>2026-05-20 12:39:31</t>
         </is>
       </c>
     </row>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-04-13 15:56:19</t>
+          <t>2026-05-20 12:53:42</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>2026-04-28 19:27:32</t>
+          <t>2026-05-20 12:30:25</t>
         </is>
       </c>
     </row>
@@ -13463,7 +13463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G406"/>
+  <dimension ref="A1:G417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17624,17 +17624,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>643</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17644,7 +17644,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-04-13 15:45:27</t>
+          <t>2026-05-20 12:39:13</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
@@ -17653,7 +17653,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>286</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -17673,7 +17673,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-04-13 15:46:25</t>
+          <t>2026-04-13 15:45:27</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
@@ -17682,17 +17682,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>287</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17702,7 +17702,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-04-13 15:53:15</t>
+          <t>2026-04-13 15:46:25</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
@@ -17711,17 +17711,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>288</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17731,7 +17731,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-04-13 15:58:50</t>
+          <t>2026-04-13 15:53:15</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
@@ -17740,17 +17740,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>289</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -17760,7 +17760,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-04-27 16:24:24</t>
+          <t>2026-04-13 15:58:50</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
@@ -17769,17 +17769,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>351</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -17789,7 +17789,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-04-27 16:28:22</t>
+          <t>2026-04-27 16:24:24</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
@@ -17798,17 +17798,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>354</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -17818,7 +17818,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-04-27 16:35:40</t>
+          <t>2026-04-27 16:28:22</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
@@ -17827,7 +17827,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>366</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -17847,7 +17847,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-04-28 19:07:14</t>
+          <t>2026-04-27 16:35:40</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
@@ -17856,7 +17856,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>419</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -17876,7 +17876,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-04-28 19:16:45</t>
+          <t>2026-04-28 19:07:14</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
@@ -17885,17 +17885,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>424</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -17905,7 +17905,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-04-27 16:29:25</t>
+          <t>2026-04-28 19:16:45</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -17914,17 +17914,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>646</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-04-27 16:31:00</t>
+          <t>2026-05-20 12:53:22</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -17943,17 +17943,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>356</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -17963,7 +17963,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-04-27 16:39:21</t>
+          <t>2026-04-27 16:29:25</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -17972,17 +17972,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>358</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -17992,7 +17992,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-04-27 16:40:26</t>
+          <t>2026-04-27 16:31:00</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
@@ -18001,7 +18001,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>371</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -18021,7 +18021,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-04-27 16:42:47</t>
+          <t>2026-04-27 16:39:21</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -18030,17 +18030,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>373</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -18050,7 +18050,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-04-15 16:05:12</t>
+          <t>2026-04-27 16:40:26</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
@@ -18059,17 +18059,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>374</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -18079,7 +18079,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-04-15 18:17:17</t>
+          <t>2026-04-27 16:42:47</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -18088,17 +18088,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>294</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -18108,7 +18108,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-04-27 16:35:57</t>
+          <t>2026-04-15 16:05:12</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
@@ -18117,17 +18117,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>295</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -18137,7 +18137,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-04-27 16:52:02</t>
+          <t>2026-04-15 18:17:17</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
@@ -18146,17 +18146,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>367</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-04-28 19:11:23</t>
+          <t>2026-04-27 16:35:57</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
@@ -18175,17 +18175,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>387</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -18195,7 +18195,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-04-30 14:38:42</t>
+          <t>2026-04-27 16:52:02</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -18204,17 +18204,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>421</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -18224,7 +18224,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-04-16 12:32:37</t>
+          <t>2026-04-28 19:11:23</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
@@ -18233,17 +18233,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>451</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -18253,7 +18253,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-04-16 12:52:16</t>
+          <t>2026-04-30 14:38:42</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
@@ -18262,7 +18262,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>644</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -18282,7 +18282,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-04-27 16:37:49</t>
+          <t>2026-05-20 12:39:23</t>
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
@@ -18291,7 +18291,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>296</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -18311,7 +18311,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-04-27 16:45:32</t>
+          <t>2026-04-16 12:32:37</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
@@ -18320,17 +18320,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>297</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -18340,7 +18340,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-04-27 16:47:40</t>
+          <t>2026-04-16 12:52:16</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
@@ -18349,17 +18349,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>368</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -18369,7 +18369,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-04-16 18:41:52</t>
+          <t>2026-04-27 16:37:49</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
@@ -18378,17 +18378,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>379</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -18398,7 +18398,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-04-23 18:27:22</t>
+          <t>2026-04-27 16:45:32</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
@@ -18407,7 +18407,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>382</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -18427,7 +18427,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-04-23 18:30:25</t>
+          <t>2026-04-27 16:47:40</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
@@ -18436,17 +18436,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>299</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -18456,7 +18456,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-04-27 16:43:45</t>
+          <t>2026-04-16 18:41:52</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -18465,17 +18465,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>312</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -18485,7 +18485,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-04-23 18:40:56</t>
+          <t>2026-04-23 18:27:22</t>
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
@@ -18494,17 +18494,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>314</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-04-21 15:49:30</t>
+          <t>2026-04-23 18:30:25</t>
         </is>
       </c>
       <c r="F174" t="inlineStr"/>
@@ -18523,17 +18523,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>377</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -18543,7 +18543,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-04-21 15:52:28</t>
+          <t>2026-04-27 16:43:45</t>
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
@@ -18552,17 +18552,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>317</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>interested</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -18572,7 +18572,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-04-21 17:03:38</t>
+          <t>2026-04-23 18:40:56</t>
         </is>
       </c>
       <c r="F176" t="inlineStr"/>
@@ -18581,17 +18581,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>300</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -18601,7 +18601,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-04-22 16:41:07</t>
+          <t>2026-04-21 15:49:30</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -18610,17 +18610,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>301</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -18630,7 +18630,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:41</t>
+          <t>2026-04-21 15:52:28</t>
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
@@ -18639,17 +18639,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>302</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>interested</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -18659,7 +18659,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-04-28 19:35:07</t>
+          <t>2026-04-21 17:03:38</t>
         </is>
       </c>
       <c r="F179" t="inlineStr"/>
@@ -18668,17 +18668,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>303</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -18688,7 +18688,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-05-06 17:53:39</t>
+          <t>2026-04-22 16:41:07</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
@@ -18697,7 +18697,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>392</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -18717,7 +18717,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-05-07 12:25:07</t>
+          <t>2026-04-27 18:05:41</t>
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
@@ -18726,17 +18726,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>437</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -18746,7 +18746,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2026-04-23 15:49:56</t>
+          <t>2026-04-28 19:35:07</t>
         </is>
       </c>
       <c r="F182" t="inlineStr"/>
@@ -18755,7 +18755,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>500</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -18775,7 +18775,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-04-23 18:16:45</t>
+          <t>2026-05-06 17:53:39</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
@@ -18784,7 +18784,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>521</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -18804,7 +18804,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-04-23 18:22:46</t>
+          <t>2026-05-07 12:25:07</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -18813,17 +18813,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>306</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -18833,7 +18833,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-04-23 18:25:02</t>
+          <t>2026-04-23 15:49:56</t>
         </is>
       </c>
       <c r="F185" t="inlineStr"/>
@@ -18842,7 +18842,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>307</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -18862,7 +18862,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-04-23 18:27:36</t>
+          <t>2026-04-23 18:16:45</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
@@ -18871,7 +18871,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>309</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -18891,7 +18891,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-04-27 18:07:45</t>
+          <t>2026-04-23 18:22:46</t>
         </is>
       </c>
       <c r="F187" t="inlineStr"/>
@@ -18900,7 +18900,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>311</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-04-27 18:12:10</t>
+          <t>2026-04-23 18:25:02</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
@@ -18929,7 +18929,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>313</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-04-23 18:30:34</t>
+          <t>2026-04-23 18:27:36</t>
         </is>
       </c>
       <c r="F189" t="inlineStr"/>
@@ -18958,17 +18958,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>394</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -18978,7 +18978,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2026-04-23 18:35:35</t>
+          <t>2026-04-27 18:07:45</t>
         </is>
       </c>
       <c r="F190" t="inlineStr"/>
@@ -18987,17 +18987,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>397</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -19007,7 +19007,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-04-23 18:41:25</t>
+          <t>2026-04-27 18:12:10</t>
         </is>
       </c>
       <c r="F191" t="inlineStr"/>
@@ -19016,7 +19016,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>315</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-04-23 18:46:12</t>
+          <t>2026-04-23 18:30:34</t>
         </is>
       </c>
       <c r="F192" t="inlineStr"/>
@@ -19045,17 +19045,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>316</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -19065,7 +19065,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-04-23 18:58:17</t>
+          <t>2026-04-23 18:35:35</t>
         </is>
       </c>
       <c r="F193" t="inlineStr"/>
@@ -19074,17 +19074,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>318</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -19094,7 +19094,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-04-23 19:09:01</t>
+          <t>2026-04-23 18:41:25</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -19103,7 +19103,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -19123,7 +19123,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-04-23 19:28:02</t>
+          <t>2026-04-23 18:46:12</t>
         </is>
       </c>
       <c r="F195" t="inlineStr"/>
@@ -19132,17 +19132,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>321</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -19152,7 +19152,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2026-04-23 19:33:02</t>
+          <t>2026-04-23 18:58:17</t>
         </is>
       </c>
       <c r="F196" t="inlineStr"/>
@@ -19161,17 +19161,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>322</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>BUSY-CALL BACK</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -19181,7 +19181,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-04-23 19:35:57</t>
+          <t>2026-04-23 19:09:01</t>
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
@@ -19190,17 +19190,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>323</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -19210,7 +19210,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-04-24 11:52:45</t>
+          <t>2026-04-23 19:28:02</t>
         </is>
       </c>
       <c r="F198" t="inlineStr"/>
@@ -19219,7 +19219,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>324</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -19239,7 +19239,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-04-24 11:55:39</t>
+          <t>2026-04-23 19:33:02</t>
         </is>
       </c>
       <c r="F199" t="inlineStr"/>
@@ -19248,17 +19248,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>325</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>BUSY-CALL BACK</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -19268,7 +19268,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2026-04-24 12:13:00</t>
+          <t>2026-04-23 19:35:57</t>
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
@@ -19277,7 +19277,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>326</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -19297,7 +19297,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-04-24 12:17:05</t>
+          <t>2026-04-24 11:52:45</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -19306,7 +19306,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>328</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -19326,7 +19326,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-04-24 12:19:39</t>
+          <t>2026-04-24 11:55:39</t>
         </is>
       </c>
       <c r="F202" t="inlineStr"/>
@@ -19335,17 +19335,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>329</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -19355,7 +19355,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-04-24 12:31:15</t>
+          <t>2026-04-24 12:13:00</t>
         </is>
       </c>
       <c r="F203" t="inlineStr"/>
@@ -19364,17 +19364,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>330</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -19384,7 +19384,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-04-24 12:33:01</t>
+          <t>2026-04-24 12:17:05</t>
         </is>
       </c>
       <c r="F204" t="inlineStr"/>
@@ -19393,17 +19393,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>331</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -19413,7 +19413,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-04-24 14:36:24</t>
+          <t>2026-04-24 12:19:39</t>
         </is>
       </c>
       <c r="F205" t="inlineStr"/>
@@ -19422,17 +19422,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>332</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -19442,7 +19442,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-04-24 14:43:03</t>
+          <t>2026-04-24 12:31:15</t>
         </is>
       </c>
       <c r="F206" t="inlineStr"/>
@@ -19451,7 +19451,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>333</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -19471,7 +19471,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-04-24 14:58:00</t>
+          <t>2026-04-24 12:33:01</t>
         </is>
       </c>
       <c r="F207" t="inlineStr"/>
@@ -19480,17 +19480,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>334</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -19500,7 +19500,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-04-27 14:06:10</t>
+          <t>2026-04-24 14:36:24</t>
         </is>
       </c>
       <c r="F208" t="inlineStr"/>
@@ -19509,17 +19509,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>335</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -19529,7 +19529,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-04-27 14:10:21</t>
+          <t>2026-04-24 14:43:03</t>
         </is>
       </c>
       <c r="F209" t="inlineStr"/>
@@ -19538,17 +19538,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>336</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -19558,7 +19558,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2026-04-27 14:13:06</t>
+          <t>2026-04-24 14:58:00</t>
         </is>
       </c>
       <c r="F210" t="inlineStr"/>
@@ -19567,7 +19567,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>337</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -19587,7 +19587,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-04-27 14:15:47</t>
+          <t>2026-04-27 14:06:10</t>
         </is>
       </c>
       <c r="F211" t="inlineStr"/>
@@ -19596,7 +19596,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>338</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-04-27 18:05:51</t>
+          <t>2026-04-27 14:10:21</t>
         </is>
       </c>
       <c r="F212" t="inlineStr"/>
@@ -19625,17 +19625,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>339</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -19645,7 +19645,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-04-27 18:08:12</t>
+          <t>2026-04-27 14:13:06</t>
         </is>
       </c>
       <c r="F213" t="inlineStr"/>
@@ -19654,17 +19654,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>340</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -19674,7 +19674,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-04-27 18:10:09</t>
+          <t>2026-04-27 14:15:47</t>
         </is>
       </c>
       <c r="F214" t="inlineStr"/>
@@ -19683,17 +19683,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>393</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-04-27 18:12:49</t>
+          <t>2026-04-27 18:05:51</t>
         </is>
       </c>
       <c r="F215" t="inlineStr"/>
@@ -19712,17 +19712,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>395</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -19732,7 +19732,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-04-27 18:25:23</t>
+          <t>2026-04-27 18:08:12</t>
         </is>
       </c>
       <c r="F216" t="inlineStr"/>
@@ -19741,7 +19741,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>396</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -19761,7 +19761,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-04-27 18:26:29</t>
+          <t>2026-04-27 18:10:09</t>
         </is>
       </c>
       <c r="F217" t="inlineStr"/>
@@ -19770,17 +19770,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>398</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -19790,7 +19790,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-04-27 18:28:56</t>
+          <t>2026-04-27 18:12:49</t>
         </is>
       </c>
       <c r="F218" t="inlineStr"/>
@@ -19799,17 +19799,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>399</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -19819,7 +19819,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-04-27 18:32:14</t>
+          <t>2026-04-27 18:25:23</t>
         </is>
       </c>
       <c r="F219" t="inlineStr"/>
@@ -19828,7 +19828,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>400</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -19848,7 +19848,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-04-27 19:10:16</t>
+          <t>2026-04-27 18:26:29</t>
         </is>
       </c>
       <c r="F220" t="inlineStr"/>
@@ -19857,7 +19857,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>401</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -19877,7 +19877,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-04-28 13:06:06</t>
+          <t>2026-04-27 18:28:56</t>
         </is>
       </c>
       <c r="F221" t="inlineStr"/>
@@ -19886,17 +19886,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>402</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -19906,7 +19906,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-04-28 13:09:10</t>
+          <t>2026-04-27 18:32:14</t>
         </is>
       </c>
       <c r="F222" t="inlineStr"/>
@@ -19915,17 +19915,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>403</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -19935,7 +19935,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-04-28 13:31:57</t>
+          <t>2026-04-27 19:10:16</t>
         </is>
       </c>
       <c r="F223" t="inlineStr"/>
@@ -19944,17 +19944,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>404</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-04-28 16:36:52</t>
+          <t>2026-04-28 13:06:06</t>
         </is>
       </c>
       <c r="F224" t="inlineStr"/>
@@ -19973,17 +19973,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>405</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -19993,7 +19993,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-04-28 16:41:55</t>
+          <t>2026-04-28 13:09:10</t>
         </is>
       </c>
       <c r="F225" t="inlineStr"/>
@@ -20002,17 +20002,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>406</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -20022,7 +20022,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-04-28 16:45:43</t>
+          <t>2026-04-28 13:31:57</t>
         </is>
       </c>
       <c r="F226" t="inlineStr"/>
@@ -20031,7 +20031,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>408</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -20051,7 +20051,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-04-28 16:50:41</t>
+          <t>2026-04-28 16:36:52</t>
         </is>
       </c>
       <c r="F227" t="inlineStr"/>
@@ -20060,17 +20060,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>409</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-04-28 16:58:22</t>
+          <t>2026-04-28 16:41:55</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
@@ -20089,17 +20089,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>410</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -20109,7 +20109,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-04-28 19:11:43</t>
+          <t>2026-04-28 16:45:43</t>
         </is>
       </c>
       <c r="F229" t="inlineStr"/>
@@ -20118,7 +20118,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>411</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -20138,7 +20138,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-04-28 19:17:29</t>
+          <t>2026-04-28 16:50:41</t>
         </is>
       </c>
       <c r="F230" t="inlineStr"/>
@@ -20147,17 +20147,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>412</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -20167,7 +20167,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-04-28 19:20:41</t>
+          <t>2026-04-28 16:58:22</t>
         </is>
       </c>
       <c r="F231" t="inlineStr"/>
@@ -20176,17 +20176,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>422</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-04-28 19:27:32</t>
+          <t>2026-04-28 19:11:43</t>
         </is>
       </c>
       <c r="F232" t="inlineStr"/>
@@ -20205,17 +20205,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>425</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -20225,7 +20225,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-04-28 19:29:59</t>
+          <t>2026-04-28 19:17:29</t>
         </is>
       </c>
       <c r="F233" t="inlineStr"/>
@@ -20234,7 +20234,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>427</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -20254,7 +20254,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-04-28 19:38:54</t>
+          <t>2026-04-28 19:20:41</t>
         </is>
       </c>
       <c r="F234" t="inlineStr"/>
@@ -20263,17 +20263,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>431</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -20283,7 +20283,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-04-28 18:59:52</t>
+          <t>2026-04-28 19:27:32</t>
         </is>
       </c>
       <c r="F235" t="inlineStr"/>
@@ -20292,17 +20292,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>432</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -20312,7 +20312,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2026-04-28 19:05:38</t>
+          <t>2026-04-28 19:29:59</t>
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
@@ -20321,7 +20321,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>438</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -20341,7 +20341,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-04-28 19:09:07</t>
+          <t>2026-04-28 19:38:54</t>
         </is>
       </c>
       <c r="F237" t="inlineStr"/>
@@ -20350,17 +20350,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>413</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-04-28 19:22:49</t>
+          <t>2026-04-28 18:59:52</t>
         </is>
       </c>
       <c r="F238" t="inlineStr"/>
@@ -20379,17 +20379,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>416</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-04-28 19:46:42</t>
+          <t>2026-04-28 19:05:38</t>
         </is>
       </c>
       <c r="F239" t="inlineStr"/>
@@ -20408,7 +20408,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>420</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -20428,7 +20428,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-04-29 15:54:41</t>
+          <t>2026-04-28 19:09:07</t>
         </is>
       </c>
       <c r="F240" t="inlineStr"/>
@@ -20437,7 +20437,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>429</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -20457,7 +20457,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-04-29 15:56:41</t>
+          <t>2026-04-28 19:22:49</t>
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
@@ -20466,17 +20466,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>439</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -20486,7 +20486,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-04-29 16:10:35</t>
+          <t>2026-04-28 19:46:42</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
@@ -20495,17 +20495,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>440</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -20515,7 +20515,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-04-29 16:13:57</t>
+          <t>2026-04-29 15:54:41</t>
         </is>
       </c>
       <c r="F243" t="inlineStr"/>
@@ -20524,7 +20524,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>441</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -20544,7 +20544,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-04-29 16:17:13</t>
+          <t>2026-04-29 15:56:41</t>
         </is>
       </c>
       <c r="F244" t="inlineStr"/>
@@ -20553,17 +20553,17 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>442</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -20573,7 +20573,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-04-29 16:21:56</t>
+          <t>2026-04-29 16:10:35</t>
         </is>
       </c>
       <c r="F245" t="inlineStr"/>
@@ -20582,17 +20582,17 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>443</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -20602,7 +20602,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-04-29 16:26:19</t>
+          <t>2026-04-29 16:13:57</t>
         </is>
       </c>
       <c r="F246" t="inlineStr"/>
@@ -20611,7 +20611,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>444</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -20631,7 +20631,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-04-30 11:56:22</t>
+          <t>2026-04-29 16:17:13</t>
         </is>
       </c>
       <c r="F247" t="inlineStr"/>
@@ -20640,7 +20640,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>445</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -20660,7 +20660,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-04-30 12:18:39</t>
+          <t>2026-04-29 16:21:56</t>
         </is>
       </c>
       <c r="F248" t="inlineStr"/>
@@ -20669,7 +20669,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>446</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -20689,7 +20689,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-04-30 12:27:47</t>
+          <t>2026-04-29 16:26:19</t>
         </is>
       </c>
       <c r="F249" t="inlineStr"/>
@@ -20698,17 +20698,17 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>447</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -20718,7 +20718,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-04-30 14:33:48</t>
+          <t>2026-04-30 11:56:22</t>
         </is>
       </c>
       <c r="F250" t="inlineStr"/>
@@ -20727,17 +20727,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>448</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -20747,7 +20747,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-04-30 14:39:11</t>
+          <t>2026-04-30 12:18:39</t>
         </is>
       </c>
       <c r="F251" t="inlineStr"/>
@@ -20756,7 +20756,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>449</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20776,7 +20776,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-04-30 14:44:06</t>
+          <t>2026-04-30 12:27:47</t>
         </is>
       </c>
       <c r="F252" t="inlineStr"/>
@@ -20785,17 +20785,17 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>450</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-04-30 14:50:48</t>
+          <t>2026-04-30 14:33:48</t>
         </is>
       </c>
       <c r="F253" t="inlineStr"/>
@@ -20814,17 +20814,17 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>452</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -20834,7 +20834,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-04-30 15:03:19</t>
+          <t>2026-04-30 14:39:11</t>
         </is>
       </c>
       <c r="F254" t="inlineStr"/>
@@ -20843,7 +20843,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>453</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20863,7 +20863,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-04-30 16:43:14</t>
+          <t>2026-04-30 14:44:06</t>
         </is>
       </c>
       <c r="F255" t="inlineStr"/>
@@ -20872,17 +20872,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>454</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -20892,7 +20892,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2026-04-30 16:49:38</t>
+          <t>2026-04-30 14:50:48</t>
         </is>
       </c>
       <c r="F256" t="inlineStr"/>
@@ -20901,17 +20901,17 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>455</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -20921,7 +20921,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-04-30 16:57:13</t>
+          <t>2026-04-30 15:03:19</t>
         </is>
       </c>
       <c r="F257" t="inlineStr"/>
@@ -20930,17 +20930,17 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>456</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -20950,7 +20950,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-04-30 16:59:14</t>
+          <t>2026-04-30 16:43:14</t>
         </is>
       </c>
       <c r="F258" t="inlineStr"/>
@@ -20959,7 +20959,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>457</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20979,7 +20979,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-04-30 17:03:09</t>
+          <t>2026-04-30 16:49:38</t>
         </is>
       </c>
       <c r="F259" t="inlineStr"/>
@@ -20988,17 +20988,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>458</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -21008,7 +21008,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-04-30 17:07:20</t>
+          <t>2026-04-30 16:57:13</t>
         </is>
       </c>
       <c r="F260" t="inlineStr"/>
@@ -21017,17 +21017,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>459</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -21037,7 +21037,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-04-30 17:20:16</t>
+          <t>2026-04-30 16:59:14</t>
         </is>
       </c>
       <c r="F261" t="inlineStr"/>
@@ -21046,7 +21046,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -21066,7 +21066,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-05-04 12:40:26</t>
+          <t>2026-04-30 17:03:09</t>
         </is>
       </c>
       <c r="F262" t="inlineStr"/>
@@ -21075,17 +21075,17 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>461</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -21095,7 +21095,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-05-04 13:27:46</t>
+          <t>2026-04-30 17:07:20</t>
         </is>
       </c>
       <c r="F263" t="inlineStr"/>
@@ -21104,7 +21104,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>462</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -21124,7 +21124,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-05-04 13:32:27</t>
+          <t>2026-04-30 17:20:16</t>
         </is>
       </c>
       <c r="F264" t="inlineStr"/>
@@ -21133,17 +21133,17 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>465</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -21153,7 +21153,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-05-04 13:35:31</t>
+          <t>2026-05-04 12:40:26</t>
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
@@ -21162,7 +21162,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>466</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21182,7 +21182,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-05-04 13:52:33</t>
+          <t>2026-05-04 13:27:46</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
@@ -21191,7 +21191,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>467</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21211,7 +21211,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-05-04 14:15:29</t>
+          <t>2026-05-04 13:32:27</t>
         </is>
       </c>
       <c r="F267" t="inlineStr"/>
@@ -21220,17 +21220,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>468</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -21240,7 +21240,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-05-04 14:21:26</t>
+          <t>2026-05-04 13:35:31</t>
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
@@ -21249,17 +21249,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>469</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -21269,7 +21269,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-05-04 14:28:28</t>
+          <t>2026-05-04 13:52:33</t>
         </is>
       </c>
       <c r="F269" t="inlineStr"/>
@@ -21278,17 +21278,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>470</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -21298,7 +21298,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-05-05 12:33:28</t>
+          <t>2026-05-04 14:15:29</t>
         </is>
       </c>
       <c r="F270" t="inlineStr"/>
@@ -21307,17 +21307,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>471</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -21327,7 +21327,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-05-05 12:36:49</t>
+          <t>2026-05-04 14:21:26</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
@@ -21336,7 +21336,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>472</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21356,7 +21356,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-05-05 13:16:10</t>
+          <t>2026-05-04 14:28:28</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
@@ -21365,17 +21365,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>473</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -21385,7 +21385,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-05-05 13:22:28</t>
+          <t>2026-05-05 12:33:28</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
@@ -21394,17 +21394,17 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>474</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -21414,7 +21414,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-05-05 15:49:32</t>
+          <t>2026-05-05 12:36:49</t>
         </is>
       </c>
       <c r="F274" t="inlineStr"/>
@@ -21423,7 +21423,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>475</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -21443,7 +21443,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-05-05 18:17:18</t>
+          <t>2026-05-05 13:16:10</t>
         </is>
       </c>
       <c r="F275" t="inlineStr"/>
@@ -21452,17 +21452,17 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>476</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -21472,7 +21472,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-05-05 18:23:24</t>
+          <t>2026-05-05 13:22:28</t>
         </is>
       </c>
       <c r="F276" t="inlineStr"/>
@@ -21481,17 +21481,17 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>478</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-05-05 18:30:18</t>
+          <t>2026-05-05 15:49:32</t>
         </is>
       </c>
       <c r="F277" t="inlineStr"/>
@@ -21510,7 +21510,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>484</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -21530,7 +21530,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-05-05 19:24:36</t>
+          <t>2026-05-05 18:17:18</t>
         </is>
       </c>
       <c r="F278" t="inlineStr"/>
@@ -21539,7 +21539,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>485</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -21559,7 +21559,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-05-06 14:07:52</t>
+          <t>2026-05-05 18:23:24</t>
         </is>
       </c>
       <c r="F279" t="inlineStr"/>
@@ -21568,17 +21568,17 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>486</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -21588,7 +21588,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-05-06 14:12:50</t>
+          <t>2026-05-05 18:30:18</t>
         </is>
       </c>
       <c r="F280" t="inlineStr"/>
@@ -21597,7 +21597,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>487</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -21617,7 +21617,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-05-06 14:15:34</t>
+          <t>2026-05-05 19:24:36</t>
         </is>
       </c>
       <c r="F281" t="inlineStr"/>
@@ -21626,17 +21626,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>488</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -21646,7 +21646,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-05-06 14:59:26</t>
+          <t>2026-05-06 14:07:52</t>
         </is>
       </c>
       <c r="F282" t="inlineStr"/>
@@ -21655,17 +21655,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>489</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-05-06 15:04:52</t>
+          <t>2026-05-06 14:12:50</t>
         </is>
       </c>
       <c r="F283" t="inlineStr"/>
@@ -21684,7 +21684,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>490</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -21704,7 +21704,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-05-06 15:08:51</t>
+          <t>2026-05-06 14:15:34</t>
         </is>
       </c>
       <c r="F284" t="inlineStr"/>
@@ -21713,17 +21713,17 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Busy</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -21733,7 +21733,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-05-06 15:28:38</t>
+          <t>2026-05-06 14:59:26</t>
         </is>
       </c>
       <c r="F285" t="inlineStr"/>
@@ -21742,17 +21742,17 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>492</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -21762,7 +21762,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-05-06 15:31:36</t>
+          <t>2026-05-06 15:04:52</t>
         </is>
       </c>
       <c r="F286" t="inlineStr"/>
@@ -21771,7 +21771,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>493</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -21791,7 +21791,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-05-06 17:53:50</t>
+          <t>2026-05-06 15:08:51</t>
         </is>
       </c>
       <c r="F287" t="inlineStr"/>
@@ -21800,17 +21800,17 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>494</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Busy</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -21820,7 +21820,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>2026-05-06 17:59:31</t>
+          <t>2026-05-06 15:28:38</t>
         </is>
       </c>
       <c r="F288" t="inlineStr"/>
@@ -21829,17 +21829,17 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>495</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -21849,7 +21849,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-05-06 19:18:14</t>
+          <t>2026-05-06 15:31:36</t>
         </is>
       </c>
       <c r="F289" t="inlineStr"/>
@@ -21858,7 +21858,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>501</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -21878,7 +21878,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-05-06 19:21:01</t>
+          <t>2026-05-06 17:53:50</t>
         </is>
       </c>
       <c r="F290" t="inlineStr"/>
@@ -21887,7 +21887,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>502</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -21907,7 +21907,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-05-06 19:25:27</t>
+          <t>2026-05-06 17:59:31</t>
         </is>
       </c>
       <c r="F291" t="inlineStr"/>
@@ -21916,17 +21916,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>503</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -21936,7 +21936,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-05-06 19:27:23</t>
+          <t>2026-05-06 19:18:14</t>
         </is>
       </c>
       <c r="F292" t="inlineStr"/>
@@ -21945,17 +21945,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>504</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -21965,7 +21965,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-05-06 19:39:21</t>
+          <t>2026-05-06 19:21:01</t>
         </is>
       </c>
       <c r="F293" t="inlineStr"/>
@@ -21974,17 +21974,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>505</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2026-05-06 20:09:52</t>
+          <t>2026-05-06 19:25:27</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
@@ -22003,7 +22003,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>506</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -22023,7 +22023,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-05-06 20:12:28</t>
+          <t>2026-05-06 19:27:23</t>
         </is>
       </c>
       <c r="F295" t="inlineStr"/>
@@ -22032,17 +22032,17 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>507</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -22052,7 +22052,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-05-07 12:02:27</t>
+          <t>2026-05-06 19:39:21</t>
         </is>
       </c>
       <c r="F296" t="inlineStr"/>
@@ -22061,17 +22061,17 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>509</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -22081,7 +22081,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-05-07 12:05:31</t>
+          <t>2026-05-06 20:09:52</t>
         </is>
       </c>
       <c r="F297" t="inlineStr"/>
@@ -22090,17 +22090,17 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>511</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -22110,7 +22110,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-05-07 12:07:46</t>
+          <t>2026-05-06 20:12:28</t>
         </is>
       </c>
       <c r="F298" t="inlineStr"/>
@@ -22119,17 +22119,17 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>512</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -22139,7 +22139,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-05-07 12:12:23</t>
+          <t>2026-05-07 12:02:27</t>
         </is>
       </c>
       <c r="F299" t="inlineStr"/>
@@ -22148,17 +22148,17 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>513</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -22168,7 +22168,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-05-07 12:21:17</t>
+          <t>2026-05-07 12:05:31</t>
         </is>
       </c>
       <c r="F300" t="inlineStr"/>
@@ -22177,17 +22177,17 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>514</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -22197,7 +22197,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-05-07 12:22:26</t>
+          <t>2026-05-07 12:07:46</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
@@ -22206,17 +22206,17 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>515</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-05-07 12:25:15</t>
+          <t>2026-05-07 12:12:23</t>
         </is>
       </c>
       <c r="F302" t="inlineStr"/>
@@ -22235,7 +22235,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>516</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -22255,7 +22255,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-05-07 12:30:09</t>
+          <t>2026-05-07 12:21:17</t>
         </is>
       </c>
       <c r="F303" t="inlineStr"/>
@@ -22264,7 +22264,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>517</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -22284,7 +22284,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-05-07 18:11:26</t>
+          <t>2026-05-07 12:22:26</t>
         </is>
       </c>
       <c r="F304" t="inlineStr"/>
@@ -22293,17 +22293,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>522</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -22313,7 +22313,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-05-07 18:21:05</t>
+          <t>2026-05-07 12:25:15</t>
         </is>
       </c>
       <c r="F305" t="inlineStr"/>
@@ -22322,7 +22322,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>524</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -22342,7 +22342,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-05-07 18:23:27</t>
+          <t>2026-05-07 12:30:09</t>
         </is>
       </c>
       <c r="F306" t="inlineStr"/>
@@ -22351,17 +22351,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>527</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -22371,7 +22371,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-05-07 18:31:47</t>
+          <t>2026-05-07 18:11:26</t>
         </is>
       </c>
       <c r="F307" t="inlineStr"/>
@@ -22380,17 +22380,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>528</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-05-07 18:41:02</t>
+          <t>2026-05-07 18:21:05</t>
         </is>
       </c>
       <c r="F308" t="inlineStr"/>
@@ -22409,17 +22409,17 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>529</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>HUNG UP</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -22429,7 +22429,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-05-07 19:04:03</t>
+          <t>2026-05-07 18:23:27</t>
         </is>
       </c>
       <c r="F309" t="inlineStr"/>
@@ -22438,17 +22438,17 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>530</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -22458,7 +22458,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-05-07 19:12:07</t>
+          <t>2026-05-07 18:31:47</t>
         </is>
       </c>
       <c r="F310" t="inlineStr"/>
@@ -22467,17 +22467,17 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>531</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -22487,7 +22487,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-05-07 19:19:47</t>
+          <t>2026-05-07 18:41:02</t>
         </is>
       </c>
       <c r="F311" t="inlineStr"/>
@@ -22496,17 +22496,17 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>532</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>HUNG UP</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -22516,7 +22516,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-05-07 19:35:25</t>
+          <t>2026-05-07 19:04:03</t>
         </is>
       </c>
       <c r="F312" t="inlineStr"/>
@@ -22525,17 +22525,17 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>533</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -22545,7 +22545,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-05-08 12:36:57</t>
+          <t>2026-05-07 19:12:07</t>
         </is>
       </c>
       <c r="F313" t="inlineStr"/>
@@ -22554,7 +22554,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>534</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -22574,7 +22574,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-05-08 12:43:59</t>
+          <t>2026-05-07 19:19:47</t>
         </is>
       </c>
       <c r="F314" t="inlineStr"/>
@@ -22583,17 +22583,17 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>535</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -22603,7 +22603,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2026-05-08 12:51:09</t>
+          <t>2026-05-07 19:35:25</t>
         </is>
       </c>
       <c r="F315" t="inlineStr"/>
@@ -22612,7 +22612,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>536</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -22632,7 +22632,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-05-08 12:55:15</t>
+          <t>2026-05-08 12:36:57</t>
         </is>
       </c>
       <c r="F316" t="inlineStr"/>
@@ -22641,7 +22641,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>537</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -22661,7 +22661,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-05-08 12:57:14</t>
+          <t>2026-05-08 12:43:59</t>
         </is>
       </c>
       <c r="F317" t="inlineStr"/>
@@ -22670,17 +22670,17 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>538</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -22690,7 +22690,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-05-08 13:00:41</t>
+          <t>2026-05-08 12:51:09</t>
         </is>
       </c>
       <c r="F318" t="inlineStr"/>
@@ -22699,17 +22699,17 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>539</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -22719,7 +22719,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-05-08 13:04:02</t>
+          <t>2026-05-08 12:55:15</t>
         </is>
       </c>
       <c r="F319" t="inlineStr"/>
@@ -22728,7 +22728,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>540</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -22748,7 +22748,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-05-08 13:09:59</t>
+          <t>2026-05-08 12:57:14</t>
         </is>
       </c>
       <c r="F320" t="inlineStr"/>
@@ -22757,17 +22757,17 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>541</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>WARM LEAD</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>warm_lead</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-05-08 13:16:49</t>
+          <t>2026-05-08 13:00:41</t>
         </is>
       </c>
       <c r="F321" t="inlineStr"/>
@@ -22786,17 +22786,17 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>542</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -22806,7 +22806,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-05-08 13:22:02</t>
+          <t>2026-05-08 13:04:02</t>
         </is>
       </c>
       <c r="F322" t="inlineStr"/>
@@ -22815,7 +22815,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>543</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -22835,7 +22835,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-05-08 15:50:51</t>
+          <t>2026-05-08 13:09:59</t>
         </is>
       </c>
       <c r="F323" t="inlineStr"/>
@@ -22844,17 +22844,17 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>544</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>WARM LEAD</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>warm_lead</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -22864,7 +22864,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-05-08 15:54:37</t>
+          <t>2026-05-08 13:16:49</t>
         </is>
       </c>
       <c r="F324" t="inlineStr"/>
@@ -22873,7 +22873,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>545</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -22893,7 +22893,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-05-08 15:59:34</t>
+          <t>2026-05-08 13:22:02</t>
         </is>
       </c>
       <c r="F325" t="inlineStr"/>
@@ -22902,7 +22902,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>546</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -22922,7 +22922,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-05-08 16:11:07</t>
+          <t>2026-05-08 15:50:51</t>
         </is>
       </c>
       <c r="F326" t="inlineStr"/>
@@ -22931,17 +22931,17 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>547</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -22951,7 +22951,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-05-08 16:19:50</t>
+          <t>2026-05-08 15:54:37</t>
         </is>
       </c>
       <c r="F327" t="inlineStr"/>
@@ -22960,7 +22960,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>548</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -22980,7 +22980,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-05-08 16:24:03</t>
+          <t>2026-05-08 15:59:34</t>
         </is>
       </c>
       <c r="F328" t="inlineStr"/>
@@ -22989,17 +22989,17 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>549</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-05-11 18:35:26</t>
+          <t>2026-05-08 16:11:07</t>
         </is>
       </c>
       <c r="F329" t="inlineStr"/>
@@ -23018,17 +23018,17 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>550</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -23038,7 +23038,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-05-12 12:12:48</t>
+          <t>2026-05-08 16:19:50</t>
         </is>
       </c>
       <c r="F330" t="inlineStr"/>
@@ -23047,17 +23047,17 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>551</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -23067,7 +23067,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-05-12 12:18:21</t>
+          <t>2026-05-08 16:24:03</t>
         </is>
       </c>
       <c r="F331" t="inlineStr"/>
@@ -23076,17 +23076,17 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>552</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -23096,7 +23096,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2026-05-12 12:22:04</t>
+          <t>2026-05-11 18:35:26</t>
         </is>
       </c>
       <c r="F332" t="inlineStr"/>
@@ -23105,17 +23105,17 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>553</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Call disconnected</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>hung_up</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -23125,7 +23125,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-05-12 12:23:33</t>
+          <t>2026-05-12 12:12:48</t>
         </is>
       </c>
       <c r="F333" t="inlineStr"/>
@@ -23134,17 +23134,17 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>554</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -23154,7 +23154,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-05-12 12:26:05</t>
+          <t>2026-05-12 12:18:21</t>
         </is>
       </c>
       <c r="F334" t="inlineStr"/>
@@ -23163,17 +23163,17 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>555</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -23183,7 +23183,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-05-12 12:31:00</t>
+          <t>2026-05-12 12:22:04</t>
         </is>
       </c>
       <c r="F335" t="inlineStr"/>
@@ -23192,17 +23192,17 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>556</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Call disconnected</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>hung_up</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -23212,7 +23212,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-05-12 12:33:59</t>
+          <t>2026-05-12 12:23:33</t>
         </is>
       </c>
       <c r="F336" t="inlineStr"/>
@@ -23221,7 +23221,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>557</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -23241,7 +23241,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-05-12 12:37:48</t>
+          <t>2026-05-12 12:26:05</t>
         </is>
       </c>
       <c r="F337" t="inlineStr"/>
@@ -23250,7 +23250,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>558</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -23270,7 +23270,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-05-12 12:48:40</t>
+          <t>2026-05-12 12:31:00</t>
         </is>
       </c>
       <c r="F338" t="inlineStr"/>
@@ -23279,17 +23279,17 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>559</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -23299,7 +23299,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-05-12 12:51:08</t>
+          <t>2026-05-12 12:33:59</t>
         </is>
       </c>
       <c r="F339" t="inlineStr"/>
@@ -23308,7 +23308,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>560</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -23328,7 +23328,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-05-12 18:19:14</t>
+          <t>2026-05-12 12:37:48</t>
         </is>
       </c>
       <c r="F340" t="inlineStr"/>
@@ -23337,17 +23337,17 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -23357,7 +23357,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>2026-05-12 18:26:39</t>
+          <t>2026-05-12 12:48:40</t>
         </is>
       </c>
       <c r="F341" t="inlineStr"/>
@@ -23366,7 +23366,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>562</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -23386,7 +23386,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-05-12 18:29:28</t>
+          <t>2026-05-12 12:51:08</t>
         </is>
       </c>
       <c r="F342" t="inlineStr"/>
@@ -23395,7 +23395,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>566</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -23415,7 +23415,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>2026-05-12 18:38:29</t>
+          <t>2026-05-12 18:19:14</t>
         </is>
       </c>
       <c r="F343" t="inlineStr"/>
@@ -23424,17 +23424,17 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>567</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -23444,7 +23444,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>2026-05-12 18:47:34</t>
+          <t>2026-05-12 18:26:39</t>
         </is>
       </c>
       <c r="F344" t="inlineStr"/>
@@ -23453,17 +23453,17 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>568</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -23473,7 +23473,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-05-12 18:54:06</t>
+          <t>2026-05-12 18:29:28</t>
         </is>
       </c>
       <c r="F345" t="inlineStr"/>
@@ -23482,17 +23482,17 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>569</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -23502,7 +23502,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-05-12 19:03:54</t>
+          <t>2026-05-12 18:38:29</t>
         </is>
       </c>
       <c r="F346" t="inlineStr"/>
@@ -23511,17 +23511,17 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>570</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -23531,7 +23531,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-05-12 19:41:52</t>
+          <t>2026-05-12 18:47:34</t>
         </is>
       </c>
       <c r="F347" t="inlineStr"/>
@@ -23540,17 +23540,17 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>571</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -23560,7 +23560,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-05-13 12:09:27</t>
+          <t>2026-05-12 18:54:06</t>
         </is>
       </c>
       <c r="F348" t="inlineStr"/>
@@ -23569,17 +23569,17 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>572</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-05-13 12:18:32</t>
+          <t>2026-05-12 19:03:54</t>
         </is>
       </c>
       <c r="F349" t="inlineStr"/>
@@ -23598,7 +23598,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>573</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -23618,7 +23618,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-05-13 12:23:52</t>
+          <t>2026-05-12 19:41:52</t>
         </is>
       </c>
       <c r="F350" t="inlineStr"/>
@@ -23627,17 +23627,17 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>574</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -23647,7 +23647,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-05-13 12:25:37</t>
+          <t>2026-05-13 12:09:27</t>
         </is>
       </c>
       <c r="F351" t="inlineStr"/>
@@ -23656,17 +23656,17 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>575</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -23676,7 +23676,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-05-13 12:28:23</t>
+          <t>2026-05-13 12:18:32</t>
         </is>
       </c>
       <c r="F352" t="inlineStr"/>
@@ -23685,7 +23685,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>576</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -23705,7 +23705,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-05-13 12:32:52</t>
+          <t>2026-05-13 12:23:52</t>
         </is>
       </c>
       <c r="F353" t="inlineStr"/>
@@ -23714,17 +23714,17 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>577</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -23734,7 +23734,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-05-13 12:40:54</t>
+          <t>2026-05-13 12:25:37</t>
         </is>
       </c>
       <c r="F354" t="inlineStr"/>
@@ -23743,7 +23743,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>580</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -23763,7 +23763,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-05-13 12:43:27</t>
+          <t>2026-05-13 12:28:23</t>
         </is>
       </c>
       <c r="F355" t="inlineStr"/>
@@ -23772,17 +23772,17 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>582</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Busy</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -23792,7 +23792,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>2026-05-13 12:45:51</t>
+          <t>2026-05-13 12:32:52</t>
         </is>
       </c>
       <c r="F356" t="inlineStr"/>
@@ -23801,17 +23801,17 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>583</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>2026-05-14 12:29:10</t>
+          <t>2026-05-13 12:40:54</t>
         </is>
       </c>
       <c r="F357" t="inlineStr"/>
@@ -23830,17 +23830,17 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>584</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -23850,7 +23850,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>2026-05-14 12:31:42</t>
+          <t>2026-05-13 12:43:27</t>
         </is>
       </c>
       <c r="F358" t="inlineStr"/>
@@ -23859,17 +23859,17 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>585</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Busy</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -23879,7 +23879,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>2026-05-14 12:34:26</t>
+          <t>2026-05-13 12:45:51</t>
         </is>
       </c>
       <c r="F359" t="inlineStr"/>
@@ -23888,17 +23888,17 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>586</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -23908,7 +23908,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>2026-05-14 12:39:18</t>
+          <t>2026-05-14 12:29:10</t>
         </is>
       </c>
       <c r="F360" t="inlineStr"/>
@@ -23917,17 +23917,17 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>587</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Busy</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -23937,7 +23937,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>2026-05-14 12:53:07</t>
+          <t>2026-05-14 12:31:42</t>
         </is>
       </c>
       <c r="F361" t="inlineStr"/>
@@ -23946,17 +23946,17 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>588</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -23966,7 +23966,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>2026-05-14 12:57:05</t>
+          <t>2026-05-14 12:34:26</t>
         </is>
       </c>
       <c r="F362" t="inlineStr"/>
@@ -23975,17 +23975,17 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>589</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -23995,7 +23995,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>2026-05-14 13:04:59</t>
+          <t>2026-05-14 12:39:18</t>
         </is>
       </c>
       <c r="F363" t="inlineStr"/>
@@ -24004,17 +24004,17 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>590</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Busy</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>2026-05-14 17:58:21</t>
+          <t>2026-05-14 12:53:07</t>
         </is>
       </c>
       <c r="F364" t="inlineStr"/>
@@ -24033,7 +24033,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>591</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -24053,7 +24053,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>2026-05-14 18:00:32</t>
+          <t>2026-05-14 12:57:05</t>
         </is>
       </c>
       <c r="F365" t="inlineStr"/>
@@ -24062,17 +24062,17 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>592</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -24082,7 +24082,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>2026-05-14 18:07:31</t>
+          <t>2026-05-14 13:04:59</t>
         </is>
       </c>
       <c r="F366" t="inlineStr"/>
@@ -24091,7 +24091,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>593</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -24111,7 +24111,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>2026-05-14 18:16:47</t>
+          <t>2026-05-14 17:58:21</t>
         </is>
       </c>
       <c r="F367" t="inlineStr"/>
@@ -24120,7 +24120,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>594</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -24140,7 +24140,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>2026-05-14 18:23:35</t>
+          <t>2026-05-14 18:00:32</t>
         </is>
       </c>
       <c r="F368" t="inlineStr"/>
@@ -24149,12 +24149,12 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>595</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Not Connecting</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -24169,7 +24169,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>2026-05-14 18:29:03</t>
+          <t>2026-05-14 18:07:31</t>
         </is>
       </c>
       <c r="F369" t="inlineStr"/>
@@ -24178,7 +24178,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>596</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -24198,7 +24198,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>2026-05-14 18:35:02</t>
+          <t>2026-05-14 18:16:47</t>
         </is>
       </c>
       <c r="F370" t="inlineStr"/>
@@ -24207,7 +24207,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>597</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -24227,7 +24227,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>2026-05-15 12:51:19</t>
+          <t>2026-05-14 18:23:35</t>
         </is>
       </c>
       <c r="F371" t="inlineStr"/>
@@ -24236,17 +24236,17 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>598</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Not Connecting</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -24256,7 +24256,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>2026-05-15 12:54:10</t>
+          <t>2026-05-14 18:29:03</t>
         </is>
       </c>
       <c r="F372" t="inlineStr"/>
@@ -24265,7 +24265,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>599</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -24285,7 +24285,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>2026-05-15 12:55:59</t>
+          <t>2026-05-14 18:35:02</t>
         </is>
       </c>
       <c r="F373" t="inlineStr"/>
@@ -24294,17 +24294,17 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>600</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -24314,7 +24314,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>2026-05-15 12:58:34</t>
+          <t>2026-05-15 12:51:19</t>
         </is>
       </c>
       <c r="F374" t="inlineStr"/>
@@ -24323,17 +24323,17 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>601</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -24343,7 +24343,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>2026-05-15 13:01:15</t>
+          <t>2026-05-15 12:54:10</t>
         </is>
       </c>
       <c r="F375" t="inlineStr"/>
@@ -24352,17 +24352,17 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>602</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -24372,7 +24372,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>2026-05-15 13:04:37</t>
+          <t>2026-05-15 12:55:59</t>
         </is>
       </c>
       <c r="F376" t="inlineStr"/>
@@ -24381,17 +24381,17 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>603</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Busy</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -24401,7 +24401,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>2026-05-15 13:09:25</t>
+          <t>2026-05-15 12:58:34</t>
         </is>
       </c>
       <c r="F377" t="inlineStr"/>
@@ -24410,17 +24410,17 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>604</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -24430,7 +24430,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>2026-05-18 12:07:32</t>
+          <t>2026-05-15 13:01:15</t>
         </is>
       </c>
       <c r="F378" t="inlineStr"/>
@@ -24439,17 +24439,17 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>605</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -24459,7 +24459,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>2026-05-18 12:10:32</t>
+          <t>2026-05-15 13:04:37</t>
         </is>
       </c>
       <c r="F379" t="inlineStr"/>
@@ -24468,17 +24468,17 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>606</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Busy</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -24488,7 +24488,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>2026-05-18 12:14:14</t>
+          <t>2026-05-15 13:09:25</t>
         </is>
       </c>
       <c r="F380" t="inlineStr"/>
@@ -24497,17 +24497,17 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>607</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>NO ANSWER</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>no_answer</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>2026-05-18 12:22:29</t>
+          <t>2026-05-18 12:07:32</t>
         </is>
       </c>
       <c r="F381" t="inlineStr"/>
@@ -24526,17 +24526,17 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>608</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -24546,7 +24546,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>2026-05-18 15:20:57</t>
+          <t>2026-05-18 12:10:32</t>
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
@@ -24555,17 +24555,17 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>609</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -24575,7 +24575,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>2026-05-18 15:29:00</t>
+          <t>2026-05-18 12:14:14</t>
         </is>
       </c>
       <c r="F383" t="inlineStr"/>
@@ -24584,17 +24584,17 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>610</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>NO ANSWER</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>no_answer</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -24604,7 +24604,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>2026-05-18 15:36:40</t>
+          <t>2026-05-18 12:22:29</t>
         </is>
       </c>
       <c r="F384" t="inlineStr"/>
@@ -24613,17 +24613,17 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>612</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Number busy</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>busy_call_back</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -24633,7 +24633,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>2026-05-18 19:00:07</t>
+          <t>2026-05-18 15:20:57</t>
         </is>
       </c>
       <c r="F385" t="inlineStr"/>
@@ -24642,17 +24642,17 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>613</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -24662,7 +24662,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>2026-05-18 19:05:01</t>
+          <t>2026-05-18 15:29:00</t>
         </is>
       </c>
       <c r="F386" t="inlineStr"/>
@@ -24671,17 +24671,17 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>614</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -24691,7 +24691,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>2026-05-18 19:14:00</t>
+          <t>2026-05-18 15:36:40</t>
         </is>
       </c>
       <c r="F387" t="inlineStr"/>
@@ -24700,17 +24700,17 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>615</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Number busy</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>busy_call_back</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -24720,7 +24720,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>2026-05-18 19:20:23</t>
+          <t>2026-05-18 19:00:07</t>
         </is>
       </c>
       <c r="F388" t="inlineStr"/>
@@ -24729,7 +24729,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>616</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -24749,7 +24749,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>2026-05-18 19:25:32</t>
+          <t>2026-05-18 19:05:01</t>
         </is>
       </c>
       <c r="F389" t="inlineStr"/>
@@ -24758,17 +24758,17 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>617</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -24778,7 +24778,7 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>2026-05-19 12:18:19</t>
+          <t>2026-05-18 19:14:00</t>
         </is>
       </c>
       <c r="F390" t="inlineStr"/>
@@ -24787,7 +24787,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>618</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -24807,7 +24807,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>2026-05-19 12:20:25</t>
+          <t>2026-05-18 19:20:23</t>
         </is>
       </c>
       <c r="F391" t="inlineStr"/>
@@ -24816,7 +24816,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>619</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -24836,7 +24836,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>2026-05-19 12:29:41</t>
+          <t>2026-05-18 19:25:32</t>
         </is>
       </c>
       <c r="F392" t="inlineStr"/>
@@ -24845,17 +24845,17 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>620</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -24865,7 +24865,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>2026-05-19 12:32:34</t>
+          <t>2026-05-19 12:18:19</t>
         </is>
       </c>
       <c r="F393" t="inlineStr"/>
@@ -24874,17 +24874,17 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>621</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -24894,7 +24894,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>2026-05-19 12:39:56</t>
+          <t>2026-05-19 12:20:25</t>
         </is>
       </c>
       <c r="F394" t="inlineStr"/>
@@ -24903,7 +24903,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>622</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -24923,7 +24923,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>2026-05-19 18:04:37</t>
+          <t>2026-05-19 12:29:41</t>
         </is>
       </c>
       <c r="F395" t="inlineStr"/>
@@ -24932,17 +24932,17 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>623</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -24952,7 +24952,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>2026-05-19 18:09:24</t>
+          <t>2026-05-19 12:32:34</t>
         </is>
       </c>
       <c r="F396" t="inlineStr"/>
@@ -24961,17 +24961,17 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>624</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT AVAILABLE</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -24981,7 +24981,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>2026-05-19 18:13:58</t>
+          <t>2026-05-19 12:39:56</t>
         </is>
       </c>
       <c r="F397" t="inlineStr"/>
@@ -24990,7 +24990,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>625</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -25010,7 +25010,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>2026-05-19 18:18:09</t>
+          <t>2026-05-19 18:04:37</t>
         </is>
       </c>
       <c r="F398" t="inlineStr"/>
@@ -25019,7 +25019,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>626</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -25039,7 +25039,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>2026-05-19 18:22:09</t>
+          <t>2026-05-19 18:09:24</t>
         </is>
       </c>
       <c r="F399" t="inlineStr"/>
@@ -25048,7 +25048,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>627</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -25068,7 +25068,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>2026-05-19 18:28:23</t>
+          <t>2026-05-19 18:13:58</t>
         </is>
       </c>
       <c r="F400" t="inlineStr"/>
@@ -25077,7 +25077,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>628</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -25097,7 +25097,7 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>2026-05-19 18:29:34</t>
+          <t>2026-05-19 18:18:09</t>
         </is>
       </c>
       <c r="F401" t="inlineStr"/>
@@ -25106,7 +25106,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>629</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -25126,7 +25126,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>2026-05-19 19:59:33</t>
+          <t>2026-05-19 18:22:09</t>
         </is>
       </c>
       <c r="F402" t="inlineStr"/>
@@ -25135,17 +25135,17 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>630</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -25155,7 +25155,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>2026-05-19 20:02:58</t>
+          <t>2026-05-19 18:28:23</t>
         </is>
       </c>
       <c r="F403" t="inlineStr"/>
@@ -25164,17 +25164,17 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>631</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -25184,7 +25184,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>2026-05-19 20:10:47</t>
+          <t>2026-05-19 18:29:34</t>
         </is>
       </c>
       <c r="F404" t="inlineStr"/>
@@ -25193,7 +25193,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>632</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -25213,7 +25213,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>2026-05-19 20:15:45</t>
+          <t>2026-05-19 19:59:33</t>
         </is>
       </c>
       <c r="F405" t="inlineStr"/>
@@ -25222,17 +25222,17 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>633</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -25242,11 +25242,330 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>2026-05-19 20:19:00</t>
+          <t>2026-05-19 20:02:58</t>
         </is>
       </c>
       <c r="F406" t="inlineStr"/>
       <c r="G406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>2026-05-19 20:10:47</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr"/>
+      <c r="G407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>2026-05-19 20:15:45</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr"/>
+      <c r="G408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>2026-05-19 20:19:00</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr"/>
+      <c r="G409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:07:44</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr"/>
+      <c r="G410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:12:34</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:16:25</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:22:22</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:28:53</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr"/>
+      <c r="G414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:30:25</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:39:31</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:53:43</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H312"/>
+  <dimension ref="A1:H313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13449,6 +13449,48 @@
       <c r="H312" t="inlineStr">
         <is>
           <t>2026-05-19 20:19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Thomas H. White</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>twhite@rhwhite.com</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(508) 832-3295 </t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Rhwhite</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>2026-05-20 18:14:58</t>
         </is>
       </c>
     </row>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H313"/>
+  <dimension ref="A1:H314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-05-08 15:54:37</t>
+          <t>2026-05-20 18:38:16</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-04-28 19:35:07</t>
+          <t>2026-05-20 18:25:13</t>
         </is>
       </c>
     </row>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-04-28 19:29:59</t>
+          <t>2026-05-20 18:29:05</t>
         </is>
       </c>
     </row>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-04-30 17:07:20</t>
+          <t>2026-05-20 18:48:19</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-04-15 12:38:26</t>
+          <t>2026-05-20 19:05:12</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-04-24 12:17:05</t>
+          <t>2026-05-20 19:12:46</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-04-24 14:36:39</t>
+          <t>2026-05-20 18:54:56</t>
         </is>
       </c>
     </row>
@@ -9401,7 +9401,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-04-24 14:43:03</t>
+          <t>2026-05-20 18:58:05</t>
         </is>
       </c>
     </row>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-05-08 15:59:34</t>
+          <t>2026-05-20 18:59:36</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>2026-04-28 19:46:42</t>
+          <t>2026-05-20 18:33:02</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,49 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>2026-05-20 18:14:58</t>
+          <t>2026-05-20 18:17:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Christopher Noonan</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>cnoonan@jpnoonan.com</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>508-588-8026</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>JP Noonan Transportation</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>2026-05-20 19:09:23</t>
         </is>
       </c>
     </row>
@@ -13505,7 +13547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G417"/>
+  <dimension ref="A1:G429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25608,6 +25650,354 @@
       </c>
       <c r="F417" t="inlineStr"/>
       <c r="G417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>2026-05-20 18:17:46</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>2026-05-20 18:25:13</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>2026-05-20 18:29:05</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>2026-05-20 18:32:40</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>2026-05-20 18:38:16</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr"/>
+      <c r="G422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>2026-05-20 18:48:19</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr"/>
+      <c r="G423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>2026-05-20 18:54:56</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr"/>
+      <c r="G424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>2026-05-20 18:58:05</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr"/>
+      <c r="G425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>2026-05-20 18:59:36</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr"/>
+      <c r="G426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>2026-05-20 19:05:12</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr"/>
+      <c r="G427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>658</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>2026-05-20 19:09:23</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr"/>
+      <c r="G428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>2026-05-20 19:12:46</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr"/>
+      <c r="G429" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H314"/>
+  <dimension ref="A1:H319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-04-30 13:21:26</t>
+          <t>2026-05-21 13:08:11</t>
         </is>
       </c>
     </row>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-04-22 16:47:57</t>
+          <t>2026-05-21 12:42:02</t>
         </is>
       </c>
     </row>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-03-25 16:55:15</t>
+          <t>2026-05-21 12:44:04</t>
         </is>
       </c>
     </row>
@@ -13533,6 +13533,216 @@
       <c r="H314" t="inlineStr">
         <is>
           <t>2026-05-20 19:09:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Wilson Duarte</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>officemanager@unitylandscaping.com</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>(617) 233-0855</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Unitylandscaping</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>2026-05-21 12:47:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>HEDYONH W AGUIAR SR.</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>hedyonh@gmail.com</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>(508) 740-4019</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>OLIMPIA LANDSCAPE CORP</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>2026-05-21 12:57:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>David Pavidis</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>dpavidis@greentreesarborcareinc.com</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>(508) 989-9800</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Greentreesarborcareinc</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>2026-05-21 12:58:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Marcelo Madrona</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>contact@madronabros.com</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>(508) 620-9369</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Madronabros</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>2026-05-21 13:01:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>ROGERIO FERRAZ</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>roger1392@hotmail.com</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>(781) 929-0681</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>rockgardenrogersconstruction</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>2026-05-21 13:03:52</t>
         </is>
       </c>
     </row>
@@ -13547,7 +13757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G429"/>
+  <dimension ref="A1:G437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25998,6 +26208,238 @@
       </c>
       <c r="F429" t="inlineStr"/>
       <c r="G429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>2026-05-21 12:42:02</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr"/>
+      <c r="G430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>2026-05-21 12:44:04</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr"/>
+      <c r="G431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>2026-05-21 12:47:18</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr"/>
+      <c r="G432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>2026-05-21 12:57:41</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr"/>
+      <c r="G433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>2026-05-21 12:58:32</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>2026-05-21 13:01:52</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr"/>
+      <c r="G435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>2026-05-21 13:03:52</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr"/>
+      <c r="G436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>2026-05-21 13:08:11</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr"/>
+      <c r="G437" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -9038,7 +9038,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-04-23 19:33:02</t>
+          <t>2026-05-21 19:17:15</t>
         </is>
       </c>
     </row>
@@ -9332,7 +9332,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-04-27 18:26:29</t>
+          <t>2026-05-21 18:23:57</t>
         </is>
       </c>
     </row>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-04-27 14:10:21</t>
+          <t>2026-05-21 19:20:45</t>
         </is>
       </c>
     </row>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>2026-05-08 16:11:07</t>
+          <t>2026-05-21 19:07:58</t>
         </is>
       </c>
     </row>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>2026-04-27 19:10:15</t>
+          <t>2026-05-21 19:13:53</t>
         </is>
       </c>
     </row>
@@ -11936,7 +11936,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>2026-05-08 16:24:03</t>
+          <t>2026-05-21 19:10:34</t>
         </is>
       </c>
     </row>
@@ -13757,7 +13757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G437"/>
+  <dimension ref="A1:G443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26440,6 +26440,180 @@
       </c>
       <c r="F437" t="inlineStr"/>
       <c r="G437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>2026-05-21 18:23:57</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr"/>
+      <c r="G438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>2026-05-21 19:07:58</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr"/>
+      <c r="G439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>2026-05-21 19:10:34</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr"/>
+      <c r="G440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>HUNG UP</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>hung_up</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>2026-05-21 19:13:54</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>2026-05-21 19:17:15</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr"/>
+      <c r="G442" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>2026-05-21 19:20:45</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr"/>
+      <c r="G443" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H319"/>
+  <dimension ref="A1:H320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>2026-04-28 13:06:06</t>
+          <t>2026-05-22 11:43:15</t>
         </is>
       </c>
     </row>
@@ -10046,7 +10046,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>2026-04-28 13:09:10</t>
+          <t>2026-05-22 11:48:57</t>
         </is>
       </c>
     </row>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>2026-04-29 15:54:41</t>
+          <t>2026-05-22 12:22:50</t>
         </is>
       </c>
     </row>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>2026-04-29 15:56:41</t>
+          <t>2026-05-22 12:25:58</t>
         </is>
       </c>
     </row>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>2026-04-29 16:26:19</t>
+          <t>2026-05-22 11:50:15</t>
         </is>
       </c>
     </row>
@@ -13743,6 +13743,48 @@
       <c r="H319" t="inlineStr">
         <is>
           <t>2026-05-21 13:03:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>DIMITRIY BRUYAKA</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>dmitriy@linicfreight.com</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>(704) 900-2200</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Linic freight</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:55:46</t>
         </is>
       </c>
     </row>
@@ -13757,7 +13799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G443"/>
+  <dimension ref="A1:G449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26614,6 +26656,180 @@
       </c>
       <c r="F443" t="inlineStr"/>
       <c r="G443" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:43:15</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr"/>
+      <c r="G444" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:48:57</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr"/>
+      <c r="G445" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Office closed call back at 8 am</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:50:15</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr"/>
+      <c r="G446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:55:46</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr"/>
+      <c r="G447" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:22:50</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr"/>
+      <c r="G448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:25:58</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr"/>
+      <c r="G449" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -2044,7 +2044,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-05-14 18:23:35</t>
+          <t>2026-05-22 17:39:35</t>
         </is>
       </c>
     </row>
@@ -13799,7 +13799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G449"/>
+  <dimension ref="A1:G450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26830,6 +26830,35 @@
       </c>
       <c r="F449" t="inlineStr"/>
       <c r="G449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:39:35</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr"/>
+      <c r="G450" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H320"/>
+  <dimension ref="A1:H323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-04-07 15:13:40</t>
+          <t>2026-05-22 18:57:22</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-03-31 19:41:40</t>
+          <t>2026-05-22 19:23:08</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-05-07 12:22:45</t>
+          <t>2026-05-22 19:15:58</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-04-20 18:09:10</t>
+          <t>2026-05-22 19:35:47</t>
         </is>
       </c>
     </row>
@@ -13785,6 +13785,132 @@
       <c r="H320" t="inlineStr">
         <is>
           <t>2026-05-22 11:55:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>ROMAN DIORDIASENCO</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>costalunatransportation@gmail.com</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>(774) 476-3897</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>COSTA LUNA LOGISTIC TRANSPORTATION CORP</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:51:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>RAUL TEJADA</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>tejadalogistic@gmail.com</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (978) 880-1353</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Tejada Logistics Llc</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:59:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>JOSEPH NICCOLI</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>info@niccolienergy.com</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>(508) 588-0979</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>Niccoli energy</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:07:44</t>
         </is>
       </c>
     </row>
@@ -13799,7 +13925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G450"/>
+  <dimension ref="A1:G456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26859,6 +26985,180 @@
       </c>
       <c r="F450" t="inlineStr"/>
       <c r="G450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:59:45</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr"/>
+      <c r="G451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>2026-05-22 18:57:22</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr"/>
+      <c r="G452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:07:44</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr"/>
+      <c r="G453" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:15:58</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr"/>
+      <c r="G454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>NO ANSWER</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>no_answer</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:23:08</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr"/>
+      <c r="G455" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>693</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:35:47</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr"/>
+      <c r="G456" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H323"/>
+  <dimension ref="A1:H332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-02-24 19:02:25</t>
+          <t>2026-05-26 12:51:18</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-03-12 14:01:00</t>
+          <t>2026-05-26 12:49:52</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-04-30 12:27:47</t>
+          <t>2026-05-26 11:49:00</t>
         </is>
       </c>
     </row>
@@ -13035,7 +13035,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Harry Leo III</t>
+          <t>Jim</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>2026-05-19 12:18:19</t>
+          <t>2026-05-26 14:59:56</t>
         </is>
       </c>
     </row>
@@ -13112,7 +13112,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>2026-05-19 12:20:25</t>
+          <t>2026-05-26 14:07:21</t>
         </is>
       </c>
     </row>
@@ -13911,6 +13911,384 @@
       <c r="H323" t="inlineStr">
         <is>
           <t>2026-05-22 19:07:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Robert Sappio</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>rsappio@seacubecontainers.com</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 201-391-0800</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>Seacube containers</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>2026-05-26 11:52:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Dale Decker</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>ddecker@deckermail.com</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>515-576-4141</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>DECKER TRUCK LINE INC</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:04:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Rick Roehl</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>rick.roehl@roehl.net</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>(715) 591-7000</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>ROEHL TRANSPORT INC</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:24:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>CHRISTOPHER DAUPHINAIS</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>chris@dauphinaisconcrete.com</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>508-726-4909</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Dauphinais concrete</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:27:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Chris Nichols</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>chris.nichols@homeworksenergy.com</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (774) 365-2446</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>Homeworksenergy</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:04:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Marsha Harris</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>mharris@strategic-es.com</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (508) 757-7782</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Strategic-es</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:13:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Michael J. Robertson</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>mrobertson@nedtinc.com</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (800) 698-1865</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>Nedtinc</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:28:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Marc Pellegrino</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>mpellegrino@pellegrinotrucking.com</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(508) 842-4114 </t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>Pellegrino trucking</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:37:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>ALFRED GERARD</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>alsrubbish@gmail.com</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(508) 865-4193 </t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>ALS RUBBISH &amp; CONTAINER SERVICE INC</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:57:29</t>
         </is>
       </c>
     </row>
@@ -13925,7 +14303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G456"/>
+  <dimension ref="A1:G469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27159,6 +27537,383 @@
       </c>
       <c r="F456" t="inlineStr"/>
       <c r="G456" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>2026-05-26 11:49:00</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr"/>
+      <c r="G457" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>NO ANSWER</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>no_answer</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>2026-05-26 11:52:14</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr"/>
+      <c r="G458" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:04:28</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr"/>
+      <c r="G459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:24:28</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr"/>
+      <c r="G460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>699</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:27:42</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr"/>
+      <c r="G461" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:04:53</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr"/>
+      <c r="G462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:13:29</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr"/>
+      <c r="G463" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:28:37</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr"/>
+      <c r="G464" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:37:09</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr"/>
+      <c r="G465" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:57:29</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr"/>
+      <c r="G466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:03:34</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr"/>
+      <c r="G467" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:07:21</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr"/>
+      <c r="G468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:59:56</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr"/>
+      <c r="G469" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H332"/>
+  <dimension ref="A1:H336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-05-07 18:41:02</t>
+          <t>2026-05-26 19:35:28</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-05-18 19:20:23</t>
+          <t>2026-05-26 19:02:55</t>
         </is>
       </c>
     </row>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-04-07 15:24:02</t>
+          <t>2026-05-26 19:56:53</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-04-07 15:27:39</t>
+          <t>2026-05-26 19:58:59</t>
         </is>
       </c>
     </row>
@@ -11852,7 +11852,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>2026-05-08 13:09:59</t>
+          <t>2026-05-26 19:45:00</t>
         </is>
       </c>
     </row>
@@ -14289,6 +14289,174 @@
       <c r="H332" t="inlineStr">
         <is>
           <t>2026-05-26 13:57:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>ROBERT CHEETHAM</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>bob@mandrtransportation.com</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>(413) 561-7450</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>M and r transportation</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>2026-05-26 18:33:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>MICHAEL FOLEY</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>foleytrans@aol.com</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>(413) 787-1155</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>FOLEY TRANSPORT INC</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>2026-05-26 18:36:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>WILLIAM ARMENT</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>will@armenttrucking.com</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>(413) 246-1175</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>Arment trucking</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>2026-05-26 18:57:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>RALPH NICHOLS</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>bnichols66@aol.com</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>(413) 245-1461</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>charlton oil</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>2026-05-26 19:54:04</t>
         </is>
       </c>
     </row>
@@ -14303,7 +14471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G470"/>
+  <dimension ref="A1:G479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27943,6 +28111,267 @@
       </c>
       <c r="F470" t="inlineStr"/>
       <c r="G470" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>2026-05-26 18:33:25</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr"/>
+      <c r="G471" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>2026-05-26 18:36:20</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr"/>
+      <c r="G472" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>2026-05-26 18:57:03</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr"/>
+      <c r="G473" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>2026-05-26 19:02:55</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr"/>
+      <c r="G474" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>2026-05-26 19:35:28</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr"/>
+      <c r="G475" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>2026-05-26 19:45:00</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr"/>
+      <c r="G476" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>2026-05-26 19:54:04</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr"/>
+      <c r="G477" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>2026-05-26 19:56:54</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr"/>
+      <c r="G478" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>721</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>2026-05-26 19:58:59</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr"/>
+      <c r="G479" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H336"/>
+  <dimension ref="A1:H339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-04-08 19:14:17</t>
+          <t>2026-05-27 11:41:47</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-04-21 14:23:48</t>
+          <t>2026-05-27 12:13:52</t>
         </is>
       </c>
     </row>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-04-21 15:49:29</t>
+          <t>2026-05-27 12:38:50</t>
         </is>
       </c>
     </row>
@@ -8660,7 +8660,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-04-21 15:56:46</t>
+          <t>2026-05-27 12:40:51</t>
         </is>
       </c>
     </row>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-05-06 17:53:50</t>
+          <t>2026-05-27 12:11:34</t>
         </is>
       </c>
     </row>
@@ -10676,7 +10676,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>2026-04-30 14:33:48</t>
+          <t>2026-05-27 12:00:14</t>
         </is>
       </c>
     </row>
@@ -14457,6 +14457,132 @@
       <c r="H336" t="inlineStr">
         <is>
           <t>2026-05-26 19:54:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>alex@egoexpress.net</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>(630)521-3206</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Ego express</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:57:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Jim Demers</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>jdemers@iba-usa.com</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>(508) 865-6911</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>Iba-usa</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>2026-05-27 12:20:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Allen Reed</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>areed@paftrans.com</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(207) 510-6900 </t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>Paftrans</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>2026-05-27 12:47:48</t>
         </is>
       </c>
     </row>
@@ -14471,7 +14597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G479"/>
+  <dimension ref="A1:G488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28372,6 +28498,267 @@
       </c>
       <c r="F479" t="inlineStr"/>
       <c r="G479" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:41:47</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr"/>
+      <c r="G480" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Number Busy</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>busy_call_back</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:57:25</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr"/>
+      <c r="G481" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>2026-05-27 12:00:14</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr"/>
+      <c r="G482" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>2026-05-27 12:11:34</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr"/>
+      <c r="G483" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>728</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>2026-05-27 12:13:52</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr"/>
+      <c r="G484" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>2026-05-27 12:20:05</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr"/>
+      <c r="G485" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>2026-05-27 12:38:50</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr"/>
+      <c r="G486" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>2026-05-27 12:40:51</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr"/>
+      <c r="G487" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>2026-05-27 12:47:48</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr"/>
+      <c r="G488" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H339"/>
+  <dimension ref="A1:H341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-04-27 18:08:12</t>
+          <t>2026-05-27 13:14:51</t>
         </is>
       </c>
     </row>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>2026-05-06 15:28:38</t>
+          <t>2026-05-27 15:34:55</t>
         </is>
       </c>
     </row>
@@ -13322,7 +13322,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>2026-05-19 18:13:58</t>
+          <t>2026-05-27 13:18:09</t>
         </is>
       </c>
     </row>
@@ -14583,6 +14583,90 @@
       <c r="H339" t="inlineStr">
         <is>
           <t>2026-05-27 12:47:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>RANDY SALVADOR</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>litchfields1843@gmail.com</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(781) 600-4712 </t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>LITCHFIELDS EXPRESS INC</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>2026-05-27 13:07:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>HOWARD PETERSON JR</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>hpeterson@petersonoil.com</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>508 294-0357</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Petersonoil</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:19:25</t>
         </is>
       </c>
     </row>
@@ -14597,7 +14681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G488"/>
+  <dimension ref="A1:G493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28759,6 +28843,151 @@
       </c>
       <c r="F488" t="inlineStr"/>
       <c r="G488" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>733</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Number Busy</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>2026-05-27 13:07:26</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr"/>
+      <c r="G489" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Not connecting</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>2026-05-27 13:14:51</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr"/>
+      <c r="G490" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>735</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>2026-05-27 13:18:10</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr"/>
+      <c r="G491" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>736</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>2026-05-27 13:28:46</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr"/>
+      <c r="G492" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:19:25</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr"/>
+      <c r="G493" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H341"/>
+  <dimension ref="A1:H342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-04-07 14:55:18</t>
+          <t>2026-05-27 18:04:06</t>
         </is>
       </c>
     </row>
@@ -13196,7 +13196,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>2026-05-19 12:32:34</t>
+          <t>2026-05-27 19:29:54</t>
         </is>
       </c>
     </row>
@@ -13238,7 +13238,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>2026-05-19 12:39:56</t>
+          <t>2026-05-27 19:34:03</t>
         </is>
       </c>
     </row>
@@ -13280,7 +13280,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>2026-05-19 18:09:24</t>
+          <t>2026-05-27 19:44:14</t>
         </is>
       </c>
     </row>
@@ -13322,7 +13322,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>2026-05-27 13:18:09</t>
+          <t>2026-05-27 19:49:45</t>
         </is>
       </c>
     </row>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>2026-05-19 18:18:09</t>
+          <t>2026-05-27 19:52:11</t>
         </is>
       </c>
     </row>
@@ -14667,6 +14667,48 @@
       <c r="H341" t="inlineStr">
         <is>
           <t>2026-05-27 15:19:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Frank Roberts</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>froberts@robertsnrg.com</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>413-262-9141</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>robertsnrg</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:02:05</t>
         </is>
       </c>
     </row>
@@ -14681,7 +14723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G493"/>
+  <dimension ref="A1:G500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28988,6 +29030,209 @@
       </c>
       <c r="F493" t="inlineStr"/>
       <c r="G493" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:02:05</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr"/>
+      <c r="G494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>742</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Number Busy</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>busy_call_back</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:04:06</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr"/>
+      <c r="G495" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>743</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>2026-05-27 19:29:54</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr"/>
+      <c r="G496" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>2026-05-27 19:34:03</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr"/>
+      <c r="G497" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>745</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>2026-05-27 19:44:14</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr"/>
+      <c r="G498" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>2026-05-27 19:49:45</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr"/>
+      <c r="G499" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>2026-05-27 19:52:11</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr"/>
+      <c r="G500" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H342"/>
+  <dimension ref="A1:H349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>2026-05-26 14:07:21</t>
+          <t>2026-06-01 12:06:20</t>
         </is>
       </c>
     </row>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>2026-05-19 12:29:41</t>
+          <t>2026-06-01 12:47:39</t>
         </is>
       </c>
     </row>
@@ -14330,7 +14330,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>2026-05-26 18:33:25</t>
+          <t>2026-06-01 12:52:00</t>
         </is>
       </c>
     </row>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>2026-05-26 18:36:20</t>
+          <t>2026-06-01 12:59:15</t>
         </is>
       </c>
     </row>
@@ -14709,6 +14709,300 @@
       <c r="H342" t="inlineStr">
         <is>
           <t>2026-05-27 18:02:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>TRAVIS J DOYLE</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>jroyle2341@aol.com</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>(774) 242-9227</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>T Doyle Snacks Llc</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:12:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>SHAWN W MANDEL</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>info@pratttrucking.com</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>(508) 987-1187</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>Pratt trucking</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:18:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>ALAN LEE STEARNS JR</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>al.stearns@stearnselectricinc.com</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(774) 696-8217 </t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Not Interested</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>Stearns electric inc</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:25:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>JARRED MAHOTA</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>jmahotaconstruction@gmail.com</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>(774) 272-3164</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Not Interested</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>J Mahota Construction Corp</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:28:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>DAVID DUHAMEL</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>duhamel@ndtransportation.com</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>(401) 762-3337</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>Nd transportation</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:39:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>MARK MAJKUT</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>dispatch@mandgtransportation.com</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(401) 726-4009 </t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Not Interested</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>M &amp; G TRUCKING AND TRANSPORTATION INC</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:47:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>KENNETH RICHARDSON</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>info@deadlineexpress.com</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>(401) 230-6060</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Deadline express</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:54:47</t>
         </is>
       </c>
     </row>
@@ -14723,7 +15017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G500"/>
+  <dimension ref="A1:G511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29233,6 +29527,325 @@
       </c>
       <c r="F500" t="inlineStr"/>
       <c r="G500" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:06:20</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr"/>
+      <c r="G501" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>749</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:47:39</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr"/>
+      <c r="G502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:52:00</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr"/>
+      <c r="G503" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:59:15</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr"/>
+      <c r="G504" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:08:10</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr"/>
+      <c r="G505" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>753</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:18:27</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr"/>
+      <c r="G506" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:25:01</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr"/>
+      <c r="G507" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>755</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:28:19</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr"/>
+      <c r="G508" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:39:30</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr"/>
+      <c r="G509" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>757</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:47:22</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr"/>
+      <c r="G510" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>758</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>2026-06-01 14:54:47</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr"/>
+      <c r="G511" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H349"/>
+  <dimension ref="A1:H350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-05-11 15:02:56</t>
+          <t>2026-06-01 18:22:53</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-05-08 12:43:59</t>
+          <t>2026-06-01 19:01:32</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-05-19 20:15:45</t>
+          <t>2026-06-01 18:33:05</t>
         </is>
       </c>
     </row>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-05-18 19:05:01</t>
+          <t>2026-06-01 18:49:08</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-05-26 19:02:55</t>
+          <t>2026-06-01 18:55:47</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-05-18 19:00:07</t>
+          <t>2026-06-01 18:44:12</t>
         </is>
       </c>
     </row>
@@ -13322,7 +13322,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>2026-05-27 19:49:45</t>
+          <t>2026-06-01 19:08:52</t>
         </is>
       </c>
     </row>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -14372,7 +14372,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>2026-06-01 12:59:15</t>
+          <t>2026-06-01 17:09:35</t>
         </is>
       </c>
     </row>
@@ -15003,6 +15003,48 @@
       <c r="H349" t="inlineStr">
         <is>
           <t>2026-06-01 14:54:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Jim Pyne</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>jpyne@pynesand.com</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>508-234-7967</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Pynesand</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:28:22</t>
         </is>
       </c>
     </row>
@@ -15017,7 +15059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G511"/>
+  <dimension ref="A1:G520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29846,6 +29888,267 @@
       </c>
       <c r="F511" t="inlineStr"/>
       <c r="G511" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>2026-06-01 17:09:29</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr"/>
+      <c r="G512" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:22:53</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr"/>
+      <c r="G513" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>761</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Not connecting</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:28:22</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr"/>
+      <c r="G514" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:33:05</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr"/>
+      <c r="G515" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>763</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Number Busy</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:44:12</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr"/>
+      <c r="G516" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:49:08</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr"/>
+      <c r="G517" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:55:47</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr"/>
+      <c r="G518" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Not connecting</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>2026-06-01 19:01:32</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr"/>
+      <c r="G519" t="inlineStr"/>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>2026-06-01 19:08:52</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr"/>
+      <c r="G520" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H354"/>
+  <dimension ref="A1:H357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15213,6 +15213,132 @@
       <c r="H354" t="inlineStr">
         <is>
           <t>2026-06-02 12:26:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>JEAN HUMPHREY</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>minexpress18@yahoo.com</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>(508) 530-8306</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>MIN EXPRESS INC</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:00:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>FAISAL WAGED</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>alinecorp1@gmail.com</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>(508) 316-3139</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>A LINE CORPORATION</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:04:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>RYAN FISHER</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>ryan@fisherbusinc.com</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (508) 673-0685</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>Fisher bus inc</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:09:19</t>
         </is>
       </c>
     </row>
@@ -15227,7 +15353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G526"/>
+  <dimension ref="A1:G529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30491,6 +30617,93 @@
       </c>
       <c r="F526" t="inlineStr"/>
       <c r="G526" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>774</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>HUNG UP</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>hung_up</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:00:32</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr"/>
+      <c r="G527" t="inlineStr"/>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>775</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:04:12</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr"/>
+      <c r="G528" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>776</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:09:19</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr"/>
+      <c r="G529" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H357"/>
+  <dimension ref="A1:H362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15339,6 +15339,216 @@
       <c r="H357" t="inlineStr">
         <is>
           <t>2026-06-02 18:09:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>TODD DOUVILLE</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>tdouville@sulco.com</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>(413) 579-5035</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Sulco-lancer</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:14:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>JEFF JIN</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>jeff@foodlandllc.com</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(857) 294-2806 </t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>FOODLAND DISTRIBUTION LLC</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:21:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>LAURENCE O'TOOLE</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>lotoole@gentlegiant.com</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(617) 661-3333 </t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>Gentlegiant</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:27:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>JASON LANDEEN</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>jlandeen@landeentransport.com</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(203) 879-1801 </t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Landeentransport</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:34:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>WILLIAM T. PACELLI</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>wpacelli@pacemotor.com</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (203) 814-3201</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Pacemotor</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:38:35</t>
         </is>
       </c>
     </row>
@@ -15353,7 +15563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G529"/>
+  <dimension ref="A1:G534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30704,6 +30914,151 @@
       </c>
       <c r="F529" t="inlineStr"/>
       <c r="G529" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:14:21</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr"/>
+      <c r="G530" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:21:33</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr"/>
+      <c r="G531" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>779</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:27:33</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr"/>
+      <c r="G532" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>780</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:34:29</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr"/>
+      <c r="G533" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>2026-06-02 18:38:35</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr"/>
+      <c r="G534" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -3746,7 +3746,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-05-08 12:36:57</t>
+          <t>2026-06-03 11:45:22</t>
         </is>
       </c>
     </row>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-05-07 18:31:47</t>
+          <t>2026-06-03 11:58:46</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-05-26 19:35:28</t>
+          <t>2026-06-03 12:05:22</t>
         </is>
       </c>
     </row>
@@ -13448,7 +13448,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>2026-05-19 20:19:00</t>
+          <t>2026-06-03 12:10:22</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G534"/>
+  <dimension ref="A1:G538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31059,6 +31059,122 @@
       </c>
       <c r="F534" t="inlineStr"/>
       <c r="G534" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>782</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:45:22</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr"/>
+      <c r="G535" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>783</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:58:46</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr"/>
+      <c r="G536" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>BUSY-CALL BACK</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>busy_call_back</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:05:22</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr"/>
+      <c r="G537" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>785</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:10:22</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr"/>
+      <c r="G538" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -13322,7 +13322,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>2026-06-01 19:08:52</t>
+          <t>2026-06-05 19:14:30</t>
         </is>
       </c>
     </row>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -7358,7 +7358,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-04-08 18:03:51</t>
+          <t>2026-06-08 17:54:21</t>
         </is>
       </c>
     </row>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H362"/>
+  <dimension ref="A1:H371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>2026-05-12 12:37:48</t>
+          <t>2026-06-09 13:30:44</t>
         </is>
       </c>
     </row>
@@ -14666,7 +14666,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>2026-05-27 15:19:25</t>
+          <t>2026-06-09 14:07:37</t>
         </is>
       </c>
     </row>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>2026-05-27 18:02:05</t>
+          <t>2026-06-09 13:58:05</t>
         </is>
       </c>
     </row>
@@ -15549,6 +15549,384 @@
       <c r="H362" t="inlineStr">
         <is>
           <t>2026-06-02 18:38:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Michael Hogan</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>mhogan@knightslimo.com</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>(508) 294-0034</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Not Interested</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>Knightslimo</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:44:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Matthew D'Auria</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>logistics@agpgas.com</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>(603) 321-8587</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>AMERICAN GAS PRODUCTS INC</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>2026-06-09 12:18:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>BOB HIGGINS</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>bobhiggins@parksite.com</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>(508) 380-2205</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>Parksite</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:54:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>JOHN CHENDO</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>jchendo@accesscorp.com</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>(216) 234-6255 (6)</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>ACCESS CIG LLC</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:58:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>CHRISTOPHER G MILTON</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>chris_milton@miltoncat.com</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>(508) 634-3400</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>Miltoncat</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>2026-06-09 12:06:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>DON BISHOP</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>bishopd@admiralmetals.com</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>(781) 937-4438</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>ADMIRAL METALS SERVICE CENTER CO INC</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>2026-06-09 12:08:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>DAVID MCLAUGHLIN</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>dmoat@roadone.com</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>(781) 961-8200</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>Roadone</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>2026-06-09 12:13:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>JAMEY LAGOR</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>jlagor@neicc.com</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>(774) 961-2000</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>NEW ENGLAND ICE CREAM</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>2026-06-09 12:22:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>MANUEL R COSTA</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>mrcosta@freshideas.com</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>(617) 912-8000</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>COSTA FRUIT&amp;PRODUCE CO</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>2026-06-09 12:30:23</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G538"/>
+  <dimension ref="A1:G550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31175,6 +31553,354 @@
       </c>
       <c r="F538" t="inlineStr"/>
       <c r="G538" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>786</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:44:46</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr"/>
+      <c r="G539" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:49:32</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr"/>
+      <c r="G540" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>788</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:54:53</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr"/>
+      <c r="G541" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>789</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Number Busy</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:58:07</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr"/>
+      <c r="G542" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>2026-06-09 12:06:20</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr"/>
+      <c r="G543" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>791</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Number Busy</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>2026-06-09 12:08:48</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr"/>
+      <c r="G544" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Wrong Number</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>wrong_number__dnc</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>2026-06-09 12:13:06</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr"/>
+      <c r="G545" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>2026-06-09 12:18:02</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr"/>
+      <c r="G546" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>794</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>2026-06-09 12:22:39</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr"/>
+      <c r="G547" t="inlineStr"/>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>795</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>2026-06-09 12:30:23</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr"/>
+      <c r="G548" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>796</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>2026-06-09 13:30:44</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr"/>
+      <c r="G549" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>797</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>2026-06-09 13:58:05</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr"/>
+      <c r="G550" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H371"/>
+  <dimension ref="A1:H377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15927,6 +15927,258 @@
       <c r="H371" t="inlineStr">
         <is>
           <t>2026-06-09 12:30:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>THOMAS ARRIGHI</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>tarrighi@aametro.com</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>(508) 697-0017</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>BILL'S TAXI SERVICE INC</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:04:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Anthony Francis DiFraia</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>tdifraia@homans.com</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>(978) 253-4660</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>HOMANS ASSOCIATES II LLC</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:30:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Frank Marandino</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>fmarandino@needco.com</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>(781) 401-8500</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>SONEPAR DISTRIBUTION NEW ENGLAND INC</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>2026-06-09 17:46:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Lisa Cinella</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>lcinella@tcshuttles.com</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>(351) 322-8400</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>TRANSACTION CORPORATE SHUTTLES INC</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>2026-06-09 17:49:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Cindy Brown</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>info@bostonducktours.com</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>(617) 267-3825</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Not Interested</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>BOSTON DUCK TOURS LP</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>2026-06-09 17:57:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Marcus Newman</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>marcus.newman@wearesouthwind.com</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>(913) 820-7472</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>BAY STATE WORKGROUP LLC</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>2026-06-09 18:01:44</t>
         </is>
       </c>
     </row>
@@ -15941,7 +16193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G550"/>
+  <dimension ref="A1:G556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31901,6 +32153,180 @@
       </c>
       <c r="F550" t="inlineStr"/>
       <c r="G550" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:04:19</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr"/>
+      <c r="G551" t="inlineStr"/>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:30:46</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr"/>
+      <c r="G552" t="inlineStr"/>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Call dropped</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>2026-06-09 17:46:48</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr"/>
+      <c r="G553" t="inlineStr"/>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>801</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>2026-06-09 17:49:51</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr"/>
+      <c r="G554" t="inlineStr"/>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>2026-06-09 17:57:26</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr"/>
+      <c r="G555" t="inlineStr"/>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>803</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>2026-06-09 18:01:44</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr"/>
+      <c r="G556" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H377"/>
+  <dimension ref="A1:H386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16179,6 +16179,384 @@
       <c r="H377" t="inlineStr">
         <is>
           <t>2026-06-09 18:01:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>DAN BUONAGURIO</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>daniel@recycleworksinc.com</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>(781) 844-6721</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>RECYCLEWORKS INC</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>2026-06-09 18:11:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>THOMAS GEDAMINSKY</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>tgedaminsky@prtbus.com</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>(617) 889-5899</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>PAUL REVERE TRANSPORTATION LLC</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>2026-06-09 18:16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>MARTIN MUIRURI</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>bwtransport1@gmail.com</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>(617) 314-9698</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>BWT LLC</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>2026-06-09 18:22:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Lisa Palmer</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>lpalmer@piercealuminum.com</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>(508) 541-7007</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>PIERCE ALUMINUM COMPANY INC</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>2026-06-09 18:25:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>DAVID WINITZER</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>dwinitzer@easternbusco.com</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>(617) 201-0783</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>EASTERN BUS COMPANY INC</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>2026-06-09 18:34:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>cjptrans@gmail.com</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>(646) 344-0271</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>CJP TRANS LLC</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>2026-06-09 18:59:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>LARS A NIIT</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>lauram@doorsys.com</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>(508) 875-3508</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>DOOR SYSTEMS INC</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>2026-06-09 19:06:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Erick Vanwagenen</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>erick.vanwagenen@wedriveu.com</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>(650) 332-4085</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>FOX BUS LINES INC</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>2026-06-09 19:36:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>PATRICK ASSAD</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>boulevardgarage1@verizon.net</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>(508) 755-2632</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>BOULEVARD GARAGE INC</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>2026-06-09 19:39:44</t>
         </is>
       </c>
     </row>
@@ -16193,7 +16571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G556"/>
+  <dimension ref="A1:G565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32327,6 +32705,267 @@
       </c>
       <c r="F556" t="inlineStr"/>
       <c r="G556" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>804</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Interested</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>interested</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>2026-06-09 18:09:26</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr"/>
+      <c r="G557" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>805</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>2026-06-09 18:16:44</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr"/>
+      <c r="G558" t="inlineStr"/>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>806</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>2026-06-09 18:22:30</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr"/>
+      <c r="G559" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>2026-06-09 18:25:34</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr"/>
+      <c r="G560" t="inlineStr"/>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>2026-06-09 18:34:42</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr"/>
+      <c r="G561" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>809</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>2026-06-09 18:59:41</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr"/>
+      <c r="G562" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>2026-06-09 19:06:10</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr"/>
+      <c r="G563" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>811</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>2026-06-09 19:36:45</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr"/>
+      <c r="G564" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>812</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>2026-06-09 19:39:44</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr"/>
+      <c r="G565" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H386"/>
+  <dimension ref="A1:H387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16557,6 +16557,48 @@
       <c r="H386" t="inlineStr">
         <is>
           <t>2026-06-09 19:39:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>JOHN PICKING</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>jpicking@ballardmack.com</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>(508) 753-1403</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>BALMACK LEASING CORP</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>2026-06-10 12:02:31</t>
         </is>
       </c>
     </row>
@@ -16571,7 +16613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G565"/>
+  <dimension ref="A1:G566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32966,6 +33008,35 @@
       </c>
       <c r="F565" t="inlineStr"/>
       <c r="G565" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>2026-06-10 12:02:31</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr"/>
+      <c r="G566" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H387"/>
+  <dimension ref="A1:H391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16599,6 +16599,174 @@
       <c r="H387" t="inlineStr">
         <is>
           <t>2026-06-10 12:02:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>DARIO D SABATINI SR.</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>dario@dariodiesel.com</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>(508) 753-8177</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>DARIO DIESEL SERVICE INC</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>2026-06-10 13:07:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>ERIC LEBOEUF</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>leboeufrubbish@gmail.com</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>(508) 764-6677</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>LEBOEUF RUBBISH REMOVAL INC</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>2026-06-10 13:18:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Jim Lundrigan</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>jlundrigan@eecnet.com</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>(508) 229-1460</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>ELECTRONIC ENVIRONMENTS CO LLC</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>2026-06-10 13:22:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>JENNIFER LANGTON</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>jennifer@einsteinsinc.com</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>(978) 257-6283</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>EINSTEINS SOLUTIONS INC</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>2026-06-10 13:39:32</t>
         </is>
       </c>
     </row>
@@ -16613,7 +16781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G566"/>
+  <dimension ref="A1:G570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33037,6 +33205,122 @@
       </c>
       <c r="F566" t="inlineStr"/>
       <c r="G566" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>814</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>2026-06-10 13:07:47</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr"/>
+      <c r="G567" t="inlineStr"/>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>2026-06-10 13:18:58</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr"/>
+      <c r="G568" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>816</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Wrong Number</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>wrong_number__dnc</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>2026-06-10 13:22:07</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr"/>
+      <c r="G569" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>2026-06-10 13:39:32</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr"/>
+      <c r="G570" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H391"/>
+  <dimension ref="A1:H403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-05-07 19:35:25</t>
+          <t>2026-06-10 17:05:06</t>
         </is>
       </c>
     </row>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>2026-06-10 13:18:58</t>
+          <t>2026-06-10 19:13:52</t>
         </is>
       </c>
     </row>
@@ -16767,6 +16767,510 @@
       <c r="H391" t="inlineStr">
         <is>
           <t>2026-06-10 13:39:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Roger Wheeler</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>roger.wheeler@stopandshop.com</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>(508) 977-5269</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>Stopandshop</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:05:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Jim Demers</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>bbelsito@iba-usa.com</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>(508) 865-6911</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>Iba-usa</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:10:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>WILLIAM MORGAN</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>bmorgan@baystateflowers.com</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>(978) 658-2400</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>AMERICAN FLORIST SUPPLY INC</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:14:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Jim GINGRAS</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>jgingras@belknapwhite.com</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>(508) 337-2700</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>THE BELKNAP WHITE GROUP</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:20:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>BRUCE ANDERSON</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>banderson@pacificpkg.com</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>(978) 661-2401</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>PACIFIC PACKAGING PRODUCTS INC</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:23:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>YONG ZHI MEI</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>jbttourma@gmail.com</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>(617) 586-6023</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>JBT TOUR INC</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:27:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>WILLIAM LUCINI</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>willlucini@lucinibus.com</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>(508) 272-4617</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>LUCINI BUS LINES INC</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:33:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Kristy Lindell</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>klindell@nrtbus.com</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>(413) 863-2595</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>F M KUZMESKUS INC</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:45:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>PETER HUMPHREY</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>phumphrey@northatlanticcorp.com</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>(800) 543-5403</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>NORTH ATLANTIC CORP</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:51:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>HENRY J LAMOUNTAIN JR</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>hank@lamountainbros.com</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>(508) 987-5322</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>Lamountainbros</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:56:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>GRECCO ALONSO</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>grecco@tangoconst.com</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>(978) 345-2510</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>TANGO CONSTRUCTION INC</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>2026-06-10 19:01:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Karen Olsen</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>kolson@sterlingconcrete.net</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>(978) 422-8282</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>STERLING CONCRETE CORP</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>2026-06-10 19:08:36</t>
         </is>
       </c>
     </row>
@@ -16781,7 +17285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G570"/>
+  <dimension ref="A1:G586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33321,6 +33825,470 @@
       </c>
       <c r="F570" t="inlineStr"/>
       <c r="G570" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:05:04</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr"/>
+      <c r="G571" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:10:06</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr"/>
+      <c r="G572" t="inlineStr"/>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:14:20</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr"/>
+      <c r="G573" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>821</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:14:32</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr"/>
+      <c r="G574" t="inlineStr"/>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:20:50</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr"/>
+      <c r="G575" t="inlineStr"/>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:23:00</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr"/>
+      <c r="G576" t="inlineStr"/>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:27:52</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr"/>
+      <c r="G577" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:33:17</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr"/>
+      <c r="G578" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:33:41</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr"/>
+      <c r="G579" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:44:45</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr"/>
+      <c r="G580" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>828</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:45:02</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr"/>
+      <c r="G581" t="inlineStr"/>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:51:02</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr"/>
+      <c r="G582" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:56:38</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr"/>
+      <c r="G583" t="inlineStr"/>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>2026-06-10 19:01:17</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr"/>
+      <c r="G584" t="inlineStr"/>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>2026-06-10 19:08:36</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr"/>
+      <c r="G585" t="inlineStr"/>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>2026-06-10 19:13:52</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr"/>
+      <c r="G586" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H403"/>
+  <dimension ref="A1:H405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17271,6 +17271,90 @@
       <c r="H403" t="inlineStr">
         <is>
           <t>2026-06-10 19:08:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Jacqueline M. Albert</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>jacqui@pjalbert.com</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>(978) 345-7828</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>P J ALBERT INC</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>2026-06-10 20:40:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>MARK TORRISI</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>mtorrisi@jacksonlumber.com</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>(603) 502-7621</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>JACKSON LUMBER &amp; MILLWORK INC</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>2026-06-10 20:43:21</t>
         </is>
       </c>
     </row>
@@ -17285,7 +17369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G586"/>
+  <dimension ref="A1:G589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34032,17 +34116,17 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>834</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
@@ -34052,7 +34136,7 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>2026-06-10 18:33:17</t>
+          <t>2026-06-10 20:40:05</t>
         </is>
       </c>
       <c r="F578" t="inlineStr"/>
@@ -34061,17 +34145,17 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>835</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
@@ -34081,7 +34165,7 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>2026-06-10 18:33:41</t>
+          <t>2026-06-10 20:42:47</t>
         </is>
       </c>
       <c r="F579" t="inlineStr"/>
@@ -34090,17 +34174,17 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>836</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
@@ -34110,7 +34194,7 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>2026-06-10 18:44:45</t>
+          <t>2026-06-10 20:43:07</t>
         </is>
       </c>
       <c r="F580" t="inlineStr"/>
@@ -34119,17 +34203,17 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>825</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
@@ -34139,7 +34223,7 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>2026-06-10 18:45:02</t>
+          <t>2026-06-10 18:33:17</t>
         </is>
       </c>
       <c r="F581" t="inlineStr"/>
@@ -34148,17 +34232,17 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>826</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>NOT INTRESTED</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>not_intrested</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
@@ -34168,7 +34252,7 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>2026-06-10 18:51:02</t>
+          <t>2026-06-10 18:33:41</t>
         </is>
       </c>
       <c r="F582" t="inlineStr"/>
@@ -34177,17 +34261,17 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>827</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Voicemail</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>voicemail</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
@@ -34197,7 +34281,7 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>2026-06-10 18:56:38</t>
+          <t>2026-06-10 18:44:45</t>
         </is>
       </c>
       <c r="F583" t="inlineStr"/>
@@ -34206,17 +34290,17 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>828</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
@@ -34226,7 +34310,7 @@
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>2026-06-10 19:01:17</t>
+          <t>2026-06-10 18:45:02</t>
         </is>
       </c>
       <c r="F584" t="inlineStr"/>
@@ -34235,17 +34319,17 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>829</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
@@ -34255,7 +34339,7 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>2026-06-10 19:08:36</t>
+          <t>2026-06-10 18:51:02</t>
         </is>
       </c>
       <c r="F585" t="inlineStr"/>
@@ -34264,17 +34348,17 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>830</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>NOT INTRESTED</t>
+          <t>Voicemail</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>not_intrested</t>
+          <t>voicemail</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
@@ -34284,11 +34368,98 @@
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>2026-06-10 19:13:52</t>
+          <t>2026-06-10 18:56:38</t>
         </is>
       </c>
       <c r="F586" t="inlineStr"/>
       <c r="G586" t="inlineStr"/>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>2026-06-10 19:01:17</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr"/>
+      <c r="G587" t="inlineStr"/>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>2026-06-10 19:08:36</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr"/>
+      <c r="G588" t="inlineStr"/>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>2026-06-10 19:13:52</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr"/>
+      <c r="G589" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H405"/>
+  <dimension ref="A1:H413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17355,6 +17355,342 @@
       <c r="H405" t="inlineStr">
         <is>
           <t>2026-06-10 20:43:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>WEI QUAN CHEN</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>victor.gogoustour@gmail.com</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>(617) 293-0232</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>GO GO SUN TOUR INC</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>2026-06-11 12:02:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>FADI BOUCHROUCHE</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>fabouche@yahoo.com</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>(978) 688-4001</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>F &amp; B DISTRIBUTORS INC</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>2026-06-11 12:04:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>ANTHONY FRANKS</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>tfranks@rentex.com</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>(800) 545-2313</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>RENTEX INCORPORATED</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>2026-06-11 12:10:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>VINCENT CAMPO</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>vcampo@ssgpools.com</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>(800) 649-8080</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>GUARINO'S SWIMMING POOL SERVICE INC</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>2026-06-11 12:13:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Adam Glenn</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>fleet@homeworksenergy.com</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>(774) 365-2446</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Homeworksenergy</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>2026-06-11 12:18:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>PAUL MARTINS</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>paul@michaels-limo.com</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>(413) 583-6392</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>Michaels-limo</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>2026-06-11 12:21:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>GEORGE J. MARKOS</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>gjmarkos@yelloglow.com</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>(617) 394-0300</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>YELL-O-GLOW CORPORATION</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>2026-06-11 12:24:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>HUIJUN ZHAO YAN</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>yanslinks@hotmail.com</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>(484) 401-2914</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>KING TRAVEL INC</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>2026-06-11 12:29:41</t>
         </is>
       </c>
     </row>
@@ -17369,7 +17705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G589"/>
+  <dimension ref="A1:G598"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34460,6 +34796,267 @@
       </c>
       <c r="F589" t="inlineStr"/>
       <c r="G589" t="inlineStr"/>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>837</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>2026-06-11 12:02:41</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr"/>
+      <c r="G590" t="inlineStr"/>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>838</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>2026-06-11 12:04:37</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr"/>
+      <c r="G591" t="inlineStr"/>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>2026-06-11 12:09:05</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr"/>
+      <c r="G592" t="inlineStr"/>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>2026-06-11 12:09:34</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr"/>
+      <c r="G593" t="inlineStr"/>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>2026-06-11 12:10:06</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr"/>
+      <c r="G594" t="inlineStr"/>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Call dropped</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>2026-06-11 12:13:22</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr"/>
+      <c r="G595" t="inlineStr"/>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>843</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>2026-06-11 12:18:06</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr"/>
+      <c r="G596" t="inlineStr"/>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>2026-06-11 12:21:27</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr"/>
+      <c r="G597" t="inlineStr"/>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>2026-06-11 12:24:29</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr"/>
+      <c r="G598" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H413"/>
+  <dimension ref="A1:H420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17691,6 +17691,296 @@
       <c r="H413" t="inlineStr">
         <is>
           <t>2026-06-11 12:29:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Gregg Laber</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>gregg@gmes.com</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>(802) 334-7963</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>GREEN MOUNTAIN ELECTRIC SUPPLY INC</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>2026-06-11 19:16:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>SERGIU TOMA</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>windstransportation@gmail.com</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>(802) 373-1156</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>WINDS TRANSPORTATION INC</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>2026-06-11 19:19:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>JEFFREY EGLINTINE</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>safety@gmhtrans.com</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>(802) 460-1300</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Gmhtrans</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>2026-06-11 19:27:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Daniel St. Onge</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>dan@stonges.com</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>(802) 334-3044</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>ST ONGE TRANSPORT INC</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>2026-06-11 19:33:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>JASON HEMENWAY</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>jason@fireballtransport.com</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>(802) 864-0700</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Fireballtransport</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>2026-06-11 19:37:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Dennis Rodenbaugh</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>drodenbaugh@dfamilk.com</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>DFA NORTHEAST LOGISTICS INC</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>2026-06-11 19:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>David Santos</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>dsantos@phoenixfeeds.net</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>(802) 453-6684</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>Phoenixfeeds</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>2026-06-11 19:47:31</t>
         </is>
       </c>
     </row>
@@ -17705,7 +17995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G598"/>
+  <dimension ref="A1:G604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35057,6 +35347,180 @@
       </c>
       <c r="F598" t="inlineStr"/>
       <c r="G598" t="inlineStr"/>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>2026-06-11 19:16:19</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr"/>
+      <c r="G599" t="inlineStr"/>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>847</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>2026-06-11 19:19:15</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr"/>
+      <c r="G600" t="inlineStr"/>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>848</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>2026-06-11 19:27:24</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr"/>
+      <c r="G601" t="inlineStr"/>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>2026-06-11 19:31:36</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr"/>
+      <c r="G602" t="inlineStr"/>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>2026-06-11 19:37:05</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr"/>
+      <c r="G603" t="inlineStr"/>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>2026-06-11 19:47:32</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr"/>
+      <c r="G604" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -15590,7 +15590,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>2026-06-09 11:44:57</t>
+          <t>2026-06-15 19:04:57</t>
         </is>
       </c>
     </row>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -5006,7 +5006,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-05-19 18:29:34</t>
+          <t>2026-06-16 11:36:17</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-01 18:33:05</t>
+          <t>2026-06-16 11:39:30</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-05-06 20:12:28</t>
+          <t>2026-06-16 11:47:20</t>
         </is>
       </c>
     </row>
@@ -5342,7 +5342,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-05-13 12:23:52</t>
+          <t>2026-06-16 11:49:06</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-06-01 18:55:47</t>
+          <t>2026-06-16 11:43:53</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-05-13 12:25:53</t>
+          <t>2026-06-16 11:50:57</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-06-01 18:44:12</t>
+          <t>2026-06-16 11:41:57</t>
         </is>
       </c>
     </row>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>2026-06-01 18:28:22</t>
+          <t>2026-06-16 11:37:27</t>
         </is>
       </c>
     </row>
@@ -17995,7 +17995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G604"/>
+  <dimension ref="A1:G612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35521,6 +35521,238 @@
       </c>
       <c r="F604" t="inlineStr"/>
       <c r="G604" t="inlineStr"/>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:36:17</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr"/>
+      <c r="G605" t="inlineStr"/>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>not connecting</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:37:27</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr"/>
+      <c r="G606" t="inlineStr"/>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>854</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:39:30</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr"/>
+      <c r="G607" t="inlineStr"/>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>855</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Number not connecting</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:41:57</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr"/>
+      <c r="G608" t="inlineStr"/>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>856</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Not accepting calls</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:43:53</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr"/>
+      <c r="G609" t="inlineStr"/>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:47:20</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr"/>
+      <c r="G610" t="inlineStr"/>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>858</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:49:06</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr"/>
+      <c r="G611" t="inlineStr"/>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>859</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>NO ANSWER</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>no_answer</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:50:57</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr"/>
+      <c r="G612" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H420"/>
+  <dimension ref="A1:H425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>2026-06-10 13:07:47</t>
+          <t>2026-06-16 18:03:42</t>
         </is>
       </c>
     </row>
@@ -17981,6 +17981,216 @@
       <c r="H420" t="inlineStr">
         <is>
           <t>2026-06-11 19:47:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>MICHAEL WARREN</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>warren.landscaping@aol.com</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>(508) 320-3799</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>Warren Landscaping Llc</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>2026-06-16 17:46:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>ANGELA OMICIOLI</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>hattrickri1397@gmail.com</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>(203) 909-7502</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>Hat Trick Delivery</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>2026-06-16 17:54:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Frederick Koury</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>dopfing@aol.com</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (508) 864-8550</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>Union Station Farms</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>2026-06-16 17:56:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>JOHN C SANTORO</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>gfantacone@santorooil.com</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (508) 753-1475</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>PETROLEX II</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>2026-06-16 17:59:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>David Klein</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>dklein@greenwood-industries.com</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (774) 248-1068</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>Greenwood-industries</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:11:15</t>
         </is>
       </c>
     </row>
@@ -17995,7 +18205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G612"/>
+  <dimension ref="A1:G619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35753,6 +35963,209 @@
       </c>
       <c r="F612" t="inlineStr"/>
       <c r="G612" t="inlineStr"/>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Cannot leave VM</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>2026-06-16 17:46:10</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr"/>
+      <c r="G613" t="inlineStr"/>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>861</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>2026-06-16 17:50:18</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr"/>
+      <c r="G614" t="inlineStr"/>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>862</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>2026-06-16 17:54:16</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr"/>
+      <c r="G615" t="inlineStr"/>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>2026-06-16 17:56:42</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr"/>
+      <c r="G616" t="inlineStr"/>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Couldnt connect to the operator</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>2026-06-16 17:59:52</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr"/>
+      <c r="G617" t="inlineStr"/>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:03:43</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr"/>
+      <c r="G618" t="inlineStr"/>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>2026-06-16 18:11:15</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr"/>
+      <c r="G619" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H425"/>
+  <dimension ref="A1:H426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18191,6 +18191,48 @@
       <c r="H425" t="inlineStr">
         <is>
           <t>2026-06-16 18:11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>DANIEL TIMOTHY AMORELLO</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>dtamorello@aol.com</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>(508) 798-6717</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>DAN AMORELLO SERVICES INC</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>2026-06-16 19:57:13</t>
         </is>
       </c>
     </row>
@@ -18205,7 +18247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G619"/>
+  <dimension ref="A1:G620"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36166,6 +36208,35 @@
       </c>
       <c r="F619" t="inlineStr"/>
       <c r="G619" t="inlineStr"/>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>867</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>2026-06-16 19:57:13</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr"/>
+      <c r="G620" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H426"/>
+  <dimension ref="A1:H428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16556,7 +16556,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>2026-06-09 19:39:44</t>
+          <t>2026-06-17 11:48:26</t>
         </is>
       </c>
     </row>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>2026-06-10 12:02:31</t>
+          <t>2026-06-17 12:33:56</t>
         </is>
       </c>
     </row>
@@ -17186,7 +17186,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>2026-06-10 18:56:38</t>
+          <t>2026-06-17 11:50:15</t>
         </is>
       </c>
     </row>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>2026-06-10 19:01:17</t>
+          <t>2026-06-17 11:59:35</t>
         </is>
       </c>
     </row>
@@ -18233,6 +18233,90 @@
       <c r="H426" t="inlineStr">
         <is>
           <t>2026-06-16 19:57:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Barner</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>barner@jleeassociates.net</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>(508) 597-1330</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>Jleeassociates</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:07:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>JOHN FIELD</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>john@fieldtreeservice.com</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>(413) 329-6519</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>JOHN W FIELD TREE SERVICE INC</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:29:16</t>
         </is>
       </c>
     </row>
@@ -18247,7 +18331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G620"/>
+  <dimension ref="A1:G630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36237,6 +36321,296 @@
       </c>
       <c r="F620" t="inlineStr"/>
       <c r="G620" t="inlineStr"/>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>868</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>2026-06-17 11:48:09</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr"/>
+      <c r="G621" t="inlineStr"/>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>2026-06-17 11:48:26</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr"/>
+      <c r="G622" t="inlineStr"/>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>870</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>2026-06-17 11:50:15</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr"/>
+      <c r="G623" t="inlineStr"/>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>871</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>2026-06-17 11:53:24</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr"/>
+      <c r="G624" t="inlineStr"/>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>872</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Left Vm on grecco cell number</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>2026-06-17 11:53:49</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr"/>
+      <c r="G625" t="inlineStr"/>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>2026-06-17 11:59:35</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr"/>
+      <c r="G626" t="inlineStr"/>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Call could not get transferred</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:07:05</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr"/>
+      <c r="G627" t="inlineStr"/>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>875</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:29:03</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr"/>
+      <c r="G628" t="inlineStr"/>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:29:16</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr"/>
+      <c r="G629" t="inlineStr"/>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>877</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:33:56</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr"/>
+      <c r="G630" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H428"/>
+  <dimension ref="A1:H429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18317,6 +18317,48 @@
       <c r="H428" t="inlineStr">
         <is>
           <t>2026-06-17 12:29:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>GERSON PEREZ</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>gersondeyna@gmail.com</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>(508) 304-0896</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>G D E TRUCKING LLC</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>2026-06-17 17:52:21</t>
         </is>
       </c>
     </row>
@@ -18331,7 +18373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G630"/>
+  <dimension ref="A1:G631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36611,6 +36653,35 @@
       </c>
       <c r="F630" t="inlineStr"/>
       <c r="G630" t="inlineStr"/>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>878</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>2026-06-17 17:52:21</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr"/>
+      <c r="G631" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H429"/>
+  <dimension ref="A1:H430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-05-20 18:38:16</t>
+          <t>2026-06-18 11:41:47</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4292,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-05-20 12:12:34</t>
+          <t>2026-06-18 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-05-21 12:42:02</t>
+          <t>2026-06-18 11:44:42</t>
         </is>
       </c>
     </row>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-03-30 15:11:28</t>
+          <t>2026-06-18 12:00:37</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-05-20 12:16:25</t>
+          <t>2026-06-18 12:34:03</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-04-27 18:12:49</t>
+          <t>2026-06-18 12:39:26</t>
         </is>
       </c>
     </row>
@@ -10241,7 +10241,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Not Interested</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>2026-04-28 19:38:54</t>
+          <t>2026-06-18 12:26:33</t>
         </is>
       </c>
     </row>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>2026-05-04 14:15:29</t>
+          <t>2026-06-18 12:46:25</t>
         </is>
       </c>
     </row>
@@ -18359,6 +18359,48 @@
       <c r="H429" t="inlineStr">
         <is>
           <t>2026-06-17 17:52:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>DANIEL J SALMON III</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>dj@djsalmon.com</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(508) 278-7206 </t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>Djsalmon</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>2026-06-18 11:53:11</t>
         </is>
       </c>
     </row>
@@ -18373,7 +18415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G631"/>
+  <dimension ref="A1:G642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36682,6 +36724,325 @@
       </c>
       <c r="F631" t="inlineStr"/>
       <c r="G631" t="inlineStr"/>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>879</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>2026-06-18 11:41:39</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr"/>
+      <c r="G632" t="inlineStr"/>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>880</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>2026-06-18 11:41:47</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr"/>
+      <c r="G633" t="inlineStr"/>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>881</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Office closed</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>2026-06-18 11:44:42</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr"/>
+      <c r="G634" t="inlineStr"/>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>882</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>2026-06-18 11:53:12</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr"/>
+      <c r="G635" t="inlineStr"/>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>883</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>2026-06-18 12:00:37</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr"/>
+      <c r="G636" t="inlineStr"/>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>884</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>2026-06-18 12:26:26</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr"/>
+      <c r="G637" t="inlineStr"/>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>885</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>2026-06-18 12:28:34</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr"/>
+      <c r="G638" t="inlineStr"/>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>886</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>2026-06-18 12:30:07</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr"/>
+      <c r="G639" t="inlineStr"/>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>2026-06-18 12:34:03</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr"/>
+      <c r="G640" t="inlineStr"/>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>2026-06-18 12:39:26</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr"/>
+      <c r="G641" t="inlineStr"/>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>889</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>2026-06-18 12:46:25</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr"/>
+      <c r="G642" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H430"/>
+  <dimension ref="A1:H431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12440,7 +12440,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>2026-05-14 12:31:42</t>
+          <t>2026-06-18 16:14:35</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>2026-05-14 12:34:25</t>
+          <t>2026-06-18 16:16:55</t>
         </is>
       </c>
     </row>
@@ -18401,6 +18401,48 @@
       <c r="H430" t="inlineStr">
         <is>
           <t>2026-06-18 11:53:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Timothy LaMotte</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>lamotte@northerntree.com</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>(800) 232-6132</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>Northerntree</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>2026-06-18 12:52:55</t>
         </is>
       </c>
     </row>
@@ -18415,7 +18457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G642"/>
+  <dimension ref="A1:G646"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37043,6 +37085,122 @@
       </c>
       <c r="F642" t="inlineStr"/>
       <c r="G642" t="inlineStr"/>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>2026-06-18 12:52:55</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr"/>
+      <c r="G643" t="inlineStr"/>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>2026-06-18 16:13:29</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr"/>
+      <c r="G644" t="inlineStr"/>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>892</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>2026-06-18 16:14:35</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr"/>
+      <c r="G645" t="inlineStr"/>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>2026-06-18 16:16:55</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr"/>
+      <c r="G646" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H431"/>
+  <dimension ref="A1:H444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18022,7 +18022,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>2026-06-16 17:46:10</t>
+          <t>2026-06-18 18:57:29</t>
         </is>
       </c>
     </row>
@@ -18443,6 +18443,552 @@
       <c r="H431" t="inlineStr">
         <is>
           <t>2026-06-18 12:52:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Julie Creedon</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>julie@creedonandco.com</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>(508) 792-3100</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>Creedon And Co Inc</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>JOSEPH FALCONE</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>office@falconeenterprise.com</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>(508) 791-0000</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>FALCONE ENTERPRISES INC</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:14:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Chris Nana K. Bonsu</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>cbonsu@krisbontruckinginc.com</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (508) 864-8665</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>Krisbontruckinginc</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:24:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>ROBERT J VILLATICO SR.</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>doallpaving@gmail.com</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>(774) 696-1690</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>DO ALL CONSTRUCTION</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:26:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>ANTHONY GLEASON</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>agleason27@gmail.com</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>(508) 414-6912</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>Creative Construction Llc</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:29:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>LAURA MARIE MAREK</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>altitudeindustriescorp@gmail.com</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>(508) 963-7794</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>ALTITUDE INDUSTRIES CORPORATION</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:32:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Kevin Tucker</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>dot@rentokil-terminix.com</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>(844) 230-8929</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>Rentokil-terminix</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:38:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>SEAN FLYNN</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>sflynn@fynnsplaza.com</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>(508) 756-7693</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>FLEET PETROLEUM LLC</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:45:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>MICHAEL L GEORGES</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>michael@shrewsburylumber.com</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>(617) 839-5138</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>Shrewsburylumber</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:50:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Peter Chambers</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>peterwchambers@aol.com</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>(508) 481-5132</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>JCS PRODUCE</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>2026-06-18 19:05:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>David Parry</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>dparry@wrenvironmental.com</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>(978) 875-2325</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>WIND RIVER ENVIRONMENTAL LLC</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>2026-06-18 19:10:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>REGINA GALLO</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>rgallo@bjs.com</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>(443) 245-1028</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>BJ'S LOGISTICS LLC</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>2026-06-18 19:16:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Mike Kingsley</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>mkingsley@energysystems.com</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>(508) 229-1460</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>Energysystems</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>2026-06-18 19:24:55</t>
         </is>
       </c>
     </row>
@@ -18457,7 +19003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G646"/>
+  <dimension ref="A1:G661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37201,6 +37747,441 @@
       </c>
       <c r="F646" t="inlineStr"/>
       <c r="G646" t="inlineStr"/>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:11:00</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr"/>
+      <c r="G647" t="inlineStr"/>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:14:44</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr"/>
+      <c r="G648" t="inlineStr"/>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:23:56</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr"/>
+      <c r="G649" t="inlineStr"/>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:24:10</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr"/>
+      <c r="G650" t="inlineStr"/>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>898</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Number not in service</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>wrong_number__dnc</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:26:11</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr"/>
+      <c r="G651" t="inlineStr"/>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:29:39</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr"/>
+      <c r="G652" t="inlineStr"/>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:32:52</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr"/>
+      <c r="G653" t="inlineStr"/>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:38:31</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr"/>
+      <c r="G654" t="inlineStr"/>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:45:15</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr"/>
+      <c r="G655" t="inlineStr"/>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>BUSY-CALL BACK</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>busy_call_back</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:50:38</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr"/>
+      <c r="G656" t="inlineStr"/>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>904</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Unable to leave VM</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:57:29</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr"/>
+      <c r="G657" t="inlineStr"/>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>905</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>HUNG UP</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>hung_up</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>2026-06-18 19:05:01</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr"/>
+      <c r="G658" t="inlineStr"/>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>2026-06-18 19:10:24</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr"/>
+      <c r="G659" t="inlineStr"/>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>2026-06-18 19:16:30</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr"/>
+      <c r="G660" t="inlineStr"/>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>908</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>2026-06-18 19:24:55</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr"/>
+      <c r="G661" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H444"/>
+  <dimension ref="A1:H454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18989,6 +18989,426 @@
       <c r="H444" t="inlineStr">
         <is>
           <t>2026-06-18 19:24:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>CRISTIANO OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>primaveralandscape@hotmail.com</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>(508) 361-2112</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>Primavera Landscaping &amp; Construction Inc</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>2026-06-22 12:16:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>VINCENT PURPURA JR</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>vin-jr@waysideglass.com</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>(508) 485-3600</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Not Interested</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>Waysideglass</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>2026-06-22 12:25:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>NOLBERTO BATRES</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>nbtruckingma@gmail.com</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>(508) 922-0863</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>N &amp; B TRUCKING INC</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>2026-06-22 12:55:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>MARCONI SANTOS</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>marconi@dacostalandscape.com</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>(508) 509-5060</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>The Dacosta Co Inc</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>2026-06-22 13:00:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>DENNIS BERNARD</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>dennis@giombettielectric.com</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>(508) 481-3299</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>Giombettielectric</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>2026-06-22 13:05:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>ALDRIN ARAUJO</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>renovoland@msn.com</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>(508) 485-8669</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>Renovo's Landscaping Const Inc</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>2026-06-22 13:11:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>IGOR COELHO BATISTA</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>ibptransportation83@gmail.com</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>(508) 904-5858</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>IBP TRANSPORTATION INC</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>2026-06-22 13:16:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>GILBERTO BATRES</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>luisbatres@live.com</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>(774) 285-3166</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>GB TRUCKING INC</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>2026-06-22 13:24:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>PAUL EHRLICH</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>paulalplumbing@aol.com</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (508) 877-8500</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>A &amp; L Plumbing Heating And Cooling Inc</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>2026-06-22 13:30:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>RICHARD MICHAEL SHARON</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>sandgconstruction49@gmail.com</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (508) 485-7188</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>S &amp; G CONSTRUCTION</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>2026-06-22 13:37:46</t>
         </is>
       </c>
     </row>
@@ -19003,7 +19423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G661"/>
+  <dimension ref="A1:G674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38182,6 +38602,383 @@
       </c>
       <c r="F661" t="inlineStr"/>
       <c r="G661" t="inlineStr"/>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>2026-06-22 12:16:52</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr"/>
+      <c r="G662" t="inlineStr"/>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>2026-06-22 12:22:33</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr"/>
+      <c r="G663" t="inlineStr"/>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>2026-06-22 12:25:14</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr"/>
+      <c r="G664" t="inlineStr"/>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>912</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>2026-06-22 12:55:19</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr"/>
+      <c r="G665" t="inlineStr"/>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>913</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>2026-06-22 13:00:51</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr"/>
+      <c r="G666" t="inlineStr"/>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>2026-06-22 13:05:55</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr"/>
+      <c r="G667" t="inlineStr"/>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>915</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>2026-06-22 13:11:07</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr"/>
+      <c r="G668" t="inlineStr"/>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>916</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>2026-06-22 13:11:24</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr"/>
+      <c r="G669" t="inlineStr"/>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>2026-06-22 13:16:27</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr"/>
+      <c r="G670" t="inlineStr"/>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>2026-06-22 13:24:34</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr"/>
+      <c r="G671" t="inlineStr"/>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>919</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Wrong Number</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>wrong_number__dnc</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>2026-06-22 13:30:01</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr"/>
+      <c r="G672" t="inlineStr"/>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>2026-06-22 13:30:29</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr"/>
+      <c r="G673" t="inlineStr"/>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>2026-06-22 13:37:46</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr"/>
+      <c r="G674" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H454"/>
+  <dimension ref="A1:H464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19409,6 +19409,426 @@
       <c r="H454" t="inlineStr">
         <is>
           <t>2026-06-22 13:37:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>JOSEPH THOMAS PAOLINI</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>joep68@live.com</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>(617) 901-0482</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>Pao Corp</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:15:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>DANIEL PELLEGRINO</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>info@jdlandscape.com</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>(617) 244-2620</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>J&amp;d Landscape Contractors Inc</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:19:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>LOURIVAL SANTOS</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>lourivalmasonry@aol.com</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>(508) 982-3842</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>Not Interested</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>Lourival Masonry Co Llc</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:21:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Marcello Mallegni</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>marcello@leamar.com</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (508) 786-1899</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>Leamar</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:26:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>LARYSSA LACERDA GOMES</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>contact@loyaltyhomesolutions.com</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>(508) 733-0837</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>Loyaltyhomesolutions</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:28:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>LINDA FOSSILE</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>lafossile@verizon.net</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>(508) 485-0919</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>Tribune Construction Inc</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:32:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>MIKEIAS QUINTAO</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>mike@mm-carrier.com</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>(508) 215-4241</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>Mm Carrier Inc</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:36:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>DOUGLAS DE SOUSA OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>doliveira301@gmail.com</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>(774) 849-6368</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>Unlimited Tree Care Llc</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:40:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>RON JACQUES</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>arborturf1988@gmail.com</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (508) 460-0000</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>ARBOR-TURF SERVICES INC</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>RICHARD MUNGOVAN</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>mungovantrucking@aol.com</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>(508) 479-8546</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>R Mungovan Trucking Llc</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>2026-06-22 19:02:16</t>
         </is>
       </c>
     </row>
@@ -19423,7 +19843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G674"/>
+  <dimension ref="A1:G685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38979,6 +39399,325 @@
       </c>
       <c r="F674" t="inlineStr"/>
       <c r="G674" t="inlineStr"/>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:15:17</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr"/>
+      <c r="G675" t="inlineStr"/>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:19:07</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr"/>
+      <c r="G676" t="inlineStr"/>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:21:36</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr"/>
+      <c r="G677" t="inlineStr"/>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:26:01</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr"/>
+      <c r="G678" t="inlineStr"/>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Number not in service</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:28:32</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr"/>
+      <c r="G679" t="inlineStr"/>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>927</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:32:34</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr"/>
+      <c r="G680" t="inlineStr"/>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>BUSY-CALL BACK</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>busy_call_back</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:36:48</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr"/>
+      <c r="G681" t="inlineStr"/>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:40:14</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr"/>
+      <c r="G682" t="inlineStr"/>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:44:38</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr"/>
+      <c r="G683" t="inlineStr"/>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:45:00</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr"/>
+      <c r="G684" t="inlineStr"/>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>932</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>2026-06-22 19:02:16</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr"/>
+      <c r="G685" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H464"/>
+  <dimension ref="A1:H466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-18 11:44:42</t>
+          <t>2026-06-23 13:00:09</t>
         </is>
       </c>
     </row>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-05-21 12:44:04</t>
+          <t>2026-06-23 14:33:49</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-16 11:47:20</t>
+          <t>2026-06-23 12:22:26</t>
         </is>
       </c>
     </row>
@@ -5342,7 +5342,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-16 11:49:06</t>
+          <t>2026-06-23 12:23:54</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-06-16 11:50:57</t>
+          <t>2026-06-23 12:31:40</t>
         </is>
       </c>
     </row>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-04-24 11:55:39</t>
+          <t>2026-06-23 12:40:16</t>
         </is>
       </c>
     </row>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>2026-05-21 12:47:18</t>
+          <t>2026-06-23 14:37:18</t>
         </is>
       </c>
     </row>
@@ -19829,6 +19829,90 @@
       <c r="H464" t="inlineStr">
         <is>
           <t>2026-06-22 19:02:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Matt Gorski</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>mgorski@phoenix-fiber.com</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>508.438.0360</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>Phoenix-fiber</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>2026-06-23 12:14:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Jim Winkler</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>jim.winkler@industrialpackaging.com</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>(800) 233-5288</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>Industrialpackaging</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>2026-06-23 12:56:50</t>
         </is>
       </c>
     </row>
@@ -19843,7 +19927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G685"/>
+  <dimension ref="A1:G696"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39718,6 +39802,325 @@
       </c>
       <c r="F685" t="inlineStr"/>
       <c r="G685" t="inlineStr"/>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>933</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>2026-06-23 12:14:10</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr"/>
+      <c r="G686" t="inlineStr"/>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>2026-06-23 12:22:26</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr"/>
+      <c r="G687" t="inlineStr"/>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>2026-06-23 12:23:54</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr"/>
+      <c r="G688" t="inlineStr"/>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>936</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>NO ANSWER</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>no_answer</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>2026-06-23 12:31:27</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr"/>
+      <c r="G689" t="inlineStr"/>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>2026-06-23 12:31:40</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr"/>
+      <c r="G690" t="inlineStr"/>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>2026-06-23 12:40:16</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr"/>
+      <c r="G691" t="inlineStr"/>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Not in service</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>2026-06-23 12:56:14</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr"/>
+      <c r="G692" t="inlineStr"/>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>2026-06-23 12:56:50</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr"/>
+      <c r="G693" t="inlineStr"/>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>2026-06-23 13:00:09</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr"/>
+      <c r="G694" t="inlineStr"/>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>2026-06-23 14:33:49</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr"/>
+      <c r="G695" t="inlineStr"/>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>943</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>2026-06-23 14:37:18</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr"/>
+      <c r="G696" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H466"/>
+  <dimension ref="A1:H472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19913,6 +19913,258 @@
       <c r="H466" t="inlineStr">
         <is>
           <t>2026-06-23 12:56:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>CRISTINA DEOLIVEIRA</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>christy@discovermarble.com</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>(508) 438-6900</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>Discovermarble</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>2026-06-24 12:53:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>EDWARD SANTON III</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>santonph@gmail.com</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>(508) 277-8694</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>Santon Plumbing &amp; Heating</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>2026-06-24 13:05:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>BRIAN KERINS</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>bkerins@primepowerrentals.com</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>(617) 797-8259</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>Primepowerrentals</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>2026-06-24 13:03:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>ELITON FIALHO</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>contact@newamericantree.com</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>(508) 250-2602</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>Newamericantree</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>2026-06-24 13:11:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>TIMOTHY EARNEST</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>tearnest@weldpower.com</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>(508) 832-3550</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>Weldpower</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>2026-06-24 13:15:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>WELLINGTON ALVERNAZ CUSTODIO</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>alvernazconstruction@gmail.com</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>508 598 8811</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>W Alvernaz Construction Inc</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>2026-06-24 13:21:18</t>
         </is>
       </c>
     </row>
@@ -19927,7 +20179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G696"/>
+  <dimension ref="A1:G706"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40121,6 +40373,296 @@
       </c>
       <c r="F696" t="inlineStr"/>
       <c r="G696" t="inlineStr"/>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>2026-06-24 12:50:24</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr"/>
+      <c r="G697" t="inlineStr"/>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>2026-06-24 12:53:40</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr"/>
+      <c r="G698" t="inlineStr"/>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>2026-06-24 12:59:39</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr"/>
+      <c r="G699" t="inlineStr"/>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>2026-06-24 13:03:33</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr"/>
+      <c r="G700" t="inlineStr"/>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>948</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>2026-06-24 13:05:18</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr"/>
+      <c r="G701" t="inlineStr"/>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>2026-06-24 13:11:12</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr"/>
+      <c r="G702" t="inlineStr"/>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>2026-06-24 13:11:25</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr"/>
+      <c r="G703" t="inlineStr"/>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>2026-06-24 13:15:12</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr"/>
+      <c r="G704" t="inlineStr"/>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>952</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>2026-06-24 13:21:05</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr"/>
+      <c r="G705" t="inlineStr"/>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>2026-06-24 13:21:18</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr"/>
+      <c r="G706" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H472"/>
+  <dimension ref="A1:H480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20122,7 +20122,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>2026-06-24 13:15:11</t>
+          <t>2026-06-24 18:57:31</t>
         </is>
       </c>
     </row>
@@ -20165,6 +20165,342 @@
       <c r="H472" t="inlineStr">
         <is>
           <t>2026-06-24 13:21:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>VINI MACHADO</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>mapletreelandscape@hotmail.com</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>(508) 570-1171</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>Maple Tree Landscape Inc</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>2026-06-24 18:39:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>ALVIMAR SILVA</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>smjhardscape@gmail.com</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>(508) 470-6363</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>Smj Hardscape Inc</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>2026-06-24 18:42:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>ISMAYIL ABILOV</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>ismayilabilov7@gmail.com</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>(774) 279-3161</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>ABILOO LLC</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>2026-06-24 18:44:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>TIMOTHY WAEGER</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>gotreeservices@gmail.com</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>(508) 887-2917</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Not Interested</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>Go Tree Services Inc</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>2026-06-24 19:12:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>THOMAS FRONGILLO</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>fdtruck14@verizon.net</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>(508) 754-9572</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>F &amp; D TRUCK CO INC</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>2026-06-24 19:15:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>MIKE ED LYNCH</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>mike@mikelynchenterprises.com</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>(508) 865-8508</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>Mikelynchenterprises</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>2026-06-24 19:18:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>NICK MITCHELL</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>mitchellassociatescorp@gmail.com</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>(508) 400-6906</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>Mitchell Associates Construction Corp</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>2026-06-24 19:22:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>DAN OLIPHANT</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>info@piecebypiecemovers.com</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>(617) 515-9886</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>Piecebypiecemovers</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>2026-06-24 19:26:15</t>
         </is>
       </c>
     </row>
@@ -20179,7 +20515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G706"/>
+  <dimension ref="A1:G716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40663,6 +40999,296 @@
       </c>
       <c r="F706" t="inlineStr"/>
       <c r="G706" t="inlineStr"/>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>954</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>2026-06-24 18:39:40</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr"/>
+      <c r="G707" t="inlineStr"/>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>955</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>2026-06-24 18:42:36</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr"/>
+      <c r="G708" t="inlineStr"/>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>956</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Interested</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>interested</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>2026-06-24 18:57:32</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr"/>
+      <c r="G709" t="inlineStr"/>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>2026-06-24 19:09:13</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr"/>
+      <c r="G710" t="inlineStr"/>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>958</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>2026-06-24 19:09:34</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr"/>
+      <c r="G711" t="inlineStr"/>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>2026-06-24 19:12:24</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr"/>
+      <c r="G712" t="inlineStr"/>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>2026-06-24 19:15:29</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr"/>
+      <c r="G713" t="inlineStr"/>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Number Busy</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>2026-06-24 19:18:10</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr"/>
+      <c r="G714" t="inlineStr"/>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>2026-06-24 19:22:01</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr"/>
+      <c r="G715" t="inlineStr"/>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>963</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>2026-06-24 19:26:15</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr"/>
+      <c r="G716" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -40675,7 +41301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41214,6 +41840,50 @@
       </c>
       <c r="J12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>15054800-6ffe-11f1-bc96-2b62b52c68fd</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Weldpower</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Manually created</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-06-24T18:54:09.024Z</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>TIMOTHY EARNEST</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Weldpower</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H480"/>
+  <dimension ref="A1:H485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20501,6 +20501,216 @@
       <c r="H480" t="inlineStr">
         <is>
           <t>2026-06-24 19:26:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>PATRICK HARRINGTON</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>pat@harringtonoilinc.com</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>(508) 829-0044</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>Harringtonoilinc</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>2026-06-24 20:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>TIMOTHY HATTON</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>info@davestreeandlandscaping.com</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (508) 829-6803</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>Davestreeandlandscaping</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>2026-06-24 20:19:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>ROBERT D GRAHAM JR</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>graham9191.rg@gmail.com</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>(508) 386-5084</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>R D GRAHAM TRUCKING</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>2026-06-24 20:24:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>BRUNO A FRONGILLO</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>bruno@jackmooreassociates.com</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>(508) 853-3991</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>Jackmooreassociates</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>2026-06-24 20:26:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>ANDREW J. LETOURNEAU</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>ajletour@aol.com</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>(508) 791-4239</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>A J LETOURNEAU INC</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>2026-06-24 20:30:30</t>
         </is>
       </c>
     </row>
@@ -20515,7 +20725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G716"/>
+  <dimension ref="A1:G721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41289,6 +41499,151 @@
       </c>
       <c r="F716" t="inlineStr"/>
       <c r="G716" t="inlineStr"/>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>964</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Office is closed</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>2026-06-24 20:15:43</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr"/>
+      <c r="G717" t="inlineStr"/>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>965</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>2026-06-24 20:19:27</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr"/>
+      <c r="G718" t="inlineStr"/>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>2026-06-24 20:24:14</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr"/>
+      <c r="G719" t="inlineStr"/>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>967</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>not_available</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>2026-06-24 20:26:48</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr"/>
+      <c r="G720" t="inlineStr"/>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>968</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>2026-06-24 20:30:30</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr"/>
+      <c r="G721" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H485"/>
+  <dimension ref="A1:H489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20711,6 +20711,174 @@
       <c r="H485" t="inlineStr">
         <is>
           <t>2026-06-24 20:30:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Jack Benisty</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>jack@jbgeneralcontractors.com</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>(978) 479-2096</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>Jbgeneralcontractors</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:23:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>FERNANDA OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>newenglandfences@gmail.com</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>(774) 239-7164</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>Newenglandfences</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:38:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>David Vick</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>val@level-10.com</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>(508) 615-1452</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>Level 10 Landworks Llc</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:52:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>SEAN KILCOYNE</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>kilcoynebros1939@comcast.net</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>(978) 337-4273</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>Kilcoyne Bros Inc</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:11:59</t>
         </is>
       </c>
     </row>
@@ -20725,7 +20893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G721"/>
+  <dimension ref="A1:G726"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41644,6 +41812,151 @@
       </c>
       <c r="F721" t="inlineStr"/>
       <c r="G721" t="inlineStr"/>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:12:16</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr"/>
+      <c r="G722" t="inlineStr"/>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>970</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>NOT INTRESTED</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>not_intrested</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:23:29</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr"/>
+      <c r="G723" t="inlineStr"/>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>971</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:38:30</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr"/>
+      <c r="G724" t="inlineStr"/>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:52:02</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr"/>
+      <c r="G725" t="inlineStr"/>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>973</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Voicemail</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>voicemail</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:11:59</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr"/>
+      <c r="G726" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H489"/>
+  <dimension ref="A1:H490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20122,7 +20122,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>2026-06-24 18:57:31</t>
+          <t>2026-06-25 15:40:14</t>
         </is>
       </c>
     </row>
@@ -20879,6 +20879,40 @@
       <c r="H489" t="inlineStr">
         <is>
           <t>2026-06-25 13:11:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Peggy Brilliant</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>peggybrilliant@deltajohnsons.com</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Christine Maitland</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr"/>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>2026-06-25 17:13:57</t>
         </is>
       </c>
     </row>

--- a/pipedrive_data.xlsx
+++ b/pipedrive_data.xlsx
@@ -2170,7 +2170,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-05-26 12:49:52</t>
+          <t>2026-08-27 13:46:53</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-03-30 16:46:09</t>
+          <t>2026-08-27 13:46:53</t>
         </is>
       </c>
     </row>
